--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1502" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="339">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1392,7 +1392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP240"/>
+  <dimension ref="A1:BP241"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -5025,7 +5025,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ18">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR18">
         <v>2.07</v>
@@ -8527,7 +8527,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ35">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR35">
         <v>1.47</v>
@@ -9760,7 +9760,7 @@
         <v>3</v>
       </c>
       <c r="AP41">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ41">
         <v>1.92</v>
@@ -9966,7 +9966,7 @@
         <v>0</v>
       </c>
       <c r="AP42">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ42">
         <v>1.09</v>
@@ -11411,7 +11411,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ49">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR49">
         <v>1.58</v>
@@ -16767,7 +16767,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ75">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR75">
         <v>1.45</v>
@@ -17588,7 +17588,7 @@
         <v>1.33</v>
       </c>
       <c r="AP79">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ79">
         <v>0.92</v>
@@ -22532,7 +22532,7 @@
         <v>2</v>
       </c>
       <c r="AP103">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ103">
         <v>1.62</v>
@@ -23359,7 +23359,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ107">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR107">
         <v>1.41</v>
@@ -24592,7 +24592,7 @@
         <v>0.2</v>
       </c>
       <c r="AP113">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ113">
         <v>0.73</v>
@@ -25828,7 +25828,7 @@
         <v>1</v>
       </c>
       <c r="AP119">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ119">
         <v>1.77</v>
@@ -27685,7 +27685,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ128">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR128">
         <v>1.57</v>
@@ -28097,7 +28097,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ130">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR130">
         <v>1.6</v>
@@ -29330,7 +29330,7 @@
         <v>1.43</v>
       </c>
       <c r="AP136">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ136">
         <v>1</v>
@@ -30154,7 +30154,7 @@
         <v>0.71</v>
       </c>
       <c r="AP140">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ140">
         <v>1</v>
@@ -31393,7 +31393,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ146">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR146">
         <v>1.26</v>
@@ -35304,7 +35304,7 @@
         <v>1.14</v>
       </c>
       <c r="AP165">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ165">
         <v>0.92</v>
@@ -36337,7 +36337,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ170">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR170">
         <v>1.87</v>
@@ -38394,7 +38394,7 @@
         <v>1.11</v>
       </c>
       <c r="AP180">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ180">
         <v>1.08</v>
@@ -40454,7 +40454,7 @@
         <v>0.63</v>
       </c>
       <c r="AP190">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ190">
         <v>0.45</v>
@@ -41899,7 +41899,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ197">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR197">
         <v>1.62</v>
@@ -50754,7 +50754,7 @@
         <v>1</v>
       </c>
       <c r="AP240">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AQ240">
         <v>0.92</v>
@@ -50833,6 +50833,212 @@
       </c>
       <c r="BP240">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="241" spans="1:68">
+      <c r="A241" s="1">
+        <v>240</v>
+      </c>
+      <c r="B241">
+        <v>7778302</v>
+      </c>
+      <c r="C241" t="s">
+        <v>68</v>
+      </c>
+      <c r="D241" t="s">
+        <v>69</v>
+      </c>
+      <c r="E241" s="2">
+        <v>45865.29166666666</v>
+      </c>
+      <c r="F241">
+        <v>23</v>
+      </c>
+      <c r="G241" t="s">
+        <v>89</v>
+      </c>
+      <c r="H241" t="s">
+        <v>71</v>
+      </c>
+      <c r="I241">
+        <v>0</v>
+      </c>
+      <c r="J241">
+        <v>0</v>
+      </c>
+      <c r="K241">
+        <v>0</v>
+      </c>
+      <c r="L241">
+        <v>0</v>
+      </c>
+      <c r="M241">
+        <v>0</v>
+      </c>
+      <c r="N241">
+        <v>0</v>
+      </c>
+      <c r="O241" t="s">
+        <v>91</v>
+      </c>
+      <c r="P241" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q241">
+        <v>3.2</v>
+      </c>
+      <c r="R241">
+        <v>1.88</v>
+      </c>
+      <c r="S241">
+        <v>3.6</v>
+      </c>
+      <c r="T241">
+        <v>1.55</v>
+      </c>
+      <c r="U241">
+        <v>2.3</v>
+      </c>
+      <c r="V241">
+        <v>3.6</v>
+      </c>
+      <c r="W241">
+        <v>1.25</v>
+      </c>
+      <c r="X241">
+        <v>10.5</v>
+      </c>
+      <c r="Y241">
+        <v>1.04</v>
+      </c>
+      <c r="Z241">
+        <v>2.21</v>
+      </c>
+      <c r="AA241">
+        <v>2.92</v>
+      </c>
+      <c r="AB241">
+        <v>3.08</v>
+      </c>
+      <c r="AC241">
+        <v>1.1</v>
+      </c>
+      <c r="AD241">
+        <v>6.5</v>
+      </c>
+      <c r="AE241">
+        <v>1.53</v>
+      </c>
+      <c r="AF241">
+        <v>2.5</v>
+      </c>
+      <c r="AG241">
+        <v>2.25</v>
+      </c>
+      <c r="AH241">
+        <v>1.57</v>
+      </c>
+      <c r="AI241">
+        <v>2.1</v>
+      </c>
+      <c r="AJ241">
+        <v>1.65</v>
+      </c>
+      <c r="AK241">
+        <v>1.38</v>
+      </c>
+      <c r="AL241">
+        <v>1.35</v>
+      </c>
+      <c r="AM241">
+        <v>1.51</v>
+      </c>
+      <c r="AN241">
+        <v>2.33</v>
+      </c>
+      <c r="AO241">
+        <v>1.3</v>
+      </c>
+      <c r="AP241">
+        <v>2.23</v>
+      </c>
+      <c r="AQ241">
+        <v>1.27</v>
+      </c>
+      <c r="AR241">
+        <v>1.47</v>
+      </c>
+      <c r="AS241">
+        <v>1.63</v>
+      </c>
+      <c r="AT241">
+        <v>3.1</v>
+      </c>
+      <c r="AU241">
+        <v>5</v>
+      </c>
+      <c r="AV241">
+        <v>3</v>
+      </c>
+      <c r="AW241">
+        <v>2</v>
+      </c>
+      <c r="AX241">
+        <v>6</v>
+      </c>
+      <c r="AY241">
+        <v>7</v>
+      </c>
+      <c r="AZ241">
+        <v>9</v>
+      </c>
+      <c r="BA241">
+        <v>4</v>
+      </c>
+      <c r="BB241">
+        <v>4</v>
+      </c>
+      <c r="BC241">
+        <v>8</v>
+      </c>
+      <c r="BD241">
+        <v>1.8</v>
+      </c>
+      <c r="BE241">
+        <v>8.5</v>
+      </c>
+      <c r="BF241">
+        <v>2.2</v>
+      </c>
+      <c r="BG241">
+        <v>1.3</v>
+      </c>
+      <c r="BH241">
+        <v>3.1</v>
+      </c>
+      <c r="BI241">
+        <v>1.57</v>
+      </c>
+      <c r="BJ241">
+        <v>2.15</v>
+      </c>
+      <c r="BK241">
+        <v>2</v>
+      </c>
+      <c r="BL241">
+        <v>1.66</v>
+      </c>
+      <c r="BM241">
+        <v>2.7</v>
+      </c>
+      <c r="BN241">
+        <v>1.38</v>
+      </c>
+      <c r="BO241">
+        <v>3.8</v>
+      </c>
+      <c r="BP241">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
@@ -43872,22 +43872,22 @@
         <v>2.96</v>
       </c>
       <c r="AU199" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV199" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW199" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX199" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AY199" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AZ199" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="BA199" t="n">
         <v>1</v>
@@ -44090,22 +44090,22 @@
         <v>2.68</v>
       </c>
       <c r="AU200" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV200" t="n">
         <v>3</v>
       </c>
       <c r="AW200" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AX200" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AY200" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AZ200" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BA200" t="n">
         <v>2</v>
@@ -44314,16 +44314,16 @@
         <v>4</v>
       </c>
       <c r="AW201" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AX201" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AY201" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AZ201" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BA201" t="n">
         <v>3</v>
@@ -44744,22 +44744,22 @@
         <v>3.1</v>
       </c>
       <c r="AU203" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV203" t="n">
         <v>2</v>
       </c>
       <c r="AW203" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX203" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY203" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ203" t="n">
         <v>6</v>
-      </c>
-      <c r="AX203" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY203" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ203" t="n">
-        <v>7</v>
       </c>
       <c r="BA203" t="n">
         <v>3</v>
@@ -44962,22 +44962,22 @@
         <v>2.93</v>
       </c>
       <c r="AU204" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV204" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW204" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AX204" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY204" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AZ204" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA204" t="n">
         <v>7</v>
@@ -46697,13 +46697,13 @@
         <v>1.92</v>
       </c>
       <c r="AR212" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AS212" t="n">
         <v>1.49</v>
       </c>
       <c r="AT212" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="AU212" t="n">
         <v>2</v>
@@ -46918,13 +46918,13 @@
         <v>1.58</v>
       </c>
       <c r="AS213" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AT213" t="n">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="AU213" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AV213" t="n">
         <v>4</v>
@@ -46933,13 +46933,13 @@
         <v>5</v>
       </c>
       <c r="AX213" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AY213" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AZ213" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BA213" t="n">
         <v>4</v>
@@ -47148,16 +47148,16 @@
         <v>4</v>
       </c>
       <c r="AW214" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AX214" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY214" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AZ214" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA214" t="n">
         <v>8</v>
@@ -47366,16 +47366,16 @@
         <v>6</v>
       </c>
       <c r="AW215" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX215" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AY215" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AZ215" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BA215" t="n">
         <v>7</v>
@@ -47581,19 +47581,19 @@
         <v>2</v>
       </c>
       <c r="AV216" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AW216" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="AX216" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY216" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="AZ216" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BA216" t="n">
         <v>6</v>
@@ -47790,10 +47790,10 @@
         <v>1.8</v>
       </c>
       <c r="AS217" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AT217" t="n">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="AU217" t="n">
         <v>7</v>
@@ -48005,31 +48005,31 @@
         <v>0.92</v>
       </c>
       <c r="AR218" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AS218" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AT218" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AU218" t="n">
         <v>7</v>
       </c>
       <c r="AV218" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW218" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AX218" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AY218" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AZ218" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BA218" t="n">
         <v>2</v>
@@ -48226,10 +48226,10 @@
         <v>1.62</v>
       </c>
       <c r="AS219" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AT219" t="n">
-        <v>3.22</v>
+        <v>3.19</v>
       </c>
       <c r="AU219" t="n">
         <v>4</v>
@@ -48441,13 +48441,13 @@
         <v>0.92</v>
       </c>
       <c r="AR220" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AS220" t="n">
         <v>1.23</v>
       </c>
       <c r="AT220" t="n">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="AU220" t="n">
         <v>3</v>
@@ -48662,10 +48662,10 @@
         <v>1.64</v>
       </c>
       <c r="AS221" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AT221" t="n">
-        <v>3.16</v>
+        <v>3.13</v>
       </c>
       <c r="AU221" t="n">
         <v>7</v>
@@ -48674,16 +48674,16 @@
         <v>4</v>
       </c>
       <c r="AW221" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AX221" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AY221" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AZ221" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BA221" t="n">
         <v>7</v>
@@ -48877,13 +48877,13 @@
         <v>1</v>
       </c>
       <c r="AR222" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AS222" t="n">
         <v>1.11</v>
       </c>
       <c r="AT222" t="n">
-        <v>2.66</v>
+        <v>2.55</v>
       </c>
       <c r="AU222" t="n">
         <v>2</v>
@@ -48892,16 +48892,16 @@
         <v>5</v>
       </c>
       <c r="AW222" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX222" t="n">
         <v>4</v>
       </c>
-      <c r="AX222" t="n">
-        <v>2</v>
-      </c>
       <c r="AY222" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ222" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA222" t="n">
         <v>4</v>
@@ -49095,28 +49095,28 @@
         <v>0.67</v>
       </c>
       <c r="AR223" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AS223" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AT223" t="n">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="AU223" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AV223" t="n">
         <v>4</v>
       </c>
       <c r="AW223" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AX223" t="n">
         <v>8</v>
       </c>
       <c r="AY223" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AZ223" t="n">
         <v>12</v>
@@ -49540,16 +49540,16 @@
         <v>3.09</v>
       </c>
       <c r="AU225" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV225" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW225" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX225" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY225" t="n">
         <v>14</v>
@@ -50200,16 +50200,16 @@
         <v>5</v>
       </c>
       <c r="AW228" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX228" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AY228" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ228" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="BA228" t="n">
         <v>0</v>
@@ -50403,13 +50403,13 @@
         <v>2.08</v>
       </c>
       <c r="AR229" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AS229" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AT229" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="AU229" t="n">
         <v>5</v>
@@ -50418,16 +50418,16 @@
         <v>3</v>
       </c>
       <c r="AW229" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AX229" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY229" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AZ229" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA229" t="n">
         <v>4</v>
@@ -50621,31 +50621,31 @@
         <v>0.45</v>
       </c>
       <c r="AR230" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="AS230" t="n">
         <v>1.23</v>
       </c>
       <c r="AT230" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AU230" t="n">
         <v>3</v>
       </c>
       <c r="AV230" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW230" t="n">
         <v>4</v>
       </c>
       <c r="AX230" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AY230" t="n">
         <v>7</v>
       </c>
       <c r="AZ230" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA230" t="n">
         <v>8</v>
@@ -50842,10 +50842,10 @@
         <v>1.39</v>
       </c>
       <c r="AS231" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AT231" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="AU231" t="n">
         <v>6</v>
@@ -50854,13 +50854,13 @@
         <v>5</v>
       </c>
       <c r="AW231" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX231" t="n">
         <v>11</v>
       </c>
       <c r="AY231" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ231" t="n">
         <v>16</v>
@@ -51057,13 +51057,13 @@
         <v>1.77</v>
       </c>
       <c r="AR232" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AS232" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AT232" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="AU232" t="n">
         <v>2</v>
@@ -51072,16 +51072,16 @@
         <v>9</v>
       </c>
       <c r="AW232" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AX232" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AY232" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AZ232" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BA232" t="n">
         <v>5</v>
@@ -51278,28 +51278,28 @@
         <v>1.58</v>
       </c>
       <c r="AS233" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AT233" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="AU233" t="n">
         <v>5</v>
       </c>
       <c r="AV233" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW233" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AX233" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY233" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AZ233" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA233" t="n">
         <v>9</v>
@@ -51711,31 +51711,31 @@
         <v>1.62</v>
       </c>
       <c r="AR235" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AS235" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AT235" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="AU235" t="n">
         <v>8</v>
       </c>
       <c r="AV235" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW235" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AX235" t="n">
         <v>2</v>
       </c>
       <c r="AY235" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AZ235" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA235" t="n">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
@@ -51505,19 +51505,19 @@
         <v>3</v>
       </c>
       <c r="AV234" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW234" t="n">
         <v>4</v>
       </c>
       <c r="AX234" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY234" t="n">
         <v>7</v>
       </c>
       <c r="AZ234" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA234" t="n">
         <v>8</v>
@@ -51726,13 +51726,13 @@
         <v>5</v>
       </c>
       <c r="AW235" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX235" t="n">
         <v>11</v>
       </c>
       <c r="AY235" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ235" t="n">
         <v>16</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
@@ -926,10 +926,10 @@
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW2" t="n">
         <v>13</v>
@@ -938,10 +938,10 @@
         <v>5</v>
       </c>
       <c r="AY2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA2" t="n">
         <v>6</v>
@@ -1144,10 +1144,10 @@
         <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW3" t="n">
         <v>7</v>
@@ -1156,10 +1156,10 @@
         <v>8</v>
       </c>
       <c r="AY3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA3" t="n">
         <v>2</v>
@@ -1362,10 +1362,10 @@
         <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW4" t="n">
         <v>3</v>
@@ -1374,10 +1374,10 @@
         <v>14</v>
       </c>
       <c r="AY4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA4" t="n">
         <v>3</v>
@@ -1580,10 +1580,10 @@
         <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW5" t="n">
         <v>10</v>
@@ -1592,10 +1592,10 @@
         <v>6</v>
       </c>
       <c r="AY5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA5" t="n">
         <v>5</v>
@@ -1798,10 +1798,10 @@
         <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW6" t="n">
         <v>6</v>
@@ -1810,10 +1810,10 @@
         <v>14</v>
       </c>
       <c r="AY6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA6" t="n">
         <v>4</v>
@@ -2016,10 +2016,10 @@
         <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW7" t="n">
         <v>5</v>
@@ -2028,10 +2028,10 @@
         <v>12</v>
       </c>
       <c r="AY7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA7" t="n">
         <v>3</v>
@@ -2234,7 +2234,7 @@
         <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -2243,13 +2243,13 @@
         <v>8</v>
       </c>
       <c r="AX8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA8" t="n">
         <v>6</v>
@@ -2452,10 +2452,10 @@
         <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW9" t="n">
         <v>7</v>
@@ -2464,10 +2464,10 @@
         <v>5</v>
       </c>
       <c r="AY9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA9" t="n">
         <v>9</v>
@@ -2670,10 +2670,10 @@
         <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW10" t="n">
         <v>5</v>
@@ -2682,10 +2682,10 @@
         <v>12</v>
       </c>
       <c r="AY10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA10" t="n">
         <v>3</v>
@@ -2888,10 +2888,10 @@
         <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW11" t="n">
         <v>5</v>
@@ -2900,10 +2900,10 @@
         <v>7</v>
       </c>
       <c r="AY11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA11" t="n">
         <v>6</v>
@@ -3106,10 +3106,10 @@
         <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW12" t="n">
         <v>5</v>
@@ -3118,10 +3118,10 @@
         <v>7</v>
       </c>
       <c r="AY12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA12" t="n">
         <v>3</v>
@@ -3324,10 +3324,10 @@
         <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW13" t="n">
         <v>7</v>
@@ -3336,10 +3336,10 @@
         <v>7</v>
       </c>
       <c r="AY13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA13" t="n">
         <v>7</v>
@@ -3533,19 +3533,19 @@
         <v>1.09</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AS14" t="n">
         <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AU14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW14" t="n">
         <v>5</v>
@@ -3554,10 +3554,10 @@
         <v>9</v>
       </c>
       <c r="AY14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA14" t="n">
         <v>4</v>
@@ -3754,16 +3754,16 @@
         <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AU15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW15" t="n">
         <v>12</v>
@@ -3772,10 +3772,10 @@
         <v>2</v>
       </c>
       <c r="AY15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA15" t="n">
         <v>7</v>
@@ -3972,16 +3972,16 @@
         <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="AU16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW16" t="n">
         <v>8</v>
@@ -3990,10 +3990,10 @@
         <v>8</v>
       </c>
       <c r="AY16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA16" t="n">
         <v>6</v>
@@ -4196,10 +4196,10 @@
         <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW17" t="n">
         <v>9</v>
@@ -4208,10 +4208,10 @@
         <v>7</v>
       </c>
       <c r="AY17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ17" t="n">
         <v>14</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>15</v>
       </c>
       <c r="BA17" t="n">
         <v>7</v>
@@ -4405,19 +4405,19 @@
         <v>1.27</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AS18" t="n">
         <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AU18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW18" t="n">
         <v>5</v>
@@ -4426,10 +4426,10 @@
         <v>11</v>
       </c>
       <c r="AY18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA18" t="n">
         <v>3</v>
@@ -4632,10 +4632,10 @@
         <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW19" t="n">
         <v>11</v>
@@ -4644,10 +4644,10 @@
         <v>7</v>
       </c>
       <c r="AY19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA19" t="n">
         <v>5</v>
@@ -4850,10 +4850,10 @@
         <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW20" t="n">
         <v>6</v>
@@ -4862,10 +4862,10 @@
         <v>3</v>
       </c>
       <c r="AY20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA20" t="n">
         <v>6</v>
@@ -5068,10 +5068,10 @@
         <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW21" t="n">
         <v>4</v>
@@ -5080,10 +5080,10 @@
         <v>7</v>
       </c>
       <c r="AY21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA21" t="n">
         <v>3</v>
@@ -5277,19 +5277,19 @@
         <v>1.33</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.91</v>
+        <v>0.78</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="AU22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW22" t="n">
         <v>8</v>
@@ -5298,10 +5298,10 @@
         <v>4</v>
       </c>
       <c r="AY22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA22" t="n">
         <v>2</v>
@@ -5495,16 +5495,16 @@
         <v>1</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AS23" t="n">
         <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AU23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV23" t="n">
         <v>0</v>
@@ -5513,13 +5513,13 @@
         <v>12</v>
       </c>
       <c r="AX23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA23" t="n">
         <v>3</v>
@@ -5713,19 +5713,19 @@
         <v>1.62</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.78</v>
+        <v>0.65</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.86</v>
+        <v>2.6</v>
       </c>
       <c r="AU24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW24" t="n">
         <v>14</v>
@@ -5734,10 +5734,10 @@
         <v>1</v>
       </c>
       <c r="AY24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA24" t="n">
         <v>9</v>
@@ -5931,19 +5931,19 @@
         <v>1.77</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AT25" t="n">
-        <v>3.34</v>
+        <v>3.07</v>
       </c>
       <c r="AU25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW25" t="n">
         <v>12</v>
@@ -5952,10 +5952,10 @@
         <v>10</v>
       </c>
       <c r="AY25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA25" t="n">
         <v>5</v>
@@ -6149,19 +6149,19 @@
         <v>0.82</v>
       </c>
       <c r="AR26" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AT26" t="n">
-        <v>3.9</v>
+        <v>3.63</v>
       </c>
       <c r="AU26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW26" t="n">
         <v>10</v>
@@ -6170,10 +6170,10 @@
         <v>5</v>
       </c>
       <c r="AY26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA26" t="n">
         <v>10</v>
@@ -6367,19 +6367,19 @@
         <v>0.67</v>
       </c>
       <c r="AR27" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AT27" t="n">
-        <v>3.47</v>
+        <v>3.2</v>
       </c>
       <c r="AU27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV27" t="n">
         <v>5</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>6</v>
       </c>
       <c r="AW27" t="n">
         <v>9</v>
@@ -6388,10 +6388,10 @@
         <v>6</v>
       </c>
       <c r="AY27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA27" t="n">
         <v>5</v>
@@ -6585,19 +6585,19 @@
         <v>1</v>
       </c>
       <c r="AR28" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AS28" t="n">
         <v>0.8</v>
       </c>
-      <c r="AS28" t="n">
-        <v>0.9399999999999999</v>
-      </c>
       <c r="AT28" t="n">
-        <v>1.74</v>
+        <v>1.47</v>
       </c>
       <c r="AU28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV28" t="n">
         <v>4</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>5</v>
       </c>
       <c r="AW28" t="n">
         <v>7</v>
@@ -6606,10 +6606,10 @@
         <v>2</v>
       </c>
       <c r="AY28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA28" t="n">
         <v>5</v>
@@ -6803,19 +6803,19 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="AU29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW29" t="n">
         <v>5</v>
@@ -6824,10 +6824,10 @@
         <v>5</v>
       </c>
       <c r="AY29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA29" t="n">
         <v>3</v>
@@ -7021,19 +7021,19 @@
         <v>1.08</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.16</v>
+        <v>2.89</v>
       </c>
       <c r="AU30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW30" t="n">
         <v>7</v>
@@ -7042,10 +7042,10 @@
         <v>8</v>
       </c>
       <c r="AY30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA30" t="n">
         <v>4</v>
@@ -7239,19 +7239,19 @@
         <v>0.45</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AS31" t="n">
         <v>0</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AU31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV31" t="n">
         <v>3</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>4</v>
       </c>
       <c r="AW31" t="n">
         <v>5</v>
@@ -7260,10 +7260,10 @@
         <v>11</v>
       </c>
       <c r="AY31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA31" t="n">
         <v>2</v>
@@ -7457,19 +7457,19 @@
         <v>0.92</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.12</v>
+        <v>0.99</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AT32" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AU32" t="n">
         <v>3</v>
       </c>
-      <c r="AU32" t="n">
-        <v>4</v>
-      </c>
       <c r="AV32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW32" t="n">
         <v>8</v>
@@ -7478,10 +7478,10 @@
         <v>4</v>
       </c>
       <c r="AY32" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA32" t="n">
         <v>3</v>
@@ -7675,19 +7675,19 @@
         <v>0.92</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="AT33" t="n">
-        <v>2.74</v>
+        <v>2.48</v>
       </c>
       <c r="AU33" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW33" t="n">
         <v>8</v>
@@ -7696,10 +7696,10 @@
         <v>11</v>
       </c>
       <c r="AY33" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ33" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA33" t="n">
         <v>7</v>
@@ -7893,19 +7893,19 @@
         <v>1.62</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AT34" t="n">
-        <v>3.53</v>
+        <v>3.27</v>
       </c>
       <c r="AU34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW34" t="n">
         <v>13</v>
@@ -7914,10 +7914,10 @@
         <v>6</v>
       </c>
       <c r="AY34" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA34" t="n">
         <v>6</v>
@@ -8111,19 +8111,19 @@
         <v>1.27</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AT35" t="n">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="AU35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV35" t="n">
         <v>2</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>3</v>
       </c>
       <c r="AW35" t="n">
         <v>10</v>
@@ -8132,10 +8132,10 @@
         <v>10</v>
       </c>
       <c r="AY35" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ35" t="n">
         <v>12</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>13</v>
       </c>
       <c r="BA35" t="n">
         <v>2</v>
@@ -8329,19 +8329,19 @@
         <v>1</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.08</v>
+        <v>0.95</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="AU36" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV36" t="n">
         <v>4</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>5</v>
       </c>
       <c r="AW36" t="n">
         <v>9</v>
@@ -8350,10 +8350,10 @@
         <v>17</v>
       </c>
       <c r="AY36" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ36" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA36" t="n">
         <v>6</v>
@@ -8550,16 +8550,16 @@
         <v>0</v>
       </c>
       <c r="AS37" t="n">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AT37" t="n">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AU37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW37" t="n">
         <v>12</v>
@@ -8568,10 +8568,10 @@
         <v>6</v>
       </c>
       <c r="AY37" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ37" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA37" t="n">
         <v>9</v>
@@ -8765,19 +8765,19 @@
         <v>2.08</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AT38" t="n">
-        <v>2.48</v>
+        <v>2.22</v>
       </c>
       <c r="AU38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW38" t="n">
         <v>3</v>
@@ -8786,10 +8786,10 @@
         <v>4</v>
       </c>
       <c r="AY38" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ38" t="n">
         <v>6</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>7</v>
       </c>
       <c r="BA38" t="n">
         <v>3</v>
@@ -8983,19 +8983,19 @@
         <v>0.92</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.08</v>
+        <v>0.95</v>
       </c>
       <c r="AT39" t="n">
-        <v>2.67</v>
+        <v>2.41</v>
       </c>
       <c r="AU39" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW39" t="n">
         <v>8</v>
@@ -9004,10 +9004,10 @@
         <v>10</v>
       </c>
       <c r="AY39" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ39" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA39" t="n">
         <v>7</v>
@@ -9201,19 +9201,19 @@
         <v>0.45</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AT40" t="n">
-        <v>2.98</v>
+        <v>2.71</v>
       </c>
       <c r="AU40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW40" t="n">
         <v>12</v>
@@ -9222,10 +9222,10 @@
         <v>3</v>
       </c>
       <c r="AY40" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA40" t="n">
         <v>3</v>
@@ -9422,16 +9422,16 @@
         <v>0</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AT41" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AU41" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW41" t="n">
         <v>10</v>
@@ -9440,10 +9440,10 @@
         <v>2</v>
       </c>
       <c r="AY41" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ41" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA41" t="n">
         <v>7</v>
@@ -9637,19 +9637,19 @@
         <v>1.09</v>
       </c>
       <c r="AR42" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="AT42" t="n">
-        <v>3.29</v>
+        <v>3.01</v>
       </c>
       <c r="AU42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW42" t="n">
         <v>9</v>
@@ -9658,10 +9658,10 @@
         <v>8</v>
       </c>
       <c r="AY42" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA42" t="n">
         <v>5</v>
@@ -9855,19 +9855,19 @@
         <v>1</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.01</v>
+        <v>0.87</v>
       </c>
       <c r="AT43" t="n">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="AU43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW43" t="n">
         <v>4</v>
@@ -9876,10 +9876,10 @@
         <v>5</v>
       </c>
       <c r="AY43" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ43" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA43" t="n">
         <v>3</v>
@@ -10073,19 +10073,19 @@
         <v>0.92</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AS44" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AT44" t="n">
-        <v>2.89</v>
+        <v>2.63</v>
       </c>
       <c r="AU44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW44" t="n">
         <v>11</v>
@@ -10094,10 +10094,10 @@
         <v>9</v>
       </c>
       <c r="AY44" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ44" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA44" t="n">
         <v>4</v>
@@ -10291,16 +10291,16 @@
         <v>0.92</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AS45" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AT45" t="n">
-        <v>3.04</v>
+        <v>2.78</v>
       </c>
       <c r="AU45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV45" t="n">
         <v>0</v>
@@ -10309,13 +10309,13 @@
         <v>10</v>
       </c>
       <c r="AX45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY45" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA45" t="n">
         <v>5</v>
@@ -10509,19 +10509,19 @@
         <v>2.08</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.01</v>
+        <v>0.88</v>
       </c>
       <c r="AT46" t="n">
-        <v>2.48</v>
+        <v>2.22</v>
       </c>
       <c r="AU46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW46" t="n">
         <v>4</v>
@@ -10530,10 +10530,10 @@
         <v>9</v>
       </c>
       <c r="AY46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ46" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA46" t="n">
         <v>1</v>
@@ -10727,19 +10727,19 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AS47" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AT47" t="n">
-        <v>2.95</v>
+        <v>2.72</v>
       </c>
       <c r="AU47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV47" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW47" t="n">
         <v>20</v>
@@ -10748,10 +10748,10 @@
         <v>4</v>
       </c>
       <c r="AY47" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ47" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA47" t="n">
         <v>9</v>
@@ -10945,19 +10945,19 @@
         <v>1.36</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AS48" t="n">
-        <v>1.78</v>
+        <v>1.64</v>
       </c>
       <c r="AT48" t="n">
-        <v>3.23</v>
+        <v>2.96</v>
       </c>
       <c r="AU48" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV48" t="n">
         <v>5</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>6</v>
       </c>
       <c r="AW48" t="n">
         <v>6</v>
@@ -10966,10 +10966,10 @@
         <v>8</v>
       </c>
       <c r="AY48" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ48" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA48" t="n">
         <v>8</v>
@@ -11163,19 +11163,19 @@
         <v>1.27</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AS49" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AT49" t="n">
-        <v>3.42</v>
+        <v>3.16</v>
       </c>
       <c r="AU49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW49" t="n">
         <v>3</v>
@@ -11184,10 +11184,10 @@
         <v>11</v>
       </c>
       <c r="AY49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ49" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA49" t="n">
         <v>2</v>
@@ -11381,19 +11381,19 @@
         <v>1.08</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AS50" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="AT50" t="n">
-        <v>2.73</v>
+        <v>2.47</v>
       </c>
       <c r="AU50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW50" t="n">
         <v>7</v>
@@ -11402,10 +11402,10 @@
         <v>6</v>
       </c>
       <c r="AY50" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ50" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA50" t="n">
         <v>5</v>
@@ -11599,19 +11599,19 @@
         <v>0.67</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.02</v>
+        <v>0.89</v>
       </c>
       <c r="AS51" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="AT51" t="n">
-        <v>2.43</v>
+        <v>2.16</v>
       </c>
       <c r="AU51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW51" t="n">
         <v>8</v>
@@ -11620,10 +11620,10 @@
         <v>4</v>
       </c>
       <c r="AY51" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ51" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA51" t="n">
         <v>6</v>
@@ -11817,19 +11817,19 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AS52" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AT52" t="n">
-        <v>2.66</v>
+        <v>2.41</v>
       </c>
       <c r="AU52" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV52" t="n">
         <v>4</v>
-      </c>
-      <c r="AV52" t="n">
-        <v>5</v>
       </c>
       <c r="AW52" t="n">
         <v>6</v>
@@ -11838,10 +11838,10 @@
         <v>4</v>
       </c>
       <c r="AY52" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ52" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA52" t="n">
         <v>5</v>
@@ -12035,19 +12035,19 @@
         <v>0.92</v>
       </c>
       <c r="AR53" t="n">
-        <v>1.12</v>
+        <v>0.99</v>
       </c>
       <c r="AS53" t="n">
-        <v>1.05</v>
+        <v>0.92</v>
       </c>
       <c r="AT53" t="n">
-        <v>2.17</v>
+        <v>1.91</v>
       </c>
       <c r="AU53" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV53" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW53" t="n">
         <v>12</v>
@@ -12056,10 +12056,10 @@
         <v>1</v>
       </c>
       <c r="AY53" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ53" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA53" t="n">
         <v>3</v>
@@ -12253,19 +12253,19 @@
         <v>1.62</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AS54" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AT54" t="n">
-        <v>2.85</v>
+        <v>2.59</v>
       </c>
       <c r="AU54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW54" t="n">
         <v>4</v>
@@ -12274,10 +12274,10 @@
         <v>5</v>
       </c>
       <c r="AY54" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ54" t="n">
         <v>9</v>
-      </c>
-      <c r="AZ54" t="n">
-        <v>10</v>
       </c>
       <c r="BA54" t="n">
         <v>5</v>
@@ -12471,19 +12471,19 @@
         <v>1</v>
       </c>
       <c r="AR55" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AS55" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="AT55" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="AU55" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV55" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW55" t="n">
         <v>1</v>
@@ -12492,10 +12492,10 @@
         <v>9</v>
       </c>
       <c r="AY55" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ55" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA55" t="n">
         <v>2</v>
@@ -12689,19 +12689,19 @@
         <v>1.33</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AS56" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AT56" t="n">
-        <v>3.05</v>
+        <v>2.79</v>
       </c>
       <c r="AU56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW56" t="n">
         <v>13</v>
@@ -12710,10 +12710,10 @@
         <v>8</v>
       </c>
       <c r="AY56" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ56" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA56" t="n">
         <v>6</v>
@@ -12907,19 +12907,19 @@
         <v>1.92</v>
       </c>
       <c r="AR57" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AS57" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AT57" t="n">
-        <v>2.73</v>
+        <v>2.47</v>
       </c>
       <c r="AU57" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV57" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW57" t="n">
         <v>8</v>
@@ -12928,10 +12928,10 @@
         <v>1</v>
       </c>
       <c r="AY57" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ57" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA57" t="n">
         <v>5</v>
@@ -13125,19 +13125,19 @@
         <v>0.82</v>
       </c>
       <c r="AR58" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AS58" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AT58" t="n">
-        <v>3.56</v>
+        <v>3.3</v>
       </c>
       <c r="AU58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV58" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW58" t="n">
         <v>3</v>
@@ -13146,10 +13146,10 @@
         <v>6</v>
       </c>
       <c r="AY58" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ58" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA58" t="n">
         <v>9</v>
@@ -13343,19 +13343,19 @@
         <v>1.92</v>
       </c>
       <c r="AR59" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AS59" t="n">
-        <v>2.01</v>
+        <v>1.87</v>
       </c>
       <c r="AT59" t="n">
-        <v>3.94</v>
+        <v>3.67</v>
       </c>
       <c r="AU59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV59" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW59" t="n">
         <v>3</v>
@@ -13364,10 +13364,10 @@
         <v>3</v>
       </c>
       <c r="AY59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ59" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA59" t="n">
         <v>1</v>
@@ -13561,19 +13561,19 @@
         <v>0.82</v>
       </c>
       <c r="AR60" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AS60" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AT60" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="AU60" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW60" t="n">
         <v>9</v>
@@ -13582,10 +13582,10 @@
         <v>13</v>
       </c>
       <c r="AY60" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ60" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA60" t="n">
         <v>8</v>
@@ -13779,19 +13779,19 @@
         <v>0.73</v>
       </c>
       <c r="AR61" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="AS61" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="AT61" t="n">
-        <v>2.64</v>
+        <v>2.38</v>
       </c>
       <c r="AU61" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV61" t="n">
         <v>5</v>
-      </c>
-      <c r="AV61" t="n">
-        <v>6</v>
       </c>
       <c r="AW61" t="n">
         <v>5</v>
@@ -13800,10 +13800,10 @@
         <v>7</v>
       </c>
       <c r="AY61" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ61" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA61" t="n">
         <v>8</v>
@@ -13997,19 +13997,19 @@
         <v>0.92</v>
       </c>
       <c r="AR62" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AS62" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AT62" t="n">
-        <v>2.69</v>
+        <v>2.45</v>
       </c>
       <c r="AU62" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW62" t="n">
         <v>4</v>
@@ -14018,10 +14018,10 @@
         <v>6</v>
       </c>
       <c r="AY62" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ62" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA62" t="n">
         <v>5</v>
@@ -14215,19 +14215,19 @@
         <v>1</v>
       </c>
       <c r="AR63" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AS63" t="n">
-        <v>1.03</v>
+        <v>0.9</v>
       </c>
       <c r="AT63" t="n">
-        <v>2.49</v>
+        <v>2.23</v>
       </c>
       <c r="AU63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV63" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW63" t="n">
         <v>6</v>
@@ -14236,10 +14236,10 @@
         <v>9</v>
       </c>
       <c r="AY63" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ63" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA63" t="n">
         <v>6</v>
@@ -14433,19 +14433,19 @@
         <v>1</v>
       </c>
       <c r="AR64" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AS64" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AT64" t="n">
-        <v>3.38</v>
+        <v>3.15</v>
       </c>
       <c r="AU64" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV64" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW64" t="n">
         <v>4</v>
@@ -14454,10 +14454,10 @@
         <v>12</v>
       </c>
       <c r="AY64" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ64" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA64" t="n">
         <v>3</v>
@@ -14651,19 +14651,19 @@
         <v>0.45</v>
       </c>
       <c r="AR65" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AS65" t="n">
         <v>1.08</v>
       </c>
-      <c r="AS65" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AT65" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="AU65" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV65" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW65" t="n">
         <v>2</v>
@@ -14672,10 +14672,10 @@
         <v>5</v>
       </c>
       <c r="AY65" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ65" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA65" t="n">
         <v>2</v>
@@ -14869,19 +14869,19 @@
         <v>1.77</v>
       </c>
       <c r="AR66" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AS66" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AT66" t="n">
-        <v>3.07</v>
+        <v>2.81</v>
       </c>
       <c r="AU66" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV66" t="n">
         <v>3</v>
-      </c>
-      <c r="AV66" t="n">
-        <v>4</v>
       </c>
       <c r="AW66" t="n">
         <v>4</v>
@@ -14890,10 +14890,10 @@
         <v>13</v>
       </c>
       <c r="AY66" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ66" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA66" t="n">
         <v>1</v>
@@ -15087,19 +15087,19 @@
         <v>1.92</v>
       </c>
       <c r="AR67" t="n">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="AS67" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AT67" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="AU67" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW67" t="n">
         <v>5</v>
@@ -15108,10 +15108,10 @@
         <v>5</v>
       </c>
       <c r="AY67" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ67" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA67" t="n">
         <v>6</v>
@@ -15305,19 +15305,19 @@
         <v>2.08</v>
       </c>
       <c r="AR68" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="AS68" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AT68" t="n">
-        <v>2.69</v>
+        <v>2.43</v>
       </c>
       <c r="AU68" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV68" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW68" t="n">
         <v>6</v>
@@ -15326,10 +15326,10 @@
         <v>7</v>
       </c>
       <c r="AY68" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ68" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA68" t="n">
         <v>5</v>
@@ -15523,19 +15523,19 @@
         <v>1.33</v>
       </c>
       <c r="AR69" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AS69" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AT69" t="n">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="AU69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV69" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW69" t="n">
         <v>7</v>
@@ -15544,10 +15544,10 @@
         <v>5</v>
       </c>
       <c r="AY69" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ69" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA69" t="n">
         <v>6</v>
@@ -15741,19 +15741,19 @@
         <v>1.36</v>
       </c>
       <c r="AR70" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="AS70" t="n">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="AT70" t="n">
-        <v>3.17</v>
+        <v>2.9</v>
       </c>
       <c r="AU70" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW70" t="n">
         <v>9</v>
@@ -15762,10 +15762,10 @@
         <v>14</v>
       </c>
       <c r="AY70" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ70" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA70" t="n">
         <v>5</v>
@@ -15959,19 +15959,19 @@
         <v>1.09</v>
       </c>
       <c r="AR71" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AS71" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AT71" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="AU71" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV71" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW71" t="n">
         <v>14</v>
@@ -15980,10 +15980,10 @@
         <v>11</v>
       </c>
       <c r="AY71" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ71" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA71" t="n">
         <v>5</v>
@@ -16177,19 +16177,19 @@
         <v>2.08</v>
       </c>
       <c r="AR72" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AS72" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AT72" t="n">
-        <v>2.92</v>
+        <v>2.64</v>
       </c>
       <c r="AU72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV72" t="n">
         <v>2</v>
-      </c>
-      <c r="AV72" t="n">
-        <v>3</v>
       </c>
       <c r="AW72" t="n">
         <v>8</v>
@@ -16198,10 +16198,10 @@
         <v>9</v>
       </c>
       <c r="AY72" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ72" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA72" t="n">
         <v>3</v>
@@ -16395,19 +16395,19 @@
         <v>1.92</v>
       </c>
       <c r="AR73" t="n">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="AS73" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AT73" t="n">
-        <v>2.43</v>
+        <v>2.16</v>
       </c>
       <c r="AU73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW73" t="n">
         <v>13</v>
@@ -16416,10 +16416,10 @@
         <v>8</v>
       </c>
       <c r="AY73" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ73" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA73" t="n">
         <v>9</v>
@@ -16613,19 +16613,19 @@
         <v>0.73</v>
       </c>
       <c r="AR74" t="n">
-        <v>1.09</v>
+        <v>0.96</v>
       </c>
       <c r="AS74" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AT74" t="n">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="AU74" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW74" t="n">
         <v>13</v>
@@ -16634,10 +16634,10 @@
         <v>7</v>
       </c>
       <c r="AY74" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ74" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA74" t="n">
         <v>9</v>
@@ -16831,19 +16831,19 @@
         <v>1.27</v>
       </c>
       <c r="AR75" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AS75" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AT75" t="n">
-        <v>3.29</v>
+        <v>3.03</v>
       </c>
       <c r="AU75" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV75" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW75" t="n">
         <v>12</v>
@@ -16852,10 +16852,10 @@
         <v>8</v>
       </c>
       <c r="AY75" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ75" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA75" t="n">
         <v>8</v>
@@ -17049,16 +17049,16 @@
         <v>0.92</v>
       </c>
       <c r="AR76" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="AS76" t="n">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="AT76" t="n">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="AU76" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV76" t="n">
         <v>0</v>
@@ -17067,13 +17067,13 @@
         <v>12</v>
       </c>
       <c r="AX76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY76" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA76" t="n">
         <v>9</v>
@@ -17267,19 +17267,19 @@
         <v>0.92</v>
       </c>
       <c r="AR77" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AS77" t="n">
-        <v>1.02</v>
+        <v>0.89</v>
       </c>
       <c r="AT77" t="n">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="AU77" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW77" t="n">
         <v>9</v>
@@ -17288,10 +17288,10 @@
         <v>5</v>
       </c>
       <c r="AY77" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ77" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA77" t="n">
         <v>6</v>
@@ -17485,31 +17485,31 @@
         <v>1.92</v>
       </c>
       <c r="AR78" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AS78" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AT78" t="n">
-        <v>2.65</v>
+        <v>2.38</v>
       </c>
       <c r="AU78" t="n">
         <v>0</v>
       </c>
       <c r="AV78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW78" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX78" t="n">
         <v>4</v>
       </c>
       <c r="AY78" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ78" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA78" t="n">
         <v>5</v>
@@ -17703,19 +17703,19 @@
         <v>0.92</v>
       </c>
       <c r="AR79" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AS79" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AT79" t="n">
-        <v>3.12</v>
+        <v>2.86</v>
       </c>
       <c r="AU79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV79" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW79" t="n">
         <v>4</v>
@@ -17724,10 +17724,10 @@
         <v>10</v>
       </c>
       <c r="AY79" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ79" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA79" t="n">
         <v>1</v>
@@ -17921,19 +17921,19 @@
         <v>1</v>
       </c>
       <c r="AR80" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AS80" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AT80" t="n">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="AU80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW80" t="n">
         <v>5</v>
@@ -17942,10 +17942,10 @@
         <v>11</v>
       </c>
       <c r="AY80" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ80" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA80" t="n">
         <v>2</v>
@@ -18139,19 +18139,19 @@
         <v>0.92</v>
       </c>
       <c r="AR81" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AS81" t="n">
-        <v>1.09</v>
+        <v>0.96</v>
       </c>
       <c r="AT81" t="n">
-        <v>2.72</v>
+        <v>2.46</v>
       </c>
       <c r="AU81" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV81" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW81" t="n">
         <v>4</v>
@@ -18160,10 +18160,10 @@
         <v>10</v>
       </c>
       <c r="AY81" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ81" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA81" t="n">
         <v>6</v>
@@ -18357,19 +18357,19 @@
         <v>0.82</v>
       </c>
       <c r="AR82" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AS82" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AT82" t="n">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="AU82" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV82" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW82" t="n">
         <v>7</v>
@@ -18378,10 +18378,10 @@
         <v>8</v>
       </c>
       <c r="AY82" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ82" t="n">
         <v>12</v>
-      </c>
-      <c r="AZ82" t="n">
-        <v>13</v>
       </c>
       <c r="BA82" t="n">
         <v>2</v>
@@ -18575,19 +18575,19 @@
         <v>1.33</v>
       </c>
       <c r="AR83" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AS83" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AT83" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="AU83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV83" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW83" t="n">
         <v>8</v>
@@ -18596,10 +18596,10 @@
         <v>11</v>
       </c>
       <c r="AY83" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ83" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA83" t="n">
         <v>4</v>
@@ -18793,16 +18793,16 @@
         <v>0.92</v>
       </c>
       <c r="AR84" t="n">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="AS84" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="AT84" t="n">
-        <v>2.71</v>
+        <v>2.46</v>
       </c>
       <c r="AU84" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV84" t="n">
         <v>0</v>
@@ -18811,13 +18811,13 @@
         <v>4</v>
       </c>
       <c r="AX84" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY84" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ84" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA84" t="n">
         <v>1</v>
@@ -19011,19 +19011,19 @@
         <v>0.67</v>
       </c>
       <c r="AR85" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AS85" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AT85" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="AU85" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW85" t="n">
         <v>13</v>
@@ -19032,10 +19032,10 @@
         <v>4</v>
       </c>
       <c r="AY85" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ85" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA85" t="n">
         <v>3</v>
@@ -19229,19 +19229,19 @@
         <v>1.62</v>
       </c>
       <c r="AR86" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AS86" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AT86" t="n">
-        <v>3.07</v>
+        <v>2.81</v>
       </c>
       <c r="AU86" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV86" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW86" t="n">
         <v>8</v>
@@ -19250,10 +19250,10 @@
         <v>5</v>
       </c>
       <c r="AY86" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ86" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA86" t="n">
         <v>4</v>
@@ -19447,19 +19447,19 @@
         <v>1</v>
       </c>
       <c r="AR87" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AS87" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AT87" t="n">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="AU87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW87" t="n">
         <v>11</v>
@@ -19468,10 +19468,10 @@
         <v>7</v>
       </c>
       <c r="AY87" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ87" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA87" t="n">
         <v>8</v>
@@ -19665,19 +19665,19 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AR88" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AS88" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AT88" t="n">
-        <v>2.96</v>
+        <v>2.72</v>
       </c>
       <c r="AU88" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV88" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW88" t="n">
         <v>2</v>
@@ -19686,10 +19686,10 @@
         <v>5</v>
       </c>
       <c r="AY88" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ88" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA88" t="n">
         <v>2</v>
@@ -19883,19 +19883,19 @@
         <v>1.08</v>
       </c>
       <c r="AR89" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AS89" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AT89" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AU89" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW89" t="n">
         <v>6</v>
@@ -19904,10 +19904,10 @@
         <v>13</v>
       </c>
       <c r="AY89" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ89" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA89" t="n">
         <v>3</v>
@@ -20101,19 +20101,19 @@
         <v>0.73</v>
       </c>
       <c r="AR90" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AS90" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AT90" t="n">
-        <v>3.05</v>
+        <v>2.79</v>
       </c>
       <c r="AU90" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV90" t="n">
         <v>5</v>
-      </c>
-      <c r="AV90" t="n">
-        <v>6</v>
       </c>
       <c r="AW90" t="n">
         <v>9</v>
@@ -20122,10 +20122,10 @@
         <v>10</v>
       </c>
       <c r="AY90" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ90" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA90" t="n">
         <v>6</v>
@@ -20319,19 +20319,19 @@
         <v>1.92</v>
       </c>
       <c r="AR91" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AS91" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AT91" t="n">
-        <v>2.52</v>
+        <v>2.26</v>
       </c>
       <c r="AU91" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW91" t="n">
         <v>6</v>
@@ -20340,10 +20340,10 @@
         <v>10</v>
       </c>
       <c r="AY91" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ91" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA91" t="n">
         <v>3</v>
@@ -20537,19 +20537,19 @@
         <v>1.09</v>
       </c>
       <c r="AR92" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AS92" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AT92" t="n">
-        <v>2.86</v>
+        <v>2.6</v>
       </c>
       <c r="AU92" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV92" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW92" t="n">
         <v>14</v>
@@ -20558,10 +20558,10 @@
         <v>5</v>
       </c>
       <c r="AY92" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ92" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA92" t="n">
         <v>9</v>
@@ -20755,19 +20755,19 @@
         <v>1.33</v>
       </c>
       <c r="AR93" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AS93" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AT93" t="n">
-        <v>2.87</v>
+        <v>2.61</v>
       </c>
       <c r="AU93" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV93" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW93" t="n">
         <v>7</v>
@@ -20776,10 +20776,10 @@
         <v>15</v>
       </c>
       <c r="AY93" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ93" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA93" t="n">
         <v>1</v>
@@ -20973,16 +20973,16 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AR94" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="AS94" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AT94" t="n">
-        <v>2.91</v>
+        <v>2.65</v>
       </c>
       <c r="AU94" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV94" t="n">
         <v>0</v>
@@ -20991,13 +20991,13 @@
         <v>10</v>
       </c>
       <c r="AX94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY94" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA94" t="n">
         <v>3</v>
@@ -21191,19 +21191,19 @@
         <v>0.73</v>
       </c>
       <c r="AR95" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AS95" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AT95" t="n">
-        <v>2.83</v>
+        <v>2.57</v>
       </c>
       <c r="AU95" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV95" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW95" t="n">
         <v>12</v>
@@ -21212,10 +21212,10 @@
         <v>5</v>
       </c>
       <c r="AY95" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ95" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA95" t="n">
         <v>4</v>
@@ -21409,19 +21409,19 @@
         <v>1.92</v>
       </c>
       <c r="AR96" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AS96" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AT96" t="n">
-        <v>2.72</v>
+        <v>2.46</v>
       </c>
       <c r="AU96" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV96" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW96" t="n">
         <v>8</v>
@@ -21430,10 +21430,10 @@
         <v>8</v>
       </c>
       <c r="AY96" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ96" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA96" t="n">
         <v>4</v>
@@ -21627,19 +21627,19 @@
         <v>1.36</v>
       </c>
       <c r="AR97" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AS97" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AT97" t="n">
-        <v>3.54</v>
+        <v>3.28</v>
       </c>
       <c r="AU97" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW97" t="n">
         <v>9</v>
@@ -21648,10 +21648,10 @@
         <v>4</v>
       </c>
       <c r="AY97" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ97" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA97" t="n">
         <v>8</v>
@@ -21845,19 +21845,19 @@
         <v>0.92</v>
       </c>
       <c r="AR98" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AS98" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="AT98" t="n">
-        <v>2.52</v>
+        <v>2.28</v>
       </c>
       <c r="AU98" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV98" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW98" t="n">
         <v>8</v>
@@ -21866,10 +21866,10 @@
         <v>7</v>
       </c>
       <c r="AY98" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ98" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA98" t="n">
         <v>4</v>
@@ -22063,19 +22063,19 @@
         <v>0.82</v>
       </c>
       <c r="AR99" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AS99" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AT99" t="n">
-        <v>2.87</v>
+        <v>2.61</v>
       </c>
       <c r="AU99" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV99" t="n">
         <v>4</v>
-      </c>
-      <c r="AV99" t="n">
-        <v>5</v>
       </c>
       <c r="AW99" t="n">
         <v>11</v>
@@ -22084,10 +22084,10 @@
         <v>5</v>
       </c>
       <c r="AY99" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ99" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA99" t="n">
         <v>2</v>
@@ -22281,19 +22281,19 @@
         <v>0.45</v>
       </c>
       <c r="AR100" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="AS100" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AT100" t="n">
-        <v>2.74</v>
+        <v>2.48</v>
       </c>
       <c r="AU100" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW100" t="n">
         <v>9</v>
@@ -22302,10 +22302,10 @@
         <v>8</v>
       </c>
       <c r="AY100" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ100" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA100" t="n">
         <v>5</v>
@@ -22499,19 +22499,19 @@
         <v>0.92</v>
       </c>
       <c r="AR101" t="n">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AS101" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="AT101" t="n">
-        <v>2.68</v>
+        <v>2.43</v>
       </c>
       <c r="AU101" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV101" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW101" t="n">
         <v>9</v>
@@ -22520,10 +22520,10 @@
         <v>8</v>
       </c>
       <c r="AY101" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ101" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA101" t="n">
         <v>6</v>
@@ -22717,19 +22717,19 @@
         <v>1.33</v>
       </c>
       <c r="AR102" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AS102" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AT102" t="n">
-        <v>3.13</v>
+        <v>2.87</v>
       </c>
       <c r="AU102" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW102" t="n">
         <v>6</v>
@@ -22738,10 +22738,10 @@
         <v>5</v>
       </c>
       <c r="AY102" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ102" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA102" t="n">
         <v>8</v>
@@ -22935,19 +22935,19 @@
         <v>1.62</v>
       </c>
       <c r="AR103" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AS103" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AT103" t="n">
-        <v>2.87</v>
+        <v>2.6</v>
       </c>
       <c r="AU103" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW103" t="n">
         <v>8</v>
@@ -22956,10 +22956,10 @@
         <v>5</v>
       </c>
       <c r="AY103" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ103" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA103" t="n">
         <v>5</v>
@@ -23153,19 +23153,19 @@
         <v>1.62</v>
       </c>
       <c r="AR104" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AS104" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AT104" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AU104" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV104" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW104" t="n">
         <v>11</v>
@@ -23174,10 +23174,10 @@
         <v>9</v>
       </c>
       <c r="AY104" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ104" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA104" t="n">
         <v>3</v>
@@ -23371,19 +23371,19 @@
         <v>1</v>
       </c>
       <c r="AR105" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AS105" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AT105" t="n">
-        <v>2.92</v>
+        <v>2.68</v>
       </c>
       <c r="AU105" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW105" t="n">
         <v>6</v>
@@ -23392,10 +23392,10 @@
         <v>4</v>
       </c>
       <c r="AY105" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ105" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA105" t="n">
         <v>4</v>
@@ -23589,19 +23589,19 @@
         <v>1.36</v>
       </c>
       <c r="AR106" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AS106" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AT106" t="n">
-        <v>2.95</v>
+        <v>2.69</v>
       </c>
       <c r="AU106" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV106" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW106" t="n">
         <v>7</v>
@@ -23610,10 +23610,10 @@
         <v>7</v>
       </c>
       <c r="AY106" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ106" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA106" t="n">
         <v>5</v>
@@ -23807,19 +23807,19 @@
         <v>1.27</v>
       </c>
       <c r="AR107" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="AS107" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AT107" t="n">
-        <v>3.2</v>
+        <v>2.93</v>
       </c>
       <c r="AU107" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV107" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW107" t="n">
         <v>3</v>
@@ -23828,10 +23828,10 @@
         <v>10</v>
       </c>
       <c r="AY107" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ107" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA107" t="n">
         <v>2</v>
@@ -24025,19 +24025,19 @@
         <v>1.77</v>
       </c>
       <c r="AR108" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AS108" t="n">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="AT108" t="n">
-        <v>3.13</v>
+        <v>2.87</v>
       </c>
       <c r="AU108" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV108" t="n">
         <v>3</v>
-      </c>
-      <c r="AV108" t="n">
-        <v>4</v>
       </c>
       <c r="AW108" t="n">
         <v>5</v>
@@ -24046,10 +24046,10 @@
         <v>11</v>
       </c>
       <c r="AY108" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ108" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA108" t="n">
         <v>0</v>
@@ -24243,19 +24243,19 @@
         <v>2.08</v>
       </c>
       <c r="AR109" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AS109" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AT109" t="n">
-        <v>2.85</v>
+        <v>2.58</v>
       </c>
       <c r="AU109" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW109" t="n">
         <v>7</v>
@@ -24264,10 +24264,10 @@
         <v>13</v>
       </c>
       <c r="AY109" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ109" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA109" t="n">
         <v>5</v>
@@ -24461,19 +24461,19 @@
         <v>0.92</v>
       </c>
       <c r="AR110" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AS110" t="n">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="AT110" t="n">
-        <v>3.25</v>
+        <v>2.97</v>
       </c>
       <c r="AU110" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW110" t="n">
         <v>10</v>
@@ -24482,10 +24482,10 @@
         <v>8</v>
       </c>
       <c r="AY110" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ110" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA110" t="n">
         <v>7</v>
@@ -24679,19 +24679,19 @@
         <v>1.92</v>
       </c>
       <c r="AR111" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="AS111" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AT111" t="n">
-        <v>2.79</v>
+        <v>2.53</v>
       </c>
       <c r="AU111" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV111" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW111" t="n">
         <v>12</v>
@@ -24700,10 +24700,10 @@
         <v>8</v>
       </c>
       <c r="AY111" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ111" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA111" t="n">
         <v>13</v>
@@ -24897,19 +24897,19 @@
         <v>1</v>
       </c>
       <c r="AR112" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AS112" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AT112" t="n">
-        <v>3.02</v>
+        <v>2.76</v>
       </c>
       <c r="AU112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW112" t="n">
         <v>8</v>
@@ -24918,10 +24918,10 @@
         <v>6</v>
       </c>
       <c r="AY112" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ112" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA112" t="n">
         <v>7</v>
@@ -25115,19 +25115,19 @@
         <v>0.73</v>
       </c>
       <c r="AR113" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AS113" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AT113" t="n">
-        <v>2.75</v>
+        <v>2.49</v>
       </c>
       <c r="AU113" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV113" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW113" t="n">
         <v>7</v>
@@ -25136,10 +25136,10 @@
         <v>10</v>
       </c>
       <c r="AY113" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ113" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA113" t="n">
         <v>10</v>
@@ -25333,19 +25333,19 @@
         <v>1.08</v>
       </c>
       <c r="AR114" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AS114" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AT114" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AU114" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV114" t="n">
         <v>5</v>
-      </c>
-      <c r="AV114" t="n">
-        <v>6</v>
       </c>
       <c r="AW114" t="n">
         <v>12</v>
@@ -25354,10 +25354,10 @@
         <v>10</v>
       </c>
       <c r="AY114" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ114" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA114" t="n">
         <v>2</v>
@@ -25551,19 +25551,19 @@
         <v>0.92</v>
       </c>
       <c r="AR115" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AS115" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AT115" t="n">
-        <v>2.49</v>
+        <v>2.24</v>
       </c>
       <c r="AU115" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV115" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW115" t="n">
         <v>7</v>
@@ -25572,10 +25572,10 @@
         <v>8</v>
       </c>
       <c r="AY115" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ115" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA115" t="n">
         <v>4</v>
@@ -25769,19 +25769,19 @@
         <v>0.45</v>
       </c>
       <c r="AR116" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AS116" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AT116" t="n">
-        <v>2.68</v>
+        <v>2.42</v>
       </c>
       <c r="AU116" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV116" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW116" t="n">
         <v>6</v>
@@ -25790,10 +25790,10 @@
         <v>10</v>
       </c>
       <c r="AY116" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ116" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA116" t="n">
         <v>4</v>
@@ -25987,19 +25987,19 @@
         <v>1.09</v>
       </c>
       <c r="AR117" t="n">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AS117" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AT117" t="n">
-        <v>2.92</v>
+        <v>2.66</v>
       </c>
       <c r="AU117" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV117" t="n">
         <v>5</v>
-      </c>
-      <c r="AV117" t="n">
-        <v>6</v>
       </c>
       <c r="AW117" t="n">
         <v>9</v>
@@ -26008,10 +26008,10 @@
         <v>6</v>
       </c>
       <c r="AY117" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ117" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA117" t="n">
         <v>4</v>
@@ -26205,19 +26205,19 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AR118" t="n">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="AS118" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="AT118" t="n">
-        <v>2.91</v>
+        <v>2.67</v>
       </c>
       <c r="AU118" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV118" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW118" t="n">
         <v>5</v>
@@ -26226,10 +26226,10 @@
         <v>6</v>
       </c>
       <c r="AY118" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ118" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA118" t="n">
         <v>4</v>
@@ -26423,19 +26423,19 @@
         <v>1.77</v>
       </c>
       <c r="AR119" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AS119" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="AT119" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="AU119" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW119" t="n">
         <v>5</v>
@@ -26444,10 +26444,10 @@
         <v>11</v>
       </c>
       <c r="AY119" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ119" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA119" t="n">
         <v>5</v>
@@ -26641,19 +26641,19 @@
         <v>1</v>
       </c>
       <c r="AR120" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AS120" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AT120" t="n">
-        <v>2.89</v>
+        <v>2.64</v>
       </c>
       <c r="AU120" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV120" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW120" t="n">
         <v>2</v>
@@ -26662,10 +26662,10 @@
         <v>11</v>
       </c>
       <c r="AY120" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ120" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA120" t="n">
         <v>2</v>
@@ -26859,19 +26859,19 @@
         <v>0.67</v>
       </c>
       <c r="AR121" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AS121" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AT121" t="n">
-        <v>2.57</v>
+        <v>2.3</v>
       </c>
       <c r="AU121" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV121" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW121" t="n">
         <v>6</v>
@@ -26880,10 +26880,10 @@
         <v>9</v>
       </c>
       <c r="AY121" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ121" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA121" t="n">
         <v>2</v>
@@ -27077,19 +27077,19 @@
         <v>0.92</v>
       </c>
       <c r="AR122" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AS122" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="AT122" t="n">
-        <v>2.96</v>
+        <v>2.71</v>
       </c>
       <c r="AU122" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV122" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW122" t="n">
         <v>7</v>
@@ -27098,10 +27098,10 @@
         <v>3</v>
       </c>
       <c r="AY122" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ122" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA122" t="n">
         <v>4</v>
@@ -27295,19 +27295,19 @@
         <v>0.67</v>
       </c>
       <c r="AR123" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="AS123" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AT123" t="n">
-        <v>2.72</v>
+        <v>2.46</v>
       </c>
       <c r="AU123" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV123" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW123" t="n">
         <v>12</v>
@@ -27316,10 +27316,10 @@
         <v>6</v>
       </c>
       <c r="AY123" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ123" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA123" t="n">
         <v>5</v>
@@ -27513,19 +27513,19 @@
         <v>1.36</v>
       </c>
       <c r="AR124" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AS124" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AT124" t="n">
-        <v>2.69</v>
+        <v>2.44</v>
       </c>
       <c r="AU124" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV124" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW124" t="n">
         <v>7</v>
@@ -27534,10 +27534,10 @@
         <v>4</v>
       </c>
       <c r="AY124" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ124" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA124" t="n">
         <v>6</v>
@@ -27731,19 +27731,19 @@
         <v>1</v>
       </c>
       <c r="AR125" t="n">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AS125" t="n">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="AT125" t="n">
-        <v>2.74</v>
+        <v>2.46</v>
       </c>
       <c r="AU125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV125" t="n">
         <v>2</v>
-      </c>
-      <c r="AV125" t="n">
-        <v>3</v>
       </c>
       <c r="AW125" t="n">
         <v>14</v>
@@ -27752,10 +27752,10 @@
         <v>6</v>
       </c>
       <c r="AY125" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ125" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA125" t="n">
         <v>7</v>
@@ -27949,19 +27949,19 @@
         <v>1.92</v>
       </c>
       <c r="AR126" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AS126" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="AT126" t="n">
-        <v>2.65</v>
+        <v>2.38</v>
       </c>
       <c r="AU126" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV126" t="n">
         <v>3</v>
-      </c>
-      <c r="AV126" t="n">
-        <v>4</v>
       </c>
       <c r="AW126" t="n">
         <v>13</v>
@@ -27970,10 +27970,10 @@
         <v>8</v>
       </c>
       <c r="AY126" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ126" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA126" t="n">
         <v>8</v>
@@ -28167,19 +28167,19 @@
         <v>1.62</v>
       </c>
       <c r="AR127" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AS127" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AT127" t="n">
-        <v>2.99</v>
+        <v>2.73</v>
       </c>
       <c r="AU127" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV127" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW127" t="n">
         <v>6</v>
@@ -28188,10 +28188,10 @@
         <v>13</v>
       </c>
       <c r="AY127" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ127" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA127" t="n">
         <v>7</v>
@@ -28385,19 +28385,19 @@
         <v>1.27</v>
       </c>
       <c r="AR128" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AS128" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AT128" t="n">
-        <v>3.33</v>
+        <v>3.07</v>
       </c>
       <c r="AU128" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV128" t="n">
         <v>3</v>
-      </c>
-      <c r="AV128" t="n">
-        <v>4</v>
       </c>
       <c r="AW128" t="n">
         <v>5</v>
@@ -28406,10 +28406,10 @@
         <v>18</v>
       </c>
       <c r="AY128" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ128" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA128" t="n">
         <v>1</v>
@@ -28603,19 +28603,19 @@
         <v>2.08</v>
       </c>
       <c r="AR129" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="AS129" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AT129" t="n">
-        <v>3.38</v>
+        <v>3.12</v>
       </c>
       <c r="AU129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV129" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW129" t="n">
         <v>4</v>
@@ -28624,10 +28624,10 @@
         <v>13</v>
       </c>
       <c r="AY129" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ129" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA129" t="n">
         <v>2</v>
@@ -28821,19 +28821,19 @@
         <v>1.27</v>
       </c>
       <c r="AR130" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AS130" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AT130" t="n">
-        <v>3.39</v>
+        <v>3.13</v>
       </c>
       <c r="AU130" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW130" t="n">
         <v>11</v>
@@ -28842,10 +28842,10 @@
         <v>7</v>
       </c>
       <c r="AY130" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ130" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA130" t="n">
         <v>8</v>
@@ -29039,19 +29039,19 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AR131" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AS131" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AT131" t="n">
-        <v>2.52</v>
+        <v>2.28</v>
       </c>
       <c r="AU131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV131" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW131" t="n">
         <v>7</v>
@@ -29060,10 +29060,10 @@
         <v>7</v>
       </c>
       <c r="AY131" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ131" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA131" t="n">
         <v>6</v>
@@ -29257,19 +29257,19 @@
         <v>0.92</v>
       </c>
       <c r="AR132" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="AS132" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AT132" t="n">
-        <v>2.67</v>
+        <v>2.41</v>
       </c>
       <c r="AU132" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV132" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW132" t="n">
         <v>8</v>
@@ -29278,10 +29278,10 @@
         <v>9</v>
       </c>
       <c r="AY132" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ132" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA132" t="n">
         <v>3</v>
@@ -29475,19 +29475,19 @@
         <v>1.09</v>
       </c>
       <c r="AR133" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AS133" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AT133" t="n">
-        <v>3.02</v>
+        <v>2.76</v>
       </c>
       <c r="AU133" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW133" t="n">
         <v>13</v>
@@ -29496,10 +29496,10 @@
         <v>6</v>
       </c>
       <c r="AY133" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ133" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA133" t="n">
         <v>6</v>
@@ -29693,19 +29693,19 @@
         <v>0.92</v>
       </c>
       <c r="AR134" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AS134" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="AT134" t="n">
-        <v>2.79</v>
+        <v>2.55</v>
       </c>
       <c r="AU134" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV134" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW134" t="n">
         <v>8</v>
@@ -29714,10 +29714,10 @@
         <v>11</v>
       </c>
       <c r="AY134" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ134" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA134" t="n">
         <v>2</v>
@@ -29911,19 +29911,19 @@
         <v>2.08</v>
       </c>
       <c r="AR135" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AS135" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AT135" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="AU135" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV135" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW135" t="n">
         <v>7</v>
@@ -29932,10 +29932,10 @@
         <v>6</v>
       </c>
       <c r="AY135" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ135" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA135" t="n">
         <v>5</v>
@@ -30129,19 +30129,19 @@
         <v>1</v>
       </c>
       <c r="AR136" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AS136" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AT136" t="n">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="AU136" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV136" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW136" t="n">
         <v>5</v>
@@ -30150,10 +30150,10 @@
         <v>5</v>
       </c>
       <c r="AY136" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ136" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA136" t="n">
         <v>3</v>
@@ -30347,19 +30347,19 @@
         <v>1.08</v>
       </c>
       <c r="AR137" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AS137" t="n">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="AT137" t="n">
-        <v>3.01</v>
+        <v>2.74</v>
       </c>
       <c r="AU137" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV137" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW137" t="n">
         <v>14</v>
@@ -30368,10 +30368,10 @@
         <v>6</v>
       </c>
       <c r="AY137" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ137" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA137" t="n">
         <v>7</v>
@@ -30565,19 +30565,19 @@
         <v>1.08</v>
       </c>
       <c r="AR138" t="n">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="AS138" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AT138" t="n">
-        <v>3.22</v>
+        <v>2.95</v>
       </c>
       <c r="AU138" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV138" t="n">
         <v>5</v>
-      </c>
-      <c r="AV138" t="n">
-        <v>6</v>
       </c>
       <c r="AW138" t="n">
         <v>12</v>
@@ -30586,10 +30586,10 @@
         <v>6</v>
       </c>
       <c r="AY138" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ138" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA138" t="n">
         <v>6</v>
@@ -30783,19 +30783,19 @@
         <v>1.36</v>
       </c>
       <c r="AR139" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AS139" t="n">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="AT139" t="n">
-        <v>3.08</v>
+        <v>2.81</v>
       </c>
       <c r="AU139" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV139" t="n">
         <v>4</v>
-      </c>
-      <c r="AV139" t="n">
-        <v>5</v>
       </c>
       <c r="AW139" t="n">
         <v>10</v>
@@ -30804,10 +30804,10 @@
         <v>10</v>
       </c>
       <c r="AY139" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ139" t="n">
         <v>14</v>
-      </c>
-      <c r="AZ139" t="n">
-        <v>15</v>
       </c>
       <c r="BA139" t="n">
         <v>3</v>
@@ -31001,31 +31001,31 @@
         <v>1</v>
       </c>
       <c r="AR140" t="n">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="AS140" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AT140" t="n">
-        <v>2.95</v>
+        <v>2.69</v>
       </c>
       <c r="AU140" t="n">
         <v>0</v>
       </c>
       <c r="AV140" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW140" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX140" t="n">
         <v>8</v>
       </c>
       <c r="AY140" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ140" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA140" t="n">
         <v>5</v>
@@ -31219,19 +31219,19 @@
         <v>1.09</v>
       </c>
       <c r="AR141" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AS141" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AT141" t="n">
-        <v>2.67</v>
+        <v>2.41</v>
       </c>
       <c r="AU141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV141" t="n">
         <v>2</v>
-      </c>
-      <c r="AV141" t="n">
-        <v>3</v>
       </c>
       <c r="AW141" t="n">
         <v>9</v>
@@ -31240,10 +31240,10 @@
         <v>7</v>
       </c>
       <c r="AY141" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ141" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA141" t="n">
         <v>4</v>
@@ -31437,19 +31437,19 @@
         <v>0.92</v>
       </c>
       <c r="AR142" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AS142" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AT142" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="AU142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV142" t="n">
         <v>2</v>
-      </c>
-      <c r="AV142" t="n">
-        <v>3</v>
       </c>
       <c r="AW142" t="n">
         <v>8</v>
@@ -31458,10 +31458,10 @@
         <v>15</v>
       </c>
       <c r="AY142" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ142" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA142" t="n">
         <v>6</v>
@@ -31655,19 +31655,19 @@
         <v>0.45</v>
       </c>
       <c r="AR143" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AS143" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AT143" t="n">
-        <v>2.69</v>
+        <v>2.43</v>
       </c>
       <c r="AU143" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW143" t="n">
         <v>0</v>
@@ -31676,10 +31676,10 @@
         <v>7</v>
       </c>
       <c r="AY143" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ143" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA143" t="n">
         <v>1</v>
@@ -31873,19 +31873,19 @@
         <v>1.62</v>
       </c>
       <c r="AR144" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AS144" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AT144" t="n">
-        <v>2.76</v>
+        <v>2.49</v>
       </c>
       <c r="AU144" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW144" t="n">
         <v>10</v>
@@ -31894,10 +31894,10 @@
         <v>9</v>
       </c>
       <c r="AY144" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ144" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA144" t="n">
         <v>1</v>
@@ -32091,19 +32091,19 @@
         <v>1.77</v>
       </c>
       <c r="AR145" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AS145" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AT145" t="n">
-        <v>3.13</v>
+        <v>2.87</v>
       </c>
       <c r="AU145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW145" t="n">
         <v>9</v>
@@ -32112,10 +32112,10 @@
         <v>3</v>
       </c>
       <c r="AY145" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ145" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA145" t="n">
         <v>2</v>
@@ -32309,19 +32309,19 @@
         <v>1.27</v>
       </c>
       <c r="AR146" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AS146" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AT146" t="n">
-        <v>2.94</v>
+        <v>2.68</v>
       </c>
       <c r="AU146" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV146" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW146" t="n">
         <v>8</v>
@@ -32330,10 +32330,10 @@
         <v>10</v>
       </c>
       <c r="AY146" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ146" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA146" t="n">
         <v>2</v>
@@ -32527,19 +32527,19 @@
         <v>1.92</v>
       </c>
       <c r="AR147" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AS147" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AT147" t="n">
-        <v>2.72</v>
+        <v>2.46</v>
       </c>
       <c r="AU147" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV147" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW147" t="n">
         <v>8</v>
@@ -32548,10 +32548,10 @@
         <v>11</v>
       </c>
       <c r="AY147" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ147" t="n">
         <v>16</v>
-      </c>
-      <c r="AZ147" t="n">
-        <v>17</v>
       </c>
       <c r="BA147" t="n">
         <v>5</v>
@@ -32745,19 +32745,19 @@
         <v>1.09</v>
       </c>
       <c r="AR148" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AS148" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AT148" t="n">
-        <v>2.73</v>
+        <v>2.47</v>
       </c>
       <c r="AU148" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV148" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW148" t="n">
         <v>11</v>
@@ -32766,10 +32766,10 @@
         <v>4</v>
       </c>
       <c r="AY148" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ148" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA148" t="n">
         <v>7</v>
@@ -32963,19 +32963,19 @@
         <v>2.08</v>
       </c>
       <c r="AR149" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AS149" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AT149" t="n">
-        <v>2.71</v>
+        <v>2.45</v>
       </c>
       <c r="AU149" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV149" t="n">
         <v>5</v>
-      </c>
-      <c r="AV149" t="n">
-        <v>6</v>
       </c>
       <c r="AW149" t="n">
         <v>9</v>
@@ -32984,10 +32984,10 @@
         <v>8</v>
       </c>
       <c r="AY149" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ149" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA149" t="n">
         <v>2</v>
@@ -33181,19 +33181,19 @@
         <v>1.33</v>
       </c>
       <c r="AR150" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AS150" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AT150" t="n">
-        <v>3.11</v>
+        <v>2.85</v>
       </c>
       <c r="AU150" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV150" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW150" t="n">
         <v>7</v>
@@ -33202,10 +33202,10 @@
         <v>14</v>
       </c>
       <c r="AY150" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ150" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA150" t="n">
         <v>5</v>
@@ -33399,19 +33399,19 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AR151" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AS151" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AT151" t="n">
-        <v>2.81</v>
+        <v>2.57</v>
       </c>
       <c r="AU151" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV151" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW151" t="n">
         <v>10</v>
@@ -33420,10 +33420,10 @@
         <v>11</v>
       </c>
       <c r="AY151" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ151" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA151" t="n">
         <v>6</v>
@@ -33617,19 +33617,19 @@
         <v>0.82</v>
       </c>
       <c r="AR152" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AS152" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AT152" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="AU152" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV152" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW152" t="n">
         <v>6</v>
@@ -33638,10 +33638,10 @@
         <v>9</v>
       </c>
       <c r="AY152" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ152" t="n">
         <v>11</v>
-      </c>
-      <c r="AZ152" t="n">
-        <v>12</v>
       </c>
       <c r="BA152" t="n">
         <v>5</v>
@@ -33835,19 +33835,19 @@
         <v>1.77</v>
       </c>
       <c r="AR153" t="n">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AS153" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AT153" t="n">
-        <v>3.13</v>
+        <v>2.87</v>
       </c>
       <c r="AU153" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV153" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW153" t="n">
         <v>8</v>
@@ -33856,10 +33856,10 @@
         <v>11</v>
       </c>
       <c r="AY153" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ153" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA153" t="n">
         <v>3</v>
@@ -34053,19 +34053,19 @@
         <v>0.73</v>
       </c>
       <c r="AR154" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AS154" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AT154" t="n">
-        <v>3.24</v>
+        <v>2.98</v>
       </c>
       <c r="AU154" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV154" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW154" t="n">
         <v>11</v>
@@ -34074,10 +34074,10 @@
         <v>14</v>
       </c>
       <c r="AY154" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ154" t="n">
         <v>16</v>
-      </c>
-      <c r="AZ154" t="n">
-        <v>17</v>
       </c>
       <c r="BA154" t="n">
         <v>3</v>
@@ -34271,31 +34271,31 @@
         <v>0.92</v>
       </c>
       <c r="AR155" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AS155" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AT155" t="n">
-        <v>2.68</v>
+        <v>2.43</v>
       </c>
       <c r="AU155" t="n">
         <v>0</v>
       </c>
       <c r="AV155" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW155" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX155" t="n">
         <v>4</v>
       </c>
       <c r="AY155" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ155" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA155" t="n">
         <v>9</v>
@@ -34489,19 +34489,19 @@
         <v>1.92</v>
       </c>
       <c r="AR156" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AS156" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AT156" t="n">
-        <v>2.67</v>
+        <v>2.41</v>
       </c>
       <c r="AU156" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV156" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW156" t="n">
         <v>9</v>
@@ -34510,10 +34510,10 @@
         <v>16</v>
       </c>
       <c r="AY156" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ156" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA156" t="n">
         <v>9</v>
@@ -34707,19 +34707,19 @@
         <v>0.45</v>
       </c>
       <c r="AR157" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AS157" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AT157" t="n">
-        <v>2.84</v>
+        <v>2.58</v>
       </c>
       <c r="AU157" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV157" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW157" t="n">
         <v>13</v>
@@ -34728,10 +34728,10 @@
         <v>6</v>
       </c>
       <c r="AY157" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ157" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA157" t="n">
         <v>4</v>
@@ -34925,19 +34925,19 @@
         <v>1.62</v>
       </c>
       <c r="AR158" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AS158" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AT158" t="n">
-        <v>2.72</v>
+        <v>2.46</v>
       </c>
       <c r="AU158" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV158" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW158" t="n">
         <v>10</v>
@@ -34946,10 +34946,10 @@
         <v>7</v>
       </c>
       <c r="AY158" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ158" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA158" t="n">
         <v>5</v>
@@ -35143,19 +35143,19 @@
         <v>1</v>
       </c>
       <c r="AR159" t="n">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="AS159" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AT159" t="n">
-        <v>3.31</v>
+        <v>3.04</v>
       </c>
       <c r="AU159" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV159" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW159" t="n">
         <v>6</v>
@@ -35164,10 +35164,10 @@
         <v>6</v>
       </c>
       <c r="AY159" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ159" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA159" t="n">
         <v>8</v>
@@ -35361,19 +35361,19 @@
         <v>1.92</v>
       </c>
       <c r="AR160" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AS160" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AT160" t="n">
-        <v>2.83</v>
+        <v>2.57</v>
       </c>
       <c r="AU160" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV160" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW160" t="n">
         <v>5</v>
@@ -35382,10 +35382,10 @@
         <v>5</v>
       </c>
       <c r="AY160" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ160" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA160" t="n">
         <v>2</v>
@@ -35579,19 +35579,19 @@
         <v>1</v>
       </c>
       <c r="AR161" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AS161" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AT161" t="n">
-        <v>2.85</v>
+        <v>2.59</v>
       </c>
       <c r="AU161" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV161" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW161" t="n">
         <v>12</v>
@@ -35600,10 +35600,10 @@
         <v>1</v>
       </c>
       <c r="AY161" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ161" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA161" t="n">
         <v>8</v>
@@ -35797,19 +35797,19 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AR162" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AS162" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AT162" t="n">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="AU162" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV162" t="n">
         <v>4</v>
-      </c>
-      <c r="AV162" t="n">
-        <v>5</v>
       </c>
       <c r="AW162" t="n">
         <v>4</v>
@@ -35818,10 +35818,10 @@
         <v>10</v>
       </c>
       <c r="AY162" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ162" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA162" t="n">
         <v>4</v>
@@ -36015,19 +36015,19 @@
         <v>0.92</v>
       </c>
       <c r="AR163" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AS163" t="n">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="AT163" t="n">
-        <v>3.14</v>
+        <v>2.89</v>
       </c>
       <c r="AU163" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV163" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW163" t="n">
         <v>8</v>
@@ -36036,10 +36036,10 @@
         <v>16</v>
       </c>
       <c r="AY163" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ163" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA163" t="n">
         <v>1</v>
@@ -36233,19 +36233,19 @@
         <v>0.45</v>
       </c>
       <c r="AR164" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AS164" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AT164" t="n">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="AU164" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV164" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW164" t="n">
         <v>5</v>
@@ -36254,10 +36254,10 @@
         <v>5</v>
       </c>
       <c r="AY164" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ164" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA164" t="n">
         <v>8</v>
@@ -36451,19 +36451,19 @@
         <v>0.92</v>
       </c>
       <c r="AR165" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AS165" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AT165" t="n">
-        <v>2.58</v>
+        <v>2.32</v>
       </c>
       <c r="AU165" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV165" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW165" t="n">
         <v>12</v>
@@ -36472,10 +36472,10 @@
         <v>6</v>
       </c>
       <c r="AY165" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ165" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA165" t="n">
         <v>8</v>
@@ -36669,19 +36669,19 @@
         <v>1.08</v>
       </c>
       <c r="AR166" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AS166" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AT166" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="AU166" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV166" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW166" t="n">
         <v>11</v>
@@ -36690,10 +36690,10 @@
         <v>9</v>
       </c>
       <c r="AY166" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ166" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA166" t="n">
         <v>5</v>
@@ -36887,19 +36887,19 @@
         <v>0.67</v>
       </c>
       <c r="AR167" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AS167" t="n">
-        <v>1.13</v>
+        <v>0.99</v>
       </c>
       <c r="AT167" t="n">
-        <v>2.66</v>
+        <v>2.39</v>
       </c>
       <c r="AU167" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV167" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW167" t="n">
         <v>14</v>
@@ -36908,10 +36908,10 @@
         <v>4</v>
       </c>
       <c r="AY167" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ167" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA167" t="n">
         <v>7</v>
@@ -37105,19 +37105,19 @@
         <v>0.82</v>
       </c>
       <c r="AR168" t="n">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="AS168" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AT168" t="n">
-        <v>3.23</v>
+        <v>2.96</v>
       </c>
       <c r="AU168" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV168" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW168" t="n">
         <v>8</v>
@@ -37126,10 +37126,10 @@
         <v>4</v>
       </c>
       <c r="AY168" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ168" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA168" t="n">
         <v>4</v>
@@ -37323,19 +37323,19 @@
         <v>1.92</v>
       </c>
       <c r="AR169" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AS169" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AT169" t="n">
-        <v>2.79</v>
+        <v>2.53</v>
       </c>
       <c r="AU169" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV169" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW169" t="n">
         <v>10</v>
@@ -37344,10 +37344,10 @@
         <v>6</v>
       </c>
       <c r="AY169" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ169" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA169" t="n">
         <v>5</v>
@@ -37541,19 +37541,19 @@
         <v>1.27</v>
       </c>
       <c r="AR170" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="AS170" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AT170" t="n">
-        <v>3.49</v>
+        <v>3.23</v>
       </c>
       <c r="AU170" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV170" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW170" t="n">
         <v>7</v>
@@ -37562,10 +37562,10 @@
         <v>10</v>
       </c>
       <c r="AY170" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ170" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA170" t="n">
         <v>4</v>
@@ -37759,19 +37759,19 @@
         <v>0.82</v>
       </c>
       <c r="AR171" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AS171" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="AT171" t="n">
-        <v>2.84</v>
+        <v>2.58</v>
       </c>
       <c r="AU171" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV171" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW171" t="n">
         <v>18</v>
@@ -37780,10 +37780,10 @@
         <v>1</v>
       </c>
       <c r="AY171" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AZ171" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA171" t="n">
         <v>7</v>
@@ -37977,19 +37977,19 @@
         <v>2.08</v>
       </c>
       <c r="AR172" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AS172" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AT172" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="AU172" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV172" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW172" t="n">
         <v>5</v>
@@ -37998,10 +37998,10 @@
         <v>9</v>
       </c>
       <c r="AY172" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ172" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA172" t="n">
         <v>2</v>
@@ -38195,19 +38195,19 @@
         <v>1.36</v>
       </c>
       <c r="AR173" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AS173" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AT173" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AU173" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV173" t="n">
         <v>5</v>
-      </c>
-      <c r="AV173" t="n">
-        <v>6</v>
       </c>
       <c r="AW173" t="n">
         <v>3</v>
@@ -38216,10 +38216,10 @@
         <v>12</v>
       </c>
       <c r="AY173" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ173" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA173" t="n">
         <v>4</v>
@@ -38413,19 +38413,19 @@
         <v>1.92</v>
       </c>
       <c r="AR174" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AS174" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AT174" t="n">
-        <v>2.65</v>
+        <v>2.39</v>
       </c>
       <c r="AU174" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV174" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW174" t="n">
         <v>10</v>
@@ -38434,10 +38434,10 @@
         <v>12</v>
       </c>
       <c r="AY174" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ174" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA174" t="n">
         <v>6</v>
@@ -38631,19 +38631,19 @@
         <v>0.92</v>
       </c>
       <c r="AR175" t="n">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="AS175" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AT175" t="n">
-        <v>2.79</v>
+        <v>2.53</v>
       </c>
       <c r="AU175" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW175" t="n">
         <v>4</v>
@@ -38652,10 +38652,10 @@
         <v>8</v>
       </c>
       <c r="AY175" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ175" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA175" t="n">
         <v>3</v>
@@ -38849,19 +38849,19 @@
         <v>1.92</v>
       </c>
       <c r="AR176" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AS176" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AT176" t="n">
-        <v>2.71</v>
+        <v>2.45</v>
       </c>
       <c r="AU176" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV176" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW176" t="n">
         <v>5</v>
@@ -38870,10 +38870,10 @@
         <v>12</v>
       </c>
       <c r="AY176" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ176" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA176" t="n">
         <v>9</v>
@@ -39067,19 +39067,19 @@
         <v>1.62</v>
       </c>
       <c r="AR177" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="AS177" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AT177" t="n">
-        <v>2.79</v>
+        <v>2.54</v>
       </c>
       <c r="AU177" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV177" t="n">
         <v>3</v>
-      </c>
-      <c r="AV177" t="n">
-        <v>4</v>
       </c>
       <c r="AW177" t="n">
         <v>10</v>
@@ -39088,10 +39088,10 @@
         <v>6</v>
       </c>
       <c r="AY177" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ177" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA177" t="n">
         <v>4</v>
@@ -39285,19 +39285,19 @@
         <v>1.77</v>
       </c>
       <c r="AR178" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AS178" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AT178" t="n">
-        <v>3.06</v>
+        <v>2.8</v>
       </c>
       <c r="AU178" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV178" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW178" t="n">
         <v>6</v>
@@ -39306,10 +39306,10 @@
         <v>12</v>
       </c>
       <c r="AY178" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ178" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA178" t="n">
         <v>2</v>
@@ -39503,19 +39503,19 @@
         <v>1</v>
       </c>
       <c r="AR179" t="n">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="AS179" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AT179" t="n">
-        <v>3.29</v>
+        <v>3.03</v>
       </c>
       <c r="AU179" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV179" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW179" t="n">
         <v>10</v>
@@ -39524,10 +39524,10 @@
         <v>8</v>
       </c>
       <c r="AY179" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ179" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA179" t="n">
         <v>3</v>
@@ -39721,31 +39721,31 @@
         <v>1.08</v>
       </c>
       <c r="AR180" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AS180" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AT180" t="n">
-        <v>2.94</v>
+        <v>2.69</v>
       </c>
       <c r="AU180" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV180" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW180" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX180" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AY180" t="n">
         <v>11</v>
       </c>
       <c r="AZ180" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="BA180" t="n">
         <v>4</v>
@@ -39939,28 +39939,28 @@
         <v>0.67</v>
       </c>
       <c r="AR181" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AS181" t="n">
-        <v>1.12</v>
+        <v>0.99</v>
       </c>
       <c r="AT181" t="n">
-        <v>2.67</v>
+        <v>2.41</v>
       </c>
       <c r="AU181" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV181" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW181" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AX181" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY181" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AZ181" t="n">
         <v>6</v>
@@ -40157,31 +40157,31 @@
         <v>0.73</v>
       </c>
       <c r="AR182" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AS182" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AT182" t="n">
-        <v>2.82</v>
+        <v>2.56</v>
       </c>
       <c r="AU182" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV182" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW182" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX182" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY182" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ182" t="n">
         <v>7</v>
-      </c>
-      <c r="AV182" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW182" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX182" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY182" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ182" t="n">
-        <v>6</v>
       </c>
       <c r="BA182" t="n">
         <v>5</v>
@@ -40375,16 +40375,16 @@
         <v>1</v>
       </c>
       <c r="AR183" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="AS183" t="n">
-        <v>1.11</v>
+        <v>0.98</v>
       </c>
       <c r="AT183" t="n">
-        <v>2.67</v>
+        <v>2.41</v>
       </c>
       <c r="AU183" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV183" t="n">
         <v>-1</v>
@@ -40396,7 +40396,7 @@
         <v>7</v>
       </c>
       <c r="AY183" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ183" t="n">
         <v>6</v>
@@ -40593,31 +40593,31 @@
         <v>1.92</v>
       </c>
       <c r="AR184" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AS184" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AT184" t="n">
-        <v>3.04</v>
+        <v>2.78</v>
       </c>
       <c r="AU184" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV184" t="n">
         <v>3</v>
       </c>
-      <c r="AV184" t="n">
-        <v>4</v>
-      </c>
       <c r="AW184" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AX184" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AY184" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AZ184" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BA184" t="n">
         <v>5</v>
@@ -40811,31 +40811,31 @@
         <v>1.33</v>
       </c>
       <c r="AR185" t="n">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="AS185" t="n">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AT185" t="n">
-        <v>3.28</v>
+        <v>3.02</v>
       </c>
       <c r="AU185" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV185" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW185" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AX185" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AY185" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AZ185" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BA185" t="n">
         <v>5</v>
@@ -41029,31 +41029,31 @@
         <v>1.36</v>
       </c>
       <c r="AR186" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AS186" t="n">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="AT186" t="n">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="AU186" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV186" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW186" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="AX186" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY186" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AZ186" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA186" t="n">
         <v>10</v>
@@ -41247,31 +41247,31 @@
         <v>0.92</v>
       </c>
       <c r="AR187" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AS187" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AT187" t="n">
-        <v>2.81</v>
+        <v>2.55</v>
       </c>
       <c r="AU187" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV187" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW187" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX187" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY187" t="n">
         <v>15</v>
       </c>
       <c r="AZ187" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA187" t="n">
         <v>3</v>
@@ -41465,19 +41465,19 @@
         <v>1.09</v>
       </c>
       <c r="AR188" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AS188" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AT188" t="n">
-        <v>2.74</v>
+        <v>2.48</v>
       </c>
       <c r="AU188" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV188" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW188" t="n">
         <v>7</v>
@@ -41486,10 +41486,10 @@
         <v>6</v>
       </c>
       <c r="AY188" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ188" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA188" t="n">
         <v>2</v>
@@ -41683,31 +41683,31 @@
         <v>0.92</v>
       </c>
       <c r="AR189" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AS189" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AT189" t="n">
-        <v>3.43</v>
+        <v>3.17</v>
       </c>
       <c r="AU189" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV189" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW189" t="n">
         <v>10</v>
       </c>
-      <c r="AV189" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW189" t="n">
-        <v>7</v>
-      </c>
       <c r="AX189" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY189" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AZ189" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA189" t="n">
         <v>13</v>
@@ -41901,31 +41901,31 @@
         <v>0.45</v>
       </c>
       <c r="AR190" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AS190" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AT190" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AU190" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV190" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW190" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AX190" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY190" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AZ190" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA190" t="n">
         <v>8</v>
@@ -42119,31 +42119,31 @@
         <v>2.08</v>
       </c>
       <c r="AR191" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AS191" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AT191" t="n">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="AU191" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV191" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW191" t="n">
         <v>7</v>
       </c>
       <c r="AX191" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AY191" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ191" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA191" t="n">
         <v>3</v>
@@ -42337,31 +42337,31 @@
         <v>1.77</v>
       </c>
       <c r="AR192" t="n">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AS192" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AT192" t="n">
-        <v>3.23</v>
+        <v>2.97</v>
       </c>
       <c r="AU192" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV192" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW192" t="n">
         <v>13</v>
       </c>
       <c r="AX192" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY192" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ192" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA192" t="n">
         <v>12</v>
@@ -42555,28 +42555,28 @@
         <v>1.33</v>
       </c>
       <c r="AR193" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AS193" t="n">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AT193" t="n">
-        <v>2.89</v>
+        <v>2.63</v>
       </c>
       <c r="AU193" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV193" t="n">
         <v>2</v>
       </c>
-      <c r="AV193" t="n">
-        <v>3</v>
-      </c>
       <c r="AW193" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AX193" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY193" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AZ193" t="n">
         <v>6</v>
@@ -42773,31 +42773,31 @@
         <v>1.08</v>
       </c>
       <c r="AR194" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AS194" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AT194" t="n">
-        <v>2.91</v>
+        <v>2.64</v>
       </c>
       <c r="AU194" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV194" t="n">
         <v>6</v>
       </c>
-      <c r="AV194" t="n">
-        <v>7</v>
-      </c>
       <c r="AW194" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX194" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY194" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ194" t="n">
         <v>12</v>
-      </c>
-      <c r="AX194" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY194" t="n">
-        <v>18</v>
-      </c>
-      <c r="AZ194" t="n">
-        <v>11</v>
       </c>
       <c r="BA194" t="n">
         <v>4</v>
@@ -42991,31 +42991,31 @@
         <v>0.73</v>
       </c>
       <c r="AR195" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AS195" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AT195" t="n">
-        <v>2.87</v>
+        <v>2.61</v>
       </c>
       <c r="AU195" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV195" t="n">
         <v>0</v>
       </c>
       <c r="AW195" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AX195" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY195" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AZ195" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA195" t="n">
         <v>7</v>
@@ -43209,28 +43209,28 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AR196" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AS196" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AT196" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="AU196" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV196" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW196" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AX196" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY196" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AZ196" t="n">
         <v>10</v>
@@ -43427,19 +43427,19 @@
         <v>1.27</v>
       </c>
       <c r="AR197" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AS197" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AT197" t="n">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="AU197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV197" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW197" t="n">
         <v>5</v>
@@ -43448,10 +43448,10 @@
         <v>12</v>
       </c>
       <c r="AY197" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ197" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA197" t="n">
         <v>3</v>
@@ -43645,31 +43645,31 @@
         <v>1.92</v>
       </c>
       <c r="AR198" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AS198" t="n">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="AT198" t="n">
-        <v>2.84</v>
+        <v>2.57</v>
       </c>
       <c r="AU198" t="n">
         <v>0</v>
       </c>
       <c r="AV198" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW198" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX198" t="n">
         <v>6</v>
       </c>
       <c r="AY198" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ198" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA198" t="n">
         <v>3</v>
@@ -43863,31 +43863,31 @@
         <v>1</v>
       </c>
       <c r="AR199" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AS199" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AT199" t="n">
-        <v>2.96</v>
+        <v>2.7</v>
       </c>
       <c r="AU199" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV199" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW199" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX199" t="n">
         <v>12</v>
       </c>
       <c r="AY199" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ199" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA199" t="n">
         <v>1</v>
@@ -44081,28 +44081,28 @@
         <v>0.67</v>
       </c>
       <c r="AR200" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="AS200" t="n">
-        <v>1.12</v>
+        <v>0.99</v>
       </c>
       <c r="AT200" t="n">
-        <v>2.68</v>
+        <v>2.42</v>
       </c>
       <c r="AU200" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV200" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW200" t="n">
         <v>3</v>
       </c>
-      <c r="AW200" t="n">
-        <v>4</v>
-      </c>
       <c r="AX200" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY200" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ200" t="n">
         <v>10</v>
@@ -44299,28 +44299,28 @@
         <v>1.36</v>
       </c>
       <c r="AR201" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AS201" t="n">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="AT201" t="n">
-        <v>2.94</v>
+        <v>2.67</v>
       </c>
       <c r="AU201" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV201" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW201" t="n">
         <v>7</v>
       </c>
       <c r="AX201" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY201" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ201" t="n">
         <v>11</v>
@@ -44517,31 +44517,31 @@
         <v>1</v>
       </c>
       <c r="AR202" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AS202" t="n">
-        <v>1.11</v>
+        <v>0.98</v>
       </c>
       <c r="AT202" t="n">
-        <v>2.99</v>
+        <v>2.73</v>
       </c>
       <c r="AU202" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV202" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW202" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX202" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AY202" t="n">
         <v>7</v>
       </c>
       <c r="AZ202" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BA202" t="n">
         <v>5</v>
@@ -44735,19 +44735,19 @@
         <v>1.09</v>
       </c>
       <c r="AR203" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AS203" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AT203" t="n">
-        <v>2.68</v>
+        <v>2.42</v>
       </c>
       <c r="AU203" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV203" t="n">
         <v>5</v>
-      </c>
-      <c r="AV203" t="n">
-        <v>6</v>
       </c>
       <c r="AW203" t="n">
         <v>10</v>
@@ -44756,10 +44756,10 @@
         <v>5</v>
       </c>
       <c r="AY203" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ203" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA203" t="n">
         <v>10</v>
@@ -44953,31 +44953,31 @@
         <v>0.92</v>
       </c>
       <c r="AR204" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AS204" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AT204" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="AU204" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV204" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW204" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AX204" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AY204" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AZ204" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="BA204" t="n">
         <v>3</v>
@@ -45171,31 +45171,31 @@
         <v>1.62</v>
       </c>
       <c r="AR205" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AS205" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AT205" t="n">
-        <v>2.93</v>
+        <v>2.67</v>
       </c>
       <c r="AU205" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV205" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW205" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AX205" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AY205" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AZ205" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA205" t="n">
         <v>7</v>
@@ -45389,31 +45389,31 @@
         <v>1.92</v>
       </c>
       <c r="AR206" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AS206" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AT206" t="n">
-        <v>3.17</v>
+        <v>2.91</v>
       </c>
       <c r="AU206" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV206" t="n">
         <v>4</v>
       </c>
-      <c r="AV206" t="n">
+      <c r="AW206" t="n">
         <v>5</v>
       </c>
-      <c r="AW206" t="n">
-        <v>2</v>
-      </c>
       <c r="AX206" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AY206" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AZ206" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BA206" t="n">
         <v>4</v>
@@ -45607,31 +45607,31 @@
         <v>1.77</v>
       </c>
       <c r="AR207" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AS207" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="AT207" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="AU207" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV207" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW207" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AX207" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY207" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AZ207" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA207" t="n">
         <v>6</v>
@@ -45825,31 +45825,31 @@
         <v>0.92</v>
       </c>
       <c r="AR208" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AS208" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AT208" t="n">
-        <v>2.81</v>
+        <v>2.55</v>
       </c>
       <c r="AU208" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV208" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW208" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX208" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY208" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ208" t="n">
         <v>7</v>
-      </c>
-      <c r="AV208" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW208" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX208" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY208" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ208" t="n">
-        <v>10</v>
       </c>
       <c r="BA208" t="n">
         <v>5</v>
@@ -46043,25 +46043,25 @@
         <v>0.67</v>
       </c>
       <c r="AR209" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AS209" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AT209" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AU209" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV209" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW209" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX209" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY209" t="n">
         <v>10</v>
@@ -46261,31 +46261,31 @@
         <v>0.92</v>
       </c>
       <c r="AR210" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AS210" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AT210" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="AU210" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV210" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW210" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX210" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY210" t="n">
         <v>8</v>
       </c>
-      <c r="AW210" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX210" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY210" t="n">
-        <v>7</v>
-      </c>
       <c r="AZ210" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BA210" t="n">
         <v>6</v>
@@ -46479,31 +46479,31 @@
         <v>1.09</v>
       </c>
       <c r="AR211" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AS211" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AT211" t="n">
-        <v>2.91</v>
+        <v>2.65</v>
       </c>
       <c r="AU211" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV211" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW211" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AX211" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AY211" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AZ211" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA211" t="n">
         <v>13</v>
@@ -46697,28 +46697,28 @@
         <v>1.92</v>
       </c>
       <c r="AR212" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AS212" t="n">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="AT212" t="n">
-        <v>2.92</v>
+        <v>2.64</v>
       </c>
       <c r="AU212" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV212" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW212" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AX212" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY212" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ212" t="n">
         <v>16</v>
@@ -46915,31 +46915,31 @@
         <v>0.45</v>
       </c>
       <c r="AR213" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AS213" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AT213" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="AU213" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV213" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW213" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX213" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY213" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ213" t="n">
         <v>8</v>
-      </c>
-      <c r="AV213" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW213" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX213" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY213" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ213" t="n">
-        <v>7</v>
       </c>
       <c r="BA213" t="n">
         <v>4</v>
@@ -47133,31 +47133,31 @@
         <v>0.73</v>
       </c>
       <c r="AR214" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AS214" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AT214" t="n">
-        <v>2.82</v>
+        <v>2.56</v>
       </c>
       <c r="AU214" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV214" t="n">
         <v>4</v>
       </c>
-      <c r="AV214" t="n">
-        <v>5</v>
-      </c>
       <c r="AW214" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX214" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AY214" t="n">
         <v>10</v>
       </c>
       <c r="AZ214" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA214" t="n">
         <v>5</v>
@@ -47351,31 +47351,31 @@
         <v>1.92</v>
       </c>
       <c r="AR215" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AS215" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AT215" t="n">
-        <v>3.03</v>
+        <v>2.76</v>
       </c>
       <c r="AU215" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV215" t="n">
         <v>2</v>
       </c>
-      <c r="AV215" t="n">
-        <v>3</v>
-      </c>
       <c r="AW215" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX215" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY215" t="n">
         <v>3</v>
       </c>
       <c r="AZ215" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA215" t="n">
         <v>8</v>
@@ -47569,31 +47569,31 @@
         <v>1</v>
       </c>
       <c r="AR216" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AS216" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AT216" t="n">
-        <v>3.19</v>
+        <v>2.94</v>
       </c>
       <c r="AU216" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV216" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW216" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AX216" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY216" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ216" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA216" t="n">
         <v>4</v>
@@ -47787,19 +47787,19 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AR217" t="n">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="AS217" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AT217" t="n">
-        <v>2.94</v>
+        <v>2.69</v>
       </c>
       <c r="AU217" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV217" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW217" t="n">
         <v>12</v>
@@ -47808,10 +47808,10 @@
         <v>7</v>
       </c>
       <c r="AY217" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ217" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA217" t="n">
         <v>8</v>
@@ -48005,19 +48005,19 @@
         <v>1.33</v>
       </c>
       <c r="AR218" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AS218" t="n">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AT218" t="n">
-        <v>2.91</v>
+        <v>2.66</v>
       </c>
       <c r="AU218" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV218" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW218" t="n">
         <v>7</v>
@@ -48026,10 +48026,10 @@
         <v>6</v>
       </c>
       <c r="AY218" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ218" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA218" t="n">
         <v>7</v>
@@ -48223,28 +48223,28 @@
         <v>2.08</v>
       </c>
       <c r="AR219" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AS219" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AT219" t="n">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="AU219" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV219" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW219" t="n">
         <v>20</v>
       </c>
       <c r="AX219" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY219" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ219" t="n">
         <v>24</v>
@@ -48441,31 +48441,31 @@
         <v>1.77</v>
       </c>
       <c r="AR220" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AS220" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AT220" t="n">
-        <v>3.37</v>
+        <v>3.11</v>
       </c>
       <c r="AU220" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV220" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW220" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX220" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AY220" t="n">
         <v>10</v>
       </c>
       <c r="AZ220" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA220" t="n">
         <v>3</v>
@@ -48659,31 +48659,31 @@
         <v>0.92</v>
       </c>
       <c r="AR221" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AS221" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AT221" t="n">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="AU221" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV221" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW221" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX221" t="n">
         <v>8</v>
       </c>
-      <c r="AX221" t="n">
-        <v>10</v>
-      </c>
       <c r="AY221" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ221" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA221" t="n">
         <v>2</v>
@@ -48877,31 +48877,31 @@
         <v>1.77</v>
       </c>
       <c r="AR222" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AS222" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AT222" t="n">
-        <v>3.19</v>
+        <v>2.93</v>
       </c>
       <c r="AU222" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV222" t="n">
         <v>4</v>
-      </c>
-      <c r="AV222" t="n">
-        <v>5</v>
       </c>
       <c r="AW222" t="n">
         <v>4</v>
       </c>
       <c r="AX222" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY222" t="n">
         <v>7</v>
       </c>
-      <c r="AY222" t="n">
-        <v>8</v>
-      </c>
       <c r="AZ222" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="BA222" t="n">
         <v>5</v>
@@ -49095,31 +49095,31 @@
         <v>0.92</v>
       </c>
       <c r="AR223" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="AS223" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AT223" t="n">
-        <v>2.81</v>
+        <v>2.58</v>
       </c>
       <c r="AU223" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV223" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW223" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AX223" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AY223" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AZ223" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BA223" t="n">
         <v>4</v>
@@ -49313,31 +49313,31 @@
         <v>1.36</v>
       </c>
       <c r="AR224" t="n">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="AS224" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AT224" t="n">
-        <v>3.13</v>
+        <v>2.88</v>
       </c>
       <c r="AU224" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV224" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW224" t="n">
         <v>10</v>
       </c>
       <c r="AX224" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY224" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ224" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA224" t="n">
         <v>7</v>
@@ -49531,31 +49531,31 @@
         <v>0.73</v>
       </c>
       <c r="AR225" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AS225" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AT225" t="n">
-        <v>2.65</v>
+        <v>2.42</v>
       </c>
       <c r="AU225" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV225" t="n">
         <v>2</v>
       </c>
-      <c r="AV225" t="n">
-        <v>3</v>
-      </c>
       <c r="AW225" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AX225" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AY225" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AZ225" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="BA225" t="n">
         <v>7</v>
@@ -49749,22 +49749,22 @@
         <v>1</v>
       </c>
       <c r="AR226" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AS226" t="n">
-        <v>1.11</v>
+        <v>0.98</v>
       </c>
       <c r="AT226" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AU226" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV226" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW226" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX226" t="n">
         <v>4</v>
@@ -49773,7 +49773,7 @@
         <v>7</v>
       </c>
       <c r="AZ226" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA226" t="n">
         <v>4</v>
@@ -49967,28 +49967,28 @@
         <v>0.67</v>
       </c>
       <c r="AR227" t="n">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="AS227" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AT227" t="n">
-        <v>2.81</v>
+        <v>2.55</v>
       </c>
       <c r="AU227" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV227" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW227" t="n">
         <v>10</v>
       </c>
       <c r="AX227" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY227" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ227" t="n">
         <v>12</v>
@@ -50185,31 +50185,31 @@
         <v>1</v>
       </c>
       <c r="AR228" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AS228" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AT228" t="n">
-        <v>3.45</v>
+        <v>3.19</v>
       </c>
       <c r="AU228" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV228" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW228" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX228" t="n">
         <v>10</v>
       </c>
-      <c r="AX228" t="n">
-        <v>4</v>
-      </c>
       <c r="AY228" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ228" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="BA228" t="n">
         <v>5</v>
@@ -50403,31 +50403,31 @@
         <v>0.92</v>
       </c>
       <c r="AR229" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AS229" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AT229" t="n">
-        <v>3.09</v>
+        <v>2.84</v>
       </c>
       <c r="AU229" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV229" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW229" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX229" t="n">
         <v>4</v>
       </c>
-      <c r="AW229" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX229" t="n">
-        <v>2</v>
-      </c>
       <c r="AY229" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ229" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA229" t="n">
         <v>6</v>
@@ -50621,31 +50621,31 @@
         <v>0.82</v>
       </c>
       <c r="AR230" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AS230" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AT230" t="n">
-        <v>2.89</v>
+        <v>2.62</v>
       </c>
       <c r="AU230" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV230" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW230" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AX230" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AY230" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AZ230" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA230" t="n">
         <v>6</v>
@@ -50839,31 +50839,31 @@
         <v>1.08</v>
       </c>
       <c r="AR231" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AS231" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AT231" t="n">
-        <v>2.89</v>
+        <v>2.63</v>
       </c>
       <c r="AU231" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV231" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW231" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AX231" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AY231" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AZ231" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="BA231" t="n">
         <v>4</v>
@@ -51057,31 +51057,31 @@
         <v>1.92</v>
       </c>
       <c r="AR232" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AS232" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AT232" t="n">
-        <v>3.08</v>
+        <v>2.82</v>
       </c>
       <c r="AU232" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV232" t="n">
         <v>4</v>
-      </c>
-      <c r="AV232" t="n">
-        <v>5</v>
       </c>
       <c r="AW232" t="n">
         <v>3</v>
       </c>
       <c r="AX232" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY232" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ232" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA232" t="n">
         <v>0</v>
@@ -51275,31 +51275,31 @@
         <v>2.08</v>
       </c>
       <c r="AR233" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AS233" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="AT233" t="n">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="AU233" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV233" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW233" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AX233" t="n">
         <v>4</v>
       </c>
       <c r="AY233" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ233" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA233" t="n">
         <v>4</v>
@@ -51493,28 +51493,28 @@
         <v>0.45</v>
       </c>
       <c r="AR234" t="n">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="AS234" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AT234" t="n">
-        <v>2.69</v>
+        <v>2.44</v>
       </c>
       <c r="AU234" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV234" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW234" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AX234" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY234" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AZ234" t="n">
         <v>7</v>
@@ -51711,28 +51711,28 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AR235" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AS235" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AT235" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AU235" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV235" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW235" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AX235" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY235" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AZ235" t="n">
         <v>16</v>
@@ -51929,28 +51929,28 @@
         <v>1.77</v>
       </c>
       <c r="AR236" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="AS236" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AT236" t="n">
-        <v>3.08</v>
+        <v>2.82</v>
       </c>
       <c r="AU236" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV236" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW236" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AX236" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY236" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ236" t="n">
         <v>19</v>
@@ -52147,28 +52147,28 @@
         <v>1.33</v>
       </c>
       <c r="AR237" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AS237" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AT237" t="n">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="AU237" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV237" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW237" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX237" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY237" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AZ237" t="n">
         <v>14</v>
@@ -52365,25 +52365,25 @@
         <v>1.92</v>
       </c>
       <c r="AR238" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AS238" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AT238" t="n">
-        <v>3.11</v>
+        <v>2.85</v>
       </c>
       <c r="AU238" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV238" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW238" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX238" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY238" t="n">
         <v>5</v>
@@ -52583,31 +52583,31 @@
         <v>1.62</v>
       </c>
       <c r="AR239" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AS239" t="n">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="AT239" t="n">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="AU239" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV239" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW239" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX239" t="n">
         <v>5</v>
-      </c>
-      <c r="AW239" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX239" t="n">
-        <v>2</v>
       </c>
       <c r="AY239" t="n">
         <v>17</v>
       </c>
       <c r="AZ239" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA239" t="n">
         <v>7</v>
@@ -52801,31 +52801,31 @@
         <v>0.92</v>
       </c>
       <c r="AR240" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AS240" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AT240" t="n">
-        <v>2.76</v>
+        <v>2.52</v>
       </c>
       <c r="AU240" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV240" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW240" t="n">
         <v>6</v>
       </c>
-      <c r="AV240" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW240" t="n">
-        <v>3</v>
-      </c>
       <c r="AX240" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AY240" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AZ240" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="BA240" t="n">
         <v>5</v>
@@ -53019,31 +53019,31 @@
         <v>1.27</v>
       </c>
       <c r="AR241" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AS241" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AT241" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="AU241" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV241" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW241" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AX241" t="n">
         <v>6</v>
       </c>
       <c r="AY241" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AZ241" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA241" t="n">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP241"/>
+  <dimension ref="A1:BP244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1350,7 +1350,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ5" t="n">
         <v>0.92</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ8" t="n">
         <v>0.6899999999999999</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ11" t="n">
         <v>0.92</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ14" t="n">
         <v>1.09</v>
@@ -3966,7 +3966,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -4402,7 +4402,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR18" t="n">
         <v>1.94</v>
@@ -5056,7 +5056,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR21" t="n">
         <v>0</v>
@@ -6146,7 +6146,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR26" t="n">
         <v>1.86</v>
@@ -7887,7 +7887,7 @@
         <v>0.5</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ34" t="n">
         <v>1.62</v>
@@ -8108,7 +8108,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR35" t="n">
         <v>1.34</v>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ36" t="n">
         <v>1</v>
@@ -10503,7 +10503,7 @@
         <v>3</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ46" t="n">
         <v>2.08</v>
@@ -11160,7 +11160,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR49" t="n">
         <v>1.45</v>
@@ -11375,7 +11375,7 @@
         <v>1.33</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ50" t="n">
         <v>1.08</v>
@@ -11811,7 +11811,7 @@
         <v>0.33</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ52" t="n">
         <v>0.6899999999999999</v>
@@ -13122,7 +13122,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR58" t="n">
         <v>1.78</v>
@@ -13558,7 +13558,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR60" t="n">
         <v>1.82</v>
@@ -13776,7 +13776,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ61" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR61" t="n">
         <v>1.58</v>
@@ -16610,7 +16610,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ74" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR74" t="n">
         <v>0.96</v>
@@ -16828,7 +16828,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR75" t="n">
         <v>1.32</v>
@@ -17043,7 +17043,7 @@
         <v>1.25</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ76" t="n">
         <v>0.92</v>
@@ -17261,7 +17261,7 @@
         <v>1</v>
       </c>
       <c r="AP77" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ77" t="n">
         <v>0.92</v>
@@ -17479,7 +17479,7 @@
         <v>1.33</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ78" t="n">
         <v>1.92</v>
@@ -18354,7 +18354,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ82" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR82" t="n">
         <v>1.4</v>
@@ -18787,7 +18787,7 @@
         <v>1</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ84" t="n">
         <v>0.92</v>
@@ -20095,10 +20095,10 @@
         <v>0</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ90" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR90" t="n">
         <v>1.77</v>
@@ -21188,7 +21188,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ95" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR95" t="n">
         <v>1.36</v>
@@ -21403,7 +21403,7 @@
         <v>1.75</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ96" t="n">
         <v>1.92</v>
@@ -22060,7 +22060,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ99" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR99" t="n">
         <v>1.11</v>
@@ -23365,7 +23365,7 @@
         <v>0.8</v>
       </c>
       <c r="AP105" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ105" t="n">
         <v>1</v>
@@ -23804,7 +23804,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR107" t="n">
         <v>1.27</v>
@@ -24891,7 +24891,7 @@
         <v>1.2</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ112" t="n">
         <v>1</v>
@@ -25112,7 +25112,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ113" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR113" t="n">
         <v>1.32</v>
@@ -25327,7 +25327,7 @@
         <v>0.8</v>
       </c>
       <c r="AP114" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ114" t="n">
         <v>1.08</v>
@@ -27507,7 +27507,7 @@
         <v>1.2</v>
       </c>
       <c r="AP124" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ124" t="n">
         <v>1.36</v>
@@ -28382,7 +28382,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR128" t="n">
         <v>1.44</v>
@@ -28818,7 +28818,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR130" t="n">
         <v>1.47</v>
@@ -31649,7 +31649,7 @@
         <v>0.4</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ143" t="n">
         <v>0.45</v>
@@ -32303,10 +32303,10 @@
         <v>1.43</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR146" t="n">
         <v>1.13</v>
@@ -33614,7 +33614,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ152" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR152" t="n">
         <v>1.4</v>
@@ -34050,7 +34050,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ154" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR154" t="n">
         <v>1.78</v>
@@ -34265,7 +34265,7 @@
         <v>1</v>
       </c>
       <c r="AP155" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ155" t="n">
         <v>0.92</v>
@@ -34701,7 +34701,7 @@
         <v>0.33</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ157" t="n">
         <v>0.45</v>
@@ -36663,7 +36663,7 @@
         <v>1.25</v>
       </c>
       <c r="AP166" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ166" t="n">
         <v>1.08</v>
@@ -37099,10 +37099,10 @@
         <v>1</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ168" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR168" t="n">
         <v>1.55</v>
@@ -37538,7 +37538,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ170" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR170" t="n">
         <v>1.74</v>
@@ -37756,7 +37756,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ171" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR171" t="n">
         <v>1.19</v>
@@ -38407,7 +38407,7 @@
         <v>2</v>
       </c>
       <c r="AP174" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ174" t="n">
         <v>1.92</v>
@@ -39061,7 +39061,7 @@
         <v>1.9</v>
       </c>
       <c r="AP177" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ177" t="n">
         <v>1.62</v>
@@ -39497,7 +39497,7 @@
         <v>0.89</v>
       </c>
       <c r="AP179" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ179" t="n">
         <v>1</v>
@@ -40154,7 +40154,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ182" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR182" t="n">
         <v>1.29</v>
@@ -42549,7 +42549,7 @@
         <v>1.44</v>
       </c>
       <c r="AP193" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ193" t="n">
         <v>1.33</v>
@@ -42988,7 +42988,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ195" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR195" t="n">
         <v>1.34</v>
@@ -43424,7 +43424,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ197" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR197" t="n">
         <v>1.49</v>
@@ -43639,7 +43639,7 @@
         <v>1.9</v>
       </c>
       <c r="AP198" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ198" t="n">
         <v>1.92</v>
@@ -45383,7 +45383,7 @@
         <v>1.78</v>
       </c>
       <c r="AP206" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ206" t="n">
         <v>1.92</v>
@@ -45601,7 +45601,7 @@
         <v>1.56</v>
       </c>
       <c r="AP207" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ207" t="n">
         <v>1.77</v>
@@ -46037,7 +46037,7 @@
         <v>0.8</v>
       </c>
       <c r="AP209" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ209" t="n">
         <v>0.67</v>
@@ -47130,7 +47130,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ214" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR214" t="n">
         <v>1.29</v>
@@ -47999,7 +47999,7 @@
         <v>1.6</v>
       </c>
       <c r="AP218" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ218" t="n">
         <v>1.33</v>
@@ -49307,7 +49307,7 @@
         <v>1.5</v>
       </c>
       <c r="AP224" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AQ224" t="n">
         <v>1.36</v>
@@ -49525,10 +49525,10 @@
         <v>0.5</v>
       </c>
       <c r="AP225" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ225" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR225" t="n">
         <v>1.15</v>
@@ -50618,7 +50618,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ230" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AR230" t="n">
         <v>1.3</v>
@@ -51269,7 +51269,7 @@
         <v>2</v>
       </c>
       <c r="AP233" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ233" t="n">
         <v>2.08</v>
@@ -53016,7 +53016,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ241" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR241" t="n">
         <v>1.35</v>
@@ -53092,6 +53092,660 @@
       </c>
       <c r="BP241" t="n">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="n">
+        <v>241</v>
+      </c>
+      <c r="B242" t="n">
+        <v>7778318</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="n">
+        <v>45878.25</v>
+      </c>
+      <c r="F242" t="n">
+        <v>25</v>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Yokohama</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Urawa Reds</t>
+        </is>
+      </c>
+      <c r="I242" t="n">
+        <v>0</v>
+      </c>
+      <c r="J242" t="n">
+        <v>1</v>
+      </c>
+      <c r="K242" t="n">
+        <v>1</v>
+      </c>
+      <c r="L242" t="n">
+        <v>1</v>
+      </c>
+      <c r="M242" t="n">
+        <v>2</v>
+      </c>
+      <c r="N242" t="n">
+        <v>3</v>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>['90+9']</t>
+        </is>
+      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>['8', '53']</t>
+        </is>
+      </c>
+      <c r="Q242" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R242" t="n">
+        <v>2</v>
+      </c>
+      <c r="S242" t="n">
+        <v>3</v>
+      </c>
+      <c r="T242" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U242" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V242" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="W242" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X242" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y242" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z242" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA242" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AB242" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AC242" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD242" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE242" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF242" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG242" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH242" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI242" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ242" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK242" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL242" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM242" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN242" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AO242" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AP242" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ242" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR242" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AS242" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AT242" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AU242" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV242" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW242" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX242" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY242" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ242" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA242" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB242" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC242" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD242" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BE242" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF242" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BG242" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH242" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI242" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ242" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BK242" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BL242" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BM242" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BN242" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BO242" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BP242" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="n">
+        <v>242</v>
+      </c>
+      <c r="B243" t="n">
+        <v>7778315</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="n">
+        <v>45878.25</v>
+      </c>
+      <c r="F243" t="n">
+        <v>25</v>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Tokyo Verdy</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>Yokohama F. Marinos</t>
+        </is>
+      </c>
+      <c r="I243" t="n">
+        <v>0</v>
+      </c>
+      <c r="J243" t="n">
+        <v>0</v>
+      </c>
+      <c r="K243" t="n">
+        <v>0</v>
+      </c>
+      <c r="L243" t="n">
+        <v>1</v>
+      </c>
+      <c r="M243" t="n">
+        <v>0</v>
+      </c>
+      <c r="N243" t="n">
+        <v>1</v>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>['62']</t>
+        </is>
+      </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q243" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R243" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S243" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T243" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U243" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V243" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="W243" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X243" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y243" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z243" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AA243" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AB243" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AC243" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD243" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE243" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF243" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG243" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AH243" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI243" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ243" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK243" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AL243" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM243" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN243" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO243" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AP243" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ243" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AR243" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AS243" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AT243" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AU243" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV243" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW243" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX243" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY243" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ243" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA243" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB243" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC243" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD243" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BE243" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF243" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BG243" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH243" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI243" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ243" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BK243" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BL243" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BM243" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BN243" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BO243" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BP243" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="n">
+        <v>243</v>
+      </c>
+      <c r="B244" t="n">
+        <v>7778317</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="n">
+        <v>45878.29166666666</v>
+      </c>
+      <c r="F244" t="n">
+        <v>25</v>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Kawasaki Frontale</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Avispa Fukuoka</t>
+        </is>
+      </c>
+      <c r="I244" t="n">
+        <v>2</v>
+      </c>
+      <c r="J244" t="n">
+        <v>2</v>
+      </c>
+      <c r="K244" t="n">
+        <v>4</v>
+      </c>
+      <c r="L244" t="n">
+        <v>2</v>
+      </c>
+      <c r="M244" t="n">
+        <v>5</v>
+      </c>
+      <c r="N244" t="n">
+        <v>7</v>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>['4', '28']</t>
+        </is>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>['24', '35', '73', '85', '88']</t>
+        </is>
+      </c>
+      <c r="Q244" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R244" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S244" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T244" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U244" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V244" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W244" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X244" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y244" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z244" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AA244" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AB244" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AC244" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD244" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE244" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF244" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG244" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AH244" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI244" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ244" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK244" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL244" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM244" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN244" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO244" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AP244" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AQ244" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR244" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS244" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AT244" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AU244" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV244" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW244" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX244" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY244" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ244" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA244" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB244" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC244" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD244" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BE244" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF244" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BG244" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH244" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI244" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ244" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BK244" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BL244" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM244" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BN244" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BO244" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BP244" t="n">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP244"/>
+  <dimension ref="A1:BP250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ2" t="n">
         <v>1.08</v>
@@ -1786,7 +1786,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ10" t="n">
         <v>1.77</v>
@@ -3091,10 +3091,10 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ13" t="n">
         <v>1.33</v>
@@ -3530,7 +3530,7 @@
         <v>1</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR14" t="n">
         <v>1.63</v>
@@ -4184,7 +4184,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.42</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ19" t="n">
         <v>2.08</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ21" t="n">
         <v>0.67</v>
@@ -5710,7 +5710,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR24" t="n">
         <v>0.65</v>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ28" t="n">
         <v>1</v>
@@ -6797,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ29" t="n">
         <v>0.6899999999999999</v>
@@ -7015,7 +7015,7 @@
         <v>3</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ30" t="n">
         <v>1.08</v>
@@ -7454,7 +7454,7 @@
         <v>1</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR32" t="n">
         <v>0.99</v>
@@ -7890,7 +7890,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR34" t="n">
         <v>1.86</v>
@@ -8759,7 +8759,7 @@
         <v>3</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ38" t="n">
         <v>2.08</v>
@@ -9195,7 +9195,7 @@
         <v>1</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ40" t="n">
         <v>0.45</v>
@@ -9634,7 +9634,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR42" t="n">
         <v>1.91</v>
@@ -10067,7 +10067,7 @@
         <v>2</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ44" t="n">
         <v>0.92</v>
@@ -10285,10 +10285,10 @@
         <v>2</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR45" t="n">
         <v>1.24</v>
@@ -10939,10 +10939,10 @@
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR48" t="n">
         <v>1.32</v>
@@ -11593,7 +11593,7 @@
         <v>0.33</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ51" t="n">
         <v>0.67</v>
@@ -12250,7 +12250,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR54" t="n">
         <v>1.31</v>
@@ -12901,7 +12901,7 @@
         <v>3</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ57" t="n">
         <v>1.92</v>
@@ -13340,7 +13340,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR59" t="n">
         <v>1.8</v>
@@ -13994,7 +13994,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ62" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR62" t="n">
         <v>1.28</v>
@@ -14209,7 +14209,7 @@
         <v>1.33</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ63" t="n">
         <v>1</v>
@@ -14645,7 +14645,7 @@
         <v>0.5</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ65" t="n">
         <v>0.45</v>
@@ -15084,7 +15084,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR67" t="n">
         <v>1.59</v>
@@ -15517,7 +15517,7 @@
         <v>1.67</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ69" t="n">
         <v>1.33</v>
@@ -15735,10 +15735,10 @@
         <v>1.5</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR70" t="n">
         <v>1.34</v>
@@ -15956,7 +15956,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR71" t="n">
         <v>1.7</v>
@@ -16171,7 +16171,7 @@
         <v>2.5</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ72" t="n">
         <v>2.08</v>
@@ -16607,7 +16607,7 @@
         <v>0</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ74" t="n">
         <v>0.67</v>
@@ -17046,7 +17046,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ76" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR76" t="n">
         <v>1.76</v>
@@ -17482,7 +17482,7 @@
         <v>1</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR78" t="n">
         <v>1.15</v>
@@ -18569,7 +18569,7 @@
         <v>2</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ83" t="n">
         <v>1.33</v>
@@ -19226,7 +19226,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR86" t="n">
         <v>1.52</v>
@@ -19441,7 +19441,7 @@
         <v>1</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ87" t="n">
         <v>1</v>
@@ -19877,7 +19877,7 @@
         <v>1</v>
       </c>
       <c r="AP89" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ89" t="n">
         <v>1.08</v>
@@ -20313,7 +20313,7 @@
         <v>2</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ91" t="n">
         <v>1.92</v>
@@ -20531,10 +20531,10 @@
         <v>0</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR92" t="n">
         <v>1.33</v>
@@ -20967,7 +20967,7 @@
         <v>0.2</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ94" t="n">
         <v>0.6899999999999999</v>
@@ -21406,7 +21406,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR96" t="n">
         <v>1.34</v>
@@ -21624,7 +21624,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR97" t="n">
         <v>1.78</v>
@@ -21842,7 +21842,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ98" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR98" t="n">
         <v>1.26</v>
@@ -22057,7 +22057,7 @@
         <v>0.67</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ99" t="n">
         <v>1</v>
@@ -22932,7 +22932,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ103" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR103" t="n">
         <v>1.33</v>
@@ -23150,7 +23150,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR104" t="n">
         <v>1.4</v>
@@ -23586,7 +23586,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ106" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR106" t="n">
         <v>1.41</v>
@@ -24019,7 +24019,7 @@
         <v>1.33</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ108" t="n">
         <v>1.77</v>
@@ -25545,10 +25545,10 @@
         <v>0.83</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ115" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR115" t="n">
         <v>1.17</v>
@@ -25984,7 +25984,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR117" t="n">
         <v>1.46</v>
@@ -26635,7 +26635,7 @@
         <v>0.83</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ120" t="n">
         <v>1</v>
@@ -26853,7 +26853,7 @@
         <v>0.8</v>
       </c>
       <c r="AP121" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ121" t="n">
         <v>0.67</v>
@@ -27071,7 +27071,7 @@
         <v>1.17</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ122" t="n">
         <v>0.92</v>
@@ -27289,7 +27289,7 @@
         <v>0.83</v>
       </c>
       <c r="AP123" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ123" t="n">
         <v>0.67</v>
@@ -27510,7 +27510,7 @@
         <v>1</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR124" t="n">
         <v>1.14</v>
@@ -27943,7 +27943,7 @@
         <v>2</v>
       </c>
       <c r="AP126" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ126" t="n">
         <v>1.92</v>
@@ -28161,10 +28161,10 @@
         <v>1.86</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ127" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR127" t="n">
         <v>1.52</v>
@@ -28815,7 +28815,7 @@
         <v>1.67</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ130" t="n">
         <v>1.42</v>
@@ -29472,7 +29472,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ133" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR133" t="n">
         <v>1.49</v>
@@ -29687,10 +29687,10 @@
         <v>1.14</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ134" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR134" t="n">
         <v>1.47</v>
@@ -30780,7 +30780,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR139" t="n">
         <v>1.5</v>
@@ -31213,10 +31213,10 @@
         <v>0.67</v>
       </c>
       <c r="AP141" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ141" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR141" t="n">
         <v>1.22</v>
@@ -31431,7 +31431,7 @@
         <v>1.43</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ142" t="n">
         <v>0.92</v>
@@ -31867,10 +31867,10 @@
         <v>1.63</v>
       </c>
       <c r="AP144" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR144" t="n">
         <v>1.22</v>
@@ -32521,10 +32521,10 @@
         <v>2</v>
       </c>
       <c r="AP147" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ147" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR147" t="n">
         <v>1.3</v>
@@ -32739,10 +32739,10 @@
         <v>0.71</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR148" t="n">
         <v>1.29</v>
@@ -33829,7 +33829,7 @@
         <v>1.17</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ153" t="n">
         <v>1.77</v>
@@ -34268,7 +34268,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ155" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR155" t="n">
         <v>1.27</v>
@@ -34922,7 +34922,7 @@
         <v>1</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR158" t="n">
         <v>1.22</v>
@@ -35355,7 +35355,7 @@
         <v>2.25</v>
       </c>
       <c r="AP160" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ160" t="n">
         <v>1.92</v>
@@ -35573,7 +35573,7 @@
         <v>1.25</v>
       </c>
       <c r="AP161" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ161" t="n">
         <v>1</v>
@@ -37320,7 +37320,7 @@
         <v>1</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR169" t="n">
         <v>1.25</v>
@@ -37753,7 +37753,7 @@
         <v>1</v>
       </c>
       <c r="AP171" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ171" t="n">
         <v>1</v>
@@ -38192,7 +38192,7 @@
         <v>1</v>
       </c>
       <c r="AQ173" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR173" t="n">
         <v>1.3</v>
@@ -38628,7 +38628,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ175" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR175" t="n">
         <v>1.37</v>
@@ -38846,7 +38846,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ176" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR176" t="n">
         <v>1.2</v>
@@ -39064,7 +39064,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ177" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR177" t="n">
         <v>1.27</v>
@@ -39279,7 +39279,7 @@
         <v>1.43</v>
       </c>
       <c r="AP178" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ178" t="n">
         <v>1.77</v>
@@ -39933,7 +39933,7 @@
         <v>1</v>
       </c>
       <c r="AP181" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ181" t="n">
         <v>0.67</v>
@@ -40151,7 +40151,7 @@
         <v>0.14</v>
       </c>
       <c r="AP182" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ182" t="n">
         <v>0.67</v>
@@ -40587,10 +40587,10 @@
         <v>1.63</v>
       </c>
       <c r="AP184" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ184" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR184" t="n">
         <v>1.42</v>
@@ -40805,7 +40805,7 @@
         <v>1.25</v>
       </c>
       <c r="AP185" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ185" t="n">
         <v>1.33</v>
@@ -41023,10 +41023,10 @@
         <v>1.5</v>
       </c>
       <c r="AP186" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ186" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR186" t="n">
         <v>1.45</v>
@@ -41462,7 +41462,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ188" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR188" t="n">
         <v>1.32</v>
@@ -42767,7 +42767,7 @@
         <v>1.1</v>
       </c>
       <c r="AP194" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ194" t="n">
         <v>1.08</v>
@@ -44293,10 +44293,10 @@
         <v>1.67</v>
       </c>
       <c r="AP201" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ201" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR201" t="n">
         <v>1.29</v>
@@ -44732,7 +44732,7 @@
         <v>1</v>
       </c>
       <c r="AQ203" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR203" t="n">
         <v>1.26</v>
@@ -44947,7 +44947,7 @@
         <v>1</v>
       </c>
       <c r="AP204" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ204" t="n">
         <v>0.92</v>
@@ -45165,10 +45165,10 @@
         <v>1.73</v>
       </c>
       <c r="AP205" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ205" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR205" t="n">
         <v>1.42</v>
@@ -45386,7 +45386,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ206" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR206" t="n">
         <v>1.55</v>
@@ -45819,7 +45819,7 @@
         <v>0.89</v>
       </c>
       <c r="AP208" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ208" t="n">
         <v>0.92</v>
@@ -46476,7 +46476,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ211" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR211" t="n">
         <v>1.49</v>
@@ -46909,7 +46909,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP213" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ213" t="n">
         <v>0.45</v>
@@ -47348,7 +47348,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ215" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR215" t="n">
         <v>1.4</v>
@@ -47781,7 +47781,7 @@
         <v>0.55</v>
       </c>
       <c r="AP217" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ217" t="n">
         <v>0.6899999999999999</v>
@@ -48653,7 +48653,7 @@
         <v>1</v>
       </c>
       <c r="AP221" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AQ221" t="n">
         <v>0.92</v>
@@ -49089,7 +49089,7 @@
         <v>1</v>
       </c>
       <c r="AP223" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AQ223" t="n">
         <v>0.92</v>
@@ -49310,7 +49310,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ224" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AR224" t="n">
         <v>1.52</v>
@@ -49743,7 +49743,7 @@
         <v>1</v>
       </c>
       <c r="AP226" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ226" t="n">
         <v>1</v>
@@ -50400,7 +50400,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ229" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR229" t="n">
         <v>1.67</v>
@@ -50615,7 +50615,7 @@
         <v>0.9</v>
       </c>
       <c r="AP230" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AQ230" t="n">
         <v>1</v>
@@ -52141,7 +52141,7 @@
         <v>1.45</v>
       </c>
       <c r="AP237" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ237" t="n">
         <v>1.33</v>
@@ -52362,7 +52362,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ238" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AR238" t="n">
         <v>1.49</v>
@@ -52580,7 +52580,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ239" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR239" t="n">
         <v>1.4</v>
@@ -52798,7 +52798,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ240" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR240" t="n">
         <v>1.35</v>
@@ -53746,6 +53746,1314 @@
       </c>
       <c r="BP244" t="n">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" t="n">
+        <v>7778322</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="n">
+        <v>45879.27083333334</v>
+      </c>
+      <c r="F245" t="n">
+        <v>25</v>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Sanfrecce Hiroshima</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Shimizu S-Pulse</t>
+        </is>
+      </c>
+      <c r="I245" t="n">
+        <v>0</v>
+      </c>
+      <c r="J245" t="n">
+        <v>0</v>
+      </c>
+      <c r="K245" t="n">
+        <v>0</v>
+      </c>
+      <c r="L245" t="n">
+        <v>0</v>
+      </c>
+      <c r="M245" t="n">
+        <v>0</v>
+      </c>
+      <c r="N245" t="n">
+        <v>0</v>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q245" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R245" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S245" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T245" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U245" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V245" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W245" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X245" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y245" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z245" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA245" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AB245" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AC245" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD245" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE245" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF245" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG245" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH245" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI245" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ245" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK245" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AL245" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM245" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AN245" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO245" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP245" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ245" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AR245" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AS245" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AT245" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU245" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV245" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW245" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX245" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY245" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ245" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA245" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB245" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC245" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD245" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BE245" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF245" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BG245" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH245" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI245" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ245" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BK245" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BL245" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM245" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BN245" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BO245" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BP245" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="n">
+        <v>245</v>
+      </c>
+      <c r="B246" t="n">
+        <v>7778314</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="n">
+        <v>45879.29166666666</v>
+      </c>
+      <c r="F246" t="n">
+        <v>25</v>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Kashima Antlers</t>
+        </is>
+      </c>
+      <c r="I246" t="n">
+        <v>0</v>
+      </c>
+      <c r="J246" t="n">
+        <v>0</v>
+      </c>
+      <c r="K246" t="n">
+        <v>0</v>
+      </c>
+      <c r="L246" t="n">
+        <v>0</v>
+      </c>
+      <c r="M246" t="n">
+        <v>1</v>
+      </c>
+      <c r="N246" t="n">
+        <v>1</v>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>['81']</t>
+        </is>
+      </c>
+      <c r="Q246" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R246" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S246" t="n">
+        <v>3</v>
+      </c>
+      <c r="T246" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U246" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V246" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W246" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X246" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y246" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z246" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AA246" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AB246" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AC246" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD246" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE246" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF246" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG246" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH246" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AI246" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ246" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK246" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL246" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM246" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN246" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO246" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AP246" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ246" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR246" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AS246" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AT246" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU246" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV246" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW246" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX246" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY246" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ246" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA246" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB246" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC246" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD246" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BE246" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF246" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BG246" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH246" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BI246" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ246" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BK246" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BL246" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BM246" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BN246" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO246" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BP246" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" t="n">
+        <v>7778319</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="n">
+        <v>45879.29166666666</v>
+      </c>
+      <c r="F247" t="n">
+        <v>25</v>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Nagoya Grampus</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Kyoto Sanga</t>
+        </is>
+      </c>
+      <c r="I247" t="n">
+        <v>0</v>
+      </c>
+      <c r="J247" t="n">
+        <v>0</v>
+      </c>
+      <c r="K247" t="n">
+        <v>0</v>
+      </c>
+      <c r="L247" t="n">
+        <v>1</v>
+      </c>
+      <c r="M247" t="n">
+        <v>2</v>
+      </c>
+      <c r="N247" t="n">
+        <v>3</v>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>['61']</t>
+        </is>
+      </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>['70', '81']</t>
+        </is>
+      </c>
+      <c r="Q247" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R247" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S247" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T247" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U247" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V247" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W247" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X247" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y247" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z247" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA247" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AB247" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AC247" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD247" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE247" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF247" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG247" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH247" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI247" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ247" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK247" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AL247" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM247" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN247" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO247" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AP247" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AQ247" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AR247" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AS247" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AT247" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AU247" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV247" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW247" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX247" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY247" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ247" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA247" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB247" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC247" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD247" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BE247" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF247" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BG247" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH247" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI247" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ247" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BK247" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BL247" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BM247" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BN247" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BO247" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BP247" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="n">
+        <v>247</v>
+      </c>
+      <c r="B248" t="n">
+        <v>7778320</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="n">
+        <v>45879.29166666666</v>
+      </c>
+      <c r="F248" t="n">
+        <v>25</v>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Gamba Osaka</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>Fagiano Okayama</t>
+        </is>
+      </c>
+      <c r="I248" t="n">
+        <v>0</v>
+      </c>
+      <c r="J248" t="n">
+        <v>2</v>
+      </c>
+      <c r="K248" t="n">
+        <v>2</v>
+      </c>
+      <c r="L248" t="n">
+        <v>0</v>
+      </c>
+      <c r="M248" t="n">
+        <v>3</v>
+      </c>
+      <c r="N248" t="n">
+        <v>3</v>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>['10', '36', '89']</t>
+        </is>
+      </c>
+      <c r="Q248" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R248" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S248" t="n">
+        <v>4</v>
+      </c>
+      <c r="T248" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U248" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V248" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="W248" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X248" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y248" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z248" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AA248" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AB248" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AC248" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD248" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE248" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF248" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AG248" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH248" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI248" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ248" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK248" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL248" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM248" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN248" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO248" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AP248" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ248" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR248" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AS248" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AT248" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU248" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV248" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW248" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX248" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY248" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ248" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA248" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB248" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC248" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD248" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BE248" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF248" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BG248" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH248" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI248" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ248" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BK248" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BL248" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BM248" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN248" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BO248" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BP248" t="n">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="n">
+        <v>248</v>
+      </c>
+      <c r="B249" t="n">
+        <v>7778316</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="n">
+        <v>45879.29166666666</v>
+      </c>
+      <c r="F249" t="n">
+        <v>25</v>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Machida Zelvia</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Vissel Kobe</t>
+        </is>
+      </c>
+      <c r="I249" t="n">
+        <v>2</v>
+      </c>
+      <c r="J249" t="n">
+        <v>0</v>
+      </c>
+      <c r="K249" t="n">
+        <v>2</v>
+      </c>
+      <c r="L249" t="n">
+        <v>2</v>
+      </c>
+      <c r="M249" t="n">
+        <v>0</v>
+      </c>
+      <c r="N249" t="n">
+        <v>2</v>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>['6', '36']</t>
+        </is>
+      </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q249" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R249" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S249" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T249" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U249" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V249" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W249" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X249" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Y249" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z249" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AA249" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AB249" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AC249" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD249" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE249" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF249" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AG249" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH249" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI249" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ249" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK249" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AL249" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM249" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN249" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AO249" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AP249" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ249" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AR249" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AS249" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AT249" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AU249" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV249" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW249" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX249" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY249" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ249" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA249" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB249" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC249" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD249" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BE249" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF249" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BG249" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BH249" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BI249" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BJ249" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BK249" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BL249" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BM249" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BN249" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BO249" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP249" t="n">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="n">
+        <v>249</v>
+      </c>
+      <c r="B250" t="n">
+        <v>7778313</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="n">
+        <v>45879.29166666666</v>
+      </c>
+      <c r="F250" t="n">
+        <v>25</v>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Kashiwa Reysol</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Shonan Bellmare</t>
+        </is>
+      </c>
+      <c r="I250" t="n">
+        <v>1</v>
+      </c>
+      <c r="J250" t="n">
+        <v>0</v>
+      </c>
+      <c r="K250" t="n">
+        <v>1</v>
+      </c>
+      <c r="L250" t="n">
+        <v>2</v>
+      </c>
+      <c r="M250" t="n">
+        <v>0</v>
+      </c>
+      <c r="N250" t="n">
+        <v>2</v>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>['44', '90']</t>
+        </is>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q250" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R250" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S250" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="T250" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U250" t="n">
+        <v>3</v>
+      </c>
+      <c r="V250" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W250" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X250" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y250" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z250" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AA250" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB250" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AC250" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD250" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE250" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF250" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AG250" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH250" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI250" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ250" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK250" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AL250" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AM250" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AN250" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO250" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP250" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AQ250" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AR250" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS250" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AT250" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU250" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV250" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW250" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX250" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY250" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ250" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA250" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB250" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC250" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD250" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BE250" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF250" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BG250" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH250" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI250" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ250" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK250" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BL250" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BM250" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BN250" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BO250" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BP250" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP250"/>
+  <dimension ref="A1:BP251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2004,7 +2004,7 @@
         <v>1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -3748,7 +3748,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ17" t="n">
         <v>0.85</v>
@@ -6364,7 +6364,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR27" t="n">
         <v>1.94</v>
@@ -10721,7 +10721,7 @@
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ47" t="n">
         <v>0.6899999999999999</v>
@@ -11596,7 +11596,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR51" t="n">
         <v>0.89</v>
@@ -13555,7 +13555,7 @@
         <v>0.75</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ60" t="n">
         <v>1</v>
@@ -15953,7 +15953,7 @@
         <v>0</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ71" t="n">
         <v>1.25</v>
@@ -19008,7 +19008,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ85" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR85" t="n">
         <v>1.26</v>
@@ -21621,7 +21621,7 @@
         <v>1</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ97" t="n">
         <v>1.5</v>
@@ -24455,7 +24455,7 @@
         <v>0.8</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ110" t="n">
         <v>0.92</v>
@@ -26856,7 +26856,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ121" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR121" t="n">
         <v>1.28</v>
@@ -27292,7 +27292,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ123" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR123" t="n">
         <v>1.43</v>
@@ -28597,7 +28597,7 @@
         <v>2.17</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ129" t="n">
         <v>2.08</v>
@@ -34047,7 +34047,7 @@
         <v>0.17</v>
       </c>
       <c r="AP154" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ154" t="n">
         <v>0.67</v>
@@ -36884,7 +36884,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ167" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR167" t="n">
         <v>1.4</v>
@@ -37535,7 +37535,7 @@
         <v>1.25</v>
       </c>
       <c r="AP170" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ170" t="n">
         <v>1.42</v>
@@ -39936,7 +39936,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ181" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR181" t="n">
         <v>1.42</v>
@@ -41677,7 +41677,7 @@
         <v>1.11</v>
       </c>
       <c r="AP189" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ189" t="n">
         <v>0.92</v>
@@ -44078,7 +44078,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ200" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR200" t="n">
         <v>1.43</v>
@@ -44511,7 +44511,7 @@
         <v>1.1</v>
       </c>
       <c r="AP202" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ202" t="n">
         <v>1</v>
@@ -46040,7 +46040,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ209" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR209" t="n">
         <v>1.55</v>
@@ -49964,7 +49964,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ227" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR227" t="n">
         <v>1.49</v>
@@ -50179,7 +50179,7 @@
         <v>0.83</v>
       </c>
       <c r="AP228" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ228" t="n">
         <v>1</v>
@@ -55054,6 +55054,224 @@
       </c>
       <c r="BP250" t="n">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="n">
+        <v>250</v>
+      </c>
+      <c r="B251" t="n">
+        <v>7778321</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="n">
+        <v>45880.29166666666</v>
+      </c>
+      <c r="F251" t="n">
+        <v>25</v>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Cerezo Osaka</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Albirex Niigata</t>
+        </is>
+      </c>
+      <c r="I251" t="n">
+        <v>1</v>
+      </c>
+      <c r="J251" t="n">
+        <v>1</v>
+      </c>
+      <c r="K251" t="n">
+        <v>2</v>
+      </c>
+      <c r="L251" t="n">
+        <v>3</v>
+      </c>
+      <c r="M251" t="n">
+        <v>1</v>
+      </c>
+      <c r="N251" t="n">
+        <v>4</v>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>['13', '54', '81']</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>['2']</t>
+        </is>
+      </c>
+      <c r="Q251" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R251" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S251" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="T251" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U251" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V251" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W251" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X251" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y251" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z251" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AA251" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AB251" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC251" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD251" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE251" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF251" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG251" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AH251" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AI251" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AJ251" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AK251" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AL251" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM251" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AN251" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO251" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP251" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ251" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AR251" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS251" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AT251" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AU251" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV251" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW251" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX251" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY251" t="n">
+        <v>26</v>
+      </c>
+      <c r="AZ251" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA251" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB251" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC251" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD251" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BE251" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF251" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BG251" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH251" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI251" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ251" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BK251" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BL251" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BM251" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BN251" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BO251" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BP251" t="n">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP251"/>
+  <dimension ref="A1:BP253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3745,7 +3745,7 @@
         <v>1</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ15" t="n">
         <v>0.62</v>
@@ -4402,7 +4402,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR18" t="n">
         <v>1.94</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AQ20" t="n">
         <v>1</v>
@@ -5056,7 +5056,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR21" t="n">
         <v>0</v>
@@ -5925,7 +5925,7 @@
         <v>3</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ25" t="n">
         <v>1.77</v>
@@ -6361,7 +6361,7 @@
         <v>0.5</v>
       </c>
       <c r="AP27" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AQ27" t="n">
         <v>0.62</v>
@@ -7669,7 +7669,7 @@
         <v>3</v>
       </c>
       <c r="AP33" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AQ33" t="n">
         <v>0.92</v>
@@ -8108,7 +8108,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR35" t="n">
         <v>1.34</v>
@@ -11160,7 +11160,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR49" t="n">
         <v>1.45</v>
@@ -12247,7 +12247,7 @@
         <v>1.33</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ54" t="n">
         <v>1.71</v>
@@ -13119,7 +13119,7 @@
         <v>0.67</v>
       </c>
       <c r="AP58" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AQ58" t="n">
         <v>1</v>
@@ -13776,7 +13776,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ61" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR61" t="n">
         <v>1.58</v>
@@ -13991,7 +13991,7 @@
         <v>1.67</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ62" t="n">
         <v>0.85</v>
@@ -15081,7 +15081,7 @@
         <v>2</v>
       </c>
       <c r="AP67" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AQ67" t="n">
         <v>1.77</v>
@@ -16610,7 +16610,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ74" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR74" t="n">
         <v>0.96</v>
@@ -16828,7 +16828,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR75" t="n">
         <v>1.32</v>
@@ -19223,7 +19223,7 @@
         <v>1.75</v>
       </c>
       <c r="AP86" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AQ86" t="n">
         <v>1.71</v>
@@ -20098,7 +20098,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ90" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR90" t="n">
         <v>1.77</v>
@@ -20749,7 +20749,7 @@
         <v>1.8</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ93" t="n">
         <v>1.33</v>
@@ -21188,7 +21188,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ95" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR95" t="n">
         <v>1.36</v>
@@ -23801,10 +23801,10 @@
         <v>2.25</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR107" t="n">
         <v>1.27</v>
@@ -25112,7 +25112,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ113" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR113" t="n">
         <v>1.32</v>
@@ -26199,7 +26199,7 @@
         <v>0.17</v>
       </c>
       <c r="AP118" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AQ118" t="n">
         <v>0.6899999999999999</v>
@@ -28382,7 +28382,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR128" t="n">
         <v>1.44</v>
@@ -28818,7 +28818,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR130" t="n">
         <v>1.47</v>
@@ -29033,7 +29033,7 @@
         <v>0.14</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ131" t="n">
         <v>0.6899999999999999</v>
@@ -29905,7 +29905,7 @@
         <v>2.29</v>
       </c>
       <c r="AP135" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AQ135" t="n">
         <v>2.08</v>
@@ -32306,7 +32306,7 @@
         <v>1</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR146" t="n">
         <v>1.13</v>
@@ -32957,7 +32957,7 @@
         <v>2</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ149" t="n">
         <v>2.08</v>
@@ -33175,7 +33175,7 @@
         <v>1.43</v>
       </c>
       <c r="AP150" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AQ150" t="n">
         <v>1.33</v>
@@ -34050,7 +34050,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ154" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR154" t="n">
         <v>1.78</v>
@@ -36009,7 +36009,7 @@
         <v>1.25</v>
       </c>
       <c r="AP163" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AQ163" t="n">
         <v>0.92</v>
@@ -37538,7 +37538,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ170" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR170" t="n">
         <v>1.74</v>
@@ -38843,7 +38843,7 @@
         <v>1.86</v>
       </c>
       <c r="AP176" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ176" t="n">
         <v>1.77</v>
@@ -40154,7 +40154,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ182" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR182" t="n">
         <v>1.29</v>
@@ -42331,7 +42331,7 @@
         <v>1.63</v>
       </c>
       <c r="AP192" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AQ192" t="n">
         <v>1.77</v>
@@ -42988,7 +42988,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ195" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR195" t="n">
         <v>1.34</v>
@@ -43424,7 +43424,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ197" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR197" t="n">
         <v>1.49</v>
@@ -43857,7 +43857,7 @@
         <v>0.9</v>
       </c>
       <c r="AP199" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ199" t="n">
         <v>1</v>
@@ -46473,7 +46473,7 @@
         <v>0.9</v>
       </c>
       <c r="AP211" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AQ211" t="n">
         <v>1.25</v>
@@ -46691,7 +46691,7 @@
         <v>2</v>
       </c>
       <c r="AP212" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ212" t="n">
         <v>1.92</v>
@@ -47130,7 +47130,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ214" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR214" t="n">
         <v>1.29</v>
@@ -49528,7 +49528,7 @@
         <v>1</v>
       </c>
       <c r="AQ225" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR225" t="n">
         <v>1.15</v>
@@ -51051,7 +51051,7 @@
         <v>2.08</v>
       </c>
       <c r="AP232" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AQ232" t="n">
         <v>1.92</v>
@@ -51487,7 +51487,7 @@
         <v>0.5</v>
       </c>
       <c r="AP234" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ234" t="n">
         <v>0.45</v>
@@ -53016,7 +53016,7 @@
         <v>2.23</v>
       </c>
       <c r="AQ241" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR241" t="n">
         <v>1.35</v>
@@ -53452,7 +53452,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ243" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR243" t="n">
         <v>1.23</v>
@@ -53670,7 +53670,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ244" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR244" t="n">
         <v>1.56</v>
@@ -54554,13 +54554,13 @@
         <v>2.65</v>
       </c>
       <c r="AU248" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV248" t="n">
         <v>5</v>
       </c>
       <c r="AW248" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AX248" t="n">
         <v>6</v>
@@ -55272,6 +55272,442 @@
       </c>
       <c r="BP251" t="n">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="n">
+        <v>251</v>
+      </c>
+      <c r="B252" t="n">
+        <v>7778323</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="n">
+        <v>45885.25</v>
+      </c>
+      <c r="F252" t="n">
+        <v>26</v>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Kashima Antlers</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Avispa Fukuoka</t>
+        </is>
+      </c>
+      <c r="I252" t="n">
+        <v>0</v>
+      </c>
+      <c r="J252" t="n">
+        <v>0</v>
+      </c>
+      <c r="K252" t="n">
+        <v>0</v>
+      </c>
+      <c r="L252" t="n">
+        <v>1</v>
+      </c>
+      <c r="M252" t="n">
+        <v>1</v>
+      </c>
+      <c r="N252" t="n">
+        <v>2</v>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>['84']</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>['50']</t>
+        </is>
+      </c>
+      <c r="Q252" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R252" t="n">
+        <v>2</v>
+      </c>
+      <c r="S252" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T252" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U252" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V252" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W252" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X252" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y252" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z252" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA252" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AB252" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AC252" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD252" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE252" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF252" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG252" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH252" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AI252" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ252" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK252" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL252" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM252" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN252" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AO252" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AP252" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AQ252" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR252" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AS252" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AT252" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU252" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV252" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW252" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX252" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY252" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ252" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA252" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB252" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC252" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD252" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BE252" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF252" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BG252" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH252" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BI252" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ252" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BK252" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BL252" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BM252" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BN252" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BO252" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BP252" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="n">
+        <v>252</v>
+      </c>
+      <c r="B253" t="n">
+        <v>7778328</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="n">
+        <v>45885.27083333334</v>
+      </c>
+      <c r="F253" t="n">
+        <v>26</v>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Shimizu S-Pulse</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Yokohama F. Marinos</t>
+        </is>
+      </c>
+      <c r="I253" t="n">
+        <v>0</v>
+      </c>
+      <c r="J253" t="n">
+        <v>2</v>
+      </c>
+      <c r="K253" t="n">
+        <v>2</v>
+      </c>
+      <c r="L253" t="n">
+        <v>1</v>
+      </c>
+      <c r="M253" t="n">
+        <v>3</v>
+      </c>
+      <c r="N253" t="n">
+        <v>4</v>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>['90']</t>
+        </is>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>['16', '29', '80']</t>
+        </is>
+      </c>
+      <c r="Q253" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R253" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S253" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T253" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U253" t="n">
+        <v>3</v>
+      </c>
+      <c r="V253" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="W253" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X253" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y253" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z253" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA253" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB253" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AC253" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD253" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE253" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF253" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AG253" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AH253" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AI253" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AJ253" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AK253" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL253" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM253" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN253" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO253" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP253" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ253" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AR253" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AS253" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AT253" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AU253" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV253" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW253" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX253" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY253" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ253" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA253" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB253" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC253" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD253" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BE253" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF253" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BG253" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH253" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="BI253" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BJ253" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BK253" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BL253" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BM253" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BN253" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BO253" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BP253" t="n">
+        <v>1.54</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP253"/>
+  <dimension ref="A1:BP260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ4" t="n">
         <v>1</v>
@@ -2222,7 +2222,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ10" t="n">
         <v>1.77</v>
@@ -3312,7 +3312,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3963,7 +3963,7 @@
         <v>1</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ16" t="n">
         <v>1</v>
@@ -4838,7 +4838,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ21" t="n">
         <v>0.85</v>
@@ -5274,7 +5274,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR22" t="n">
         <v>0.78</v>
@@ -5492,7 +5492,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR23" t="n">
         <v>1.11</v>
@@ -5707,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ24" t="n">
         <v>1.71</v>
@@ -6579,10 +6579,10 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR28" t="n">
         <v>0.67</v>
@@ -6800,7 +6800,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR29" t="n">
         <v>1.03</v>
@@ -7018,7 +7018,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR30" t="n">
         <v>1.25</v>
@@ -7236,7 +7236,7 @@
         <v>1</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR31" t="n">
         <v>1.01</v>
@@ -8105,7 +8105,7 @@
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ35" t="n">
         <v>1.38</v>
@@ -8326,7 +8326,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR36" t="n">
         <v>0.95</v>
@@ -8544,7 +8544,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR37" t="n">
         <v>0</v>
@@ -9195,10 +9195,10 @@
         <v>1</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR40" t="n">
         <v>1.11</v>
@@ -9413,7 +9413,7 @@
         <v>3</v>
       </c>
       <c r="AP41" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ41" t="n">
         <v>1.92</v>
@@ -9631,7 +9631,7 @@
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ42" t="n">
         <v>1.25</v>
@@ -9852,7 +9852,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR43" t="n">
         <v>1.61</v>
@@ -10724,7 +10724,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR47" t="n">
         <v>1.5</v>
@@ -11157,7 +11157,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ49" t="n">
         <v>1.38</v>
@@ -11378,7 +11378,7 @@
         <v>1</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR50" t="n">
         <v>1.08</v>
@@ -11593,7 +11593,7 @@
         <v>0.33</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ51" t="n">
         <v>0.62</v>
@@ -11814,7 +11814,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR52" t="n">
         <v>1.14</v>
@@ -12468,7 +12468,7 @@
         <v>1</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR55" t="n">
         <v>1.11</v>
@@ -12686,7 +12686,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR56" t="n">
         <v>1.53</v>
@@ -12901,7 +12901,7 @@
         <v>3</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ57" t="n">
         <v>1.92</v>
@@ -14212,7 +14212,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR63" t="n">
         <v>1.33</v>
@@ -14430,7 +14430,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR64" t="n">
         <v>1.34</v>
@@ -14648,7 +14648,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR65" t="n">
         <v>0.95</v>
@@ -14863,7 +14863,7 @@
         <v>2</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ66" t="n">
         <v>1.77</v>
@@ -15520,7 +15520,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR69" t="n">
         <v>1.25</v>
@@ -15735,7 +15735,7 @@
         <v>1.5</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ70" t="n">
         <v>1.5</v>
@@ -16389,7 +16389,7 @@
         <v>2.33</v>
       </c>
       <c r="AP73" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ73" t="n">
         <v>1.92</v>
@@ -17697,7 +17697,7 @@
         <v>1.33</v>
       </c>
       <c r="AP79" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ79" t="n">
         <v>0.92</v>
@@ -17918,7 +17918,7 @@
         <v>1</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR80" t="n">
         <v>1.12</v>
@@ -18569,10 +18569,10 @@
         <v>2</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR83" t="n">
         <v>1.1</v>
@@ -19005,7 +19005,7 @@
         <v>0.25</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ85" t="n">
         <v>0.62</v>
@@ -19444,7 +19444,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ87" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR87" t="n">
         <v>1.21</v>
@@ -19662,7 +19662,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ88" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR88" t="n">
         <v>1.47</v>
@@ -19877,10 +19877,10 @@
         <v>1</v>
       </c>
       <c r="AP89" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ89" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR89" t="n">
         <v>1.35</v>
@@ -20531,7 +20531,7 @@
         <v>0</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ92" t="n">
         <v>1.25</v>
@@ -20752,7 +20752,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR93" t="n">
         <v>1.26</v>
@@ -20970,7 +20970,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ94" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR94" t="n">
         <v>1.41</v>
@@ -21839,7 +21839,7 @@
         <v>1</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ98" t="n">
         <v>0.85</v>
@@ -22057,7 +22057,7 @@
         <v>0.67</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ99" t="n">
         <v>1</v>
@@ -22278,7 +22278,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ100" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR100" t="n">
         <v>1.43</v>
@@ -22711,10 +22711,10 @@
         <v>1.67</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR102" t="n">
         <v>1.42</v>
@@ -22929,7 +22929,7 @@
         <v>2</v>
       </c>
       <c r="AP103" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ103" t="n">
         <v>1.71</v>
@@ -23368,7 +23368,7 @@
         <v>1</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR105" t="n">
         <v>1.08</v>
@@ -24237,7 +24237,7 @@
         <v>2.6</v>
       </c>
       <c r="AP109" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ109" t="n">
         <v>2.08</v>
@@ -24894,7 +24894,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ112" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR112" t="n">
         <v>1.65</v>
@@ -25109,7 +25109,7 @@
         <v>0.2</v>
       </c>
       <c r="AP113" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ113" t="n">
         <v>0.85</v>
@@ -25330,7 +25330,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR114" t="n">
         <v>1.33</v>
@@ -25545,7 +25545,7 @@
         <v>0.83</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ115" t="n">
         <v>0.85</v>
@@ -25763,10 +25763,10 @@
         <v>0.5</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ116" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR116" t="n">
         <v>1.41</v>
@@ -26202,7 +26202,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ118" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR118" t="n">
         <v>1.59</v>
@@ -26417,7 +26417,7 @@
         <v>1</v>
       </c>
       <c r="AP119" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ119" t="n">
         <v>1.77</v>
@@ -26638,7 +26638,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR120" t="n">
         <v>1.18</v>
@@ -27289,7 +27289,7 @@
         <v>0.83</v>
       </c>
       <c r="AP123" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ123" t="n">
         <v>0.62</v>
@@ -27728,7 +27728,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ125" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR125" t="n">
         <v>1.39</v>
@@ -28815,7 +28815,7 @@
         <v>1.67</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ130" t="n">
         <v>1.38</v>
@@ -29036,7 +29036,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ131" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR131" t="n">
         <v>1.21</v>
@@ -29469,7 +29469,7 @@
         <v>0.8</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ133" t="n">
         <v>1.25</v>
@@ -30123,10 +30123,10 @@
         <v>1.43</v>
       </c>
       <c r="AP136" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ136" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR136" t="n">
         <v>1.29</v>
@@ -30341,10 +30341,10 @@
         <v>0.67</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR137" t="n">
         <v>1.37</v>
@@ -30559,10 +30559,10 @@
         <v>1</v>
       </c>
       <c r="AP138" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ138" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR138" t="n">
         <v>1.59</v>
@@ -30995,10 +30995,10 @@
         <v>0.71</v>
       </c>
       <c r="AP140" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ140" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR140" t="n">
         <v>1.23</v>
@@ -31652,7 +31652,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ143" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR143" t="n">
         <v>1.35</v>
@@ -31867,7 +31867,7 @@
         <v>1.63</v>
       </c>
       <c r="AP144" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ144" t="n">
         <v>1.71</v>
@@ -33178,7 +33178,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR150" t="n">
         <v>1.51</v>
@@ -33393,10 +33393,10 @@
         <v>0.5</v>
       </c>
       <c r="AP151" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ151" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR151" t="n">
         <v>1.48</v>
@@ -34704,7 +34704,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ157" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR157" t="n">
         <v>1.51</v>
@@ -35137,10 +35137,10 @@
         <v>1</v>
       </c>
       <c r="AP159" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ159" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR159" t="n">
         <v>1.6</v>
@@ -35355,7 +35355,7 @@
         <v>2.25</v>
       </c>
       <c r="AP160" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ160" t="n">
         <v>1.92</v>
@@ -35573,10 +35573,10 @@
         <v>1.25</v>
       </c>
       <c r="AP161" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ161" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR161" t="n">
         <v>1.55</v>
@@ -35794,7 +35794,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ162" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR162" t="n">
         <v>1.48</v>
@@ -36230,7 +36230,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ164" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR164" t="n">
         <v>1.33</v>
@@ -36445,7 +36445,7 @@
         <v>1.14</v>
       </c>
       <c r="AP165" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ165" t="n">
         <v>0.92</v>
@@ -36666,7 +36666,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ166" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR166" t="n">
         <v>1.53</v>
@@ -39500,7 +39500,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ179" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR179" t="n">
         <v>1.59</v>
@@ -39715,10 +39715,10 @@
         <v>1.11</v>
       </c>
       <c r="AP180" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ180" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR180" t="n">
         <v>1.35</v>
@@ -40151,7 +40151,7 @@
         <v>0.14</v>
       </c>
       <c r="AP182" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ182" t="n">
         <v>0.85</v>
@@ -40372,7 +40372,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ183" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR183" t="n">
         <v>1.43</v>
@@ -40805,10 +40805,10 @@
         <v>1.25</v>
       </c>
       <c r="AP185" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ185" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR185" t="n">
         <v>1.56</v>
@@ -41241,7 +41241,7 @@
         <v>1</v>
       </c>
       <c r="AP187" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ187" t="n">
         <v>0.92</v>
@@ -41895,10 +41895,10 @@
         <v>0.63</v>
       </c>
       <c r="AP190" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ190" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR190" t="n">
         <v>1.35</v>
@@ -42552,7 +42552,7 @@
         <v>1</v>
       </c>
       <c r="AQ193" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR193" t="n">
         <v>1.17</v>
@@ -42770,7 +42770,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ194" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR194" t="n">
         <v>1.3</v>
@@ -43203,10 +43203,10 @@
         <v>0.6</v>
       </c>
       <c r="AP196" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ196" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR196" t="n">
         <v>1.67</v>
@@ -43860,7 +43860,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ199" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR199" t="n">
         <v>1.26</v>
@@ -44293,7 +44293,7 @@
         <v>1.67</v>
       </c>
       <c r="AP201" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ201" t="n">
         <v>1.5</v>
@@ -44514,7 +44514,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ202" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR202" t="n">
         <v>1.75</v>
@@ -46912,7 +46912,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ213" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR213" t="n">
         <v>1.3</v>
@@ -47563,10 +47563,10 @@
         <v>0.91</v>
       </c>
       <c r="AP216" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ216" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR216" t="n">
         <v>1.45</v>
@@ -47781,10 +47781,10 @@
         <v>0.55</v>
       </c>
       <c r="AP217" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ217" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR217" t="n">
         <v>1.56</v>
@@ -48002,7 +48002,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ218" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR218" t="n">
         <v>1.2</v>
@@ -48435,7 +48435,7 @@
         <v>1.7</v>
       </c>
       <c r="AP220" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ220" t="n">
         <v>1.77</v>
@@ -48653,7 +48653,7 @@
         <v>1</v>
       </c>
       <c r="AP221" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ221" t="n">
         <v>0.92</v>
@@ -49746,7 +49746,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ226" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR226" t="n">
         <v>1.35</v>
@@ -49961,7 +49961,7 @@
         <v>0.73</v>
       </c>
       <c r="AP227" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ227" t="n">
         <v>0.62</v>
@@ -50182,7 +50182,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ228" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR228" t="n">
         <v>1.75</v>
@@ -50397,7 +50397,7 @@
         <v>1.1</v>
       </c>
       <c r="AP229" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AQ229" t="n">
         <v>0.85</v>
@@ -50836,7 +50836,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ231" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AR231" t="n">
         <v>1.29</v>
@@ -51490,7 +51490,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ234" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR234" t="n">
         <v>1.34</v>
@@ -51708,7 +51708,7 @@
         <v>1</v>
       </c>
       <c r="AQ235" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AR235" t="n">
         <v>1.26</v>
@@ -52144,7 +52144,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ237" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR237" t="n">
         <v>1.45</v>
@@ -52795,7 +52795,7 @@
         <v>1</v>
       </c>
       <c r="AP240" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ240" t="n">
         <v>0.85</v>
@@ -53013,7 +53013,7 @@
         <v>1.3</v>
       </c>
       <c r="AP241" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ241" t="n">
         <v>1.38</v>
@@ -53885,7 +53885,7 @@
         <v>0.92</v>
       </c>
       <c r="AP245" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ245" t="n">
         <v>0.92</v>
@@ -54757,7 +54757,7 @@
         <v>1.92</v>
       </c>
       <c r="AP249" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ249" t="n">
         <v>1.77</v>
@@ -55708,6 +55708,1532 @@
       </c>
       <c r="BP253" t="n">
         <v>1.54</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="n">
+        <v>253</v>
+      </c>
+      <c r="B254" t="n">
+        <v>7778330</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="n">
+        <v>45885.29166666666</v>
+      </c>
+      <c r="F254" t="n">
+        <v>26</v>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Vissel Kobe</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>Yokohama</t>
+        </is>
+      </c>
+      <c r="I254" t="n">
+        <v>0</v>
+      </c>
+      <c r="J254" t="n">
+        <v>0</v>
+      </c>
+      <c r="K254" t="n">
+        <v>0</v>
+      </c>
+      <c r="L254" t="n">
+        <v>0</v>
+      </c>
+      <c r="M254" t="n">
+        <v>1</v>
+      </c>
+      <c r="N254" t="n">
+        <v>1</v>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>['90+4']</t>
+        </is>
+      </c>
+      <c r="Q254" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R254" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S254" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="T254" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U254" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V254" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W254" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X254" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y254" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z254" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AA254" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB254" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AC254" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD254" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE254" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF254" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG254" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AH254" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AI254" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ254" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK254" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AL254" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM254" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AN254" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO254" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AP254" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AQ254" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AR254" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS254" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AT254" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AU254" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV254" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW254" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX254" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY254" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ254" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA254" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB254" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC254" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD254" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BE254" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF254" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BG254" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH254" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BI254" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ254" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BK254" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BL254" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM254" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BN254" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BO254" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BP254" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="n">
+        <v>254</v>
+      </c>
+      <c r="B255" t="n">
+        <v>7778332</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="n">
+        <v>45885.29166666666</v>
+      </c>
+      <c r="F255" t="n">
+        <v>26</v>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Sanfrecce Hiroshima</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>Gamba Osaka</t>
+        </is>
+      </c>
+      <c r="I255" t="n">
+        <v>1</v>
+      </c>
+      <c r="J255" t="n">
+        <v>0</v>
+      </c>
+      <c r="K255" t="n">
+        <v>1</v>
+      </c>
+      <c r="L255" t="n">
+        <v>1</v>
+      </c>
+      <c r="M255" t="n">
+        <v>0</v>
+      </c>
+      <c r="N255" t="n">
+        <v>1</v>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>['19']</t>
+        </is>
+      </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q255" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R255" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S255" t="n">
+        <v>5</v>
+      </c>
+      <c r="T255" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U255" t="n">
+        <v>3</v>
+      </c>
+      <c r="V255" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W255" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X255" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y255" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z255" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA255" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="AB255" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AC255" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD255" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE255" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF255" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AG255" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AH255" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AI255" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ255" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK255" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AL255" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM255" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AN255" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO255" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP255" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AQ255" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AR255" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS255" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AT255" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AU255" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW255" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX255" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY255" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ255" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA255" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB255" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC255" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD255" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BE255" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF255" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BG255" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH255" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI255" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ255" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BK255" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BL255" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM255" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BN255" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BO255" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BP255" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="n">
+        <v>255</v>
+      </c>
+      <c r="B256" t="n">
+        <v>7778324</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="n">
+        <v>45885.29166666666</v>
+      </c>
+      <c r="F256" t="n">
+        <v>26</v>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Urawa Reds</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>Nagoya Grampus</t>
+        </is>
+      </c>
+      <c r="I256" t="n">
+        <v>2</v>
+      </c>
+      <c r="J256" t="n">
+        <v>0</v>
+      </c>
+      <c r="K256" t="n">
+        <v>2</v>
+      </c>
+      <c r="L256" t="n">
+        <v>2</v>
+      </c>
+      <c r="M256" t="n">
+        <v>1</v>
+      </c>
+      <c r="N256" t="n">
+        <v>3</v>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>['7', '32']</t>
+        </is>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>['66']</t>
+        </is>
+      </c>
+      <c r="Q256" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R256" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S256" t="n">
+        <v>4</v>
+      </c>
+      <c r="T256" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U256" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V256" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W256" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X256" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Y256" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z256" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AA256" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AB256" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AC256" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD256" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE256" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF256" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG256" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH256" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AI256" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ256" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AK256" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL256" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM256" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN256" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AO256" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AP256" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AQ256" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AR256" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AS256" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AT256" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AU256" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV256" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW256" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX256" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY256" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ256" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA256" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB256" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC256" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD256" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BE256" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF256" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BG256" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH256" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI256" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ256" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK256" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BL256" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BM256" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN256" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BO256" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BP256" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="n">
+        <v>256</v>
+      </c>
+      <c r="B257" t="n">
+        <v>7778325</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="n">
+        <v>45885.29166666666</v>
+      </c>
+      <c r="F257" t="n">
+        <v>26</v>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Machida Zelvia</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>Cerezo Osaka</t>
+        </is>
+      </c>
+      <c r="I257" t="n">
+        <v>2</v>
+      </c>
+      <c r="J257" t="n">
+        <v>0</v>
+      </c>
+      <c r="K257" t="n">
+        <v>2</v>
+      </c>
+      <c r="L257" t="n">
+        <v>3</v>
+      </c>
+      <c r="M257" t="n">
+        <v>0</v>
+      </c>
+      <c r="N257" t="n">
+        <v>3</v>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>['21', '42', '78']</t>
+        </is>
+      </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q257" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R257" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S257" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T257" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U257" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V257" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W257" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X257" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y257" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z257" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AA257" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB257" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="AC257" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD257" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE257" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF257" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AG257" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AH257" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AI257" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ257" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK257" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL257" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM257" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN257" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO257" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AP257" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ257" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR257" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AS257" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AT257" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU257" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV257" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW257" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX257" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY257" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ257" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA257" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB257" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC257" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD257" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BE257" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF257" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BG257" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH257" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI257" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ257" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BK257" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL257" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BM257" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BN257" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BO257" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BP257" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="n">
+        <v>257</v>
+      </c>
+      <c r="B258" t="n">
+        <v>7778326</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="n">
+        <v>45885.29166666666</v>
+      </c>
+      <c r="F258" t="n">
+        <v>26</v>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Shonan Bellmare</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="I258" t="n">
+        <v>0</v>
+      </c>
+      <c r="J258" t="n">
+        <v>1</v>
+      </c>
+      <c r="K258" t="n">
+        <v>1</v>
+      </c>
+      <c r="L258" t="n">
+        <v>2</v>
+      </c>
+      <c r="M258" t="n">
+        <v>2</v>
+      </c>
+      <c r="N258" t="n">
+        <v>4</v>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>['66', '90+7']</t>
+        </is>
+      </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>['6', '52']</t>
+        </is>
+      </c>
+      <c r="Q258" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R258" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S258" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T258" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U258" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V258" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W258" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X258" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y258" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z258" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AA258" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AB258" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AC258" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD258" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE258" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF258" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AG258" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AH258" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AI258" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ258" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK258" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL258" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM258" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN258" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AO258" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP258" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AQ258" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AR258" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AS258" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AT258" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AU258" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV258" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW258" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX258" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY258" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ258" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA258" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB258" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC258" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD258" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BE258" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF258" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BG258" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH258" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI258" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ258" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BK258" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BL258" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BM258" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BN258" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BO258" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BP258" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" t="n">
+        <v>7778327</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="n">
+        <v>45885.29166666666</v>
+      </c>
+      <c r="F259" t="n">
+        <v>26</v>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Albirex Niigata</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>Kawasaki Frontale</t>
+        </is>
+      </c>
+      <c r="I259" t="n">
+        <v>1</v>
+      </c>
+      <c r="J259" t="n">
+        <v>1</v>
+      </c>
+      <c r="K259" t="n">
+        <v>2</v>
+      </c>
+      <c r="L259" t="n">
+        <v>1</v>
+      </c>
+      <c r="M259" t="n">
+        <v>1</v>
+      </c>
+      <c r="N259" t="n">
+        <v>2</v>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>['6']</t>
+        </is>
+      </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>['45+1']</t>
+        </is>
+      </c>
+      <c r="Q259" t="n">
+        <v>4</v>
+      </c>
+      <c r="R259" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S259" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T259" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U259" t="n">
+        <v>3</v>
+      </c>
+      <c r="V259" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="W259" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X259" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y259" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z259" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA259" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB259" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC259" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD259" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE259" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF259" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG259" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AH259" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AI259" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ259" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK259" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL259" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM259" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN259" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AO259" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP259" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AQ259" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR259" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AS259" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AT259" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AU259" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV259" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW259" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX259" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY259" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ259" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA259" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB259" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC259" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD259" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BE259" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF259" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BG259" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH259" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI259" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ259" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK259" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BL259" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BM259" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN259" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BO259" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BP259" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="B260" t="n">
+        <v>7778329</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="n">
+        <v>45885.29166666666</v>
+      </c>
+      <c r="F260" t="n">
+        <v>26</v>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Kyoto Sanga</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>Tokyo Verdy</t>
+        </is>
+      </c>
+      <c r="I260" t="n">
+        <v>0</v>
+      </c>
+      <c r="J260" t="n">
+        <v>0</v>
+      </c>
+      <c r="K260" t="n">
+        <v>0</v>
+      </c>
+      <c r="L260" t="n">
+        <v>1</v>
+      </c>
+      <c r="M260" t="n">
+        <v>0</v>
+      </c>
+      <c r="N260" t="n">
+        <v>1</v>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>['66']</t>
+        </is>
+      </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q260" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R260" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S260" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T260" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U260" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V260" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W260" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X260" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y260" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z260" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA260" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AB260" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AC260" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD260" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE260" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF260" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AG260" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH260" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI260" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ260" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK260" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL260" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM260" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN260" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO260" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP260" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ260" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AR260" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AS260" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AT260" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AU260" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV260" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW260" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX260" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY260" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ260" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA260" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB260" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC260" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD260" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BE260" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF260" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BG260" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH260" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI260" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ260" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BK260" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL260" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BM260" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BN260" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BO260" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BP260" t="n">
+        <v>1.37</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
@@ -45607,13 +45607,13 @@
         <v>1.77</v>
       </c>
       <c r="AR207" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AS207" t="n">
         <v>1.46</v>
       </c>
       <c r="AT207" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AU207" t="n">
         <v>1</v>
@@ -46043,13 +46043,13 @@
         <v>0.62</v>
       </c>
       <c r="AR209" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AS209" t="n">
         <v>1</v>
       </c>
       <c r="AT209" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="AU209" t="n">
         <v>6</v>
@@ -46261,13 +46261,13 @@
         <v>0.92</v>
       </c>
       <c r="AR210" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AS210" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AT210" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="AU210" t="n">
         <v>2</v>
@@ -46915,13 +46915,13 @@
         <v>0.67</v>
       </c>
       <c r="AR213" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AS213" t="n">
         <v>1.1</v>
       </c>
       <c r="AT213" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="AU213" t="n">
         <v>7</v>
@@ -47136,10 +47136,10 @@
         <v>1.29</v>
       </c>
       <c r="AS214" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AT214" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="AU214" t="n">
         <v>3</v>
@@ -47354,10 +47354,10 @@
         <v>1.4</v>
       </c>
       <c r="AS215" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AT215" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="AU215" t="n">
         <v>1</v>
@@ -48008,10 +48008,10 @@
         <v>1.2</v>
       </c>
       <c r="AS218" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="AT218" t="n">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="AU218" t="n">
         <v>2</v>
@@ -48223,13 +48223,13 @@
         <v>2.08</v>
       </c>
       <c r="AR219" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AS219" t="n">
         <v>1.36</v>
       </c>
       <c r="AT219" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AU219" t="n">
         <v>1</v>
@@ -48441,13 +48441,13 @@
         <v>1.77</v>
       </c>
       <c r="AR220" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AS220" t="n">
         <v>1.44</v>
       </c>
       <c r="AT220" t="n">
-        <v>3.11</v>
+        <v>3.15</v>
       </c>
       <c r="AU220" t="n">
         <v>6</v>
@@ -48877,13 +48877,13 @@
         <v>1.77</v>
       </c>
       <c r="AR222" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="AS222" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AT222" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="AU222" t="n">
         <v>3</v>
@@ -49098,10 +49098,10 @@
         <v>1.48</v>
       </c>
       <c r="AS223" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AT223" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="AU223" t="n">
         <v>2</v>
@@ -49313,13 +49313,13 @@
         <v>1.5</v>
       </c>
       <c r="AR224" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AS224" t="n">
         <v>1.36</v>
       </c>
       <c r="AT224" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="AU224" t="n">
         <v>6</v>
@@ -49534,10 +49534,10 @@
         <v>1.15</v>
       </c>
       <c r="AS225" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AT225" t="n">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="AU225" t="n">
         <v>1</v>
@@ -49752,10 +49752,10 @@
         <v>1.35</v>
       </c>
       <c r="AS226" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="AT226" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="AU226" t="n">
         <v>1</v>
@@ -50185,13 +50185,13 @@
         <v>0.93</v>
       </c>
       <c r="AR228" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AS228" t="n">
         <v>1.44</v>
       </c>
       <c r="AT228" t="n">
-        <v>3.19</v>
+        <v>3.11</v>
       </c>
       <c r="AU228" t="n">
         <v>6</v>
@@ -50403,13 +50403,13 @@
         <v>0.85</v>
       </c>
       <c r="AR229" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AS229" t="n">
         <v>1.17</v>
       </c>
       <c r="AT229" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="AU229" t="n">
         <v>9</v>
@@ -50621,13 +50621,13 @@
         <v>1</v>
       </c>
       <c r="AR230" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AS230" t="n">
         <v>1.32</v>
       </c>
       <c r="AT230" t="n">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="AU230" t="n">
         <v>5</v>
@@ -50839,13 +50839,13 @@
         <v>1</v>
       </c>
       <c r="AR231" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AS231" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AT231" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="AU231" t="n">
         <v>6</v>
@@ -51057,13 +51057,13 @@
         <v>1.92</v>
       </c>
       <c r="AR232" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AS232" t="n">
         <v>1.33</v>
       </c>
       <c r="AT232" t="n">
-        <v>2.82</v>
+        <v>2.87</v>
       </c>
       <c r="AU232" t="n">
         <v>3</v>
@@ -51496,10 +51496,10 @@
         <v>1.34</v>
       </c>
       <c r="AS234" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AT234" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="AU234" t="n">
         <v>2</v>
@@ -51711,13 +51711,13 @@
         <v>0.64</v>
       </c>
       <c r="AR235" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AS235" t="n">
         <v>1.12</v>
       </c>
       <c r="AT235" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="AU235" t="n">
         <v>5</v>
@@ -51929,13 +51929,13 @@
         <v>1.77</v>
       </c>
       <c r="AR236" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AS236" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AT236" t="n">
-        <v>2.82</v>
+        <v>2.91</v>
       </c>
       <c r="AU236" t="n">
         <v>1</v>
@@ -52147,13 +52147,13 @@
         <v>1.31</v>
       </c>
       <c r="AR237" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AS237" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AT237" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="AU237" t="n">
         <v>4</v>
@@ -52365,13 +52365,13 @@
         <v>1.77</v>
       </c>
       <c r="AR238" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="AS238" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AT238" t="n">
-        <v>2.85</v>
+        <v>2.68</v>
       </c>
       <c r="AU238" t="n">
         <v>1</v>
@@ -52583,13 +52583,13 @@
         <v>1.71</v>
       </c>
       <c r="AR239" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AS239" t="n">
         <v>1.23</v>
       </c>
       <c r="AT239" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AU239" t="n">
         <v>7</v>
@@ -52804,10 +52804,10 @@
         <v>1.35</v>
       </c>
       <c r="AS240" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AT240" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="AU240" t="n">
         <v>5</v>
@@ -53019,13 +53019,13 @@
         <v>1.38</v>
       </c>
       <c r="AR241" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AS241" t="n">
         <v>1.5</v>
       </c>
       <c r="AT241" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="AU241" t="n">
         <v>4</v>
@@ -53237,13 +53237,13 @@
         <v>1</v>
       </c>
       <c r="AR242" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AS242" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AT242" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="AU242" t="n">
         <v>2</v>
@@ -53458,10 +53458,10 @@
         <v>1.23</v>
       </c>
       <c r="AS243" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AT243" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="AU243" t="n">
         <v>1</v>
@@ -53673,13 +53673,13 @@
         <v>1.38</v>
       </c>
       <c r="AR244" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AS244" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AT244" t="n">
-        <v>3.06</v>
+        <v>2.96</v>
       </c>
       <c r="AU244" t="n">
         <v>4</v>
@@ -54109,13 +54109,13 @@
         <v>1.5</v>
       </c>
       <c r="AR246" t="n">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="AS246" t="n">
         <v>1.33</v>
       </c>
       <c r="AT246" t="n">
-        <v>2.63</v>
+        <v>2.84</v>
       </c>
       <c r="AU246" t="n">
         <v>3</v>
@@ -54545,10 +54545,10 @@
         <v>1.25</v>
       </c>
       <c r="AR248" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AS248" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AT248" t="n">
         <v>2.65</v>
@@ -54766,10 +54766,10 @@
         <v>1.36</v>
       </c>
       <c r="AS249" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AT249" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="AU249" t="n">
         <v>5</v>
@@ -54981,13 +54981,13 @@
         <v>0.85</v>
       </c>
       <c r="AR250" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AS250" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AT250" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="AU250" t="n">
         <v>5</v>
@@ -55199,13 +55199,13 @@
         <v>0.62</v>
       </c>
       <c r="AR251" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AS251" t="n">
         <v>1.08</v>
       </c>
       <c r="AT251" t="n">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="AU251" t="n">
         <v>5</v>
@@ -55417,10 +55417,10 @@
         <v>1.38</v>
       </c>
       <c r="AR252" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AS252" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AT252" t="n">
         <v>3</v>
@@ -55638,10 +55638,10 @@
         <v>1.34</v>
       </c>
       <c r="AS253" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AT253" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="AU253" t="n">
         <v>6</v>
@@ -55853,13 +55853,13 @@
         <v>0.67</v>
       </c>
       <c r="AR254" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AS254" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AT254" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="AU254" t="n">
         <v>3</v>
@@ -56292,10 +56292,10 @@
         <v>1.35</v>
       </c>
       <c r="AS256" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AT256" t="n">
-        <v>2.47</v>
+        <v>2.51</v>
       </c>
       <c r="AU256" t="n">
         <v>5</v>
@@ -56510,10 +56510,10 @@
         <v>1.36</v>
       </c>
       <c r="AS257" t="n">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="AT257" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="AU257" t="n">
         <v>4</v>
@@ -56725,13 +56725,13 @@
         <v>0.92</v>
       </c>
       <c r="AR258" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AS258" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AT258" t="n">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="AU258" t="n">
         <v>5</v>
@@ -56943,13 +56943,13 @@
         <v>1.31</v>
       </c>
       <c r="AR259" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AS259" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AT259" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="AU259" t="n">
         <v>4</v>
@@ -57164,10 +57164,10 @@
         <v>1.49</v>
       </c>
       <c r="AS260" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="AT260" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="AU260" t="n">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP260"/>
+  <dimension ref="A1:BP261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,7 +1132,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ6" t="n">
         <v>1.71</v>
@@ -5489,7 +5489,7 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ23" t="n">
         <v>0.93</v>
@@ -8977,7 +8977,7 @@
         <v>3</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ39" t="n">
         <v>0.92</v>
@@ -9416,7 +9416,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AR41" t="n">
         <v>0</v>
@@ -12683,7 +12683,7 @@
         <v>2</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ56" t="n">
         <v>1.31</v>
@@ -12904,7 +12904,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AR57" t="n">
         <v>1.33</v>
@@ -13773,7 +13773,7 @@
         <v>0</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ61" t="n">
         <v>0.85</v>
@@ -16392,7 +16392,7 @@
         <v>2</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AR73" t="n">
         <v>1.07</v>
@@ -18133,7 +18133,7 @@
         <v>1</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ81" t="n">
         <v>0.92</v>
@@ -20316,7 +20316,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AR91" t="n">
         <v>1.19</v>
@@ -23583,7 +23583,7 @@
         <v>0.75</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ106" t="n">
         <v>1.5</v>
@@ -24676,7 +24676,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AR111" t="n">
         <v>1.39</v>
@@ -27725,7 +27725,7 @@
         <v>1.17</v>
       </c>
       <c r="AP125" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ125" t="n">
         <v>0.92</v>
@@ -27946,7 +27946,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AR126" t="n">
         <v>1.18</v>
@@ -34486,7 +34486,7 @@
         <v>1</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AR156" t="n">
         <v>1.22</v>
@@ -35358,7 +35358,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ160" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AR160" t="n">
         <v>1.29</v>
@@ -36881,7 +36881,7 @@
         <v>1.14</v>
       </c>
       <c r="AP167" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ167" t="n">
         <v>0.62</v>
@@ -37971,7 +37971,7 @@
         <v>1.89</v>
       </c>
       <c r="AP172" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ172" t="n">
         <v>2.08</v>
@@ -38410,7 +38410,7 @@
         <v>1</v>
       </c>
       <c r="AQ174" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AR174" t="n">
         <v>1.14</v>
@@ -43421,7 +43421,7 @@
         <v>1.11</v>
       </c>
       <c r="AP197" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ197" t="n">
         <v>1.38</v>
@@ -43642,7 +43642,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ198" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AR198" t="n">
         <v>1.26</v>
@@ -46694,7 +46694,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ212" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AR212" t="n">
         <v>1.33</v>
@@ -48871,7 +48871,7 @@
         <v>1.55</v>
       </c>
       <c r="AP222" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ222" t="n">
         <v>1.77</v>
@@ -51054,7 +51054,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ232" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AR232" t="n">
         <v>1.54</v>
@@ -52359,7 +52359,7 @@
         <v>1.82</v>
       </c>
       <c r="AP238" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AQ238" t="n">
         <v>1.77</v>
@@ -57234,6 +57234,224 @@
       </c>
       <c r="BP260" t="n">
         <v>1.37</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="n">
+        <v>260</v>
+      </c>
+      <c r="B261" t="n">
+        <v>7778331</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="n">
+        <v>45886.3125</v>
+      </c>
+      <c r="F261" t="n">
+        <v>26</v>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Fagiano Okayama</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Kashiwa Reysol</t>
+        </is>
+      </c>
+      <c r="I261" t="n">
+        <v>1</v>
+      </c>
+      <c r="J261" t="n">
+        <v>0</v>
+      </c>
+      <c r="K261" t="n">
+        <v>1</v>
+      </c>
+      <c r="L261" t="n">
+        <v>2</v>
+      </c>
+      <c r="M261" t="n">
+        <v>1</v>
+      </c>
+      <c r="N261" t="n">
+        <v>3</v>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>['4', '90']</t>
+        </is>
+      </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>['90+5']</t>
+        </is>
+      </c>
+      <c r="Q261" t="n">
+        <v>4</v>
+      </c>
+      <c r="R261" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S261" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T261" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U261" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V261" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="W261" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X261" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y261" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z261" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA261" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AB261" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC261" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD261" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE261" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF261" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG261" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH261" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI261" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ261" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK261" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL261" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM261" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN261" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO261" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AP261" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ261" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AR261" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AS261" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AT261" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AU261" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV261" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW261" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX261" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY261" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ261" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA261" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB261" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC261" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD261" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BE261" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF261" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BG261" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH261" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI261" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BJ261" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BK261" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BL261" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BM261" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BN261" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BO261" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BP261" t="n">
+        <v>1.62</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
@@ -56298,16 +56298,16 @@
         <v>2.51</v>
       </c>
       <c r="AU256" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV256" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW256" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX256" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY256" t="n">
         <v>13</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP261"/>
+  <dimension ref="A1:BP263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ10" t="n">
         <v>1.77</v>
@@ -3094,7 +3094,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ21" t="n">
         <v>0.85</v>
@@ -5492,7 +5492,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR23" t="n">
         <v>1.11</v>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ28" t="n">
         <v>0.92</v>
@@ -8326,7 +8326,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR36" t="n">
         <v>0.95</v>
@@ -9195,7 +9195,7 @@
         <v>1</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ40" t="n">
         <v>0.67</v>
@@ -11593,7 +11593,7 @@
         <v>0.33</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ51" t="n">
         <v>0.62</v>
@@ -12468,7 +12468,7 @@
         <v>1</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR55" t="n">
         <v>1.11</v>
@@ -12901,7 +12901,7 @@
         <v>3</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ57" t="n">
         <v>1.79</v>
@@ -13340,7 +13340,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR59" t="n">
         <v>1.8</v>
@@ -14430,7 +14430,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ64" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR64" t="n">
         <v>1.34</v>
@@ -15084,7 +15084,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR67" t="n">
         <v>1.59</v>
@@ -15735,7 +15735,7 @@
         <v>1.5</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ70" t="n">
         <v>1.5</v>
@@ -17482,7 +17482,7 @@
         <v>1</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR78" t="n">
         <v>1.15</v>
@@ -18569,7 +18569,7 @@
         <v>2</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ83" t="n">
         <v>1.31</v>
@@ -19444,7 +19444,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ87" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR87" t="n">
         <v>1.21</v>
@@ -19877,7 +19877,7 @@
         <v>1</v>
       </c>
       <c r="AP89" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ89" t="n">
         <v>1</v>
@@ -20531,7 +20531,7 @@
         <v>0</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ92" t="n">
         <v>1.25</v>
@@ -21406,7 +21406,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR96" t="n">
         <v>1.34</v>
@@ -22057,7 +22057,7 @@
         <v>0.67</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ99" t="n">
         <v>1</v>
@@ -23368,7 +23368,7 @@
         <v>1</v>
       </c>
       <c r="AQ105" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR105" t="n">
         <v>1.08</v>
@@ -25545,7 +25545,7 @@
         <v>0.83</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ115" t="n">
         <v>0.85</v>
@@ -26638,7 +26638,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ120" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR120" t="n">
         <v>1.18</v>
@@ -27289,7 +27289,7 @@
         <v>0.83</v>
       </c>
       <c r="AP123" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ123" t="n">
         <v>0.62</v>
@@ -28815,7 +28815,7 @@
         <v>1.67</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ130" t="n">
         <v>1.38</v>
@@ -30998,7 +30998,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ140" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR140" t="n">
         <v>1.23</v>
@@ -31867,7 +31867,7 @@
         <v>1.63</v>
       </c>
       <c r="AP144" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ144" t="n">
         <v>1.71</v>
@@ -32524,7 +32524,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ147" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR147" t="n">
         <v>1.3</v>
@@ -35140,7 +35140,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ159" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR159" t="n">
         <v>1.6</v>
@@ -35355,7 +35355,7 @@
         <v>2.25</v>
       </c>
       <c r="AP160" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ160" t="n">
         <v>1.79</v>
@@ -35573,7 +35573,7 @@
         <v>1.25</v>
       </c>
       <c r="AP161" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ161" t="n">
         <v>0.92</v>
@@ -37320,7 +37320,7 @@
         <v>1</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR169" t="n">
         <v>1.25</v>
@@ -38846,7 +38846,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ176" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR176" t="n">
         <v>1.2</v>
@@ -39500,7 +39500,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ179" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR179" t="n">
         <v>1.59</v>
@@ -40151,7 +40151,7 @@
         <v>0.14</v>
       </c>
       <c r="AP182" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ182" t="n">
         <v>0.85</v>
@@ -40590,7 +40590,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ184" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR184" t="n">
         <v>1.42</v>
@@ -40805,7 +40805,7 @@
         <v>1.25</v>
       </c>
       <c r="AP185" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ185" t="n">
         <v>1.31</v>
@@ -43860,7 +43860,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ199" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR199" t="n">
         <v>1.26</v>
@@ -44293,7 +44293,7 @@
         <v>1.67</v>
       </c>
       <c r="AP201" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ201" t="n">
         <v>1.5</v>
@@ -45386,7 +45386,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ206" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR206" t="n">
         <v>1.55</v>
@@ -47348,7 +47348,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ215" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR215" t="n">
         <v>1.4</v>
@@ -47566,7 +47566,7 @@
         <v>2</v>
       </c>
       <c r="AQ216" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR216" t="n">
         <v>1.45</v>
@@ -47781,7 +47781,7 @@
         <v>0.55</v>
       </c>
       <c r="AP217" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ217" t="n">
         <v>0.64</v>
@@ -48653,7 +48653,7 @@
         <v>1</v>
       </c>
       <c r="AP221" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ221" t="n">
         <v>0.92</v>
@@ -50182,7 +50182,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ228" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR228" t="n">
         <v>1.67</v>
@@ -52362,7 +52362,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ238" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR238" t="n">
         <v>1.37</v>
@@ -53885,7 +53885,7 @@
         <v>0.92</v>
       </c>
       <c r="AP245" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ245" t="n">
         <v>0.92</v>
@@ -54757,10 +54757,10 @@
         <v>1.92</v>
       </c>
       <c r="AP249" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ249" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR249" t="n">
         <v>1.36</v>
@@ -56065,10 +56065,10 @@
         <v>1</v>
       </c>
       <c r="AP255" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AQ255" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR255" t="n">
         <v>1.55</v>
@@ -56501,7 +56501,7 @@
         <v>1.08</v>
       </c>
       <c r="AP257" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ257" t="n">
         <v>1</v>
@@ -57452,6 +57452,442 @@
       </c>
       <c r="BP261" t="n">
         <v>1.62</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="n">
+        <v>261</v>
+      </c>
+      <c r="B262" t="n">
+        <v>7778371</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="n">
+        <v>45889.29166666666</v>
+      </c>
+      <c r="F262" t="n">
+        <v>30</v>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Sanfrecce Hiroshima</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>Vissel Kobe</t>
+        </is>
+      </c>
+      <c r="I262" t="n">
+        <v>0</v>
+      </c>
+      <c r="J262" t="n">
+        <v>0</v>
+      </c>
+      <c r="K262" t="n">
+        <v>0</v>
+      </c>
+      <c r="L262" t="n">
+        <v>0</v>
+      </c>
+      <c r="M262" t="n">
+        <v>1</v>
+      </c>
+      <c r="N262" t="n">
+        <v>1</v>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>['87']</t>
+        </is>
+      </c>
+      <c r="Q262" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="R262" t="n">
+        <v>2</v>
+      </c>
+      <c r="S262" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T262" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U262" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V262" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="W262" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X262" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="Y262" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z262" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AA262" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AB262" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AC262" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD262" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="AE262" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF262" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG262" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH262" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI262" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ262" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK262" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL262" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM262" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN262" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO262" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AP262" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AQ262" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AR262" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS262" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AT262" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AU262" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV262" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW262" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX262" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY262" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ262" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA262" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB262" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC262" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD262" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE262" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF262" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BG262" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH262" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI262" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ262" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BK262" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BL262" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BM262" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BN262" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BO262" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BP262" t="n">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="n">
+        <v>262</v>
+      </c>
+      <c r="B263" t="n">
+        <v>7778372</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="n">
+        <v>45889.29166666666</v>
+      </c>
+      <c r="F263" t="n">
+        <v>30</v>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Machida Zelvia</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>Gamba Osaka</t>
+        </is>
+      </c>
+      <c r="I263" t="n">
+        <v>1</v>
+      </c>
+      <c r="J263" t="n">
+        <v>0</v>
+      </c>
+      <c r="K263" t="n">
+        <v>1</v>
+      </c>
+      <c r="L263" t="n">
+        <v>3</v>
+      </c>
+      <c r="M263" t="n">
+        <v>1</v>
+      </c>
+      <c r="N263" t="n">
+        <v>4</v>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>['17', '78', '90']</t>
+        </is>
+      </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>['61']</t>
+        </is>
+      </c>
+      <c r="Q263" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R263" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S263" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T263" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U263" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V263" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W263" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X263" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="Y263" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z263" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AA263" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AB263" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AC263" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD263" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE263" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF263" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG263" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH263" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI263" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ263" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK263" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AL263" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AM263" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AN263" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AO263" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AP263" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AQ263" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AR263" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AS263" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AT263" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AU263" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV263" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW263" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX263" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY263" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ263" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA263" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB263" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC263" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD263" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BE263" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF263" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BG263" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BH263" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI263" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BJ263" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BK263" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BL263" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BM263" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BN263" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BO263" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP263" t="n">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
@@ -37117,19 +37117,19 @@
         <v>6</v>
       </c>
       <c r="AV168" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW168" t="n">
         <v>5</v>
       </c>
-      <c r="AW168" t="n">
-        <v>8</v>
-      </c>
       <c r="AX168" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY168" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ168" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA168" t="n">
         <v>4</v>
@@ -37332,22 +37332,22 @@
         <v>2.53</v>
       </c>
       <c r="AU169" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV169" t="n">
         <v>3</v>
       </c>
       <c r="AW169" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AX169" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY169" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ169" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA169" t="n">
         <v>5</v>
@@ -37553,19 +37553,19 @@
         <v>8</v>
       </c>
       <c r="AV170" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW170" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX170" t="n">
         <v>5</v>
       </c>
-      <c r="AW170" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX170" t="n">
-        <v>10</v>
-      </c>
       <c r="AY170" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ170" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BA170" t="n">
         <v>4</v>
@@ -37762,28 +37762,28 @@
         <v>1.19</v>
       </c>
       <c r="AS171" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AT171" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="AU171" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AV171" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW171" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX171" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY171" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ171" t="n">
         <v>3</v>
-      </c>
-      <c r="AW171" t="n">
-        <v>18</v>
-      </c>
-      <c r="AX171" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY171" t="n">
-        <v>29</v>
-      </c>
-      <c r="AZ171" t="n">
-        <v>4</v>
       </c>
       <c r="BA171" t="n">
         <v>7</v>
@@ -37795,43 +37795,43 @@
         <v>9</v>
       </c>
       <c r="BD171" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="BE171" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="BF171" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="BG171" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BH171" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="BI171" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BJ171" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BK171" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BL171" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BM171" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BN171" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BO171" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="BP171" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="172">
@@ -37992,16 +37992,16 @@
         <v>3</v>
       </c>
       <c r="AW172" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX172" t="n">
         <v>5</v>
       </c>
-      <c r="AX172" t="n">
-        <v>9</v>
-      </c>
       <c r="AY172" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ172" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BA172" t="n">
         <v>2</v>
@@ -38195,31 +38195,31 @@
         <v>1.5</v>
       </c>
       <c r="AR173" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AS173" t="n">
         <v>1.32</v>
       </c>
       <c r="AT173" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="AU173" t="n">
         <v>4</v>
       </c>
       <c r="AV173" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX173" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY173" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ173" t="n">
         <v>12</v>
-      </c>
-      <c r="AY173" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ173" t="n">
-        <v>17</v>
       </c>
       <c r="BA173" t="n">
         <v>4</v>
@@ -38231,43 +38231,43 @@
         <v>14</v>
       </c>
       <c r="BD173" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BE173" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF173" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BG173" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BH173" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BI173" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BJ173" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BK173" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BL173" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BM173" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BN173" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BO173" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BP173" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="174">
@@ -38425,19 +38425,19 @@
         <v>3</v>
       </c>
       <c r="AV174" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW174" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX174" t="n">
         <v>5</v>
       </c>
-      <c r="AW174" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX174" t="n">
-        <v>12</v>
-      </c>
       <c r="AY174" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ174" t="n">
         <v>13</v>
-      </c>
-      <c r="AZ174" t="n">
-        <v>17</v>
       </c>
       <c r="BA174" t="n">
         <v>6</v>
@@ -38646,16 +38646,16 @@
         <v>2</v>
       </c>
       <c r="AW175" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY175" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ175" t="n">
         <v>4</v>
-      </c>
-      <c r="AX175" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY175" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ175" t="n">
-        <v>10</v>
       </c>
       <c r="BA175" t="n">
         <v>3</v>
@@ -38852,28 +38852,28 @@
         <v>1.2</v>
       </c>
       <c r="AS176" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AT176" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="AU176" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV176" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW176" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AX176" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AY176" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ176" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BA176" t="n">
         <v>9</v>
@@ -38885,43 +38885,43 @@
         <v>13</v>
       </c>
       <c r="BD176" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BE176" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BF176" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BG176" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BH176" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BI176" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BJ176" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BK176" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BL176" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BM176" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BN176" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BO176" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BP176" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="177">
@@ -39082,16 +39082,16 @@
         <v>3</v>
       </c>
       <c r="AW177" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AX177" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY177" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ177" t="n">
         <v>6</v>
-      </c>
-      <c r="AY177" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ177" t="n">
-        <v>9</v>
       </c>
       <c r="BA177" t="n">
         <v>4</v>
@@ -39297,19 +39297,19 @@
         <v>1</v>
       </c>
       <c r="AV178" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW178" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX178" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY178" t="n">
         <v>6</v>
       </c>
-      <c r="AX178" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY178" t="n">
-        <v>7</v>
-      </c>
       <c r="AZ178" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="BA178" t="n">
         <v>2</v>
@@ -39503,31 +39503,31 @@
         <v>0.87</v>
       </c>
       <c r="AR179" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AS179" t="n">
         <v>1.44</v>
       </c>
       <c r="AT179" t="n">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="AU179" t="n">
         <v>2</v>
       </c>
       <c r="AV179" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW179" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX179" t="n">
         <v>4</v>
       </c>
-      <c r="AW179" t="n">
+      <c r="AY179" t="n">
         <v>10</v>
       </c>
-      <c r="AX179" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY179" t="n">
-        <v>12</v>
-      </c>
       <c r="AZ179" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="BA179" t="n">
         <v>3</v>
@@ -39539,43 +39539,43 @@
         <v>7</v>
       </c>
       <c r="BD179" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BE179" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF179" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BG179" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BH179" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BI179" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BJ179" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BK179" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BL179" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BM179" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BN179" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BO179" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BP179" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="180">
@@ -39939,13 +39939,13 @@
         <v>0.62</v>
       </c>
       <c r="AR181" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="AS181" t="n">
         <v>0.99</v>
       </c>
       <c r="AT181" t="n">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="AU181" t="n">
         <v>4</v>
@@ -40387,7 +40387,7 @@
         <v>3</v>
       </c>
       <c r="AV183" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AW183" t="n">
         <v>3</v>
@@ -40399,7 +40399,7 @@
         <v>6</v>
       </c>
       <c r="AZ183" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA183" t="n">
         <v>3</v>
@@ -40596,10 +40596,10 @@
         <v>1.42</v>
       </c>
       <c r="AS184" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AT184" t="n">
-        <v>2.78</v>
+        <v>2.73</v>
       </c>
       <c r="AU184" t="n">
         <v>2</v>
@@ -41032,10 +41032,10 @@
         <v>1.45</v>
       </c>
       <c r="AS186" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AT186" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="AU186" t="n">
         <v>1</v>
@@ -41683,13 +41683,13 @@
         <v>0.92</v>
       </c>
       <c r="AR189" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AS189" t="n">
         <v>1.42</v>
       </c>
       <c r="AT189" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="AU189" t="n">
         <v>9</v>
@@ -41901,13 +41901,13 @@
         <v>0.67</v>
       </c>
       <c r="AR190" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AS190" t="n">
         <v>1.1</v>
       </c>
       <c r="AT190" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="AU190" t="n">
         <v>3</v>
@@ -42119,13 +42119,13 @@
         <v>2.08</v>
       </c>
       <c r="AR191" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AS191" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AT191" t="n">
-        <v>2.64</v>
+        <v>2.59</v>
       </c>
       <c r="AU191" t="n">
         <v>3</v>
@@ -42340,10 +42340,10 @@
         <v>1.46</v>
       </c>
       <c r="AS192" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="AT192" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AU192" t="n">
         <v>4</v>
@@ -42555,13 +42555,13 @@
         <v>1.31</v>
       </c>
       <c r="AR193" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AS193" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AT193" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="AU193" t="n">
         <v>1</v>
@@ -42776,10 +42776,10 @@
         <v>1.3</v>
       </c>
       <c r="AS194" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="AT194" t="n">
-        <v>2.64</v>
+        <v>2.73</v>
       </c>
       <c r="AU194" t="n">
         <v>5</v>
@@ -42994,10 +42994,10 @@
         <v>1.34</v>
       </c>
       <c r="AS195" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AT195" t="n">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
       <c r="AU195" t="n">
         <v>6</v>
@@ -43427,13 +43427,13 @@
         <v>1.38</v>
       </c>
       <c r="AR197" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AS197" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AT197" t="n">
-        <v>2.99</v>
+        <v>2.93</v>
       </c>
       <c r="AU197" t="n">
         <v>1</v>
@@ -43645,13 +43645,13 @@
         <v>1.79</v>
       </c>
       <c r="AR198" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AS198" t="n">
         <v>1.31</v>
       </c>
       <c r="AT198" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="AU198" t="n">
         <v>0</v>
@@ -43863,13 +43863,13 @@
         <v>0.87</v>
       </c>
       <c r="AR199" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AS199" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AT199" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AU199" t="n">
         <v>9</v>
@@ -44081,13 +44081,13 @@
         <v>0.62</v>
       </c>
       <c r="AR200" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AS200" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="AT200" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="AU200" t="n">
         <v>5</v>
@@ -44299,13 +44299,13 @@
         <v>1.5</v>
       </c>
       <c r="AR201" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AS201" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AT201" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="AU201" t="n">
         <v>6</v>
@@ -44517,13 +44517,13 @@
         <v>0.92</v>
       </c>
       <c r="AR202" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AS202" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="AT202" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="AU202" t="n">
         <v>4</v>
@@ -44735,13 +44735,13 @@
         <v>1.25</v>
       </c>
       <c r="AR203" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AS203" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AT203" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="AU203" t="n">
         <v>4</v>
@@ -44953,13 +44953,13 @@
         <v>0.92</v>
       </c>
       <c r="AR204" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AS204" t="n">
         <v>1.42</v>
       </c>
       <c r="AT204" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="AU204" t="n">
         <v>1</v>
@@ -45171,13 +45171,13 @@
         <v>1.71</v>
       </c>
       <c r="AR205" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AS205" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AT205" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="AU205" t="n">
         <v>8</v>
@@ -45389,13 +45389,13 @@
         <v>1.86</v>
       </c>
       <c r="AR206" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AS206" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AT206" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="AU206" t="n">
         <v>3</v>
@@ -45607,13 +45607,13 @@
         <v>1.77</v>
       </c>
       <c r="AR207" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AS207" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AT207" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AU207" t="n">
         <v>1</v>
@@ -45825,13 +45825,13 @@
         <v>0.92</v>
       </c>
       <c r="AR208" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AS208" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AT208" t="n">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
       <c r="AU208" t="n">
         <v>6</v>
@@ -46043,13 +46043,13 @@
         <v>0.62</v>
       </c>
       <c r="AR209" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AS209" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="AT209" t="n">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="AU209" t="n">
         <v>6</v>
@@ -46261,13 +46261,13 @@
         <v>0.92</v>
       </c>
       <c r="AR210" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AS210" t="n">
         <v>1.07</v>
       </c>
       <c r="AT210" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AU210" t="n">
         <v>2</v>
@@ -46482,10 +46482,10 @@
         <v>1.49</v>
       </c>
       <c r="AS211" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AT211" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="AU211" t="n">
         <v>4</v>
@@ -46697,13 +46697,13 @@
         <v>1.79</v>
       </c>
       <c r="AR212" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AS212" t="n">
         <v>1.31</v>
       </c>
       <c r="AT212" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="AU212" t="n">
         <v>1</v>
@@ -46915,13 +46915,13 @@
         <v>0.67</v>
       </c>
       <c r="AR213" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AS213" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AT213" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="AU213" t="n">
         <v>7</v>
@@ -47133,13 +47133,13 @@
         <v>0.85</v>
       </c>
       <c r="AR214" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AS214" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AT214" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="AU214" t="n">
         <v>3</v>
@@ -47351,13 +47351,13 @@
         <v>1.86</v>
       </c>
       <c r="AR215" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AS215" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AT215" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="AU215" t="n">
         <v>1</v>
@@ -47569,13 +47569,13 @@
         <v>0.87</v>
       </c>
       <c r="AR216" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AS216" t="n">
         <v>1.45</v>
       </c>
-      <c r="AS216" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AT216" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="AU216" t="n">
         <v>9</v>
@@ -47787,13 +47787,13 @@
         <v>0.64</v>
       </c>
       <c r="AR217" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AS217" t="n">
         <v>1.13</v>
       </c>
       <c r="AT217" t="n">
-        <v>2.69</v>
+        <v>2.74</v>
       </c>
       <c r="AU217" t="n">
         <v>4</v>
@@ -48005,10 +48005,10 @@
         <v>1.31</v>
       </c>
       <c r="AR218" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AS218" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AT218" t="n">
         <v>2.59</v>
@@ -48223,13 +48223,13 @@
         <v>2.08</v>
       </c>
       <c r="AR219" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AS219" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AT219" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="AU219" t="n">
         <v>1</v>
@@ -48444,10 +48444,10 @@
         <v>1.71</v>
       </c>
       <c r="AS220" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AT220" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="AU220" t="n">
         <v>6</v>
@@ -48659,13 +48659,13 @@
         <v>0.92</v>
       </c>
       <c r="AR221" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AS221" t="n">
         <v>1.38</v>
       </c>
       <c r="AT221" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="AU221" t="n">
         <v>6</v>
@@ -48877,13 +48877,13 @@
         <v>1.77</v>
       </c>
       <c r="AR222" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AS222" t="n">
         <v>1.42</v>
       </c>
-      <c r="AS222" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AT222" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="AU222" t="n">
         <v>3</v>
@@ -49095,13 +49095,13 @@
         <v>0.92</v>
       </c>
       <c r="AR223" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AS223" t="n">
         <v>1.07</v>
       </c>
       <c r="AT223" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="AU223" t="n">
         <v>2</v>
@@ -49313,13 +49313,13 @@
         <v>1.5</v>
       </c>
       <c r="AR224" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AS224" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AT224" t="n">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="AU224" t="n">
         <v>6</v>
@@ -49531,13 +49531,13 @@
         <v>0.85</v>
       </c>
       <c r="AR225" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AS225" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AT225" t="n">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="AU225" t="n">
         <v>1</v>
@@ -49749,13 +49749,13 @@
         <v>0.92</v>
       </c>
       <c r="AR226" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AS226" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="AT226" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="AU226" t="n">
         <v>1</v>
@@ -49967,13 +49967,13 @@
         <v>0.62</v>
       </c>
       <c r="AR227" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AS227" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AT227" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="AU227" t="n">
         <v>4</v>
@@ -50185,10 +50185,10 @@
         <v>0.87</v>
       </c>
       <c r="AR228" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AS228" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AT228" t="n">
         <v>3.11</v>
@@ -50406,10 +50406,10 @@
         <v>1.68</v>
       </c>
       <c r="AS229" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AT229" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="AU229" t="n">
         <v>9</v>
@@ -50621,13 +50621,13 @@
         <v>1</v>
       </c>
       <c r="AR230" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AS230" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AT230" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="AU230" t="n">
         <v>5</v>
@@ -50839,13 +50839,13 @@
         <v>1</v>
       </c>
       <c r="AR231" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AS231" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AT231" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="AU231" t="n">
         <v>6</v>
@@ -51275,13 +51275,13 @@
         <v>2.08</v>
       </c>
       <c r="AR233" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AS233" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AT233" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="AU233" t="n">
         <v>4</v>
@@ -51493,13 +51493,13 @@
         <v>0.67</v>
       </c>
       <c r="AR234" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AS234" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AT234" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AU234" t="n">
         <v>2</v>
@@ -51711,13 +51711,13 @@
         <v>0.64</v>
       </c>
       <c r="AR235" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AS235" t="n">
         <v>1.12</v>
       </c>
       <c r="AT235" t="n">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="AU235" t="n">
         <v>5</v>
@@ -51932,10 +51932,10 @@
         <v>1.43</v>
       </c>
       <c r="AS236" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AT236" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="AU236" t="n">
         <v>1</v>
@@ -52147,13 +52147,13 @@
         <v>1.31</v>
       </c>
       <c r="AR237" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AS237" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AT237" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="AU237" t="n">
         <v>4</v>
@@ -52365,13 +52365,13 @@
         <v>1.86</v>
       </c>
       <c r="AR238" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AS238" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AT238" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="AU238" t="n">
         <v>1</v>
@@ -52583,13 +52583,13 @@
         <v>1.71</v>
       </c>
       <c r="AR239" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AS239" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AT239" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="AU239" t="n">
         <v>7</v>
@@ -52801,13 +52801,13 @@
         <v>0.85</v>
       </c>
       <c r="AR240" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AS240" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AT240" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="AU240" t="n">
         <v>5</v>
@@ -53019,13 +53019,13 @@
         <v>1.38</v>
       </c>
       <c r="AR241" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AS241" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AT241" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="AU241" t="n">
         <v>4</v>
@@ -53237,13 +53237,13 @@
         <v>1</v>
       </c>
       <c r="AR242" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AS242" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AT242" t="n">
-        <v>2.43</v>
+        <v>2.37</v>
       </c>
       <c r="AU242" t="n">
         <v>2</v>
@@ -53455,13 +53455,13 @@
         <v>0.85</v>
       </c>
       <c r="AR243" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AS243" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AT243" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AU243" t="n">
         <v>1</v>
@@ -53673,13 +53673,13 @@
         <v>1.38</v>
       </c>
       <c r="AR244" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AS244" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AT244" t="n">
-        <v>2.96</v>
+        <v>2.89</v>
       </c>
       <c r="AU244" t="n">
         <v>4</v>
@@ -53891,13 +53891,13 @@
         <v>0.92</v>
       </c>
       <c r="AR245" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AS245" t="n">
         <v>1.38</v>
       </c>
       <c r="AT245" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AU245" t="n">
         <v>3</v>
@@ -54109,13 +54109,13 @@
         <v>1.5</v>
       </c>
       <c r="AR246" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AS246" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AT246" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="AU246" t="n">
         <v>3</v>
@@ -54327,13 +54327,13 @@
         <v>1.71</v>
       </c>
       <c r="AR247" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AS247" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AT247" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="AU247" t="n">
         <v>3</v>
@@ -54545,13 +54545,13 @@
         <v>1.25</v>
       </c>
       <c r="AR248" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AS248" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AT248" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="AU248" t="n">
         <v>3</v>
@@ -54763,13 +54763,13 @@
         <v>1.86</v>
       </c>
       <c r="AR249" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AS249" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AT249" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="AU249" t="n">
         <v>5</v>
@@ -54981,13 +54981,13 @@
         <v>0.85</v>
       </c>
       <c r="AR250" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AS250" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AT250" t="n">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="AU250" t="n">
         <v>5</v>
@@ -55199,10 +55199,10 @@
         <v>0.62</v>
       </c>
       <c r="AR251" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AS251" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AT251" t="n">
         <v>2.78</v>
@@ -55420,10 +55420,10 @@
         <v>1.48</v>
       </c>
       <c r="AS252" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AT252" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="AU252" t="n">
         <v>2</v>
@@ -55635,13 +55635,13 @@
         <v>0.85</v>
       </c>
       <c r="AR253" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AS253" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AT253" t="n">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="AU253" t="n">
         <v>6</v>
@@ -55856,10 +55856,10 @@
         <v>1.7</v>
       </c>
       <c r="AS254" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AT254" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="AU254" t="n">
         <v>3</v>
@@ -56071,13 +56071,13 @@
         <v>0.87</v>
       </c>
       <c r="AR255" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AS255" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AT255" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="AU255" t="n">
         <v>5</v>
@@ -56289,13 +56289,13 @@
         <v>0.64</v>
       </c>
       <c r="AR256" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AS256" t="n">
         <v>1.16</v>
       </c>
       <c r="AT256" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="AU256" t="n">
         <v>4</v>
@@ -56507,13 +56507,13 @@
         <v>1</v>
       </c>
       <c r="AR257" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AS257" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="AT257" t="n">
-        <v>2.81</v>
+        <v>2.91</v>
       </c>
       <c r="AU257" t="n">
         <v>4</v>
@@ -56725,13 +56725,13 @@
         <v>0.92</v>
       </c>
       <c r="AR258" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AS258" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AT258" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="AU258" t="n">
         <v>5</v>
@@ -56946,10 +56946,10 @@
         <v>1.4</v>
       </c>
       <c r="AS259" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AT259" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="AU259" t="n">
         <v>4</v>
@@ -57161,10 +57161,10 @@
         <v>0.92</v>
       </c>
       <c r="AR260" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AS260" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="AT260" t="n">
         <v>2.47</v>
@@ -57379,13 +57379,13 @@
         <v>1.79</v>
       </c>
       <c r="AR261" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AS261" t="n">
         <v>1.37</v>
       </c>
       <c r="AT261" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="AU261" t="n">
         <v>4</v>
@@ -57597,13 +57597,13 @@
         <v>1.86</v>
       </c>
       <c r="AR262" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AS262" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AT262" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="AU262" t="n">
         <v>2</v>
@@ -57815,13 +57815,13 @@
         <v>0.87</v>
       </c>
       <c r="AR263" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AS263" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AT263" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="AU263" t="n">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
@@ -42131,13 +42131,13 @@
         <v>3</v>
       </c>
       <c r="AV191" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW191" t="n">
         <v>7</v>
       </c>
       <c r="AX191" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY191" t="n">
         <v>10</v>
@@ -43660,16 +43660,16 @@
         <v>5</v>
       </c>
       <c r="AW198" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX198" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY198" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ198" t="n">
         <v>8</v>
-      </c>
-      <c r="AX198" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY198" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ198" t="n">
-        <v>11</v>
       </c>
       <c r="BA198" t="n">
         <v>3</v>
@@ -43872,16 +43872,16 @@
         <v>2.63</v>
       </c>
       <c r="AU199" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV199" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW199" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX199" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY199" t="n">
         <v>16</v>
@@ -44090,13 +44090,13 @@
         <v>2.34</v>
       </c>
       <c r="AU200" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV200" t="n">
         <v>2</v>
       </c>
       <c r="AW200" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX200" t="n">
         <v>8</v>
@@ -44744,16 +44744,16 @@
         <v>2.34</v>
       </c>
       <c r="AU203" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV203" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW203" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX203" t="n">
         <v>4</v>
-      </c>
-      <c r="AV203" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW203" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX203" t="n">
-        <v>5</v>
       </c>
       <c r="AY203" t="n">
         <v>14</v>
@@ -44962,13 +44962,13 @@
         <v>2.8</v>
       </c>
       <c r="AU204" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV204" t="n">
         <v>1</v>
       </c>
       <c r="AW204" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX204" t="n">
         <v>10</v>
@@ -45180,16 +45180,16 @@
         <v>2.63</v>
       </c>
       <c r="AU205" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV205" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW205" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX205" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY205" t="n">
         <v>19</v>
@@ -46052,13 +46052,13 @@
         <v>2.43</v>
       </c>
       <c r="AU209" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AV209" t="n">
         <v>6</v>
       </c>
       <c r="AW209" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX209" t="n">
         <v>9</v>
@@ -46261,25 +46261,25 @@
         <v>0.92</v>
       </c>
       <c r="AR210" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AS210" t="n">
         <v>1.07</v>
       </c>
       <c r="AT210" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AU210" t="n">
         <v>2</v>
       </c>
       <c r="AV210" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW210" t="n">
         <v>6</v>
       </c>
       <c r="AX210" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY210" t="n">
         <v>8</v>
@@ -46482,10 +46482,10 @@
         <v>1.49</v>
       </c>
       <c r="AS211" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AT211" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AU211" t="n">
         <v>4</v>
@@ -46697,25 +46697,25 @@
         <v>1.79</v>
       </c>
       <c r="AR212" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AS212" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AT212" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AU212" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AV212" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW212" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AX212" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY212" t="n">
         <v>15</v>
@@ -47351,13 +47351,13 @@
         <v>1.86</v>
       </c>
       <c r="AR215" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AS215" t="n">
         <v>1.3</v>
       </c>
       <c r="AT215" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="AU215" t="n">
         <v>1</v>
@@ -47572,19 +47572,19 @@
         <v>1.47</v>
       </c>
       <c r="AS216" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AT216" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="AU216" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AV216" t="n">
         <v>3</v>
       </c>
       <c r="AW216" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AX216" t="n">
         <v>3</v>
@@ -48005,13 +48005,13 @@
         <v>1.31</v>
       </c>
       <c r="AR218" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AS218" t="n">
         <v>1.42</v>
       </c>
       <c r="AT218" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="AU218" t="n">
         <v>2</v>
@@ -48235,13 +48235,13 @@
         <v>1</v>
       </c>
       <c r="AV219" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AW219" t="n">
         <v>20</v>
       </c>
       <c r="AX219" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AY219" t="n">
         <v>21</v>
@@ -48444,10 +48444,10 @@
         <v>1.71</v>
       </c>
       <c r="AS220" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AT220" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="AU220" t="n">
         <v>6</v>
@@ -48671,13 +48671,13 @@
         <v>6</v>
       </c>
       <c r="AV221" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW221" t="n">
         <v>10</v>
       </c>
       <c r="AX221" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AY221" t="n">
         <v>16</v>
@@ -48880,10 +48880,10 @@
         <v>1.41</v>
       </c>
       <c r="AS222" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AT222" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AU222" t="n">
         <v>3</v>
@@ -49095,13 +49095,13 @@
         <v>0.92</v>
       </c>
       <c r="AR223" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AS223" t="n">
         <v>1.07</v>
       </c>
       <c r="AT223" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="AU223" t="n">
         <v>2</v>
@@ -49313,13 +49313,13 @@
         <v>1.5</v>
       </c>
       <c r="AR224" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AS224" t="n">
         <v>1.27</v>
       </c>
       <c r="AT224" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AU224" t="n">
         <v>6</v>
@@ -49531,25 +49531,25 @@
         <v>0.85</v>
       </c>
       <c r="AR225" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AS225" t="n">
         <v>1.21</v>
       </c>
       <c r="AT225" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="AU225" t="n">
         <v>1</v>
       </c>
       <c r="AV225" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW225" t="n">
         <v>9</v>
       </c>
       <c r="AX225" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY225" t="n">
         <v>10</v>
@@ -49749,13 +49749,13 @@
         <v>0.92</v>
       </c>
       <c r="AR226" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AS226" t="n">
         <v>0.96</v>
       </c>
       <c r="AT226" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="AU226" t="n">
         <v>1</v>
@@ -49967,22 +49967,22 @@
         <v>0.62</v>
       </c>
       <c r="AR227" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AS227" t="n">
         <v>1.04</v>
       </c>
       <c r="AT227" t="n">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="AU227" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AV227" t="n">
         <v>3</v>
       </c>
       <c r="AW227" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AX227" t="n">
         <v>9</v>
@@ -50412,16 +50412,16 @@
         <v>2.81</v>
       </c>
       <c r="AU229" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV229" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW229" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX229" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY229" t="n">
         <v>15</v>
@@ -51060,10 +51060,10 @@
         <v>1.54</v>
       </c>
       <c r="AS232" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AT232" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="AU232" t="n">
         <v>3</v>
@@ -51275,13 +51275,13 @@
         <v>2.08</v>
       </c>
       <c r="AR233" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AS233" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AT233" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="AU233" t="n">
         <v>4</v>
@@ -51493,13 +51493,13 @@
         <v>0.67</v>
       </c>
       <c r="AR234" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AS234" t="n">
         <v>1.05</v>
       </c>
       <c r="AT234" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="AU234" t="n">
         <v>2</v>
@@ -51711,13 +51711,13 @@
         <v>0.64</v>
       </c>
       <c r="AR235" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AS235" t="n">
         <v>1.12</v>
       </c>
       <c r="AT235" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="AU235" t="n">
         <v>5</v>
@@ -51932,10 +51932,10 @@
         <v>1.43</v>
       </c>
       <c r="AS236" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AT236" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="AU236" t="n">
         <v>1</v>
@@ -52159,13 +52159,13 @@
         <v>4</v>
       </c>
       <c r="AV237" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW237" t="n">
         <v>14</v>
       </c>
       <c r="AX237" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY237" t="n">
         <v>18</v>
@@ -52586,22 +52586,22 @@
         <v>1.27</v>
       </c>
       <c r="AS239" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AT239" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="AU239" t="n">
         <v>7</v>
       </c>
       <c r="AV239" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW239" t="n">
         <v>10</v>
       </c>
       <c r="AX239" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY239" t="n">
         <v>17</v>
@@ -52804,10 +52804,10 @@
         <v>1.37</v>
       </c>
       <c r="AS240" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AT240" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="AU240" t="n">
         <v>5</v>
@@ -53237,13 +53237,13 @@
         <v>1</v>
       </c>
       <c r="AR242" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AS242" t="n">
         <v>1.27</v>
       </c>
       <c r="AT242" t="n">
-        <v>2.37</v>
+        <v>2.42</v>
       </c>
       <c r="AU242" t="n">
         <v>2</v>
@@ -53455,13 +53455,13 @@
         <v>0.85</v>
       </c>
       <c r="AR243" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AS243" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AT243" t="n">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="AU243" t="n">
         <v>1</v>
@@ -53673,13 +53673,13 @@
         <v>1.38</v>
       </c>
       <c r="AR244" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AS244" t="n">
         <v>1.42</v>
       </c>
       <c r="AT244" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="AU244" t="n">
         <v>4</v>
@@ -53894,22 +53894,22 @@
         <v>1.62</v>
       </c>
       <c r="AS245" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AT245" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="AU245" t="n">
         <v>3</v>
       </c>
       <c r="AV245" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW245" t="n">
         <v>11</v>
       </c>
       <c r="AX245" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY245" t="n">
         <v>14</v>
@@ -54336,16 +54336,16 @@
         <v>2.48</v>
       </c>
       <c r="AU247" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV247" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW247" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX247" t="n">
         <v>3</v>
-      </c>
-      <c r="AV247" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW247" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX247" t="n">
-        <v>4</v>
       </c>
       <c r="AY247" t="n">
         <v>12</v>
@@ -54548,10 +54548,10 @@
         <v>1.55</v>
       </c>
       <c r="AS248" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AT248" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="AU248" t="n">
         <v>3</v>
@@ -54981,22 +54981,22 @@
         <v>0.85</v>
       </c>
       <c r="AR250" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AS250" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AT250" t="n">
         <v>2.57</v>
       </c>
       <c r="AU250" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV250" t="n">
         <v>1</v>
       </c>
       <c r="AW250" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AX250" t="n">
         <v>5</v>
@@ -55426,13 +55426,13 @@
         <v>2.96</v>
       </c>
       <c r="AU252" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV252" t="n">
         <v>3</v>
       </c>
       <c r="AW252" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX252" t="n">
         <v>9</v>
@@ -55635,13 +55635,13 @@
         <v>0.85</v>
       </c>
       <c r="AR253" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AS253" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AT253" t="n">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="AU253" t="n">
         <v>6</v>
@@ -56074,19 +56074,19 @@
         <v>1.6</v>
       </c>
       <c r="AS255" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AT255" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="AU255" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV255" t="n">
         <v>0</v>
       </c>
       <c r="AW255" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX255" t="n">
         <v>3</v>
@@ -56946,10 +56946,10 @@
         <v>1.4</v>
       </c>
       <c r="AS259" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AT259" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="AU259" t="n">
         <v>4</v>
@@ -57161,13 +57161,13 @@
         <v>0.92</v>
       </c>
       <c r="AR260" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AS260" t="n">
         <v>0.96</v>
       </c>
       <c r="AT260" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="AU260" t="n">
         <v>5</v>
@@ -57382,10 +57382,10 @@
         <v>1.31</v>
       </c>
       <c r="AS261" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AT261" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="AU261" t="n">
         <v>4</v>
@@ -57597,13 +57597,13 @@
         <v>1.86</v>
       </c>
       <c r="AR262" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AS262" t="n">
         <v>1.36</v>
       </c>
       <c r="AT262" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="AU262" t="n">
         <v>2</v>
@@ -57818,22 +57818,22 @@
         <v>1.39</v>
       </c>
       <c r="AS263" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AT263" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="AU263" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV263" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AW263" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX263" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AY263" t="n">
         <v>12</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
@@ -57824,16 +57824,16 @@
         <v>2.74</v>
       </c>
       <c r="AU263" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV263" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AW263" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX263" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AY263" t="n">
         <v>12</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
@@ -57824,16 +57824,16 @@
         <v>2.74</v>
       </c>
       <c r="AU263" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV263" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AW263" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX263" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AY263" t="n">
         <v>12</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP263"/>
+  <dimension ref="A1:BP264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1350,7 +1350,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ13" t="n">
         <v>1.31</v>
@@ -3966,7 +3966,7 @@
         <v>2</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -6146,7 +6146,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR26" t="n">
         <v>1.86</v>
@@ -7015,7 +7015,7 @@
         <v>3</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ30" t="n">
         <v>1</v>
@@ -10939,7 +10939,7 @@
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ48" t="n">
         <v>1.5</v>
@@ -13122,7 +13122,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR58" t="n">
         <v>1.78</v>
@@ -13558,7 +13558,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR60" t="n">
         <v>1.82</v>
@@ -14209,7 +14209,7 @@
         <v>1.33</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ63" t="n">
         <v>0.92</v>
@@ -18354,7 +18354,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR82" t="n">
         <v>1.4</v>
@@ -19441,7 +19441,7 @@
         <v>1</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ87" t="n">
         <v>0.87</v>
@@ -22060,7 +22060,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR99" t="n">
         <v>1.11</v>
@@ -26853,7 +26853,7 @@
         <v>0.8</v>
       </c>
       <c r="AP121" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ121" t="n">
         <v>0.62</v>
@@ -31431,7 +31431,7 @@
         <v>1.43</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ142" t="n">
         <v>0.92</v>
@@ -32739,7 +32739,7 @@
         <v>0.71</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ148" t="n">
         <v>1.25</v>
@@ -33614,7 +33614,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ152" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR152" t="n">
         <v>1.4</v>
@@ -37102,7 +37102,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ168" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR168" t="n">
         <v>1.55</v>
@@ -37756,7 +37756,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ171" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR171" t="n">
         <v>1.19</v>
@@ -40587,7 +40587,7 @@
         <v>1.63</v>
       </c>
       <c r="AP184" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ184" t="n">
         <v>1.86</v>
@@ -45165,7 +45165,7 @@
         <v>1.73</v>
       </c>
       <c r="AP205" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ205" t="n">
         <v>1.71</v>
@@ -49089,7 +49089,7 @@
         <v>1</v>
       </c>
       <c r="AP223" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ223" t="n">
         <v>0.92</v>
@@ -50618,7 +50618,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ230" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR230" t="n">
         <v>1.46</v>
@@ -53234,7 +53234,7 @@
         <v>1</v>
       </c>
       <c r="AQ242" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR242" t="n">
         <v>1.15</v>
@@ -54975,7 +54975,7 @@
         <v>0.92</v>
       </c>
       <c r="AP250" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ250" t="n">
         <v>0.85</v>
@@ -57888,6 +57888,224 @@
       </c>
       <c r="BP263" t="n">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="n">
+        <v>263</v>
+      </c>
+      <c r="B264" t="n">
+        <v>7778333</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="n">
+        <v>45891.29166666666</v>
+      </c>
+      <c r="F264" t="n">
+        <v>27</v>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Kashiwa Reysol</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Urawa Reds</t>
+        </is>
+      </c>
+      <c r="I264" t="n">
+        <v>0</v>
+      </c>
+      <c r="J264" t="n">
+        <v>2</v>
+      </c>
+      <c r="K264" t="n">
+        <v>2</v>
+      </c>
+      <c r="L264" t="n">
+        <v>4</v>
+      </c>
+      <c r="M264" t="n">
+        <v>2</v>
+      </c>
+      <c r="N264" t="n">
+        <v>6</v>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>['54', '83', '90', '90+6']</t>
+        </is>
+      </c>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>['5', '43']</t>
+        </is>
+      </c>
+      <c r="Q264" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R264" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S264" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T264" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U264" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V264" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W264" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X264" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Y264" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z264" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA264" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB264" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC264" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD264" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE264" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF264" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG264" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH264" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI264" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ264" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK264" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL264" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM264" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN264" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO264" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP264" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AQ264" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AR264" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS264" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AT264" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU264" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV264" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW264" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX264" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY264" t="n">
+        <v>23</v>
+      </c>
+      <c r="AZ264" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA264" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB264" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC264" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD264" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BE264" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF264" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BG264" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH264" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI264" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ264" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK264" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BL264" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BM264" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BN264" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO264" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BP264" t="n">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
@@ -58048,13 +58048,13 @@
         <v>5</v>
       </c>
       <c r="AW264" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX264" t="n">
         <v>2</v>
       </c>
       <c r="AY264" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ264" t="n">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
@@ -58042,13 +58042,13 @@
         <v>2.78</v>
       </c>
       <c r="AU264" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AV264" t="n">
         <v>5</v>
       </c>
       <c r="AW264" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AX264" t="n">
         <v>2</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP264"/>
+  <dimension ref="A1:BP272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ2" t="n">
         <v>1</v>
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.79</v>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ6" t="n">
         <v>1.71</v>
@@ -2440,7 +2440,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2658,7 +2658,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3091,10 +3091,10 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -4181,10 +4181,10 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.38</v>
@@ -4620,7 +4620,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ19" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -5271,10 +5271,10 @@
         <v>1</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR22" t="n">
         <v>0.78</v>
@@ -5489,7 +5489,7 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ23" t="n">
         <v>0.87</v>
@@ -5928,7 +5928,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR25" t="n">
         <v>1.44</v>
@@ -7236,7 +7236,7 @@
         <v>1</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR31" t="n">
         <v>1.01</v>
@@ -7454,7 +7454,7 @@
         <v>1</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR32" t="n">
         <v>0.99</v>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ36" t="n">
         <v>0.87</v>
@@ -8541,7 +8541,7 @@
         <v>1.5</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ37" t="n">
         <v>1</v>
@@ -8759,10 +8759,10 @@
         <v>3</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ38" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR38" t="n">
         <v>1.22</v>
@@ -8977,10 +8977,10 @@
         <v>3</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR39" t="n">
         <v>1.46</v>
@@ -9198,7 +9198,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR40" t="n">
         <v>1.11</v>
@@ -9849,7 +9849,7 @@
         <v>1.5</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ43" t="n">
         <v>0.92</v>
@@ -10067,10 +10067,10 @@
         <v>2</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR44" t="n">
         <v>1.4</v>
@@ -10288,7 +10288,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR45" t="n">
         <v>1.24</v>
@@ -10506,7 +10506,7 @@
         <v>1</v>
       </c>
       <c r="AQ46" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR46" t="n">
         <v>1.34</v>
@@ -10721,7 +10721,7 @@
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ47" t="n">
         <v>0.64</v>
@@ -10942,7 +10942,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR48" t="n">
         <v>1.32</v>
@@ -11811,7 +11811,7 @@
         <v>0.33</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ52" t="n">
         <v>0.64</v>
@@ -12029,7 +12029,7 @@
         <v>1.5</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ53" t="n">
         <v>0.92</v>
@@ -12683,10 +12683,10 @@
         <v>2</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR56" t="n">
         <v>1.53</v>
@@ -13340,7 +13340,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR59" t="n">
         <v>1.8</v>
@@ -13555,7 +13555,7 @@
         <v>0.75</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ60" t="n">
         <v>0.92</v>
@@ -13773,7 +13773,7 @@
         <v>0</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ61" t="n">
         <v>0.85</v>
@@ -13994,7 +13994,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ62" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR62" t="n">
         <v>1.28</v>
@@ -14427,7 +14427,7 @@
         <v>1</v>
       </c>
       <c r="AP64" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ64" t="n">
         <v>0.87</v>
@@ -14645,10 +14645,10 @@
         <v>0.5</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR65" t="n">
         <v>0.95</v>
@@ -14866,7 +14866,7 @@
         <v>2</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR66" t="n">
         <v>1.3</v>
@@ -15084,7 +15084,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR67" t="n">
         <v>1.59</v>
@@ -15299,10 +15299,10 @@
         <v>3</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ68" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR68" t="n">
         <v>1.38</v>
@@ -15520,7 +15520,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR69" t="n">
         <v>1.25</v>
@@ -15738,7 +15738,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR70" t="n">
         <v>1.34</v>
@@ -15953,7 +15953,7 @@
         <v>0</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ71" t="n">
         <v>1.25</v>
@@ -16171,10 +16171,10 @@
         <v>2.5</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ72" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR72" t="n">
         <v>1.5</v>
@@ -16607,7 +16607,7 @@
         <v>0</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ74" t="n">
         <v>0.85</v>
@@ -16825,7 +16825,7 @@
         <v>2</v>
       </c>
       <c r="AP75" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ75" t="n">
         <v>1.38</v>
@@ -17046,7 +17046,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ76" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR76" t="n">
         <v>1.76</v>
@@ -17261,7 +17261,7 @@
         <v>1</v>
       </c>
       <c r="AP77" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ77" t="n">
         <v>0.92</v>
@@ -17482,7 +17482,7 @@
         <v>1</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR78" t="n">
         <v>1.15</v>
@@ -17700,7 +17700,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ79" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR79" t="n">
         <v>1.65</v>
@@ -18133,7 +18133,7 @@
         <v>1</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ81" t="n">
         <v>0.92</v>
@@ -18351,7 +18351,7 @@
         <v>0.8</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ82" t="n">
         <v>0.92</v>
@@ -18572,7 +18572,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR83" t="n">
         <v>1.1</v>
@@ -18790,7 +18790,7 @@
         <v>1</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR84" t="n">
         <v>1.07</v>
@@ -20752,7 +20752,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR93" t="n">
         <v>1.26</v>
@@ -20967,7 +20967,7 @@
         <v>0.2</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ94" t="n">
         <v>0.64</v>
@@ -21185,7 +21185,7 @@
         <v>0.25</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ95" t="n">
         <v>0.85</v>
@@ -21403,10 +21403,10 @@
         <v>1.75</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR96" t="n">
         <v>1.34</v>
@@ -21621,10 +21621,10 @@
         <v>1</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR97" t="n">
         <v>1.78</v>
@@ -21842,7 +21842,7 @@
         <v>2</v>
       </c>
       <c r="AQ98" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR98" t="n">
         <v>1.26</v>
@@ -22275,10 +22275,10 @@
         <v>0.33</v>
       </c>
       <c r="AP100" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ100" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR100" t="n">
         <v>1.43</v>
@@ -22496,7 +22496,7 @@
         <v>1</v>
       </c>
       <c r="AQ101" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR101" t="n">
         <v>1.06</v>
@@ -22714,7 +22714,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR102" t="n">
         <v>1.42</v>
@@ -23147,7 +23147,7 @@
         <v>1.67</v>
       </c>
       <c r="AP104" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ104" t="n">
         <v>1.71</v>
@@ -23583,10 +23583,10 @@
         <v>0.75</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ106" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR106" t="n">
         <v>1.41</v>
@@ -24019,10 +24019,10 @@
         <v>1.33</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR108" t="n">
         <v>1.28</v>
@@ -24240,7 +24240,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ109" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR109" t="n">
         <v>1.43</v>
@@ -24455,7 +24455,7 @@
         <v>0.8</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ110" t="n">
         <v>0.92</v>
@@ -25327,7 +25327,7 @@
         <v>0.8</v>
       </c>
       <c r="AP114" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ114" t="n">
         <v>1</v>
@@ -25548,7 +25548,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ115" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR115" t="n">
         <v>1.17</v>
@@ -25766,7 +25766,7 @@
         <v>2</v>
       </c>
       <c r="AQ116" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR116" t="n">
         <v>1.41</v>
@@ -25981,7 +25981,7 @@
         <v>0.75</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ117" t="n">
         <v>1.25</v>
@@ -26420,7 +26420,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR119" t="n">
         <v>1.3</v>
@@ -27074,7 +27074,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ122" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR122" t="n">
         <v>1.28</v>
@@ -27510,7 +27510,7 @@
         <v>1</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR124" t="n">
         <v>1.14</v>
@@ -27725,7 +27725,7 @@
         <v>1.17</v>
       </c>
       <c r="AP125" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ125" t="n">
         <v>0.92</v>
@@ -27943,7 +27943,7 @@
         <v>2</v>
       </c>
       <c r="AP126" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ126" t="n">
         <v>1.79</v>
@@ -28161,7 +28161,7 @@
         <v>1.86</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ127" t="n">
         <v>1.71</v>
@@ -28597,10 +28597,10 @@
         <v>2.17</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ129" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR129" t="n">
         <v>1.94</v>
@@ -29251,7 +29251,7 @@
         <v>0.83</v>
       </c>
       <c r="AP132" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ132" t="n">
         <v>0.92</v>
@@ -29687,10 +29687,10 @@
         <v>1.14</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ134" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR134" t="n">
         <v>1.47</v>
@@ -29908,7 +29908,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ135" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR135" t="n">
         <v>1.55</v>
@@ -30777,10 +30777,10 @@
         <v>1.5</v>
       </c>
       <c r="AP139" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR139" t="n">
         <v>1.5</v>
@@ -31213,7 +31213,7 @@
         <v>0.67</v>
       </c>
       <c r="AP141" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ141" t="n">
         <v>1.25</v>
@@ -31434,7 +31434,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ142" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR142" t="n">
         <v>1.35</v>
@@ -31649,10 +31649,10 @@
         <v>0.4</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ143" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR143" t="n">
         <v>1.35</v>
@@ -32088,7 +32088,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ145" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR145" t="n">
         <v>1.35</v>
@@ -32524,7 +32524,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ147" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR147" t="n">
         <v>1.3</v>
@@ -32960,7 +32960,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ149" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR149" t="n">
         <v>1.17</v>
@@ -33178,7 +33178,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR150" t="n">
         <v>1.51</v>
@@ -33611,7 +33611,7 @@
         <v>1</v>
       </c>
       <c r="AP152" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ152" t="n">
         <v>0.92</v>
@@ -33829,10 +33829,10 @@
         <v>1.17</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR153" t="n">
         <v>1.46</v>
@@ -34047,7 +34047,7 @@
         <v>0.17</v>
       </c>
       <c r="AP154" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ154" t="n">
         <v>0.85</v>
@@ -34265,10 +34265,10 @@
         <v>1</v>
       </c>
       <c r="AP155" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ155" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR155" t="n">
         <v>1.27</v>
@@ -34704,7 +34704,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ157" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR157" t="n">
         <v>1.51</v>
@@ -35791,7 +35791,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ162" t="n">
         <v>0.64</v>
@@ -36012,7 +36012,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ163" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR163" t="n">
         <v>1.5</v>
@@ -36230,7 +36230,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ164" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR164" t="n">
         <v>1.33</v>
@@ -36881,7 +36881,7 @@
         <v>1.14</v>
       </c>
       <c r="AP167" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ167" t="n">
         <v>0.62</v>
@@ -37320,7 +37320,7 @@
         <v>1</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR169" t="n">
         <v>1.25</v>
@@ -37535,7 +37535,7 @@
         <v>1.25</v>
       </c>
       <c r="AP170" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ170" t="n">
         <v>1.38</v>
@@ -37753,7 +37753,7 @@
         <v>1</v>
       </c>
       <c r="AP171" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ171" t="n">
         <v>0.92</v>
@@ -37971,10 +37971,10 @@
         <v>1.89</v>
       </c>
       <c r="AP172" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ172" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR172" t="n">
         <v>1.53</v>
@@ -38192,7 +38192,7 @@
         <v>1</v>
       </c>
       <c r="AQ173" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR173" t="n">
         <v>1.26</v>
@@ -38625,10 +38625,10 @@
         <v>1.22</v>
       </c>
       <c r="AP175" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ175" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR175" t="n">
         <v>1.37</v>
@@ -38846,7 +38846,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ176" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR176" t="n">
         <v>1.2</v>
@@ -39061,7 +39061,7 @@
         <v>1.9</v>
       </c>
       <c r="AP177" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ177" t="n">
         <v>1.71</v>
@@ -39282,7 +39282,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ178" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR178" t="n">
         <v>1.36</v>
@@ -39933,7 +39933,7 @@
         <v>1</v>
       </c>
       <c r="AP181" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ181" t="n">
         <v>0.62</v>
@@ -40369,7 +40369,7 @@
         <v>1.11</v>
       </c>
       <c r="AP183" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ183" t="n">
         <v>0.92</v>
@@ -40590,7 +40590,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ184" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR184" t="n">
         <v>1.42</v>
@@ -40808,7 +40808,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ185" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR185" t="n">
         <v>1.56</v>
@@ -41023,10 +41023,10 @@
         <v>1.5</v>
       </c>
       <c r="AP186" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ186" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR186" t="n">
         <v>1.45</v>
@@ -41677,10 +41677,10 @@
         <v>1.11</v>
       </c>
       <c r="AP189" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ189" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR189" t="n">
         <v>1.73</v>
@@ -41898,7 +41898,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ190" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR190" t="n">
         <v>1.36</v>
@@ -42116,7 +42116,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ191" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR191" t="n">
         <v>1.3</v>
@@ -42334,7 +42334,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ192" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR192" t="n">
         <v>1.46</v>
@@ -42552,7 +42552,7 @@
         <v>1</v>
       </c>
       <c r="AQ193" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR193" t="n">
         <v>1.15</v>
@@ -42985,7 +42985,7 @@
         <v>0.5</v>
       </c>
       <c r="AP195" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ195" t="n">
         <v>0.85</v>
@@ -43421,7 +43421,7 @@
         <v>1.11</v>
       </c>
       <c r="AP197" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ197" t="n">
         <v>1.38</v>
@@ -43639,7 +43639,7 @@
         <v>1.9</v>
       </c>
       <c r="AP198" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ198" t="n">
         <v>1.79</v>
@@ -44075,7 +44075,7 @@
         <v>0.89</v>
       </c>
       <c r="AP200" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ200" t="n">
         <v>0.62</v>
@@ -44296,7 +44296,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ201" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR201" t="n">
         <v>1.36</v>
@@ -44511,7 +44511,7 @@
         <v>1.1</v>
       </c>
       <c r="AP202" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ202" t="n">
         <v>0.92</v>
@@ -44947,10 +44947,10 @@
         <v>1</v>
       </c>
       <c r="AP204" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ204" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR204" t="n">
         <v>1.38</v>
@@ -45386,7 +45386,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ206" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR206" t="n">
         <v>1.51</v>
@@ -45604,7 +45604,7 @@
         <v>1</v>
       </c>
       <c r="AQ207" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR207" t="n">
         <v>1.14</v>
@@ -45819,7 +45819,7 @@
         <v>0.89</v>
       </c>
       <c r="AP208" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ208" t="n">
         <v>0.92</v>
@@ -46912,7 +46912,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ213" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR213" t="n">
         <v>1.36</v>
@@ -47345,10 +47345,10 @@
         <v>1.9</v>
       </c>
       <c r="AP215" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ215" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR215" t="n">
         <v>1.34</v>
@@ -47999,10 +47999,10 @@
         <v>1.6</v>
       </c>
       <c r="AP218" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ218" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR218" t="n">
         <v>1.16</v>
@@ -48217,10 +48217,10 @@
         <v>1.91</v>
       </c>
       <c r="AP219" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ219" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR219" t="n">
         <v>1.4</v>
@@ -48438,7 +48438,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ220" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR220" t="n">
         <v>1.71</v>
@@ -48656,7 +48656,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ221" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR221" t="n">
         <v>1.38</v>
@@ -48871,10 +48871,10 @@
         <v>1.55</v>
       </c>
       <c r="AP222" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ222" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR222" t="n">
         <v>1.41</v>
@@ -49310,7 +49310,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ224" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR224" t="n">
         <v>1.42</v>
@@ -49743,7 +49743,7 @@
         <v>1</v>
       </c>
       <c r="AP226" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ226" t="n">
         <v>0.92</v>
@@ -50179,7 +50179,7 @@
         <v>0.83</v>
       </c>
       <c r="AP228" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ228" t="n">
         <v>0.87</v>
@@ -50400,7 +50400,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ229" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR229" t="n">
         <v>1.68</v>
@@ -51269,10 +51269,10 @@
         <v>2</v>
       </c>
       <c r="AP233" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ233" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AR233" t="n">
         <v>1.14</v>
@@ -51490,7 +51490,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ234" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR234" t="n">
         <v>1.32</v>
@@ -51923,10 +51923,10 @@
         <v>1.67</v>
       </c>
       <c r="AP236" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ236" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AR236" t="n">
         <v>1.43</v>
@@ -52141,10 +52141,10 @@
         <v>1.45</v>
       </c>
       <c r="AP237" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ237" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR237" t="n">
         <v>1.53</v>
@@ -52359,10 +52359,10 @@
         <v>1.82</v>
       </c>
       <c r="AP238" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ238" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR238" t="n">
         <v>1.36</v>
@@ -52577,7 +52577,7 @@
         <v>1.67</v>
       </c>
       <c r="AP239" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ239" t="n">
         <v>1.71</v>
@@ -52798,7 +52798,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ240" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR240" t="n">
         <v>1.37</v>
@@ -53449,7 +53449,7 @@
         <v>0.73</v>
       </c>
       <c r="AP243" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ243" t="n">
         <v>0.85</v>
@@ -53888,7 +53888,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ245" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR245" t="n">
         <v>1.62</v>
@@ -54106,7 +54106,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ246" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AR246" t="n">
         <v>1.5</v>
@@ -54321,7 +54321,7 @@
         <v>1.62</v>
       </c>
       <c r="AP247" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ247" t="n">
         <v>1.71</v>
@@ -54539,7 +54539,7 @@
         <v>1.09</v>
       </c>
       <c r="AP248" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ248" t="n">
         <v>1.25</v>
@@ -54760,7 +54760,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ249" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR249" t="n">
         <v>1.41</v>
@@ -54978,7 +54978,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ250" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR250" t="n">
         <v>1.45</v>
@@ -55193,7 +55193,7 @@
         <v>0.67</v>
       </c>
       <c r="AP251" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ251" t="n">
         <v>0.62</v>
@@ -55850,7 +55850,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ254" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR254" t="n">
         <v>1.7</v>
@@ -56937,10 +56937,10 @@
         <v>1.33</v>
       </c>
       <c r="AP259" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AQ259" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR259" t="n">
         <v>1.4</v>
@@ -57373,7 +57373,7 @@
         <v>1.92</v>
       </c>
       <c r="AP261" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AQ261" t="n">
         <v>1.79</v>
@@ -57594,7 +57594,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ262" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR262" t="n">
         <v>1.59</v>
@@ -58106,6 +58106,1750 @@
       </c>
       <c r="BP264" t="n">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="n">
+        <v>264</v>
+      </c>
+      <c r="B265" t="n">
+        <v>7778342</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="n">
+        <v>45892.25</v>
+      </c>
+      <c r="F265" t="n">
+        <v>27</v>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Avispa Fukuoka</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Shimizu S-Pulse</t>
+        </is>
+      </c>
+      <c r="I265" t="n">
+        <v>0</v>
+      </c>
+      <c r="J265" t="n">
+        <v>0</v>
+      </c>
+      <c r="K265" t="n">
+        <v>0</v>
+      </c>
+      <c r="L265" t="n">
+        <v>0</v>
+      </c>
+      <c r="M265" t="n">
+        <v>0</v>
+      </c>
+      <c r="N265" t="n">
+        <v>0</v>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q265" t="n">
+        <v>3</v>
+      </c>
+      <c r="R265" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S265" t="n">
+        <v>4</v>
+      </c>
+      <c r="T265" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U265" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V265" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W265" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X265" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y265" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z265" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA265" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB265" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AC265" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD265" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE265" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF265" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG265" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH265" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI265" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ265" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK265" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL265" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM265" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN265" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO265" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP265" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ265" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AR265" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AS265" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AT265" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AU265" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV265" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW265" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX265" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY265" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ265" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA265" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB265" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC265" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD265" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BE265" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF265" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BG265" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH265" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI265" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ265" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BK265" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BL265" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM265" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BN265" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO265" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP265" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="n">
+        <v>265</v>
+      </c>
+      <c r="B266" t="n">
+        <v>7778335</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="n">
+        <v>45892.29166666666</v>
+      </c>
+      <c r="F266" t="n">
+        <v>27</v>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Tokyo Verdy</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>Sanfrecce Hiroshima</t>
+        </is>
+      </c>
+      <c r="I266" t="n">
+        <v>0</v>
+      </c>
+      <c r="J266" t="n">
+        <v>1</v>
+      </c>
+      <c r="K266" t="n">
+        <v>1</v>
+      </c>
+      <c r="L266" t="n">
+        <v>0</v>
+      </c>
+      <c r="M266" t="n">
+        <v>3</v>
+      </c>
+      <c r="N266" t="n">
+        <v>3</v>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>['6', '62', '83']</t>
+        </is>
+      </c>
+      <c r="Q266" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R266" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S266" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T266" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U266" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V266" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W266" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X266" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="Y266" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z266" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AA266" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AB266" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AC266" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD266" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE266" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF266" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG266" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH266" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI266" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ266" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK266" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL266" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM266" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN266" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AO266" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AP266" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ266" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AR266" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AS266" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AT266" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AU266" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV266" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW266" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX266" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY266" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ266" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA266" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB266" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC266" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD266" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BE266" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF266" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BG266" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH266" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI266" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ266" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BK266" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BL266" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BM266" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BN266" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BO266" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BP266" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="n">
+        <v>266</v>
+      </c>
+      <c r="B267" t="n">
+        <v>7778337</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="n">
+        <v>45892.29166666666</v>
+      </c>
+      <c r="F267" t="n">
+        <v>27</v>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Albirex Niigata</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>Kashima Antlers</t>
+        </is>
+      </c>
+      <c r="I267" t="n">
+        <v>1</v>
+      </c>
+      <c r="J267" t="n">
+        <v>1</v>
+      </c>
+      <c r="K267" t="n">
+        <v>2</v>
+      </c>
+      <c r="L267" t="n">
+        <v>1</v>
+      </c>
+      <c r="M267" t="n">
+        <v>2</v>
+      </c>
+      <c r="N267" t="n">
+        <v>3</v>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>['17']</t>
+        </is>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>['4', '87']</t>
+        </is>
+      </c>
+      <c r="Q267" t="n">
+        <v>4</v>
+      </c>
+      <c r="R267" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S267" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T267" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U267" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V267" t="n">
+        <v>3</v>
+      </c>
+      <c r="W267" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X267" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y267" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z267" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AA267" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AB267" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AC267" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD267" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE267" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF267" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG267" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AH267" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AI267" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ267" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK267" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL267" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM267" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN267" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AO267" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP267" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AQ267" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AR267" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AS267" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AT267" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AU267" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV267" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW267" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX267" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY267" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ267" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA267" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB267" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC267" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD267" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BE267" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF267" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BG267" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH267" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BI267" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BJ267" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BK267" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BL267" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BM267" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BN267" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BO267" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BP267" t="n">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="n">
+        <v>267</v>
+      </c>
+      <c r="B268" t="n">
+        <v>7778338</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="n">
+        <v>45892.29166666666</v>
+      </c>
+      <c r="F268" t="n">
+        <v>27</v>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Nagoya Grampus</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>Kawasaki Frontale</t>
+        </is>
+      </c>
+      <c r="I268" t="n">
+        <v>2</v>
+      </c>
+      <c r="J268" t="n">
+        <v>2</v>
+      </c>
+      <c r="K268" t="n">
+        <v>4</v>
+      </c>
+      <c r="L268" t="n">
+        <v>3</v>
+      </c>
+      <c r="M268" t="n">
+        <v>4</v>
+      </c>
+      <c r="N268" t="n">
+        <v>7</v>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>['32', '45+3', '81']</t>
+        </is>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>['7', '17', '80', '90+5']</t>
+        </is>
+      </c>
+      <c r="Q268" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R268" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S268" t="n">
+        <v>3</v>
+      </c>
+      <c r="T268" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U268" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V268" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W268" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X268" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="Y268" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z268" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AA268" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB268" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AC268" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD268" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE268" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF268" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG268" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AH268" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI268" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ268" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK268" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL268" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM268" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN268" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO268" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AP268" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ268" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR268" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AS268" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AT268" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AU268" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV268" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW268" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX268" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY268" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ268" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA268" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB268" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC268" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD268" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BE268" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF268" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BG268" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH268" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI268" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ268" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK268" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BL268" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM268" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN268" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BO268" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BP268" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="n">
+        <v>268</v>
+      </c>
+      <c r="B269" t="n">
+        <v>7778339</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="n">
+        <v>45892.29166666666</v>
+      </c>
+      <c r="F269" t="n">
+        <v>27</v>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Gamba Osaka</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Yokohama</t>
+        </is>
+      </c>
+      <c r="I269" t="n">
+        <v>1</v>
+      </c>
+      <c r="J269" t="n">
+        <v>1</v>
+      </c>
+      <c r="K269" t="n">
+        <v>2</v>
+      </c>
+      <c r="L269" t="n">
+        <v>3</v>
+      </c>
+      <c r="M269" t="n">
+        <v>2</v>
+      </c>
+      <c r="N269" t="n">
+        <v>5</v>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>['45+4', '56', '81']</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>['41', '90+2']</t>
+        </is>
+      </c>
+      <c r="Q269" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R269" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S269" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T269" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U269" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V269" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="W269" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X269" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Y269" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z269" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AA269" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AB269" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AC269" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD269" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE269" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF269" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG269" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH269" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI269" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ269" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK269" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL269" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM269" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN269" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO269" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP269" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ269" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AR269" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AS269" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT269" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AU269" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV269" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW269" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX269" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY269" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ269" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA269" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB269" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC269" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD269" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BE269" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF269" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BG269" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BH269" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BI269" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BJ269" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BK269" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL269" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM269" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BN269" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BO269" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP269" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="n">
+        <v>269</v>
+      </c>
+      <c r="B270" t="n">
+        <v>7778340</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="n">
+        <v>45892.29166666666</v>
+      </c>
+      <c r="F270" t="n">
+        <v>27</v>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Cerezo Osaka</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>Vissel Kobe</t>
+        </is>
+      </c>
+      <c r="I270" t="n">
+        <v>1</v>
+      </c>
+      <c r="J270" t="n">
+        <v>0</v>
+      </c>
+      <c r="K270" t="n">
+        <v>1</v>
+      </c>
+      <c r="L270" t="n">
+        <v>1</v>
+      </c>
+      <c r="M270" t="n">
+        <v>1</v>
+      </c>
+      <c r="N270" t="n">
+        <v>2</v>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>['35']</t>
+        </is>
+      </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>['47']</t>
+        </is>
+      </c>
+      <c r="Q270" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R270" t="n">
+        <v>2</v>
+      </c>
+      <c r="S270" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T270" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U270" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V270" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="W270" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X270" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y270" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z270" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AA270" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AB270" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AC270" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD270" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE270" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF270" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG270" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AH270" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AI270" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AJ270" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AK270" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL270" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM270" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN270" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO270" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AP270" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AQ270" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR270" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AS270" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AT270" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AU270" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV270" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW270" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX270" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY270" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ270" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA270" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB270" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC270" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD270" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BE270" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF270" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BG270" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH270" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI270" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BJ270" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BK270" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BL270" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BM270" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BN270" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BO270" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP270" t="n">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="n">
+        <v>270</v>
+      </c>
+      <c r="B271" t="n">
+        <v>7778341</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="n">
+        <v>45892.29166666666</v>
+      </c>
+      <c r="F271" t="n">
+        <v>27</v>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Fagiano Okayama</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>Shonan Bellmare</t>
+        </is>
+      </c>
+      <c r="I271" t="n">
+        <v>0</v>
+      </c>
+      <c r="J271" t="n">
+        <v>0</v>
+      </c>
+      <c r="K271" t="n">
+        <v>0</v>
+      </c>
+      <c r="L271" t="n">
+        <v>1</v>
+      </c>
+      <c r="M271" t="n">
+        <v>0</v>
+      </c>
+      <c r="N271" t="n">
+        <v>1</v>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>['65']</t>
+        </is>
+      </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q271" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R271" t="n">
+        <v>2</v>
+      </c>
+      <c r="S271" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T271" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U271" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V271" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="W271" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X271" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Y271" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z271" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AA271" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AB271" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AC271" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD271" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE271" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF271" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG271" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AH271" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI271" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ271" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK271" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL271" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM271" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN271" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO271" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AP271" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ271" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AR271" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AS271" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AT271" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AU271" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV271" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW271" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX271" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY271" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ271" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA271" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB271" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC271" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD271" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BE271" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF271" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BG271" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH271" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="BI271" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BJ271" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BK271" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BL271" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BM271" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BN271" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BO271" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BP271" t="n">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="n">
+        <v>271</v>
+      </c>
+      <c r="B272" t="n">
+        <v>7778336</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="n">
+        <v>45892.3125</v>
+      </c>
+      <c r="F272" t="n">
+        <v>27</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Yokohama F. Marinos</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>Machida Zelvia</t>
+        </is>
+      </c>
+      <c r="I272" t="n">
+        <v>0</v>
+      </c>
+      <c r="J272" t="n">
+        <v>0</v>
+      </c>
+      <c r="K272" t="n">
+        <v>0</v>
+      </c>
+      <c r="L272" t="n">
+        <v>0</v>
+      </c>
+      <c r="M272" t="n">
+        <v>0</v>
+      </c>
+      <c r="N272" t="n">
+        <v>0</v>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q272" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R272" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S272" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T272" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U272" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V272" t="n">
+        <v>3</v>
+      </c>
+      <c r="W272" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X272" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y272" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z272" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AA272" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AB272" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AC272" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD272" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE272" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF272" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG272" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AH272" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AI272" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ272" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK272" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AL272" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM272" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN272" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO272" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AP272" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ272" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR272" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AS272" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AT272" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AU272" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV272" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW272" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX272" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY272" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ272" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA272" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB272" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC272" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD272" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BE272" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF272" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BG272" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH272" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI272" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BJ272" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BK272" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BL272" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM272" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BN272" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BO272" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP272" t="n">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
@@ -58478,13 +58478,13 @@
         <v>2.69</v>
       </c>
       <c r="AU266" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AV266" t="n">
         <v>4</v>
       </c>
       <c r="AW266" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AX266" t="n">
         <v>10</v>
@@ -58696,16 +58696,16 @@
         <v>2.66</v>
       </c>
       <c r="AU267" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV267" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW267" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX267" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY267" t="n">
         <v>8</v>
@@ -58914,13 +58914,13 @@
         <v>2.69</v>
       </c>
       <c r="AU268" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV268" t="n">
         <v>5</v>
       </c>
       <c r="AW268" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX268" t="n">
         <v>13</v>
@@ -59132,13 +59132,13 @@
         <v>2.58</v>
       </c>
       <c r="AU269" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV269" t="n">
         <v>6</v>
       </c>
       <c r="AW269" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX269" t="n">
         <v>9</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP272"/>
+  <dimension ref="A1:BP273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1786,7 +1786,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ19" t="n">
         <v>2</v>
@@ -5710,7 +5710,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR24" t="n">
         <v>0.65</v>
@@ -6797,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ29" t="n">
         <v>0.64</v>
@@ -7890,7 +7890,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR34" t="n">
         <v>1.86</v>
@@ -10285,7 +10285,7 @@
         <v>2</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ45" t="n">
         <v>0.79</v>
@@ -12250,7 +12250,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR54" t="n">
         <v>1.31</v>
@@ -15517,7 +15517,7 @@
         <v>1.67</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ69" t="n">
         <v>1.43</v>
@@ -19226,7 +19226,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR86" t="n">
         <v>1.52</v>
@@ -20313,7 +20313,7 @@
         <v>2</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ91" t="n">
         <v>1.79</v>
@@ -22932,7 +22932,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ103" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR103" t="n">
         <v>1.33</v>
@@ -23150,7 +23150,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR104" t="n">
         <v>1.4</v>
@@ -26635,7 +26635,7 @@
         <v>0.83</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ120" t="n">
         <v>0.87</v>
@@ -27071,7 +27071,7 @@
         <v>1.17</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ122" t="n">
         <v>0.93</v>
@@ -28164,7 +28164,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ127" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR127" t="n">
         <v>1.52</v>
@@ -31870,7 +31870,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR144" t="n">
         <v>1.22</v>
@@ -32521,7 +32521,7 @@
         <v>2</v>
       </c>
       <c r="AP147" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ147" t="n">
         <v>1.8</v>
@@ -34922,7 +34922,7 @@
         <v>1</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR158" t="n">
         <v>1.22</v>
@@ -39064,7 +39064,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ177" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR177" t="n">
         <v>1.27</v>
@@ -39279,7 +39279,7 @@
         <v>1.43</v>
       </c>
       <c r="AP178" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ178" t="n">
         <v>1.86</v>
@@ -42767,7 +42767,7 @@
         <v>1.1</v>
       </c>
       <c r="AP194" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ194" t="n">
         <v>1</v>
@@ -45168,7 +45168,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ205" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR205" t="n">
         <v>1.4</v>
@@ -46909,7 +46909,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP213" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ213" t="n">
         <v>0.62</v>
@@ -50615,7 +50615,7 @@
         <v>0.9</v>
       </c>
       <c r="AP230" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ230" t="n">
         <v>0.92</v>
@@ -52580,7 +52580,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ239" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR239" t="n">
         <v>1.27</v>
@@ -54103,7 +54103,7 @@
         <v>1.36</v>
       </c>
       <c r="AP246" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ246" t="n">
         <v>1.62</v>
@@ -54324,7 +54324,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ247" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR247" t="n">
         <v>1.28</v>
@@ -58478,22 +58478,22 @@
         <v>2.69</v>
       </c>
       <c r="AU266" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AV266" t="n">
         <v>4</v>
       </c>
       <c r="AW266" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX266" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY266" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ266" t="n">
         <v>15</v>
-      </c>
-      <c r="AX266" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY266" t="n">
-        <v>18</v>
-      </c>
-      <c r="AZ266" t="n">
-        <v>14</v>
       </c>
       <c r="BA266" t="n">
         <v>10</v>
@@ -58696,19 +58696,19 @@
         <v>2.66</v>
       </c>
       <c r="AU267" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV267" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW267" t="n">
         <v>5</v>
       </c>
       <c r="AX267" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY267" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ267" t="n">
         <v>13</v>
@@ -58914,13 +58914,13 @@
         <v>2.69</v>
       </c>
       <c r="AU268" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV268" t="n">
         <v>5</v>
       </c>
       <c r="AW268" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX268" t="n">
         <v>13</v>
@@ -59132,13 +59132,13 @@
         <v>2.58</v>
       </c>
       <c r="AU269" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV269" t="n">
         <v>6</v>
       </c>
       <c r="AW269" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX269" t="n">
         <v>9</v>
@@ -59795,13 +59795,13 @@
         <v>6</v>
       </c>
       <c r="AX272" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY272" t="n">
         <v>7</v>
       </c>
       <c r="AZ272" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA272" t="n">
         <v>2</v>
@@ -59850,6 +59850,224 @@
       </c>
       <c r="BP272" t="n">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="n">
+        <v>272</v>
+      </c>
+      <c r="B273" t="n">
+        <v>7778334</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="n">
+        <v>45893.29166666666</v>
+      </c>
+      <c r="F273" t="n">
+        <v>27</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>Kyoto Sanga</t>
+        </is>
+      </c>
+      <c r="I273" t="n">
+        <v>0</v>
+      </c>
+      <c r="J273" t="n">
+        <v>3</v>
+      </c>
+      <c r="K273" t="n">
+        <v>3</v>
+      </c>
+      <c r="L273" t="n">
+        <v>0</v>
+      </c>
+      <c r="M273" t="n">
+        <v>4</v>
+      </c>
+      <c r="N273" t="n">
+        <v>4</v>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>['8', '13', '45', '81']</t>
+        </is>
+      </c>
+      <c r="Q273" t="n">
+        <v>3</v>
+      </c>
+      <c r="R273" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="S273" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T273" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U273" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V273" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W273" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X273" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y273" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z273" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AA273" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB273" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AC273" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD273" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE273" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF273" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG273" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH273" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AI273" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ273" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK273" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AL273" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM273" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN273" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO273" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AP273" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ273" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR273" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AS273" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT273" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AU273" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV273" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW273" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX273" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY273" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ273" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA273" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB273" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC273" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD273" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BE273" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="BF273" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BG273" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH273" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="BI273" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BJ273" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BK273" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BL273" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BM273" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN273" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BO273" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="BP273" t="n">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
@@ -58487,13 +58487,13 @@
         <v>14</v>
       </c>
       <c r="AX266" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY266" t="n">
         <v>20</v>
       </c>
       <c r="AZ266" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA266" t="n">
         <v>10</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP273"/>
+  <dimension ref="A1:BP276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ4" t="n">
         <v>0.92</v>
@@ -3530,7 +3530,7 @@
         <v>1</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR14" t="n">
         <v>1.63</v>
@@ -3963,7 +3963,7 @@
         <v>1</v>
       </c>
       <c r="AP16" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ16" t="n">
         <v>0.92</v>
@@ -4838,7 +4838,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -5056,7 +5056,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR21" t="n">
         <v>0</v>
@@ -5707,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ24" t="n">
         <v>1.8</v>
@@ -6582,7 +6582,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR28" t="n">
         <v>0.67</v>
@@ -8105,7 +8105,7 @@
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ35" t="n">
         <v>1.38</v>
@@ -9634,7 +9634,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR42" t="n">
         <v>1.91</v>
@@ -9852,7 +9852,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR43" t="n">
         <v>1.61</v>
@@ -11157,7 +11157,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ49" t="n">
         <v>1.38</v>
@@ -13776,7 +13776,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ61" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR61" t="n">
         <v>1.58</v>
@@ -14212,7 +14212,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ63" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR63" t="n">
         <v>1.33</v>
@@ -14863,7 +14863,7 @@
         <v>2</v>
       </c>
       <c r="AP66" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ66" t="n">
         <v>1.86</v>
@@ -15956,7 +15956,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR71" t="n">
         <v>1.7</v>
@@ -16389,7 +16389,7 @@
         <v>2.33</v>
       </c>
       <c r="AP73" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ73" t="n">
         <v>1.79</v>
@@ -16610,7 +16610,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ74" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR74" t="n">
         <v>0.96</v>
@@ -17918,7 +17918,7 @@
         <v>1</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR80" t="n">
         <v>1.12</v>
@@ -19005,7 +19005,7 @@
         <v>0.25</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ85" t="n">
         <v>0.62</v>
@@ -20098,7 +20098,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ90" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR90" t="n">
         <v>1.77</v>
@@ -20534,7 +20534,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR92" t="n">
         <v>1.33</v>
@@ -21188,7 +21188,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ95" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR95" t="n">
         <v>1.36</v>
@@ -21839,7 +21839,7 @@
         <v>1</v>
       </c>
       <c r="AP98" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ98" t="n">
         <v>0.79</v>
@@ -22711,7 +22711,7 @@
         <v>1.67</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ102" t="n">
         <v>1.43</v>
@@ -24237,7 +24237,7 @@
         <v>2.6</v>
       </c>
       <c r="AP109" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ109" t="n">
         <v>2</v>
@@ -24894,7 +24894,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ112" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR112" t="n">
         <v>1.65</v>
@@ -25112,7 +25112,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ113" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR113" t="n">
         <v>1.32</v>
@@ -25763,7 +25763,7 @@
         <v>0.5</v>
       </c>
       <c r="AP116" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ116" t="n">
         <v>0.62</v>
@@ -25984,7 +25984,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR117" t="n">
         <v>1.46</v>
@@ -27728,7 +27728,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ125" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR125" t="n">
         <v>1.39</v>
@@ -29469,10 +29469,10 @@
         <v>0.8</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ133" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR133" t="n">
         <v>1.49</v>
@@ -30126,7 +30126,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ136" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR136" t="n">
         <v>1.29</v>
@@ -30341,7 +30341,7 @@
         <v>0.67</v>
       </c>
       <c r="AP137" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ137" t="n">
         <v>1</v>
@@ -30559,7 +30559,7 @@
         <v>1</v>
       </c>
       <c r="AP138" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ138" t="n">
         <v>1</v>
@@ -31216,7 +31216,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ141" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR141" t="n">
         <v>1.22</v>
@@ -32742,7 +32742,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR148" t="n">
         <v>1.29</v>
@@ -33393,7 +33393,7 @@
         <v>0.5</v>
       </c>
       <c r="AP151" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ151" t="n">
         <v>0.64</v>
@@ -34050,7 +34050,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ154" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR154" t="n">
         <v>1.78</v>
@@ -35137,7 +35137,7 @@
         <v>1</v>
       </c>
       <c r="AP159" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ159" t="n">
         <v>0.87</v>
@@ -35576,7 +35576,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ161" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR161" t="n">
         <v>1.55</v>
@@ -40154,7 +40154,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ182" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR182" t="n">
         <v>1.29</v>
@@ -40372,7 +40372,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ183" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR183" t="n">
         <v>1.43</v>
@@ -41241,7 +41241,7 @@
         <v>1</v>
       </c>
       <c r="AP187" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ187" t="n">
         <v>0.92</v>
@@ -41462,7 +41462,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ188" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR188" t="n">
         <v>1.32</v>
@@ -42988,7 +42988,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ195" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR195" t="n">
         <v>1.34</v>
@@ -43203,7 +43203,7 @@
         <v>0.6</v>
       </c>
       <c r="AP196" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ196" t="n">
         <v>0.64</v>
@@ -44514,7 +44514,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ202" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR202" t="n">
         <v>1.77</v>
@@ -44732,7 +44732,7 @@
         <v>1</v>
       </c>
       <c r="AQ203" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR203" t="n">
         <v>1.22</v>
@@ -46476,7 +46476,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ211" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR211" t="n">
         <v>1.49</v>
@@ -47130,7 +47130,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ214" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR214" t="n">
         <v>1.28</v>
@@ -47563,7 +47563,7 @@
         <v>0.91</v>
       </c>
       <c r="AP216" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ216" t="n">
         <v>0.87</v>
@@ -48435,7 +48435,7 @@
         <v>1.7</v>
       </c>
       <c r="AP220" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ220" t="n">
         <v>1.86</v>
@@ -49528,7 +49528,7 @@
         <v>1</v>
       </c>
       <c r="AQ225" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR225" t="n">
         <v>1.15</v>
@@ -49746,7 +49746,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ226" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR226" t="n">
         <v>1.33</v>
@@ -49961,7 +49961,7 @@
         <v>0.73</v>
       </c>
       <c r="AP227" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ227" t="n">
         <v>0.62</v>
@@ -50397,7 +50397,7 @@
         <v>1.1</v>
       </c>
       <c r="AP229" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ229" t="n">
         <v>0.79</v>
@@ -53452,7 +53452,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ243" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR243" t="n">
         <v>1.18</v>
@@ -54542,7 +54542,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ248" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR248" t="n">
         <v>1.55</v>
@@ -55632,7 +55632,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ253" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AR253" t="n">
         <v>1.33</v>
@@ -55847,7 +55847,7 @@
         <v>0.45</v>
       </c>
       <c r="AP254" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AQ254" t="n">
         <v>0.62</v>
@@ -57155,10 +57155,10 @@
         <v>1</v>
       </c>
       <c r="AP260" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ260" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR260" t="n">
         <v>1.49</v>
@@ -60068,6 +60068,660 @@
       </c>
       <c r="BP273" t="n">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="n">
+        <v>273</v>
+      </c>
+      <c r="B274" t="n">
+        <v>7778346</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="n">
+        <v>45899.25</v>
+      </c>
+      <c r="F274" t="n">
+        <v>28</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Yokohama</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>Tokyo Verdy</t>
+        </is>
+      </c>
+      <c r="I274" t="n">
+        <v>0</v>
+      </c>
+      <c r="J274" t="n">
+        <v>0</v>
+      </c>
+      <c r="K274" t="n">
+        <v>0</v>
+      </c>
+      <c r="L274" t="n">
+        <v>0</v>
+      </c>
+      <c r="M274" t="n">
+        <v>0</v>
+      </c>
+      <c r="N274" t="n">
+        <v>0</v>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q274" t="n">
+        <v>4</v>
+      </c>
+      <c r="R274" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="S274" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="T274" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="U274" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="V274" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="W274" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X274" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y274" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z274" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AA274" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AB274" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AC274" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD274" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AE274" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF274" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG274" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH274" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI274" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ274" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AK274" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AL274" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AM274" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN274" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO274" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP274" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ274" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AR274" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AS274" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AT274" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AU274" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV274" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW274" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX274" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY274" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ274" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA274" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB274" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC274" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD274" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BE274" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF274" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BG274" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH274" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI274" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BJ274" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BK274" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BL274" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BM274" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BN274" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BO274" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP274" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="n">
+        <v>274</v>
+      </c>
+      <c r="B275" t="n">
+        <v>7778350</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="n">
+        <v>45899.29166666666</v>
+      </c>
+      <c r="F275" t="n">
+        <v>28</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Kyoto Sanga</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>Fagiano Okayama</t>
+        </is>
+      </c>
+      <c r="I275" t="n">
+        <v>3</v>
+      </c>
+      <c r="J275" t="n">
+        <v>0</v>
+      </c>
+      <c r="K275" t="n">
+        <v>3</v>
+      </c>
+      <c r="L275" t="n">
+        <v>5</v>
+      </c>
+      <c r="M275" t="n">
+        <v>0</v>
+      </c>
+      <c r="N275" t="n">
+        <v>5</v>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>['15', '20', '30', '80', '90+2']</t>
+        </is>
+      </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q275" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="R275" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S275" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="T275" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U275" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="V275" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="W275" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X275" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y275" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z275" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA275" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB275" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AC275" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD275" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE275" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF275" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AG275" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AH275" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AI275" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AJ275" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AK275" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL275" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM275" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AN275" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO275" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP275" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ275" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AR275" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS275" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AT275" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AU275" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV275" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW275" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX275" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY275" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ275" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA275" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB275" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC275" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD275" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BE275" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF275" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BG275" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH275" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="BI275" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BJ275" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BK275" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BL275" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM275" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BN275" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BO275" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP275" t="n">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="n">
+        <v>275</v>
+      </c>
+      <c r="B276" t="n">
+        <v>7778352</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="n">
+        <v>45899.29166666666</v>
+      </c>
+      <c r="F276" t="n">
+        <v>28</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Vissel Kobe</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>Yokohama F. Marinos</t>
+        </is>
+      </c>
+      <c r="I276" t="n">
+        <v>1</v>
+      </c>
+      <c r="J276" t="n">
+        <v>0</v>
+      </c>
+      <c r="K276" t="n">
+        <v>1</v>
+      </c>
+      <c r="L276" t="n">
+        <v>1</v>
+      </c>
+      <c r="M276" t="n">
+        <v>0</v>
+      </c>
+      <c r="N276" t="n">
+        <v>1</v>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>['37']</t>
+        </is>
+      </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q276" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R276" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S276" t="n">
+        <v>5</v>
+      </c>
+      <c r="T276" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U276" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="V276" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W276" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X276" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y276" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z276" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA276" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="AB276" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC276" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD276" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="AE276" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF276" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AG276" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AH276" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AI276" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AJ276" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AK276" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL276" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AM276" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AN276" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO276" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AP276" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ276" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AR276" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS276" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AT276" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AU276" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV276" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW276" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX276" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY276" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ276" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA276" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB276" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC276" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD276" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BE276" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF276" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BG276" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH276" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI276" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BJ276" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BK276" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BL276" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BM276" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BN276" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BO276" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BP276" t="n">
+        <v>1.61</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP276"/>
+  <dimension ref="A1:BP283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1568,7 +1568,7 @@
         <v>1</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ8" t="n">
         <v>0.64</v>
@@ -2437,10 +2437,10 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2658,7 +2658,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.8</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ13" t="n">
         <v>1.43</v>
@@ -3745,10 +3745,10 @@
         <v>1</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ17" t="n">
         <v>0.79</v>
@@ -4402,7 +4402,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR18" t="n">
         <v>1.94</v>
@@ -4620,7 +4620,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ19" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -5492,7 +5492,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR23" t="n">
         <v>1.11</v>
@@ -5925,10 +5925,10 @@
         <v>3</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR25" t="n">
         <v>1.44</v>
@@ -6143,7 +6143,7 @@
         <v>1</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ26" t="n">
         <v>0.92</v>
@@ -6364,7 +6364,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR27" t="n">
         <v>1.94</v>
@@ -7015,7 +7015,7 @@
         <v>3</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ30" t="n">
         <v>1</v>
@@ -7672,7 +7672,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR33" t="n">
         <v>1.73</v>
@@ -7887,7 +7887,7 @@
         <v>0.5</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ34" t="n">
         <v>1.8</v>
@@ -8108,7 +8108,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR35" t="n">
         <v>1.34</v>
@@ -8326,7 +8326,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR36" t="n">
         <v>0.95</v>
@@ -8759,10 +8759,10 @@
         <v>3</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ38" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AR38" t="n">
         <v>1.22</v>
@@ -9413,7 +9413,7 @@
         <v>3</v>
       </c>
       <c r="AP41" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ41" t="n">
         <v>1.79</v>
@@ -9631,7 +9631,7 @@
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ42" t="n">
         <v>1.15</v>
@@ -10506,7 +10506,7 @@
         <v>1</v>
       </c>
       <c r="AQ46" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AR46" t="n">
         <v>1.34</v>
@@ -10721,7 +10721,7 @@
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ47" t="n">
         <v>0.64</v>
@@ -10939,10 +10939,10 @@
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR48" t="n">
         <v>1.32</v>
@@ -11160,7 +11160,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR49" t="n">
         <v>1.45</v>
@@ -11596,7 +11596,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR51" t="n">
         <v>0.89</v>
@@ -12032,7 +12032,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR53" t="n">
         <v>0.99</v>
@@ -12247,7 +12247,7 @@
         <v>1.33</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ54" t="n">
         <v>1.8</v>
@@ -12468,7 +12468,7 @@
         <v>1</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR55" t="n">
         <v>1.11</v>
@@ -13337,7 +13337,7 @@
         <v>1</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ59" t="n">
         <v>1.8</v>
@@ -13555,7 +13555,7 @@
         <v>0.75</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ60" t="n">
         <v>0.92</v>
@@ -13991,7 +13991,7 @@
         <v>1.67</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ62" t="n">
         <v>0.79</v>
@@ -14209,7 +14209,7 @@
         <v>1.33</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ63" t="n">
         <v>0.93</v>
@@ -14430,7 +14430,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ64" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR64" t="n">
         <v>1.34</v>
@@ -14645,7 +14645,7 @@
         <v>0.5</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ65" t="n">
         <v>0.62</v>
@@ -14866,7 +14866,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR66" t="n">
         <v>1.3</v>
@@ -15302,7 +15302,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ68" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AR68" t="n">
         <v>1.38</v>
@@ -15738,7 +15738,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR70" t="n">
         <v>1.34</v>
@@ -15953,7 +15953,7 @@
         <v>0</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ71" t="n">
         <v>1.15</v>
@@ -16174,7 +16174,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ72" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AR72" t="n">
         <v>1.5</v>
@@ -16607,7 +16607,7 @@
         <v>0</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ74" t="n">
         <v>0.79</v>
@@ -16828,7 +16828,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR75" t="n">
         <v>1.32</v>
@@ -17043,7 +17043,7 @@
         <v>1.25</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ76" t="n">
         <v>0.79</v>
@@ -17264,7 +17264,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ77" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR77" t="n">
         <v>1.15</v>
@@ -17697,7 +17697,7 @@
         <v>1.33</v>
       </c>
       <c r="AP79" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ79" t="n">
         <v>0.93</v>
@@ -18136,7 +18136,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ81" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR81" t="n">
         <v>1.5</v>
@@ -19008,7 +19008,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ85" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR85" t="n">
         <v>1.26</v>
@@ -19441,10 +19441,10 @@
         <v>1</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ87" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR87" t="n">
         <v>1.21</v>
@@ -19659,7 +19659,7 @@
         <v>0.25</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ88" t="n">
         <v>0.64</v>
@@ -20095,7 +20095,7 @@
         <v>0</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ90" t="n">
         <v>0.79</v>
@@ -20749,7 +20749,7 @@
         <v>1.8</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ93" t="n">
         <v>1.43</v>
@@ -21621,10 +21621,10 @@
         <v>1</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR97" t="n">
         <v>1.78</v>
@@ -22929,7 +22929,7 @@
         <v>2</v>
       </c>
       <c r="AP103" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ103" t="n">
         <v>1.8</v>
@@ -23368,7 +23368,7 @@
         <v>1</v>
       </c>
       <c r="AQ105" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR105" t="n">
         <v>1.08</v>
@@ -23586,7 +23586,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ106" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR106" t="n">
         <v>1.41</v>
@@ -23801,10 +23801,10 @@
         <v>2.25</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR107" t="n">
         <v>1.27</v>
@@ -24019,10 +24019,10 @@
         <v>1.33</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR108" t="n">
         <v>1.28</v>
@@ -24240,7 +24240,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ109" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AR109" t="n">
         <v>1.43</v>
@@ -24455,10 +24455,10 @@
         <v>0.8</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ110" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR110" t="n">
         <v>1.93</v>
@@ -24673,7 +24673,7 @@
         <v>1.8</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ111" t="n">
         <v>1.79</v>
@@ -24891,7 +24891,7 @@
         <v>1.2</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ112" t="n">
         <v>0.93</v>
@@ -25109,7 +25109,7 @@
         <v>0.2</v>
       </c>
       <c r="AP113" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ113" t="n">
         <v>0.79</v>
@@ -26417,10 +26417,10 @@
         <v>1</v>
       </c>
       <c r="AP119" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR119" t="n">
         <v>1.3</v>
@@ -26638,7 +26638,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ120" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR120" t="n">
         <v>1.18</v>
@@ -26853,10 +26853,10 @@
         <v>0.8</v>
       </c>
       <c r="AP121" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ121" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR121" t="n">
         <v>1.28</v>
@@ -27292,7 +27292,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ123" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR123" t="n">
         <v>1.43</v>
@@ -27510,7 +27510,7 @@
         <v>1</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR124" t="n">
         <v>1.14</v>
@@ -27943,7 +27943,7 @@
         <v>2</v>
       </c>
       <c r="AP126" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ126" t="n">
         <v>1.79</v>
@@ -28379,10 +28379,10 @@
         <v>1.8</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR128" t="n">
         <v>1.44</v>
@@ -28597,10 +28597,10 @@
         <v>2.17</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ129" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AR129" t="n">
         <v>1.94</v>
@@ -28818,7 +28818,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR130" t="n">
         <v>1.47</v>
@@ -29033,7 +29033,7 @@
         <v>0.14</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ131" t="n">
         <v>0.64</v>
@@ -29254,7 +29254,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ132" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR132" t="n">
         <v>1.39</v>
@@ -29908,7 +29908,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ135" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AR135" t="n">
         <v>1.55</v>
@@ -30123,7 +30123,7 @@
         <v>1.43</v>
       </c>
       <c r="AP136" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ136" t="n">
         <v>0.93</v>
@@ -30780,7 +30780,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR139" t="n">
         <v>1.5</v>
@@ -30995,10 +30995,10 @@
         <v>0.71</v>
       </c>
       <c r="AP140" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ140" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR140" t="n">
         <v>1.23</v>
@@ -31213,7 +31213,7 @@
         <v>0.67</v>
       </c>
       <c r="AP141" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ141" t="n">
         <v>1.15</v>
@@ -31431,7 +31431,7 @@
         <v>1.43</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ142" t="n">
         <v>0.93</v>
@@ -32085,10 +32085,10 @@
         <v>0.8</v>
       </c>
       <c r="AP145" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ145" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR145" t="n">
         <v>1.35</v>
@@ -32306,7 +32306,7 @@
         <v>1</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR146" t="n">
         <v>1.13</v>
@@ -32739,7 +32739,7 @@
         <v>0.71</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ148" t="n">
         <v>1.15</v>
@@ -32957,10 +32957,10 @@
         <v>2</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ149" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AR149" t="n">
         <v>1.17</v>
@@ -33832,7 +33832,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR153" t="n">
         <v>1.46</v>
@@ -34047,7 +34047,7 @@
         <v>0.17</v>
       </c>
       <c r="AP154" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ154" t="n">
         <v>0.79</v>
@@ -34701,7 +34701,7 @@
         <v>0.33</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ157" t="n">
         <v>0.62</v>
@@ -35140,7 +35140,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ159" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR159" t="n">
         <v>1.6</v>
@@ -36227,7 +36227,7 @@
         <v>0.29</v>
       </c>
       <c r="AP164" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ164" t="n">
         <v>0.62</v>
@@ -36445,10 +36445,10 @@
         <v>1.14</v>
       </c>
       <c r="AP165" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ165" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR165" t="n">
         <v>1.24</v>
@@ -36663,7 +36663,7 @@
         <v>1.25</v>
       </c>
       <c r="AP166" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ166" t="n">
         <v>1</v>
@@ -36884,7 +36884,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ167" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR167" t="n">
         <v>1.4</v>
@@ -37099,7 +37099,7 @@
         <v>1</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ168" t="n">
         <v>0.92</v>
@@ -37535,10 +37535,10 @@
         <v>1.25</v>
       </c>
       <c r="AP170" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ170" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR170" t="n">
         <v>1.74</v>
@@ -37753,7 +37753,7 @@
         <v>1</v>
       </c>
       <c r="AP171" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ171" t="n">
         <v>0.92</v>
@@ -37974,7 +37974,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ172" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AR172" t="n">
         <v>1.53</v>
@@ -38192,7 +38192,7 @@
         <v>1</v>
       </c>
       <c r="AQ173" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR173" t="n">
         <v>1.26</v>
@@ -38843,7 +38843,7 @@
         <v>1.86</v>
       </c>
       <c r="AP176" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ176" t="n">
         <v>1.8</v>
@@ -39282,7 +39282,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ178" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR178" t="n">
         <v>1.36</v>
@@ -39497,10 +39497,10 @@
         <v>0.89</v>
       </c>
       <c r="AP179" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ179" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR179" t="n">
         <v>1.56</v>
@@ -39715,7 +39715,7 @@
         <v>1.11</v>
       </c>
       <c r="AP180" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ180" t="n">
         <v>1</v>
@@ -39933,10 +39933,10 @@
         <v>1</v>
       </c>
       <c r="AP181" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ181" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR181" t="n">
         <v>1.34</v>
@@ -40587,7 +40587,7 @@
         <v>1.63</v>
       </c>
       <c r="AP184" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ184" t="n">
         <v>1.8</v>
@@ -41026,7 +41026,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ186" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR186" t="n">
         <v>1.45</v>
@@ -41244,7 +41244,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ187" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR187" t="n">
         <v>1.45</v>
@@ -41459,7 +41459,7 @@
         <v>0.63</v>
       </c>
       <c r="AP188" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ188" t="n">
         <v>1.15</v>
@@ -41677,7 +41677,7 @@
         <v>1.11</v>
       </c>
       <c r="AP189" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ189" t="n">
         <v>0.93</v>
@@ -41895,7 +41895,7 @@
         <v>0.63</v>
       </c>
       <c r="AP190" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ190" t="n">
         <v>0.62</v>
@@ -42113,10 +42113,10 @@
         <v>1.8</v>
       </c>
       <c r="AP191" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ191" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AR191" t="n">
         <v>1.3</v>
@@ -42334,7 +42334,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ192" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR192" t="n">
         <v>1.46</v>
@@ -43424,7 +43424,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ197" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR197" t="n">
         <v>1.48</v>
@@ -43857,10 +43857,10 @@
         <v>0.9</v>
       </c>
       <c r="AP199" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ199" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR199" t="n">
         <v>1.23</v>
@@ -44078,7 +44078,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ200" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR200" t="n">
         <v>1.37</v>
@@ -44296,7 +44296,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ201" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR201" t="n">
         <v>1.36</v>
@@ -44511,7 +44511,7 @@
         <v>1.1</v>
       </c>
       <c r="AP202" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ202" t="n">
         <v>0.93</v>
@@ -44947,7 +44947,7 @@
         <v>1</v>
       </c>
       <c r="AP204" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ204" t="n">
         <v>0.93</v>
@@ -45165,7 +45165,7 @@
         <v>1.73</v>
       </c>
       <c r="AP205" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ205" t="n">
         <v>1.8</v>
@@ -45383,7 +45383,7 @@
         <v>1.78</v>
       </c>
       <c r="AP206" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ206" t="n">
         <v>1.8</v>
@@ -45604,7 +45604,7 @@
         <v>1</v>
       </c>
       <c r="AQ207" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR207" t="n">
         <v>1.14</v>
@@ -45822,7 +45822,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ208" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR208" t="n">
         <v>1.52</v>
@@ -46037,10 +46037,10 @@
         <v>0.8</v>
       </c>
       <c r="AP209" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ209" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR209" t="n">
         <v>1.45</v>
@@ -46258,7 +46258,7 @@
         <v>1</v>
       </c>
       <c r="AQ210" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR210" t="n">
         <v>1.24</v>
@@ -46691,7 +46691,7 @@
         <v>2</v>
       </c>
       <c r="AP212" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ212" t="n">
         <v>1.79</v>
@@ -47127,7 +47127,7 @@
         <v>0.44</v>
       </c>
       <c r="AP214" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ214" t="n">
         <v>0.79</v>
@@ -47566,7 +47566,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ216" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR216" t="n">
         <v>1.47</v>
@@ -48220,7 +48220,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ219" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AR219" t="n">
         <v>1.4</v>
@@ -48438,7 +48438,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ220" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR220" t="n">
         <v>1.71</v>
@@ -48874,7 +48874,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ222" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR222" t="n">
         <v>1.41</v>
@@ -49089,10 +49089,10 @@
         <v>1</v>
       </c>
       <c r="AP223" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ223" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR223" t="n">
         <v>1.46</v>
@@ -49307,10 +49307,10 @@
         <v>1.5</v>
       </c>
       <c r="AP224" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ224" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR224" t="n">
         <v>1.42</v>
@@ -49743,7 +49743,7 @@
         <v>1</v>
       </c>
       <c r="AP226" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ226" t="n">
         <v>0.93</v>
@@ -49964,7 +49964,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ227" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR227" t="n">
         <v>1.47</v>
@@ -50179,10 +50179,10 @@
         <v>0.83</v>
       </c>
       <c r="AP228" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ228" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR228" t="n">
         <v>1.7</v>
@@ -50833,7 +50833,7 @@
         <v>1.09</v>
       </c>
       <c r="AP231" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ231" t="n">
         <v>1</v>
@@ -51272,7 +51272,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ233" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AR233" t="n">
         <v>1.14</v>
@@ -51487,7 +51487,7 @@
         <v>0.5</v>
       </c>
       <c r="AP234" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ234" t="n">
         <v>0.62</v>
@@ -51926,7 +51926,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ236" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR236" t="n">
         <v>1.43</v>
@@ -52795,7 +52795,7 @@
         <v>1</v>
       </c>
       <c r="AP240" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ240" t="n">
         <v>0.79</v>
@@ -53013,10 +53013,10 @@
         <v>1.3</v>
       </c>
       <c r="AP241" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ241" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR241" t="n">
         <v>1.37</v>
@@ -53667,10 +53667,10 @@
         <v>1.27</v>
       </c>
       <c r="AP244" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ244" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR244" t="n">
         <v>1.46</v>
@@ -54106,7 +54106,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ246" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR246" t="n">
         <v>1.5</v>
@@ -54321,7 +54321,7 @@
         <v>1.62</v>
       </c>
       <c r="AP247" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ247" t="n">
         <v>1.8</v>
@@ -54975,7 +54975,7 @@
         <v>0.92</v>
       </c>
       <c r="AP250" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ250" t="n">
         <v>0.79</v>
@@ -55193,10 +55193,10 @@
         <v>0.67</v>
       </c>
       <c r="AP251" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ251" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR251" t="n">
         <v>1.73</v>
@@ -55414,7 +55414,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ252" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AR252" t="n">
         <v>1.48</v>
@@ -55629,7 +55629,7 @@
         <v>0.67</v>
       </c>
       <c r="AP253" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ253" t="n">
         <v>0.79</v>
@@ -56068,7 +56068,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ255" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR255" t="n">
         <v>1.6</v>
@@ -56283,7 +56283,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP256" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ256" t="n">
         <v>0.64</v>
@@ -56719,10 +56719,10 @@
         <v>0.92</v>
       </c>
       <c r="AP258" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ258" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR258" t="n">
         <v>1.29</v>
@@ -57812,7 +57812,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ263" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AR263" t="n">
         <v>1.39</v>
@@ -58027,7 +58027,7 @@
         <v>1</v>
       </c>
       <c r="AP264" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ264" t="n">
         <v>0.92</v>
@@ -58466,7 +58466,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ266" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AR266" t="n">
         <v>1.17</v>
@@ -58684,7 +58684,7 @@
         <v>0.86</v>
       </c>
       <c r="AQ267" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR267" t="n">
         <v>1.41</v>
@@ -58899,7 +58899,7 @@
         <v>1.31</v>
       </c>
       <c r="AP268" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ268" t="n">
         <v>1.43</v>
@@ -59335,7 +59335,7 @@
         <v>1.86</v>
       </c>
       <c r="AP270" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AQ270" t="n">
         <v>1.8</v>
@@ -59774,7 +59774,7 @@
         <v>1</v>
       </c>
       <c r="AQ272" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AR272" t="n">
         <v>1.27</v>
@@ -60722,6 +60722,1532 @@
       </c>
       <c r="BP276" t="n">
         <v>1.61</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="n">
+        <v>276</v>
+      </c>
+      <c r="B277" t="n">
+        <v>7778348</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="n">
+        <v>45900.27083333334</v>
+      </c>
+      <c r="F277" t="n">
+        <v>28</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Shimizu S-Pulse</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>Kashima Antlers</t>
+        </is>
+      </c>
+      <c r="I277" t="n">
+        <v>1</v>
+      </c>
+      <c r="J277" t="n">
+        <v>0</v>
+      </c>
+      <c r="K277" t="n">
+        <v>1</v>
+      </c>
+      <c r="L277" t="n">
+        <v>1</v>
+      </c>
+      <c r="M277" t="n">
+        <v>1</v>
+      </c>
+      <c r="N277" t="n">
+        <v>2</v>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>['20']</t>
+        </is>
+      </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>['74']</t>
+        </is>
+      </c>
+      <c r="Q277" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R277" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S277" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T277" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U277" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="V277" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="W277" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X277" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="Y277" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z277" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AA277" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB277" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AC277" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD277" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE277" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF277" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG277" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AH277" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI277" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ277" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK277" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL277" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM277" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN277" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AO277" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AP277" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AQ277" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR277" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AS277" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AT277" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU277" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV277" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW277" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX277" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY277" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ277" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA277" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB277" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC277" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD277" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BE277" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF277" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BG277" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH277" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="BI277" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ277" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BK277" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BL277" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BM277" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN277" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO277" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BP277" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="n">
+        <v>277</v>
+      </c>
+      <c r="B278" t="n">
+        <v>7778347</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="n">
+        <v>45900.29166666666</v>
+      </c>
+      <c r="F278" t="n">
+        <v>28</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Shonan Bellmare</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>Gamba Osaka</t>
+        </is>
+      </c>
+      <c r="I278" t="n">
+        <v>3</v>
+      </c>
+      <c r="J278" t="n">
+        <v>1</v>
+      </c>
+      <c r="K278" t="n">
+        <v>4</v>
+      </c>
+      <c r="L278" t="n">
+        <v>4</v>
+      </c>
+      <c r="M278" t="n">
+        <v>5</v>
+      </c>
+      <c r="N278" t="n">
+        <v>9</v>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>['13', '37', '45+4', '90+10']</t>
+        </is>
+      </c>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>['40', '49', '53', '88', '90+7']</t>
+        </is>
+      </c>
+      <c r="Q278" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="R278" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="S278" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T278" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="U278" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V278" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W278" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X278" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="Y278" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z278" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA278" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AB278" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AC278" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD278" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE278" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF278" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG278" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AH278" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AI278" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ278" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AK278" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL278" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM278" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN278" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AO278" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AP278" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ278" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR278" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AS278" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AT278" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU278" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV278" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW278" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX278" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY278" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ278" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA278" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB278" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC278" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD278" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BE278" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF278" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BG278" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH278" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI278" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ278" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BK278" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BL278" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM278" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BN278" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BO278" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BP278" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="n">
+        <v>278</v>
+      </c>
+      <c r="B279" t="n">
+        <v>7778349</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="n">
+        <v>45900.29166666666</v>
+      </c>
+      <c r="F279" t="n">
+        <v>28</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Nagoya Grampus</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="I279" t="n">
+        <v>0</v>
+      </c>
+      <c r="J279" t="n">
+        <v>0</v>
+      </c>
+      <c r="K279" t="n">
+        <v>0</v>
+      </c>
+      <c r="L279" t="n">
+        <v>1</v>
+      </c>
+      <c r="M279" t="n">
+        <v>1</v>
+      </c>
+      <c r="N279" t="n">
+        <v>2</v>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>['65']</t>
+        </is>
+      </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>['82']</t>
+        </is>
+      </c>
+      <c r="Q279" t="n">
+        <v>3</v>
+      </c>
+      <c r="R279" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S279" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T279" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U279" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="V279" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="W279" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X279" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="Y279" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z279" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA279" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AB279" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AC279" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD279" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE279" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF279" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG279" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AH279" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI279" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ279" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AK279" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL279" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM279" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN279" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AO279" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP279" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AQ279" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AR279" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AS279" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AT279" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AU279" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV279" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW279" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX279" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY279" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ279" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA279" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB279" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC279" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD279" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BE279" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF279" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BG279" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH279" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="BI279" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BJ279" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BK279" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BL279" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BM279" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BN279" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BO279" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BP279" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="n">
+        <v>279</v>
+      </c>
+      <c r="B280" t="n">
+        <v>7778351</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="n">
+        <v>45900.29166666666</v>
+      </c>
+      <c r="F280" t="n">
+        <v>28</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Cerezo Osaka</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>Sanfrecce Hiroshima</t>
+        </is>
+      </c>
+      <c r="I280" t="n">
+        <v>1</v>
+      </c>
+      <c r="J280" t="n">
+        <v>0</v>
+      </c>
+      <c r="K280" t="n">
+        <v>1</v>
+      </c>
+      <c r="L280" t="n">
+        <v>1</v>
+      </c>
+      <c r="M280" t="n">
+        <v>1</v>
+      </c>
+      <c r="N280" t="n">
+        <v>2</v>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>['35']</t>
+        </is>
+      </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>['72']</t>
+        </is>
+      </c>
+      <c r="Q280" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R280" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="S280" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T280" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U280" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="V280" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="W280" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X280" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="Y280" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z280" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA280" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AB280" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AC280" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD280" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE280" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF280" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG280" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AH280" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AI280" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ280" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AK280" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL280" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM280" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN280" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AO280" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AP280" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ280" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR280" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AS280" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AT280" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AU280" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV280" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW280" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX280" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY280" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ280" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA280" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB280" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC280" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD280" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BE280" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="BF280" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BG280" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH280" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="BI280" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BJ280" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BK280" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BL280" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BM280" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BN280" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BO280" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BP280" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="n">
+        <v>280</v>
+      </c>
+      <c r="B281" t="n">
+        <v>7778344</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="n">
+        <v>45900.29166666666</v>
+      </c>
+      <c r="F281" t="n">
+        <v>28</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Kashiwa Reysol</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>Avispa Fukuoka</t>
+        </is>
+      </c>
+      <c r="I281" t="n">
+        <v>1</v>
+      </c>
+      <c r="J281" t="n">
+        <v>1</v>
+      </c>
+      <c r="K281" t="n">
+        <v>2</v>
+      </c>
+      <c r="L281" t="n">
+        <v>2</v>
+      </c>
+      <c r="M281" t="n">
+        <v>1</v>
+      </c>
+      <c r="N281" t="n">
+        <v>3</v>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>['45+5', '76']</t>
+        </is>
+      </c>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>['34']</t>
+        </is>
+      </c>
+      <c r="Q281" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="R281" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="S281" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T281" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U281" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V281" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="W281" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X281" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y281" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z281" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AA281" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AB281" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AC281" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD281" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE281" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF281" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AG281" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH281" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI281" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ281" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK281" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL281" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM281" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN281" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO281" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AP281" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ281" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR281" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS281" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AT281" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AU281" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV281" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW281" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX281" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY281" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ281" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA281" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB281" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC281" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD281" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BE281" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="BF281" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="BG281" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH281" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="BI281" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ281" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BK281" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BL281" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BM281" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BN281" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO281" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BP281" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="n">
+        <v>281</v>
+      </c>
+      <c r="B282" t="n">
+        <v>7778343</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="n">
+        <v>45900.29166666666</v>
+      </c>
+      <c r="F282" t="n">
+        <v>28</v>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Urawa Reds</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>Albirex Niigata</t>
+        </is>
+      </c>
+      <c r="I282" t="n">
+        <v>1</v>
+      </c>
+      <c r="J282" t="n">
+        <v>0</v>
+      </c>
+      <c r="K282" t="n">
+        <v>1</v>
+      </c>
+      <c r="L282" t="n">
+        <v>1</v>
+      </c>
+      <c r="M282" t="n">
+        <v>0</v>
+      </c>
+      <c r="N282" t="n">
+        <v>1</v>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>['30']</t>
+        </is>
+      </c>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q282" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R282" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S282" t="n">
+        <v>5</v>
+      </c>
+      <c r="T282" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="U282" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V282" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="W282" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X282" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="Y282" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z282" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA282" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AB282" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC282" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD282" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE282" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF282" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG282" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AH282" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AI282" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ282" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK282" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL282" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM282" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN282" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AO282" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AP282" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AQ282" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AR282" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AS282" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AT282" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AU282" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV282" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW282" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX282" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY282" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ282" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA282" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB282" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC282" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD282" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BE282" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="BF282" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BG282" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH282" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="BI282" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ282" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BK282" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BL282" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BM282" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BN282" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO282" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BP282" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="n">
+        <v>282</v>
+      </c>
+      <c r="B283" t="n">
+        <v>7778345</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="n">
+        <v>45900.29166666666</v>
+      </c>
+      <c r="F283" t="n">
+        <v>28</v>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>Kawasaki Frontale</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>Machida Zelvia</t>
+        </is>
+      </c>
+      <c r="I283" t="n">
+        <v>2</v>
+      </c>
+      <c r="J283" t="n">
+        <v>2</v>
+      </c>
+      <c r="K283" t="n">
+        <v>4</v>
+      </c>
+      <c r="L283" t="n">
+        <v>5</v>
+      </c>
+      <c r="M283" t="n">
+        <v>3</v>
+      </c>
+      <c r="N283" t="n">
+        <v>8</v>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>['20', '45+4', '65', '78', '90+10']</t>
+        </is>
+      </c>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>['28', '36', '71']</t>
+        </is>
+      </c>
+      <c r="Q283" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="R283" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S283" t="n">
+        <v>3</v>
+      </c>
+      <c r="T283" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U283" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="V283" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="W283" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X283" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y283" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z283" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AA283" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB283" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC283" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD283" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE283" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF283" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG283" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH283" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AI283" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ283" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK283" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL283" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM283" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN283" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AO283" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP283" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AQ283" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AR283" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AS283" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AT283" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AU283" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV283" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW283" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX283" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY283" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ283" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA283" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB283" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC283" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD283" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BE283" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF283" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BG283" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH283" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BI283" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BJ283" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BK283" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BL283" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BM283" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BN283" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BO283" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BP283" t="n">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
@@ -60849,7 +60849,7 @@
         <v>1.3</v>
       </c>
       <c r="AL277" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AM277" t="n">
         <v>1.36</v>
@@ -61067,7 +61067,7 @@
         <v>1.3</v>
       </c>
       <c r="AL278" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AM278" t="n">
         <v>1.33</v>
@@ -61285,7 +61285,7 @@
         <v>1.3</v>
       </c>
       <c r="AL279" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AM279" t="n">
         <v>1.5</v>
@@ -61503,7 +61503,7 @@
         <v>1.3</v>
       </c>
       <c r="AL280" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AM280" t="n">
         <v>1.33</v>
@@ -61530,7 +61530,7 @@
         <v>3.29</v>
       </c>
       <c r="AU280" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV280" t="n">
         <v>2</v>
@@ -61542,7 +61542,7 @@
         <v>8</v>
       </c>
       <c r="AY280" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ280" t="n">
         <v>10</v>
@@ -61721,7 +61721,7 @@
         <v>1.33</v>
       </c>
       <c r="AL281" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AM281" t="n">
         <v>1.85</v>
@@ -61939,7 +61939,7 @@
         <v>1.3</v>
       </c>
       <c r="AL282" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AM282" t="n">
         <v>2</v>
@@ -62157,7 +62157,7 @@
         <v>1.33</v>
       </c>
       <c r="AL283" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AM283" t="n">
         <v>1.4</v>
@@ -62193,13 +62193,13 @@
         <v>10</v>
       </c>
       <c r="AX283" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY283" t="n">
         <v>15</v>
       </c>
       <c r="AZ283" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA283" t="n">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
@@ -60876,13 +60876,13 @@
         <v>2.65</v>
       </c>
       <c r="AU277" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV277" t="n">
         <v>5</v>
       </c>
       <c r="AW277" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX277" t="n">
         <v>12</v>
@@ -61097,13 +61097,13 @@
         <v>7</v>
       </c>
       <c r="AV278" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW278" t="n">
         <v>3</v>
       </c>
       <c r="AX278" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY278" t="n">
         <v>10</v>
@@ -61530,13 +61530,13 @@
         <v>3.29</v>
       </c>
       <c r="AU280" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV280" t="n">
         <v>2</v>
       </c>
       <c r="AW280" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX280" t="n">
         <v>8</v>
@@ -61748,13 +61748,13 @@
         <v>3.01</v>
       </c>
       <c r="AU281" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV281" t="n">
         <v>4</v>
       </c>
       <c r="AW281" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX281" t="n">
         <v>4</v>
@@ -62184,13 +62184,13 @@
         <v>2.79</v>
       </c>
       <c r="AU283" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV283" t="n">
         <v>6</v>
       </c>
       <c r="AW283" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX283" t="n">
         <v>12</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
@@ -61318,13 +61318,13 @@
         <v>4</v>
       </c>
       <c r="AW279" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX279" t="n">
         <v>6</v>
       </c>
       <c r="AY279" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ279" t="n">
         <v>10</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
@@ -60876,13 +60876,13 @@
         <v>2.65</v>
       </c>
       <c r="AU277" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV277" t="n">
         <v>5</v>
       </c>
       <c r="AW277" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX277" t="n">
         <v>12</v>
@@ -61097,13 +61097,13 @@
         <v>7</v>
       </c>
       <c r="AV278" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW278" t="n">
         <v>3</v>
       </c>
       <c r="AX278" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY278" t="n">
         <v>10</v>
@@ -61530,13 +61530,13 @@
         <v>3.29</v>
       </c>
       <c r="AU280" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV280" t="n">
         <v>2</v>
       </c>
       <c r="AW280" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX280" t="n">
         <v>8</v>
@@ -61748,13 +61748,13 @@
         <v>3.01</v>
       </c>
       <c r="AU281" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV281" t="n">
         <v>4</v>
       </c>
       <c r="AW281" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX281" t="n">
         <v>4</v>
@@ -62184,13 +62184,13 @@
         <v>2.79</v>
       </c>
       <c r="AU283" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV283" t="n">
         <v>6</v>
       </c>
       <c r="AW283" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX283" t="n">
         <v>12</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP283"/>
+  <dimension ref="A1:BP293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1783,10 +1783,10 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ7" t="n">
         <v>0.57</v>
@@ -2222,7 +2222,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ10" t="n">
         <v>1.8</v>
@@ -2876,7 +2876,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -4184,7 +4184,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.29</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ19" t="n">
         <v>1.87</v>
@@ -4835,10 +4835,10 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ21" t="n">
         <v>0.79</v>
@@ -5271,10 +5271,10 @@
         <v>1</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR22" t="n">
         <v>0.78</v>
@@ -5489,7 +5489,7 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ23" t="n">
         <v>1</v>
@@ -5707,10 +5707,10 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR24" t="n">
         <v>0.65</v>
@@ -6146,7 +6146,7 @@
         <v>1</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR26" t="n">
         <v>1.86</v>
@@ -6361,7 +6361,7 @@
         <v>0.5</v>
       </c>
       <c r="AP27" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ27" t="n">
         <v>0.57</v>
@@ -6579,10 +6579,10 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR28" t="n">
         <v>0.67</v>
@@ -6797,10 +6797,10 @@
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR29" t="n">
         <v>1.03</v>
@@ -7018,7 +7018,7 @@
         <v>2</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR30" t="n">
         <v>1.25</v>
@@ -7233,10 +7233,10 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR31" t="n">
         <v>1.01</v>
@@ -7451,10 +7451,10 @@
         <v>3</v>
       </c>
       <c r="AP32" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR32" t="n">
         <v>0.99</v>
@@ -7669,7 +7669,7 @@
         <v>3</v>
       </c>
       <c r="AP33" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ33" t="n">
         <v>0.93</v>
@@ -7890,7 +7890,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR34" t="n">
         <v>1.86</v>
@@ -8105,7 +8105,7 @@
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ35" t="n">
         <v>1.29</v>
@@ -8541,10 +8541,10 @@
         <v>1.5</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR37" t="n">
         <v>0</v>
@@ -8977,10 +8977,10 @@
         <v>3</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR39" t="n">
         <v>1.46</v>
@@ -9195,10 +9195,10 @@
         <v>1</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR40" t="n">
         <v>1.11</v>
@@ -9416,7 +9416,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR41" t="n">
         <v>0</v>
@@ -9849,10 +9849,10 @@
         <v>1.5</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR43" t="n">
         <v>1.61</v>
@@ -10067,10 +10067,10 @@
         <v>2</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR44" t="n">
         <v>1.4</v>
@@ -10285,10 +10285,10 @@
         <v>2</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR45" t="n">
         <v>1.24</v>
@@ -10724,7 +10724,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR47" t="n">
         <v>1.5</v>
@@ -11378,7 +11378,7 @@
         <v>1</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR50" t="n">
         <v>1.08</v>
@@ -11593,7 +11593,7 @@
         <v>0.33</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ51" t="n">
         <v>0.57</v>
@@ -11814,7 +11814,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR52" t="n">
         <v>1.14</v>
@@ -12029,7 +12029,7 @@
         <v>1.5</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ53" t="n">
         <v>0.93</v>
@@ -12250,7 +12250,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR54" t="n">
         <v>1.31</v>
@@ -12465,7 +12465,7 @@
         <v>1.5</v>
       </c>
       <c r="AP55" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ55" t="n">
         <v>1</v>
@@ -12683,10 +12683,10 @@
         <v>2</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR56" t="n">
         <v>1.53</v>
@@ -12901,10 +12901,10 @@
         <v>3</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR57" t="n">
         <v>1.33</v>
@@ -13119,10 +13119,10 @@
         <v>0.67</v>
       </c>
       <c r="AP58" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR58" t="n">
         <v>1.78</v>
@@ -13558,7 +13558,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR60" t="n">
         <v>1.82</v>
@@ -13773,7 +13773,7 @@
         <v>0</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ61" t="n">
         <v>0.79</v>
@@ -13994,7 +13994,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ62" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR62" t="n">
         <v>1.28</v>
@@ -14212,7 +14212,7 @@
         <v>2</v>
       </c>
       <c r="AQ63" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR63" t="n">
         <v>1.33</v>
@@ -14427,7 +14427,7 @@
         <v>1</v>
       </c>
       <c r="AP64" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ64" t="n">
         <v>1</v>
@@ -14648,7 +14648,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR65" t="n">
         <v>0.95</v>
@@ -15081,7 +15081,7 @@
         <v>2</v>
       </c>
       <c r="AP67" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ67" t="n">
         <v>1.8</v>
@@ -15299,7 +15299,7 @@
         <v>3</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ68" t="n">
         <v>1.87</v>
@@ -15517,10 +15517,10 @@
         <v>1.67</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR69" t="n">
         <v>1.25</v>
@@ -15735,7 +15735,7 @@
         <v>1.5</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ70" t="n">
         <v>1.57</v>
@@ -16171,7 +16171,7 @@
         <v>2.5</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ72" t="n">
         <v>1.87</v>
@@ -16392,7 +16392,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR73" t="n">
         <v>1.07</v>
@@ -16825,7 +16825,7 @@
         <v>2</v>
       </c>
       <c r="AP75" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ75" t="n">
         <v>1.29</v>
@@ -17046,7 +17046,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ76" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR76" t="n">
         <v>1.76</v>
@@ -17700,7 +17700,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ79" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR79" t="n">
         <v>1.65</v>
@@ -17915,10 +17915,10 @@
         <v>1.25</v>
       </c>
       <c r="AP80" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR80" t="n">
         <v>1.12</v>
@@ -18133,7 +18133,7 @@
         <v>1</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ81" t="n">
         <v>0.93</v>
@@ -18351,10 +18351,10 @@
         <v>0.8</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ82" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR82" t="n">
         <v>1.4</v>
@@ -18569,10 +18569,10 @@
         <v>2</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR83" t="n">
         <v>1.1</v>
@@ -18790,7 +18790,7 @@
         <v>1</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR84" t="n">
         <v>1.07</v>
@@ -19005,7 +19005,7 @@
         <v>0.25</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ85" t="n">
         <v>0.57</v>
@@ -19223,10 +19223,10 @@
         <v>1.75</v>
       </c>
       <c r="AP86" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR86" t="n">
         <v>1.52</v>
@@ -19662,7 +19662,7 @@
         <v>1</v>
       </c>
       <c r="AQ88" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR88" t="n">
         <v>1.47</v>
@@ -19877,10 +19877,10 @@
         <v>1</v>
       </c>
       <c r="AP89" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ89" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR89" t="n">
         <v>1.35</v>
@@ -20313,10 +20313,10 @@
         <v>2</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR91" t="n">
         <v>1.19</v>
@@ -20531,7 +20531,7 @@
         <v>0</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ92" t="n">
         <v>1.15</v>
@@ -20752,7 +20752,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR93" t="n">
         <v>1.26</v>
@@ -20967,10 +20967,10 @@
         <v>0.2</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ94" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR94" t="n">
         <v>1.41</v>
@@ -21185,7 +21185,7 @@
         <v>0.25</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ95" t="n">
         <v>0.79</v>
@@ -21842,7 +21842,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ98" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR98" t="n">
         <v>1.26</v>
@@ -22057,10 +22057,10 @@
         <v>0.67</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ99" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR99" t="n">
         <v>1.11</v>
@@ -22275,10 +22275,10 @@
         <v>0.33</v>
       </c>
       <c r="AP100" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ100" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR100" t="n">
         <v>1.43</v>
@@ -22493,10 +22493,10 @@
         <v>0.8</v>
       </c>
       <c r="AP101" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ101" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR101" t="n">
         <v>1.06</v>
@@ -22711,10 +22711,10 @@
         <v>1.67</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR102" t="n">
         <v>1.42</v>
@@ -22932,7 +22932,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ103" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR103" t="n">
         <v>1.33</v>
@@ -23147,10 +23147,10 @@
         <v>1.67</v>
       </c>
       <c r="AP104" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR104" t="n">
         <v>1.4</v>
@@ -23583,7 +23583,7 @@
         <v>0.75</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ106" t="n">
         <v>1.57</v>
@@ -24237,7 +24237,7 @@
         <v>2.6</v>
       </c>
       <c r="AP109" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ109" t="n">
         <v>1.87</v>
@@ -24676,7 +24676,7 @@
         <v>1</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR111" t="n">
         <v>1.39</v>
@@ -24894,7 +24894,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ112" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR112" t="n">
         <v>1.65</v>
@@ -25330,7 +25330,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR114" t="n">
         <v>1.33</v>
@@ -25545,10 +25545,10 @@
         <v>0.83</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ115" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR115" t="n">
         <v>1.17</v>
@@ -25766,7 +25766,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ116" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR116" t="n">
         <v>1.41</v>
@@ -25981,7 +25981,7 @@
         <v>0.75</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ117" t="n">
         <v>1.15</v>
@@ -26199,10 +26199,10 @@
         <v>0.17</v>
       </c>
       <c r="AP118" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ118" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR118" t="n">
         <v>1.59</v>
@@ -26635,7 +26635,7 @@
         <v>0.83</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ120" t="n">
         <v>1</v>
@@ -27071,10 +27071,10 @@
         <v>1.17</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ122" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR122" t="n">
         <v>1.28</v>
@@ -27289,7 +27289,7 @@
         <v>0.83</v>
       </c>
       <c r="AP123" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ123" t="n">
         <v>0.57</v>
@@ -27725,10 +27725,10 @@
         <v>1.17</v>
       </c>
       <c r="AP125" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ125" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR125" t="n">
         <v>1.39</v>
@@ -27946,7 +27946,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR126" t="n">
         <v>1.18</v>
@@ -28161,10 +28161,10 @@
         <v>1.86</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ127" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR127" t="n">
         <v>1.52</v>
@@ -28815,7 +28815,7 @@
         <v>1.67</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ130" t="n">
         <v>1.29</v>
@@ -29036,7 +29036,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ131" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR131" t="n">
         <v>1.21</v>
@@ -29251,7 +29251,7 @@
         <v>0.83</v>
       </c>
       <c r="AP132" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ132" t="n">
         <v>0.93</v>
@@ -29469,7 +29469,7 @@
         <v>0.8</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ133" t="n">
         <v>1.15</v>
@@ -29687,10 +29687,10 @@
         <v>1.14</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ134" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR134" t="n">
         <v>1.47</v>
@@ -29905,7 +29905,7 @@
         <v>2.29</v>
       </c>
       <c r="AP135" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ135" t="n">
         <v>1.87</v>
@@ -30126,7 +30126,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ136" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR136" t="n">
         <v>1.29</v>
@@ -30344,7 +30344,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR137" t="n">
         <v>1.37</v>
@@ -30559,10 +30559,10 @@
         <v>1</v>
       </c>
       <c r="AP138" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ138" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR138" t="n">
         <v>1.59</v>
@@ -30777,7 +30777,7 @@
         <v>1.5</v>
       </c>
       <c r="AP139" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ139" t="n">
         <v>1.57</v>
@@ -31434,7 +31434,7 @@
         <v>2</v>
       </c>
       <c r="AQ142" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR142" t="n">
         <v>1.35</v>
@@ -31652,7 +31652,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ143" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR143" t="n">
         <v>1.35</v>
@@ -31867,10 +31867,10 @@
         <v>1.63</v>
       </c>
       <c r="AP144" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR144" t="n">
         <v>1.22</v>
@@ -32521,7 +32521,7 @@
         <v>2</v>
       </c>
       <c r="AP147" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ147" t="n">
         <v>1.8</v>
@@ -33175,10 +33175,10 @@
         <v>1.43</v>
       </c>
       <c r="AP150" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR150" t="n">
         <v>1.51</v>
@@ -33396,7 +33396,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ151" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR151" t="n">
         <v>1.48</v>
@@ -33611,10 +33611,10 @@
         <v>1</v>
       </c>
       <c r="AP152" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AQ152" t="n">
         <v>0.86</v>
-      </c>
-      <c r="AQ152" t="n">
-        <v>0.92</v>
       </c>
       <c r="AR152" t="n">
         <v>1.4</v>
@@ -33829,7 +33829,7 @@
         <v>1.17</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ153" t="n">
         <v>1.8</v>
@@ -34268,7 +34268,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ155" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR155" t="n">
         <v>1.27</v>
@@ -34483,10 +34483,10 @@
         <v>2.14</v>
       </c>
       <c r="AP156" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR156" t="n">
         <v>1.22</v>
@@ -34704,7 +34704,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ157" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR157" t="n">
         <v>1.51</v>
@@ -34919,10 +34919,10 @@
         <v>1.78</v>
       </c>
       <c r="AP158" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR158" t="n">
         <v>1.22</v>
@@ -35137,7 +35137,7 @@
         <v>1</v>
       </c>
       <c r="AP159" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ159" t="n">
         <v>1</v>
@@ -35355,10 +35355,10 @@
         <v>2.25</v>
       </c>
       <c r="AP160" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ160" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR160" t="n">
         <v>1.29</v>
@@ -35573,10 +35573,10 @@
         <v>1.25</v>
       </c>
       <c r="AP161" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ161" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR161" t="n">
         <v>1.55</v>
@@ -35791,10 +35791,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ162" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR162" t="n">
         <v>1.48</v>
@@ -36009,10 +36009,10 @@
         <v>1.25</v>
       </c>
       <c r="AP163" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ163" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR163" t="n">
         <v>1.5</v>
@@ -36230,7 +36230,7 @@
         <v>1</v>
       </c>
       <c r="AQ164" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR164" t="n">
         <v>1.33</v>
@@ -36666,7 +36666,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ166" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR166" t="n">
         <v>1.53</v>
@@ -36881,7 +36881,7 @@
         <v>1.14</v>
       </c>
       <c r="AP167" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ167" t="n">
         <v>0.57</v>
@@ -37102,7 +37102,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ168" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR168" t="n">
         <v>1.55</v>
@@ -37317,7 +37317,7 @@
         <v>1.67</v>
       </c>
       <c r="AP169" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ169" t="n">
         <v>1.8</v>
@@ -37756,7 +37756,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ171" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR171" t="n">
         <v>1.19</v>
@@ -37971,7 +37971,7 @@
         <v>1.89</v>
       </c>
       <c r="AP172" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ172" t="n">
         <v>1.87</v>
@@ -38189,7 +38189,7 @@
         <v>1.71</v>
       </c>
       <c r="AP173" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ173" t="n">
         <v>1.57</v>
@@ -38410,7 +38410,7 @@
         <v>1</v>
       </c>
       <c r="AQ174" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR174" t="n">
         <v>1.14</v>
@@ -38625,10 +38625,10 @@
         <v>1.22</v>
       </c>
       <c r="AP175" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ175" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR175" t="n">
         <v>1.37</v>
@@ -39064,7 +39064,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ177" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR177" t="n">
         <v>1.27</v>
@@ -39279,7 +39279,7 @@
         <v>1.43</v>
       </c>
       <c r="AP178" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ178" t="n">
         <v>1.8</v>
@@ -39718,7 +39718,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ180" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR180" t="n">
         <v>1.35</v>
@@ -40151,7 +40151,7 @@
         <v>0.14</v>
       </c>
       <c r="AP182" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ182" t="n">
         <v>0.79</v>
@@ -40369,10 +40369,10 @@
         <v>1.11</v>
       </c>
       <c r="AP183" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ183" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR183" t="n">
         <v>1.43</v>
@@ -40805,10 +40805,10 @@
         <v>1.25</v>
       </c>
       <c r="AP185" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ185" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR185" t="n">
         <v>1.56</v>
@@ -41023,7 +41023,7 @@
         <v>1.5</v>
       </c>
       <c r="AP186" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ186" t="n">
         <v>1.57</v>
@@ -41680,7 +41680,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ189" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR189" t="n">
         <v>1.73</v>
@@ -41898,7 +41898,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ190" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR190" t="n">
         <v>1.36</v>
@@ -42331,7 +42331,7 @@
         <v>1.63</v>
       </c>
       <c r="AP192" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ192" t="n">
         <v>1.8</v>
@@ -42552,7 +42552,7 @@
         <v>1</v>
       </c>
       <c r="AQ193" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR193" t="n">
         <v>1.15</v>
@@ -42767,10 +42767,10 @@
         <v>1.1</v>
       </c>
       <c r="AP194" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ194" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR194" t="n">
         <v>1.3</v>
@@ -42985,7 +42985,7 @@
         <v>0.5</v>
       </c>
       <c r="AP195" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ195" t="n">
         <v>0.79</v>
@@ -43203,10 +43203,10 @@
         <v>0.6</v>
       </c>
       <c r="AP196" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ196" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR196" t="n">
         <v>1.67</v>
@@ -43421,7 +43421,7 @@
         <v>1.11</v>
       </c>
       <c r="AP197" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ197" t="n">
         <v>1.29</v>
@@ -43642,7 +43642,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ198" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR198" t="n">
         <v>1.23</v>
@@ -44075,7 +44075,7 @@
         <v>0.89</v>
       </c>
       <c r="AP200" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ200" t="n">
         <v>0.57</v>
@@ -44293,7 +44293,7 @@
         <v>1.67</v>
       </c>
       <c r="AP201" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ201" t="n">
         <v>1.57</v>
@@ -44514,7 +44514,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ202" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR202" t="n">
         <v>1.77</v>
@@ -44729,7 +44729,7 @@
         <v>0.67</v>
       </c>
       <c r="AP203" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ203" t="n">
         <v>1.15</v>
@@ -44950,7 +44950,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ204" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR204" t="n">
         <v>1.38</v>
@@ -45168,7 +45168,7 @@
         <v>2</v>
       </c>
       <c r="AQ205" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR205" t="n">
         <v>1.4</v>
@@ -45819,7 +45819,7 @@
         <v>0.89</v>
       </c>
       <c r="AP208" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ208" t="n">
         <v>0.93</v>
@@ -46255,7 +46255,7 @@
         <v>0.8</v>
       </c>
       <c r="AP210" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ210" t="n">
         <v>0.93</v>
@@ -46473,7 +46473,7 @@
         <v>0.9</v>
       </c>
       <c r="AP211" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ211" t="n">
         <v>1.15</v>
@@ -46694,7 +46694,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ212" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR212" t="n">
         <v>1.3</v>
@@ -46909,10 +46909,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP213" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ213" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR213" t="n">
         <v>1.36</v>
@@ -47345,7 +47345,7 @@
         <v>1.9</v>
       </c>
       <c r="AP215" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ215" t="n">
         <v>1.8</v>
@@ -47781,10 +47781,10 @@
         <v>0.55</v>
       </c>
       <c r="AP217" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ217" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR217" t="n">
         <v>1.61</v>
@@ -48002,7 +48002,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ218" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR218" t="n">
         <v>1.16</v>
@@ -48217,7 +48217,7 @@
         <v>1.91</v>
       </c>
       <c r="AP219" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ219" t="n">
         <v>1.87</v>
@@ -48435,7 +48435,7 @@
         <v>1.7</v>
       </c>
       <c r="AP220" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ220" t="n">
         <v>1.8</v>
@@ -48653,10 +48653,10 @@
         <v>1</v>
       </c>
       <c r="AP221" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ221" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR221" t="n">
         <v>1.38</v>
@@ -48871,7 +48871,7 @@
         <v>1.55</v>
       </c>
       <c r="AP222" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ222" t="n">
         <v>1.8</v>
@@ -49746,7 +49746,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ226" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR226" t="n">
         <v>1.33</v>
@@ -50397,10 +50397,10 @@
         <v>1.1</v>
       </c>
       <c r="AP229" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ229" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR229" t="n">
         <v>1.68</v>
@@ -50615,10 +50615,10 @@
         <v>0.9</v>
       </c>
       <c r="AP230" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ230" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR230" t="n">
         <v>1.46</v>
@@ -50836,7 +50836,7 @@
         <v>1</v>
       </c>
       <c r="AQ231" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR231" t="n">
         <v>1.26</v>
@@ -51051,10 +51051,10 @@
         <v>2.08</v>
       </c>
       <c r="AP232" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ232" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR232" t="n">
         <v>1.54</v>
@@ -51490,7 +51490,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ234" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR234" t="n">
         <v>1.32</v>
@@ -51705,10 +51705,10 @@
         <v>0.75</v>
       </c>
       <c r="AP235" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ235" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR235" t="n">
         <v>1.24</v>
@@ -51923,7 +51923,7 @@
         <v>1.67</v>
       </c>
       <c r="AP236" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ236" t="n">
         <v>1.8</v>
@@ -52141,10 +52141,10 @@
         <v>1.45</v>
       </c>
       <c r="AP237" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ237" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR237" t="n">
         <v>1.53</v>
@@ -52359,7 +52359,7 @@
         <v>1.82</v>
       </c>
       <c r="AP238" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ238" t="n">
         <v>1.8</v>
@@ -52577,10 +52577,10 @@
         <v>1.67</v>
       </c>
       <c r="AP239" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ239" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR239" t="n">
         <v>1.27</v>
@@ -52798,7 +52798,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ240" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR240" t="n">
         <v>1.37</v>
@@ -53234,7 +53234,7 @@
         <v>1</v>
       </c>
       <c r="AQ242" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR242" t="n">
         <v>1.15</v>
@@ -53885,10 +53885,10 @@
         <v>0.92</v>
       </c>
       <c r="AP245" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ245" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR245" t="n">
         <v>1.62</v>
@@ -54103,7 +54103,7 @@
         <v>1.36</v>
       </c>
       <c r="AP246" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ246" t="n">
         <v>1.57</v>
@@ -54324,7 +54324,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ247" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR247" t="n">
         <v>1.28</v>
@@ -54539,7 +54539,7 @@
         <v>1.09</v>
       </c>
       <c r="AP248" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ248" t="n">
         <v>1.15</v>
@@ -54757,7 +54757,7 @@
         <v>1.92</v>
       </c>
       <c r="AP249" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ249" t="n">
         <v>1.8</v>
@@ -54978,7 +54978,7 @@
         <v>2</v>
       </c>
       <c r="AQ250" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR250" t="n">
         <v>1.45</v>
@@ -55411,7 +55411,7 @@
         <v>1.42</v>
       </c>
       <c r="AP252" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ252" t="n">
         <v>1.29</v>
@@ -55847,10 +55847,10 @@
         <v>0.45</v>
       </c>
       <c r="AP254" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ254" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR254" t="n">
         <v>1.7</v>
@@ -56065,7 +56065,7 @@
         <v>1</v>
       </c>
       <c r="AP255" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ255" t="n">
         <v>1</v>
@@ -56286,7 +56286,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ256" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="AR256" t="n">
         <v>1.37</v>
@@ -56501,10 +56501,10 @@
         <v>1.08</v>
       </c>
       <c r="AP257" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ257" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR257" t="n">
         <v>1.4</v>
@@ -56937,10 +56937,10 @@
         <v>1.33</v>
       </c>
       <c r="AP259" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ259" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR259" t="n">
         <v>1.4</v>
@@ -57158,7 +57158,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ260" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR260" t="n">
         <v>1.49</v>
@@ -57373,10 +57373,10 @@
         <v>1.92</v>
       </c>
       <c r="AP261" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ261" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR261" t="n">
         <v>1.31</v>
@@ -57591,7 +57591,7 @@
         <v>1.77</v>
       </c>
       <c r="AP262" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AQ262" t="n">
         <v>1.8</v>
@@ -57809,7 +57809,7 @@
         <v>0.93</v>
       </c>
       <c r="AP263" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AQ263" t="n">
         <v>1</v>
@@ -58030,7 +58030,7 @@
         <v>2</v>
       </c>
       <c r="AQ264" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR264" t="n">
         <v>1.44</v>
@@ -58245,10 +58245,10 @@
         <v>0.92</v>
       </c>
       <c r="AP265" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ265" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR265" t="n">
         <v>1.32</v>
@@ -58681,7 +58681,7 @@
         <v>1.5</v>
       </c>
       <c r="AP267" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AQ267" t="n">
         <v>1.57</v>
@@ -58902,7 +58902,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ268" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AR268" t="n">
         <v>1.27</v>
@@ -59117,10 +59117,10 @@
         <v>0.67</v>
       </c>
       <c r="AP269" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ269" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR269" t="n">
         <v>1.57</v>
@@ -59553,10 +59553,10 @@
         <v>0.85</v>
       </c>
       <c r="AP271" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ271" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR271" t="n">
         <v>1.34</v>
@@ -59771,7 +59771,7 @@
         <v>2.08</v>
       </c>
       <c r="AP272" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ272" t="n">
         <v>1.87</v>
@@ -59989,10 +59989,10 @@
         <v>1.71</v>
       </c>
       <c r="AP273" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AQ273" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR273" t="n">
         <v>1.51</v>
@@ -60210,7 +60210,7 @@
         <v>1</v>
       </c>
       <c r="AQ274" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR274" t="n">
         <v>1.14</v>
@@ -60643,7 +60643,7 @@
         <v>0.85</v>
       </c>
       <c r="AP276" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ276" t="n">
         <v>0.79</v>
@@ -62248,6 +62248,2186 @@
       </c>
       <c r="BP283" t="n">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="n">
+        <v>283</v>
+      </c>
+      <c r="B284" t="n">
+        <v>7778355</v>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="n">
+        <v>45912.29166666666</v>
+      </c>
+      <c r="F284" t="n">
+        <v>29</v>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>Machida Zelvia</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>Yokohama</t>
+        </is>
+      </c>
+      <c r="I284" t="n">
+        <v>0</v>
+      </c>
+      <c r="J284" t="n">
+        <v>0</v>
+      </c>
+      <c r="K284" t="n">
+        <v>0</v>
+      </c>
+      <c r="L284" t="n">
+        <v>1</v>
+      </c>
+      <c r="M284" t="n">
+        <v>1</v>
+      </c>
+      <c r="N284" t="n">
+        <v>2</v>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>['88']</t>
+        </is>
+      </c>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>['56']</t>
+        </is>
+      </c>
+      <c r="Q284" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R284" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S284" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T284" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U284" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V284" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W284" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X284" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y284" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z284" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA284" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="AB284" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AC284" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD284" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE284" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF284" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG284" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH284" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI284" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ284" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK284" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL284" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM284" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AN284" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AO284" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AP284" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AQ284" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AR284" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AS284" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AT284" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AU284" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV284" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW284" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX284" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY284" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ284" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA284" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB284" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC284" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD284" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BE284" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BF284" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BG284" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BH284" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BI284" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BJ284" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BK284" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BL284" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BM284" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BN284" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BO284" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BP284" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="n">
+        <v>284</v>
+      </c>
+      <c r="B285" t="n">
+        <v>7778361</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="n">
+        <v>45912.29166666666</v>
+      </c>
+      <c r="F285" t="n">
+        <v>29</v>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>Sanfrecce Hiroshima</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>Kyoto Sanga</t>
+        </is>
+      </c>
+      <c r="I285" t="n">
+        <v>0</v>
+      </c>
+      <c r="J285" t="n">
+        <v>0</v>
+      </c>
+      <c r="K285" t="n">
+        <v>0</v>
+      </c>
+      <c r="L285" t="n">
+        <v>1</v>
+      </c>
+      <c r="M285" t="n">
+        <v>1</v>
+      </c>
+      <c r="N285" t="n">
+        <v>2</v>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>['63']</t>
+        </is>
+      </c>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>['88']</t>
+        </is>
+      </c>
+      <c r="Q285" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R285" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S285" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T285" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U285" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V285" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="W285" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X285" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y285" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z285" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA285" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AB285" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AC285" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD285" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AE285" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AF285" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AG285" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AH285" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AI285" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AJ285" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK285" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL285" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM285" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN285" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AO285" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP285" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ285" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AR285" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AS285" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AT285" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU285" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV285" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW285" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX285" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY285" t="n">
+        <v>27</v>
+      </c>
+      <c r="AZ285" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA285" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB285" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC285" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD285" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BE285" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF285" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BG285" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH285" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI285" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ285" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BK285" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BL285" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BM285" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BN285" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BO285" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BP285" t="n">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="n">
+        <v>285</v>
+      </c>
+      <c r="B286" t="n">
+        <v>7778359</v>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="n">
+        <v>45912.29166666666</v>
+      </c>
+      <c r="F286" t="n">
+        <v>29</v>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>Vissel Kobe</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>Kashiwa Reysol</t>
+        </is>
+      </c>
+      <c r="I286" t="n">
+        <v>0</v>
+      </c>
+      <c r="J286" t="n">
+        <v>0</v>
+      </c>
+      <c r="K286" t="n">
+        <v>0</v>
+      </c>
+      <c r="L286" t="n">
+        <v>0</v>
+      </c>
+      <c r="M286" t="n">
+        <v>0</v>
+      </c>
+      <c r="N286" t="n">
+        <v>0</v>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q286" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R286" t="n">
+        <v>2</v>
+      </c>
+      <c r="S286" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="T286" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U286" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V286" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="W286" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X286" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y286" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z286" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA286" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AB286" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AC286" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD286" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE286" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AF286" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AG286" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH286" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI286" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ286" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK286" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL286" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM286" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN286" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO286" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AP286" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ286" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AR286" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS286" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AT286" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU286" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV286" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW286" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX286" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY286" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ286" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA286" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB286" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC286" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD286" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BE286" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF286" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BG286" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH286" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI286" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ286" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BK286" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BL286" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM286" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BN286" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BO286" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BP286" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="n">
+        <v>286</v>
+      </c>
+      <c r="B287" t="n">
+        <v>7778362</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="n">
+        <v>45913.25</v>
+      </c>
+      <c r="F287" t="n">
+        <v>29</v>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>Avispa Fukuoka</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>Cerezo Osaka</t>
+        </is>
+      </c>
+      <c r="I287" t="n">
+        <v>1</v>
+      </c>
+      <c r="J287" t="n">
+        <v>0</v>
+      </c>
+      <c r="K287" t="n">
+        <v>1</v>
+      </c>
+      <c r="L287" t="n">
+        <v>2</v>
+      </c>
+      <c r="M287" t="n">
+        <v>4</v>
+      </c>
+      <c r="N287" t="n">
+        <v>6</v>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>['41', '90+8']</t>
+        </is>
+      </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>['54', '64', '77', '89']</t>
+        </is>
+      </c>
+      <c r="Q287" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="R287" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="S287" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T287" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U287" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="V287" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W287" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X287" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y287" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z287" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AA287" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB287" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AC287" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD287" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="AE287" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF287" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AG287" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH287" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AI287" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AJ287" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AK287" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL287" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM287" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN287" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO287" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP287" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ287" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR287" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AS287" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AT287" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU287" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV287" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW287" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX287" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY287" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ287" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA287" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB287" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC287" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD287" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BE287" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BF287" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BG287" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BH287" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BI287" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BJ287" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BK287" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BL287" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BM287" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BN287" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BO287" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP287" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="n">
+        <v>287</v>
+      </c>
+      <c r="B288" t="n">
+        <v>7778360</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="n">
+        <v>45913.28819444445</v>
+      </c>
+      <c r="F288" t="n">
+        <v>29</v>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>Fagiano Okayama</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>Nagoya Grampus</t>
+        </is>
+      </c>
+      <c r="I288" t="n">
+        <v>0</v>
+      </c>
+      <c r="J288" t="n">
+        <v>0</v>
+      </c>
+      <c r="K288" t="n">
+        <v>0</v>
+      </c>
+      <c r="L288" t="n">
+        <v>0</v>
+      </c>
+      <c r="M288" t="n">
+        <v>1</v>
+      </c>
+      <c r="N288" t="n">
+        <v>1</v>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>['61']</t>
+        </is>
+      </c>
+      <c r="Q288" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R288" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="S288" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T288" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U288" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V288" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="W288" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X288" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Y288" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z288" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA288" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AB288" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AC288" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD288" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE288" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF288" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG288" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH288" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI288" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AJ288" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK288" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL288" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AM288" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN288" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AO288" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AP288" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ288" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AR288" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AS288" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AT288" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AU288" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV288" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW288" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX288" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY288" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ288" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA288" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB288" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC288" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD288" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BE288" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF288" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BG288" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH288" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BI288" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BJ288" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BK288" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BL288" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM288" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BN288" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BO288" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BP288" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="n">
+        <v>288</v>
+      </c>
+      <c r="B289" t="n">
+        <v>7778353</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="n">
+        <v>45913.29166666666</v>
+      </c>
+      <c r="F289" t="n">
+        <v>29</v>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>Kashima Antlers</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>Shonan Bellmare</t>
+        </is>
+      </c>
+      <c r="I289" t="n">
+        <v>0</v>
+      </c>
+      <c r="J289" t="n">
+        <v>0</v>
+      </c>
+      <c r="K289" t="n">
+        <v>0</v>
+      </c>
+      <c r="L289" t="n">
+        <v>3</v>
+      </c>
+      <c r="M289" t="n">
+        <v>0</v>
+      </c>
+      <c r="N289" t="n">
+        <v>3</v>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>['48', '55', '68']</t>
+        </is>
+      </c>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q289" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R289" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S289" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T289" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="U289" t="n">
+        <v>3</v>
+      </c>
+      <c r="V289" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W289" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X289" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y289" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z289" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AA289" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="AB289" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AC289" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD289" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE289" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF289" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG289" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AH289" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AI289" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AJ289" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AK289" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AL289" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AM289" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AN289" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AO289" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AP289" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AQ289" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AR289" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AS289" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AT289" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AU289" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV289" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW289" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX289" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY289" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ289" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA289" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB289" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC289" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD289" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BE289" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="BF289" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BG289" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH289" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="BI289" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ289" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BK289" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL289" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BM289" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BN289" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BO289" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BP289" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="n">
+        <v>289</v>
+      </c>
+      <c r="B290" t="n">
+        <v>7778357</v>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="n">
+        <v>45913.29166666666</v>
+      </c>
+      <c r="F290" t="n">
+        <v>29</v>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Albirex Niigata</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>Shimizu S-Pulse</t>
+        </is>
+      </c>
+      <c r="I290" t="n">
+        <v>0</v>
+      </c>
+      <c r="J290" t="n">
+        <v>1</v>
+      </c>
+      <c r="K290" t="n">
+        <v>1</v>
+      </c>
+      <c r="L290" t="n">
+        <v>0</v>
+      </c>
+      <c r="M290" t="n">
+        <v>1</v>
+      </c>
+      <c r="N290" t="n">
+        <v>1</v>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>['16']</t>
+        </is>
+      </c>
+      <c r="Q290" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R290" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S290" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T290" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U290" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V290" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W290" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X290" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="Y290" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z290" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AA290" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AB290" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC290" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD290" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AE290" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF290" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG290" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AH290" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AI290" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ290" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AK290" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL290" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM290" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN290" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AO290" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AP290" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AQ290" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AR290" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AS290" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AT290" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AU290" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV290" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW290" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX290" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY290" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ290" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA290" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB290" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC290" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD290" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BE290" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF290" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BG290" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH290" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI290" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ290" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BK290" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL290" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BM290" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BN290" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BO290" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BP290" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="n">
+        <v>290</v>
+      </c>
+      <c r="B291" t="n">
+        <v>7778358</v>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="n">
+        <v>45913.29166666666</v>
+      </c>
+      <c r="F291" t="n">
+        <v>29</v>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>Gamba Osaka</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>Urawa Reds</t>
+        </is>
+      </c>
+      <c r="I291" t="n">
+        <v>0</v>
+      </c>
+      <c r="J291" t="n">
+        <v>0</v>
+      </c>
+      <c r="K291" t="n">
+        <v>0</v>
+      </c>
+      <c r="L291" t="n">
+        <v>1</v>
+      </c>
+      <c r="M291" t="n">
+        <v>0</v>
+      </c>
+      <c r="N291" t="n">
+        <v>1</v>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>['85']</t>
+        </is>
+      </c>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q291" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R291" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S291" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T291" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="U291" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V291" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="W291" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X291" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y291" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z291" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AA291" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AB291" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AC291" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD291" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="AE291" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF291" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG291" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AH291" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AI291" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AJ291" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AK291" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AL291" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM291" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN291" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO291" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP291" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AQ291" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AR291" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AS291" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AT291" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AU291" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV291" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW291" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX291" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY291" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ291" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA291" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB291" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC291" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD291" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BE291" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF291" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BG291" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH291" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI291" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ291" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK291" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BL291" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM291" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BN291" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BO291" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BP291" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="n">
+        <v>291</v>
+      </c>
+      <c r="B292" t="n">
+        <v>7778356</v>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="n">
+        <v>45913.29166666666</v>
+      </c>
+      <c r="F292" t="n">
+        <v>29</v>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>Yokohama F. Marinos</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>Kawasaki Frontale</t>
+        </is>
+      </c>
+      <c r="I292" t="n">
+        <v>0</v>
+      </c>
+      <c r="J292" t="n">
+        <v>1</v>
+      </c>
+      <c r="K292" t="n">
+        <v>1</v>
+      </c>
+      <c r="L292" t="n">
+        <v>0</v>
+      </c>
+      <c r="M292" t="n">
+        <v>3</v>
+      </c>
+      <c r="N292" t="n">
+        <v>3</v>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P292" t="inlineStr">
+        <is>
+          <t>['4', '62', '90+8']</t>
+        </is>
+      </c>
+      <c r="Q292" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R292" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="S292" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T292" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U292" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V292" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="W292" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X292" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y292" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z292" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA292" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AB292" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AC292" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD292" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE292" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF292" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AG292" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AH292" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AI292" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AJ292" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AK292" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL292" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AM292" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN292" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO292" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AP292" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AQ292" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR292" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AS292" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AT292" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU292" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV292" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW292" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX292" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY292" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ292" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA292" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB292" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC292" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD292" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BE292" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF292" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BG292" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH292" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI292" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ292" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BK292" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BL292" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BM292" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BN292" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BO292" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BP292" t="n">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="n">
+        <v>292</v>
+      </c>
+      <c r="B293" t="n">
+        <v>7778354</v>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E293" s="2" t="n">
+        <v>45915.29166666666</v>
+      </c>
+      <c r="F293" t="n">
+        <v>29</v>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>Tokyo Verdy</t>
+        </is>
+      </c>
+      <c r="I293" t="n">
+        <v>0</v>
+      </c>
+      <c r="J293" t="n">
+        <v>0</v>
+      </c>
+      <c r="K293" t="n">
+        <v>0</v>
+      </c>
+      <c r="L293" t="n">
+        <v>1</v>
+      </c>
+      <c r="M293" t="n">
+        <v>0</v>
+      </c>
+      <c r="N293" t="n">
+        <v>1</v>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>['60']</t>
+        </is>
+      </c>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q293" t="n">
+        <v>3</v>
+      </c>
+      <c r="R293" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S293" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="T293" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U293" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V293" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W293" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X293" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y293" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z293" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AA293" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AB293" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC293" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD293" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE293" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AF293" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG293" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH293" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI293" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ293" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK293" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL293" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM293" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN293" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AO293" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AP293" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ293" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AR293" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AS293" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AT293" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AU293" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV293" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW293" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX293" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY293" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ293" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA293" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB293" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC293" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD293" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BE293" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="BF293" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BG293" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BH293" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BI293" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BJ293" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BK293" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BL293" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BM293" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BN293" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BO293" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BP293" t="n">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP293"/>
+  <dimension ref="A1:BP308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -2001,10 +2001,10 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2219,10 +2219,10 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2437,10 +2437,10 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2658,7 +2658,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.8</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3527,10 +3527,10 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR14" t="n">
         <v>1.63</v>
@@ -3748,7 +3748,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -3963,7 +3963,7 @@
         <v>1</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="AQ16" t="n">
         <v>0.86</v>
@@ -4181,10 +4181,10 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -4399,10 +4399,10 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR18" t="n">
         <v>1.94</v>
@@ -4617,10 +4617,10 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ20" t="n">
         <v>0.87</v>
@@ -5056,7 +5056,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR21" t="n">
         <v>0</v>
@@ -5274,7 +5274,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR22" t="n">
         <v>0.78</v>
@@ -5928,7 +5928,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR25" t="n">
         <v>1.44</v>
@@ -6143,7 +6143,7 @@
         <v>1</v>
       </c>
       <c r="AP26" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ26" t="n">
         <v>0.86</v>
@@ -6361,10 +6361,10 @@
         <v>0.5</v>
       </c>
       <c r="AP27" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR27" t="n">
         <v>1.94</v>
@@ -6797,10 +6797,10 @@
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR29" t="n">
         <v>1.03</v>
@@ -7015,10 +7015,10 @@
         <v>3</v>
       </c>
       <c r="AP30" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR30" t="n">
         <v>1.25</v>
@@ -7233,7 +7233,7 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ31" t="n">
         <v>0.64</v>
@@ -7451,10 +7451,10 @@
         <v>3</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR32" t="n">
         <v>0.99</v>
@@ -7669,10 +7669,10 @@
         <v>3</v>
       </c>
       <c r="AP33" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR33" t="n">
         <v>1.73</v>
@@ -7887,7 +7887,7 @@
         <v>0.5</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ34" t="n">
         <v>1.75</v>
@@ -8108,7 +8108,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR35" t="n">
         <v>1.34</v>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ36" t="n">
         <v>1</v>
@@ -8541,10 +8541,10 @@
         <v>1.5</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR37" t="n">
         <v>0</v>
@@ -8759,10 +8759,10 @@
         <v>3</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AR38" t="n">
         <v>1.22</v>
@@ -8980,7 +8980,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR39" t="n">
         <v>1.46</v>
@@ -9413,10 +9413,10 @@
         <v>3</v>
       </c>
       <c r="AP41" t="n">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AR41" t="n">
         <v>0</v>
@@ -9631,10 +9631,10 @@
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR42" t="n">
         <v>1.91</v>
@@ -9849,7 +9849,7 @@
         <v>1.5</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ43" t="n">
         <v>0.87</v>
@@ -10067,10 +10067,10 @@
         <v>2</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR44" t="n">
         <v>1.4</v>
@@ -10285,10 +10285,10 @@
         <v>2</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR45" t="n">
         <v>1.24</v>
@@ -10503,10 +10503,10 @@
         <v>3</v>
       </c>
       <c r="AP46" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AR46" t="n">
         <v>1.34</v>
@@ -10721,10 +10721,10 @@
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR47" t="n">
         <v>1.5</v>
@@ -10939,10 +10939,10 @@
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR48" t="n">
         <v>1.32</v>
@@ -11157,10 +11157,10 @@
         <v>1.5</v>
       </c>
       <c r="AP49" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR49" t="n">
         <v>1.45</v>
@@ -11375,10 +11375,10 @@
         <v>1.33</v>
       </c>
       <c r="AP50" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR50" t="n">
         <v>1.08</v>
@@ -11596,7 +11596,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR51" t="n">
         <v>0.89</v>
@@ -11811,10 +11811,10 @@
         <v>0.33</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR52" t="n">
         <v>1.14</v>
@@ -12032,7 +12032,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR53" t="n">
         <v>0.99</v>
@@ -12465,7 +12465,7 @@
         <v>1.5</v>
       </c>
       <c r="AP55" t="n">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ55" t="n">
         <v>1</v>
@@ -12686,7 +12686,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR56" t="n">
         <v>1.53</v>
@@ -12904,7 +12904,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AR57" t="n">
         <v>1.33</v>
@@ -13119,7 +13119,7 @@
         <v>0.67</v>
       </c>
       <c r="AP58" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ58" t="n">
         <v>0.86</v>
@@ -13337,7 +13337,7 @@
         <v>1</v>
       </c>
       <c r="AP59" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ59" t="n">
         <v>1.8</v>
@@ -13555,7 +13555,7 @@
         <v>0.75</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AQ60" t="n">
         <v>0.86</v>
@@ -13776,7 +13776,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ61" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR61" t="n">
         <v>1.58</v>
@@ -13994,7 +13994,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ62" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR62" t="n">
         <v>1.28</v>
@@ -14209,7 +14209,7 @@
         <v>1.33</v>
       </c>
       <c r="AP63" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ63" t="n">
         <v>0.87</v>
@@ -14427,7 +14427,7 @@
         <v>1</v>
       </c>
       <c r="AP64" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ64" t="n">
         <v>1</v>
@@ -14645,7 +14645,7 @@
         <v>0.5</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ65" t="n">
         <v>0.64</v>
@@ -14863,10 +14863,10 @@
         <v>2</v>
       </c>
       <c r="AP66" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR66" t="n">
         <v>1.3</v>
@@ -15081,7 +15081,7 @@
         <v>2</v>
       </c>
       <c r="AP67" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ67" t="n">
         <v>1.8</v>
@@ -15302,7 +15302,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AR68" t="n">
         <v>1.38</v>
@@ -15517,10 +15517,10 @@
         <v>1.67</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR69" t="n">
         <v>1.25</v>
@@ -15738,7 +15738,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR70" t="n">
         <v>1.34</v>
@@ -15953,10 +15953,10 @@
         <v>0</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR71" t="n">
         <v>1.7</v>
@@ -16171,10 +16171,10 @@
         <v>2.5</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AR72" t="n">
         <v>1.5</v>
@@ -16389,10 +16389,10 @@
         <v>2.33</v>
       </c>
       <c r="AP73" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AR73" t="n">
         <v>1.07</v>
@@ -16607,10 +16607,10 @@
         <v>0</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ74" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR74" t="n">
         <v>0.96</v>
@@ -16825,10 +16825,10 @@
         <v>2</v>
       </c>
       <c r="AP75" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR75" t="n">
         <v>1.32</v>
@@ -17043,10 +17043,10 @@
         <v>1.25</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ76" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR76" t="n">
         <v>1.76</v>
@@ -17261,10 +17261,10 @@
         <v>1</v>
       </c>
       <c r="AP77" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ77" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR77" t="n">
         <v>1.15</v>
@@ -17479,7 +17479,7 @@
         <v>1.33</v>
       </c>
       <c r="AP78" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ78" t="n">
         <v>1.8</v>
@@ -17697,10 +17697,10 @@
         <v>1.33</v>
       </c>
       <c r="AP79" t="n">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR79" t="n">
         <v>1.65</v>
@@ -17915,7 +17915,7 @@
         <v>1.25</v>
       </c>
       <c r="AP80" t="n">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ80" t="n">
         <v>0.87</v>
@@ -18136,7 +18136,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ81" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR81" t="n">
         <v>1.5</v>
@@ -18572,7 +18572,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR83" t="n">
         <v>1.1</v>
@@ -18787,10 +18787,10 @@
         <v>1</v>
       </c>
       <c r="AP84" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ84" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR84" t="n">
         <v>1.07</v>
@@ -19008,7 +19008,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ85" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR85" t="n">
         <v>1.26</v>
@@ -19223,7 +19223,7 @@
         <v>1.75</v>
       </c>
       <c r="AP86" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ86" t="n">
         <v>1.75</v>
@@ -19441,7 +19441,7 @@
         <v>1</v>
       </c>
       <c r="AP87" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ87" t="n">
         <v>1</v>
@@ -19659,10 +19659,10 @@
         <v>0.25</v>
       </c>
       <c r="AP88" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ88" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR88" t="n">
         <v>1.47</v>
@@ -19880,7 +19880,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ89" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR89" t="n">
         <v>1.35</v>
@@ -20095,10 +20095,10 @@
         <v>0</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ90" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR90" t="n">
         <v>1.77</v>
@@ -20313,10 +20313,10 @@
         <v>2</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AR91" t="n">
         <v>1.19</v>
@@ -20534,7 +20534,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR92" t="n">
         <v>1.33</v>
@@ -20752,7 +20752,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR93" t="n">
         <v>1.26</v>
@@ -20967,10 +20967,10 @@
         <v>0.2</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ94" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR94" t="n">
         <v>1.41</v>
@@ -21188,7 +21188,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ95" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR95" t="n">
         <v>1.36</v>
@@ -21403,7 +21403,7 @@
         <v>1.75</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ96" t="n">
         <v>1.8</v>
@@ -21621,10 +21621,10 @@
         <v>1</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR97" t="n">
         <v>1.78</v>
@@ -21839,10 +21839,10 @@
         <v>1</v>
       </c>
       <c r="AP98" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="AQ98" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR98" t="n">
         <v>1.26</v>
@@ -22275,7 +22275,7 @@
         <v>0.33</v>
       </c>
       <c r="AP100" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ100" t="n">
         <v>0.64</v>
@@ -22493,10 +22493,10 @@
         <v>0.8</v>
       </c>
       <c r="AP101" t="n">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR101" t="n">
         <v>1.06</v>
@@ -22714,7 +22714,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR102" t="n">
         <v>1.42</v>
@@ -22929,7 +22929,7 @@
         <v>2</v>
       </c>
       <c r="AP103" t="n">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AQ103" t="n">
         <v>1.75</v>
@@ -23147,7 +23147,7 @@
         <v>1.67</v>
       </c>
       <c r="AP104" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ104" t="n">
         <v>1.75</v>
@@ -23365,7 +23365,7 @@
         <v>0.8</v>
       </c>
       <c r="AP105" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ105" t="n">
         <v>1</v>
@@ -23586,7 +23586,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ106" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR106" t="n">
         <v>1.41</v>
@@ -23804,7 +23804,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR107" t="n">
         <v>1.27</v>
@@ -24019,10 +24019,10 @@
         <v>1.33</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR108" t="n">
         <v>1.28</v>
@@ -24240,7 +24240,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AR109" t="n">
         <v>1.43</v>
@@ -24455,10 +24455,10 @@
         <v>0.8</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AQ110" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR110" t="n">
         <v>1.93</v>
@@ -24673,10 +24673,10 @@
         <v>1.8</v>
       </c>
       <c r="AP111" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AR111" t="n">
         <v>1.39</v>
@@ -24891,7 +24891,7 @@
         <v>1.2</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ112" t="n">
         <v>0.87</v>
@@ -25109,10 +25109,10 @@
         <v>0.2</v>
       </c>
       <c r="AP113" t="n">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AQ113" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR113" t="n">
         <v>1.32</v>
@@ -25327,10 +25327,10 @@
         <v>0.8</v>
       </c>
       <c r="AP114" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR114" t="n">
         <v>1.33</v>
@@ -25548,7 +25548,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ115" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR115" t="n">
         <v>1.17</v>
@@ -25763,7 +25763,7 @@
         <v>0.5</v>
       </c>
       <c r="AP116" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="AQ116" t="n">
         <v>0.64</v>
@@ -25984,7 +25984,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR117" t="n">
         <v>1.46</v>
@@ -26199,10 +26199,10 @@
         <v>0.17</v>
       </c>
       <c r="AP118" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ118" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR118" t="n">
         <v>1.59</v>
@@ -26417,10 +26417,10 @@
         <v>1</v>
       </c>
       <c r="AP119" t="n">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR119" t="n">
         <v>1.3</v>
@@ -26635,7 +26635,7 @@
         <v>0.83</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ120" t="n">
         <v>1</v>
@@ -26853,10 +26853,10 @@
         <v>0.8</v>
       </c>
       <c r="AP121" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ121" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR121" t="n">
         <v>1.28</v>
@@ -27071,10 +27071,10 @@
         <v>1.17</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ122" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR122" t="n">
         <v>1.28</v>
@@ -27292,7 +27292,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ123" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR123" t="n">
         <v>1.43</v>
@@ -27507,10 +27507,10 @@
         <v>1.2</v>
       </c>
       <c r="AP124" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR124" t="n">
         <v>1.14</v>
@@ -27943,10 +27943,10 @@
         <v>2</v>
       </c>
       <c r="AP126" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AR126" t="n">
         <v>1.18</v>
@@ -28161,7 +28161,7 @@
         <v>1.86</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ127" t="n">
         <v>1.75</v>
@@ -28379,10 +28379,10 @@
         <v>1.8</v>
       </c>
       <c r="AP128" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR128" t="n">
         <v>1.44</v>
@@ -28597,10 +28597,10 @@
         <v>2.17</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AQ129" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AR129" t="n">
         <v>1.94</v>
@@ -28818,7 +28818,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR130" t="n">
         <v>1.47</v>
@@ -29036,7 +29036,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ131" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR131" t="n">
         <v>1.21</v>
@@ -29251,10 +29251,10 @@
         <v>0.83</v>
       </c>
       <c r="AP132" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ132" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR132" t="n">
         <v>1.39</v>
@@ -29472,7 +29472,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ133" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR133" t="n">
         <v>1.49</v>
@@ -29687,10 +29687,10 @@
         <v>1.14</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ134" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR134" t="n">
         <v>1.47</v>
@@ -29905,10 +29905,10 @@
         <v>2.29</v>
       </c>
       <c r="AP135" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AR135" t="n">
         <v>1.55</v>
@@ -30123,7 +30123,7 @@
         <v>1.43</v>
       </c>
       <c r="AP136" t="n">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AQ136" t="n">
         <v>0.87</v>
@@ -30341,10 +30341,10 @@
         <v>0.67</v>
       </c>
       <c r="AP137" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR137" t="n">
         <v>1.37</v>
@@ -30562,7 +30562,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ138" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR138" t="n">
         <v>1.59</v>
@@ -30780,7 +30780,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR139" t="n">
         <v>1.5</v>
@@ -30995,7 +30995,7 @@
         <v>0.71</v>
       </c>
       <c r="AP140" t="n">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AQ140" t="n">
         <v>1</v>
@@ -31213,10 +31213,10 @@
         <v>0.67</v>
       </c>
       <c r="AP141" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ141" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR141" t="n">
         <v>1.22</v>
@@ -31431,10 +31431,10 @@
         <v>1.43</v>
       </c>
       <c r="AP142" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ142" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR142" t="n">
         <v>1.35</v>
@@ -31649,7 +31649,7 @@
         <v>0.4</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ143" t="n">
         <v>0.64</v>
@@ -32085,10 +32085,10 @@
         <v>0.8</v>
       </c>
       <c r="AP145" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ145" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR145" t="n">
         <v>1.35</v>
@@ -32303,10 +32303,10 @@
         <v>1.43</v>
       </c>
       <c r="AP146" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR146" t="n">
         <v>1.13</v>
@@ -32521,7 +32521,7 @@
         <v>2</v>
       </c>
       <c r="AP147" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ147" t="n">
         <v>1.8</v>
@@ -32739,10 +32739,10 @@
         <v>0.71</v>
       </c>
       <c r="AP148" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR148" t="n">
         <v>1.29</v>
@@ -32960,7 +32960,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ149" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AR149" t="n">
         <v>1.17</v>
@@ -33175,10 +33175,10 @@
         <v>1.43</v>
       </c>
       <c r="AP150" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR150" t="n">
         <v>1.51</v>
@@ -33393,10 +33393,10 @@
         <v>0.5</v>
       </c>
       <c r="AP151" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="AQ151" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR151" t="n">
         <v>1.48</v>
@@ -33611,7 +33611,7 @@
         <v>1</v>
       </c>
       <c r="AP152" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ152" t="n">
         <v>0.86</v>
@@ -33829,10 +33829,10 @@
         <v>1.17</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR153" t="n">
         <v>1.46</v>
@@ -34047,10 +34047,10 @@
         <v>0.17</v>
       </c>
       <c r="AP154" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AQ154" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR154" t="n">
         <v>1.78</v>
@@ -34265,10 +34265,10 @@
         <v>1</v>
       </c>
       <c r="AP155" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ155" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR155" t="n">
         <v>1.27</v>
@@ -34483,10 +34483,10 @@
         <v>2.14</v>
       </c>
       <c r="AP156" t="n">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AR156" t="n">
         <v>1.22</v>
@@ -34701,7 +34701,7 @@
         <v>0.33</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ157" t="n">
         <v>0.64</v>
@@ -34919,7 +34919,7 @@
         <v>1.78</v>
       </c>
       <c r="AP158" t="n">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ158" t="n">
         <v>1.75</v>
@@ -35358,7 +35358,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ160" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AR160" t="n">
         <v>1.29</v>
@@ -35794,7 +35794,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ162" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR162" t="n">
         <v>1.48</v>
@@ -36009,10 +36009,10 @@
         <v>1.25</v>
       </c>
       <c r="AP163" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ163" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR163" t="n">
         <v>1.5</v>
@@ -36227,7 +36227,7 @@
         <v>0.29</v>
       </c>
       <c r="AP164" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ164" t="n">
         <v>0.64</v>
@@ -36445,10 +36445,10 @@
         <v>1.14</v>
       </c>
       <c r="AP165" t="n">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AQ165" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR165" t="n">
         <v>1.24</v>
@@ -36663,10 +36663,10 @@
         <v>1.25</v>
       </c>
       <c r="AP166" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ166" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR166" t="n">
         <v>1.53</v>
@@ -36884,7 +36884,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ167" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR167" t="n">
         <v>1.4</v>
@@ -37099,7 +37099,7 @@
         <v>1</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ168" t="n">
         <v>0.86</v>
@@ -37317,7 +37317,7 @@
         <v>1.67</v>
       </c>
       <c r="AP169" t="n">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ169" t="n">
         <v>1.8</v>
@@ -37535,10 +37535,10 @@
         <v>1.25</v>
       </c>
       <c r="AP170" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AQ170" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR170" t="n">
         <v>1.74</v>
@@ -37753,7 +37753,7 @@
         <v>1</v>
       </c>
       <c r="AP171" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ171" t="n">
         <v>0.86</v>
@@ -37974,7 +37974,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ172" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AR172" t="n">
         <v>1.53</v>
@@ -38189,10 +38189,10 @@
         <v>1.71</v>
       </c>
       <c r="AP173" t="n">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ173" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR173" t="n">
         <v>1.26</v>
@@ -38407,10 +38407,10 @@
         <v>2</v>
       </c>
       <c r="AP174" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ174" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AR174" t="n">
         <v>1.14</v>
@@ -38625,10 +38625,10 @@
         <v>1.22</v>
       </c>
       <c r="AP175" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ175" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR175" t="n">
         <v>1.37</v>
@@ -39061,7 +39061,7 @@
         <v>1.9</v>
       </c>
       <c r="AP177" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ177" t="n">
         <v>1.75</v>
@@ -39279,10 +39279,10 @@
         <v>1.43</v>
       </c>
       <c r="AP178" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ178" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR178" t="n">
         <v>1.36</v>
@@ -39497,7 +39497,7 @@
         <v>0.89</v>
       </c>
       <c r="AP179" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ179" t="n">
         <v>1</v>
@@ -39715,10 +39715,10 @@
         <v>1.11</v>
       </c>
       <c r="AP180" t="n">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AQ180" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR180" t="n">
         <v>1.35</v>
@@ -39933,10 +39933,10 @@
         <v>1</v>
       </c>
       <c r="AP181" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ181" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR181" t="n">
         <v>1.34</v>
@@ -40154,7 +40154,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ182" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR182" t="n">
         <v>1.29</v>
@@ -40587,7 +40587,7 @@
         <v>1.63</v>
       </c>
       <c r="AP184" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ184" t="n">
         <v>1.8</v>
@@ -40808,7 +40808,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ185" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR185" t="n">
         <v>1.56</v>
@@ -41023,10 +41023,10 @@
         <v>1.5</v>
       </c>
       <c r="AP186" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ186" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR186" t="n">
         <v>1.45</v>
@@ -41241,10 +41241,10 @@
         <v>1</v>
       </c>
       <c r="AP187" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="AQ187" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR187" t="n">
         <v>1.45</v>
@@ -41459,10 +41459,10 @@
         <v>0.63</v>
       </c>
       <c r="AP188" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ188" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR188" t="n">
         <v>1.32</v>
@@ -41677,10 +41677,10 @@
         <v>1.11</v>
       </c>
       <c r="AP189" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AQ189" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR189" t="n">
         <v>1.73</v>
@@ -41895,7 +41895,7 @@
         <v>0.63</v>
       </c>
       <c r="AP190" t="n">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AQ190" t="n">
         <v>0.64</v>
@@ -42113,10 +42113,10 @@
         <v>1.8</v>
       </c>
       <c r="AP191" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ191" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AR191" t="n">
         <v>1.3</v>
@@ -42331,10 +42331,10 @@
         <v>1.63</v>
       </c>
       <c r="AP192" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ192" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR192" t="n">
         <v>1.46</v>
@@ -42549,10 +42549,10 @@
         <v>1.44</v>
       </c>
       <c r="AP193" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ193" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR193" t="n">
         <v>1.15</v>
@@ -42767,10 +42767,10 @@
         <v>1.1</v>
       </c>
       <c r="AP194" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ194" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR194" t="n">
         <v>1.3</v>
@@ -42985,10 +42985,10 @@
         <v>0.5</v>
       </c>
       <c r="AP195" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ195" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR195" t="n">
         <v>1.34</v>
@@ -43206,7 +43206,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ196" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR196" t="n">
         <v>1.67</v>
@@ -43424,7 +43424,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ197" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR197" t="n">
         <v>1.48</v>
@@ -43639,10 +43639,10 @@
         <v>1.9</v>
       </c>
       <c r="AP198" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ198" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AR198" t="n">
         <v>1.23</v>
@@ -44078,7 +44078,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ200" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR200" t="n">
         <v>1.37</v>
@@ -44296,7 +44296,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ201" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR201" t="n">
         <v>1.36</v>
@@ -44511,7 +44511,7 @@
         <v>1.1</v>
       </c>
       <c r="AP202" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AQ202" t="n">
         <v>0.87</v>
@@ -44729,10 +44729,10 @@
         <v>0.67</v>
       </c>
       <c r="AP203" t="n">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ203" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR203" t="n">
         <v>1.22</v>
@@ -44947,10 +44947,10 @@
         <v>1</v>
       </c>
       <c r="AP204" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ204" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR204" t="n">
         <v>1.38</v>
@@ -45165,7 +45165,7 @@
         <v>1.73</v>
       </c>
       <c r="AP205" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ205" t="n">
         <v>1.75</v>
@@ -45383,7 +45383,7 @@
         <v>1.78</v>
       </c>
       <c r="AP206" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ206" t="n">
         <v>1.8</v>
@@ -45601,10 +45601,10 @@
         <v>1.56</v>
       </c>
       <c r="AP207" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ207" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR207" t="n">
         <v>1.14</v>
@@ -45819,10 +45819,10 @@
         <v>0.89</v>
       </c>
       <c r="AP208" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ208" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR208" t="n">
         <v>1.52</v>
@@ -46037,10 +46037,10 @@
         <v>0.8</v>
       </c>
       <c r="AP209" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ209" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR209" t="n">
         <v>1.45</v>
@@ -46255,10 +46255,10 @@
         <v>0.8</v>
       </c>
       <c r="AP210" t="n">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ210" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR210" t="n">
         <v>1.24</v>
@@ -46473,10 +46473,10 @@
         <v>0.9</v>
       </c>
       <c r="AP211" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ211" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR211" t="n">
         <v>1.49</v>
@@ -46694,7 +46694,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ212" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AR212" t="n">
         <v>1.3</v>
@@ -46909,7 +46909,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP213" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ213" t="n">
         <v>0.64</v>
@@ -47127,10 +47127,10 @@
         <v>0.44</v>
       </c>
       <c r="AP214" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ214" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR214" t="n">
         <v>1.28</v>
@@ -47563,7 +47563,7 @@
         <v>0.91</v>
       </c>
       <c r="AP216" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="AQ216" t="n">
         <v>1</v>
@@ -47784,7 +47784,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ217" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR217" t="n">
         <v>1.61</v>
@@ -47999,10 +47999,10 @@
         <v>1.6</v>
       </c>
       <c r="AP218" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ218" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR218" t="n">
         <v>1.16</v>
@@ -48217,10 +48217,10 @@
         <v>1.91</v>
       </c>
       <c r="AP219" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ219" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AR219" t="n">
         <v>1.4</v>
@@ -48438,7 +48438,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ220" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR220" t="n">
         <v>1.71</v>
@@ -48656,7 +48656,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ221" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR221" t="n">
         <v>1.38</v>
@@ -48874,7 +48874,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ222" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR222" t="n">
         <v>1.41</v>
@@ -49089,10 +49089,10 @@
         <v>1</v>
       </c>
       <c r="AP223" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ223" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR223" t="n">
         <v>1.46</v>
@@ -49307,10 +49307,10 @@
         <v>1.5</v>
       </c>
       <c r="AP224" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ224" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR224" t="n">
         <v>1.42</v>
@@ -49525,10 +49525,10 @@
         <v>0.5</v>
       </c>
       <c r="AP225" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ225" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR225" t="n">
         <v>1.15</v>
@@ -49743,7 +49743,7 @@
         <v>1</v>
       </c>
       <c r="AP226" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ226" t="n">
         <v>0.87</v>
@@ -49961,10 +49961,10 @@
         <v>0.73</v>
       </c>
       <c r="AP227" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="AQ227" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR227" t="n">
         <v>1.47</v>
@@ -50179,7 +50179,7 @@
         <v>0.83</v>
       </c>
       <c r="AP228" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AQ228" t="n">
         <v>1</v>
@@ -50400,7 +50400,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ229" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR229" t="n">
         <v>1.68</v>
@@ -50615,7 +50615,7 @@
         <v>0.9</v>
       </c>
       <c r="AP230" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ230" t="n">
         <v>0.86</v>
@@ -50833,10 +50833,10 @@
         <v>1.09</v>
       </c>
       <c r="AP231" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ231" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR231" t="n">
         <v>1.26</v>
@@ -51051,10 +51051,10 @@
         <v>2.08</v>
       </c>
       <c r="AP232" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ232" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AR232" t="n">
         <v>1.54</v>
@@ -51269,10 +51269,10 @@
         <v>2</v>
       </c>
       <c r="AP233" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ233" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AR233" t="n">
         <v>1.14</v>
@@ -51705,10 +51705,10 @@
         <v>0.75</v>
       </c>
       <c r="AP235" t="n">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ235" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR235" t="n">
         <v>1.24</v>
@@ -51923,10 +51923,10 @@
         <v>1.67</v>
       </c>
       <c r="AP236" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ236" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR236" t="n">
         <v>1.43</v>
@@ -52141,10 +52141,10 @@
         <v>1.45</v>
       </c>
       <c r="AP237" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ237" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR237" t="n">
         <v>1.53</v>
@@ -52795,10 +52795,10 @@
         <v>1</v>
       </c>
       <c r="AP240" t="n">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AQ240" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR240" t="n">
         <v>1.37</v>
@@ -53013,10 +53013,10 @@
         <v>1.3</v>
       </c>
       <c r="AP241" t="n">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AQ241" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR241" t="n">
         <v>1.37</v>
@@ -53231,7 +53231,7 @@
         <v>0.82</v>
       </c>
       <c r="AP242" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ242" t="n">
         <v>0.86</v>
@@ -53449,10 +53449,10 @@
         <v>0.73</v>
       </c>
       <c r="AP243" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ243" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR243" t="n">
         <v>1.18</v>
@@ -53667,10 +53667,10 @@
         <v>1.27</v>
       </c>
       <c r="AP244" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ244" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR244" t="n">
         <v>1.46</v>
@@ -53888,7 +53888,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ245" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR245" t="n">
         <v>1.62</v>
@@ -54103,10 +54103,10 @@
         <v>1.36</v>
       </c>
       <c r="AP246" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ246" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR246" t="n">
         <v>1.5</v>
@@ -54321,7 +54321,7 @@
         <v>1.62</v>
       </c>
       <c r="AP247" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ247" t="n">
         <v>1.75</v>
@@ -54539,10 +54539,10 @@
         <v>1.09</v>
       </c>
       <c r="AP248" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ248" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR248" t="n">
         <v>1.55</v>
@@ -54975,10 +54975,10 @@
         <v>0.92</v>
       </c>
       <c r="AP250" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ250" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR250" t="n">
         <v>1.45</v>
@@ -55193,10 +55193,10 @@
         <v>0.67</v>
       </c>
       <c r="AP251" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AQ251" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR251" t="n">
         <v>1.73</v>
@@ -55411,10 +55411,10 @@
         <v>1.42</v>
       </c>
       <c r="AP252" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ252" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR252" t="n">
         <v>1.48</v>
@@ -55632,7 +55632,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ253" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR253" t="n">
         <v>1.33</v>
@@ -56283,10 +56283,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP256" t="n">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AQ256" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR256" t="n">
         <v>1.37</v>
@@ -56504,7 +56504,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ257" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR257" t="n">
         <v>1.4</v>
@@ -56719,10 +56719,10 @@
         <v>0.92</v>
       </c>
       <c r="AP258" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ258" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR258" t="n">
         <v>1.29</v>
@@ -56937,10 +56937,10 @@
         <v>1.33</v>
       </c>
       <c r="AP259" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ259" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR259" t="n">
         <v>1.4</v>
@@ -57155,7 +57155,7 @@
         <v>1</v>
       </c>
       <c r="AP260" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="AQ260" t="n">
         <v>0.87</v>
@@ -57376,7 +57376,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ261" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AR261" t="n">
         <v>1.31</v>
@@ -58027,7 +58027,7 @@
         <v>1</v>
       </c>
       <c r="AP264" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ264" t="n">
         <v>0.86</v>
@@ -58248,7 +58248,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ265" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR265" t="n">
         <v>1.32</v>
@@ -58463,10 +58463,10 @@
         <v>1.77</v>
       </c>
       <c r="AP266" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ266" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR266" t="n">
         <v>1.17</v>
@@ -58681,10 +58681,10 @@
         <v>1.5</v>
       </c>
       <c r="AP267" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ267" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR267" t="n">
         <v>1.41</v>
@@ -58899,10 +58899,10 @@
         <v>1.31</v>
       </c>
       <c r="AP268" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ268" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR268" t="n">
         <v>1.27</v>
@@ -59117,7 +59117,7 @@
         <v>0.67</v>
       </c>
       <c r="AP269" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ269" t="n">
         <v>0.64</v>
@@ -59335,7 +59335,7 @@
         <v>1.86</v>
       </c>
       <c r="AP270" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AQ270" t="n">
         <v>1.8</v>
@@ -59556,7 +59556,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ271" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR271" t="n">
         <v>1.34</v>
@@ -59771,10 +59771,10 @@
         <v>2.08</v>
       </c>
       <c r="AP272" t="n">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ272" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AR272" t="n">
         <v>1.27</v>
@@ -59989,7 +59989,7 @@
         <v>1.71</v>
       </c>
       <c r="AP273" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ273" t="n">
         <v>1.75</v>
@@ -60207,7 +60207,7 @@
         <v>0.92</v>
       </c>
       <c r="AP274" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ274" t="n">
         <v>0.87</v>
@@ -60425,10 +60425,10 @@
         <v>1.25</v>
       </c>
       <c r="AP275" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="AQ275" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR275" t="n">
         <v>1.48</v>
@@ -60646,7 +60646,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ276" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR276" t="n">
         <v>1.7</v>
@@ -60864,7 +60864,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ277" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR277" t="n">
         <v>1.38</v>
@@ -61079,7 +61079,7 @@
         <v>0.87</v>
       </c>
       <c r="AP278" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ278" t="n">
         <v>1</v>
@@ -61297,10 +61297,10 @@
         <v>0.92</v>
       </c>
       <c r="AP279" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ279" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR279" t="n">
         <v>1.28</v>
@@ -61515,10 +61515,10 @@
         <v>1.86</v>
       </c>
       <c r="AP280" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AQ280" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AR280" t="n">
         <v>1.76</v>
@@ -61733,10 +61733,10 @@
         <v>1.38</v>
       </c>
       <c r="AP281" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ281" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AR281" t="n">
         <v>1.55</v>
@@ -61951,10 +61951,10 @@
         <v>0.62</v>
       </c>
       <c r="AP282" t="n">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AQ282" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR282" t="n">
         <v>1.36</v>
@@ -62169,10 +62169,10 @@
         <v>2</v>
       </c>
       <c r="AP283" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ283" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AR283" t="n">
         <v>1.42</v>
@@ -62826,7 +62826,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ286" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AR286" t="n">
         <v>1.66</v>
@@ -63044,7 +63044,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ287" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR287" t="n">
         <v>1.35</v>
@@ -63262,7 +63262,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ288" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR288" t="n">
         <v>1.35</v>
@@ -63477,10 +63477,10 @@
         <v>0.79</v>
       </c>
       <c r="AP289" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ289" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR289" t="n">
         <v>1.47</v>
@@ -63695,10 +63695,10 @@
         <v>0.93</v>
       </c>
       <c r="AP290" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ290" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AR290" t="n">
         <v>1.4</v>
@@ -63913,7 +63913,7 @@
         <v>0.92</v>
       </c>
       <c r="AP291" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ291" t="n">
         <v>0.86</v>
@@ -64131,10 +64131,10 @@
         <v>1.43</v>
       </c>
       <c r="AP292" t="n">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AQ292" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR292" t="n">
         <v>1.24</v>
@@ -64349,7 +64349,7 @@
         <v>0.93</v>
       </c>
       <c r="AP293" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ293" t="n">
         <v>0.87</v>
@@ -64428,6 +64428,3276 @@
       </c>
       <c r="BP293" t="n">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="n">
+        <v>293</v>
+      </c>
+      <c r="B294" t="n">
+        <v>7778368</v>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="n">
+        <v>45920.20833333334</v>
+      </c>
+      <c r="F294" t="n">
+        <v>30</v>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>Nagoya Grampus</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>Shonan Bellmare</t>
+        </is>
+      </c>
+      <c r="I294" t="n">
+        <v>3</v>
+      </c>
+      <c r="J294" t="n">
+        <v>0</v>
+      </c>
+      <c r="K294" t="n">
+        <v>3</v>
+      </c>
+      <c r="L294" t="n">
+        <v>3</v>
+      </c>
+      <c r="M294" t="n">
+        <v>1</v>
+      </c>
+      <c r="N294" t="n">
+        <v>4</v>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>['19', '31', '45+3']</t>
+        </is>
+      </c>
+      <c r="P294" t="inlineStr">
+        <is>
+          <t>['78']</t>
+        </is>
+      </c>
+      <c r="Q294" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R294" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="S294" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="T294" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="U294" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="V294" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W294" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X294" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Y294" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z294" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA294" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB294" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC294" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD294" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE294" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AF294" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AG294" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH294" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI294" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ294" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK294" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL294" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM294" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AN294" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO294" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AP294" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AQ294" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR294" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AS294" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AT294" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AU294" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV294" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW294" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX294" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY294" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ294" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA294" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB294" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC294" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD294" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BE294" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF294" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BG294" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH294" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI294" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BJ294" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BK294" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BL294" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BM294" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BN294" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BO294" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP294" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="n">
+        <v>294</v>
+      </c>
+      <c r="B295" t="n">
+        <v>7778364</v>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E295" s="2" t="n">
+        <v>45920.25</v>
+      </c>
+      <c r="F295" t="n">
+        <v>30</v>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>Tokyo Verdy</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>Fagiano Okayama</t>
+        </is>
+      </c>
+      <c r="I295" t="n">
+        <v>2</v>
+      </c>
+      <c r="J295" t="n">
+        <v>2</v>
+      </c>
+      <c r="K295" t="n">
+        <v>4</v>
+      </c>
+      <c r="L295" t="n">
+        <v>4</v>
+      </c>
+      <c r="M295" t="n">
+        <v>2</v>
+      </c>
+      <c r="N295" t="n">
+        <v>6</v>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>['8', '45+4', '69', '88']</t>
+        </is>
+      </c>
+      <c r="P295" t="inlineStr">
+        <is>
+          <t>['37', '45+3']</t>
+        </is>
+      </c>
+      <c r="Q295" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R295" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S295" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T295" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U295" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V295" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="W295" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X295" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y295" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z295" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA295" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AB295" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AC295" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD295" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AE295" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF295" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG295" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH295" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI295" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AJ295" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AK295" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AL295" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AM295" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN295" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO295" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AP295" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AQ295" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AR295" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AS295" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AT295" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AU295" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV295" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW295" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX295" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY295" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ295" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA295" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB295" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC295" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD295" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BE295" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF295" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BG295" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH295" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI295" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ295" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BK295" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BL295" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BM295" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BN295" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BO295" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BP295" t="n">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="n">
+        <v>295</v>
+      </c>
+      <c r="B296" t="n">
+        <v>7778367</v>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E296" s="2" t="n">
+        <v>45920.25</v>
+      </c>
+      <c r="F296" t="n">
+        <v>30</v>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>Yokohama</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>Albirex Niigata</t>
+        </is>
+      </c>
+      <c r="I296" t="n">
+        <v>0</v>
+      </c>
+      <c r="J296" t="n">
+        <v>0</v>
+      </c>
+      <c r="K296" t="n">
+        <v>0</v>
+      </c>
+      <c r="L296" t="n">
+        <v>1</v>
+      </c>
+      <c r="M296" t="n">
+        <v>0</v>
+      </c>
+      <c r="N296" t="n">
+        <v>1</v>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>['86']</t>
+        </is>
+      </c>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q296" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R296" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="S296" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="T296" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U296" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V296" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W296" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X296" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y296" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z296" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AA296" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AB296" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AC296" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD296" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="AE296" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF296" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AG296" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH296" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI296" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AJ296" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK296" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AL296" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AM296" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN296" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO296" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AP296" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ296" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AR296" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AS296" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AT296" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AU296" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV296" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW296" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX296" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY296" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ296" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA296" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB296" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC296" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD296" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BE296" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF296" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BG296" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BH296" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BI296" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BJ296" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BK296" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BL296" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BM296" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BN296" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BO296" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP296" t="n">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="n">
+        <v>296</v>
+      </c>
+      <c r="B297" t="n">
+        <v>7778370</v>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="n">
+        <v>45920.27083333334</v>
+      </c>
+      <c r="F297" t="n">
+        <v>30</v>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>Cerezo Osaka</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>Kashiwa Reysol</t>
+        </is>
+      </c>
+      <c r="I297" t="n">
+        <v>1</v>
+      </c>
+      <c r="J297" t="n">
+        <v>1</v>
+      </c>
+      <c r="K297" t="n">
+        <v>2</v>
+      </c>
+      <c r="L297" t="n">
+        <v>1</v>
+      </c>
+      <c r="M297" t="n">
+        <v>1</v>
+      </c>
+      <c r="N297" t="n">
+        <v>2</v>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>['40']</t>
+        </is>
+      </c>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>['25']</t>
+        </is>
+      </c>
+      <c r="Q297" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R297" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="S297" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T297" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U297" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V297" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W297" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X297" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="Y297" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z297" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AA297" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AB297" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AC297" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD297" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE297" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF297" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AG297" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH297" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI297" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ297" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK297" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL297" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM297" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN297" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO297" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AP297" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AQ297" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AR297" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS297" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AT297" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU297" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV297" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW297" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX297" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY297" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ297" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA297" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB297" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC297" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD297" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BE297" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF297" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BG297" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH297" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="BI297" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BJ297" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BK297" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BL297" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BM297" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BN297" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BO297" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BP297" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="n">
+        <v>297</v>
+      </c>
+      <c r="B298" t="n">
+        <v>7778363</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E298" s="2" t="n">
+        <v>45920.29166666666</v>
+      </c>
+      <c r="F298" t="n">
+        <v>30</v>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>Urawa Reds</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>Kashima Antlers</t>
+        </is>
+      </c>
+      <c r="I298" t="n">
+        <v>0</v>
+      </c>
+      <c r="J298" t="n">
+        <v>1</v>
+      </c>
+      <c r="K298" t="n">
+        <v>1</v>
+      </c>
+      <c r="L298" t="n">
+        <v>0</v>
+      </c>
+      <c r="M298" t="n">
+        <v>1</v>
+      </c>
+      <c r="N298" t="n">
+        <v>1</v>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>['14']</t>
+        </is>
+      </c>
+      <c r="Q298" t="n">
+        <v>3</v>
+      </c>
+      <c r="R298" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="S298" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T298" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U298" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V298" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W298" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X298" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Y298" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z298" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AA298" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AB298" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AC298" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD298" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE298" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF298" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AG298" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH298" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AI298" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AJ298" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK298" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL298" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AM298" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AN298" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO298" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AP298" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AQ298" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR298" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AS298" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AT298" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AU298" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV298" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW298" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX298" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY298" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ298" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA298" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB298" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC298" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD298" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE298" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF298" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG298" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH298" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="BI298" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ298" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BK298" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BL298" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BM298" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BN298" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BO298" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BP298" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="n">
+        <v>298</v>
+      </c>
+      <c r="B299" t="n">
+        <v>7778366</v>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E299" s="2" t="n">
+        <v>45920.29166666666</v>
+      </c>
+      <c r="F299" t="n">
+        <v>30</v>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>Yokohama F. Marinos</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>Avispa Fukuoka</t>
+        </is>
+      </c>
+      <c r="I299" t="n">
+        <v>2</v>
+      </c>
+      <c r="J299" t="n">
+        <v>0</v>
+      </c>
+      <c r="K299" t="n">
+        <v>2</v>
+      </c>
+      <c r="L299" t="n">
+        <v>2</v>
+      </c>
+      <c r="M299" t="n">
+        <v>0</v>
+      </c>
+      <c r="N299" t="n">
+        <v>2</v>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>['20', '42']</t>
+        </is>
+      </c>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q299" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="R299" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="S299" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="T299" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U299" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V299" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W299" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X299" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="Y299" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z299" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA299" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AB299" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AC299" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD299" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE299" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF299" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG299" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH299" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI299" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AJ299" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AK299" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AL299" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM299" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN299" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AO299" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AP299" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AQ299" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AR299" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AS299" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AT299" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AU299" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV299" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW299" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX299" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY299" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ299" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA299" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB299" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC299" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD299" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BE299" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF299" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG299" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH299" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI299" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ299" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BK299" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BL299" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BM299" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BN299" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BO299" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BP299" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="B300" t="n">
+        <v>7778365</v>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="n">
+        <v>45920.29166666666</v>
+      </c>
+      <c r="F300" t="n">
+        <v>30</v>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>Kawasaki Frontale</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="I300" t="n">
+        <v>0</v>
+      </c>
+      <c r="J300" t="n">
+        <v>1</v>
+      </c>
+      <c r="K300" t="n">
+        <v>1</v>
+      </c>
+      <c r="L300" t="n">
+        <v>0</v>
+      </c>
+      <c r="M300" t="n">
+        <v>1</v>
+      </c>
+      <c r="N300" t="n">
+        <v>1</v>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>['23']</t>
+        </is>
+      </c>
+      <c r="Q300" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R300" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S300" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T300" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U300" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="V300" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="W300" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X300" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Y300" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z300" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA300" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AB300" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AC300" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD300" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE300" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF300" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AG300" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AH300" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AI300" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AJ300" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AK300" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL300" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AM300" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN300" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AO300" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AP300" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ300" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AR300" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AS300" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AT300" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU300" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV300" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW300" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX300" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY300" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ300" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA300" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB300" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC300" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD300" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BE300" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF300" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BG300" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH300" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BI300" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ300" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BK300" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BL300" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BM300" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BN300" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BO300" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BP300" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="B301" t="n">
+        <v>7778369</v>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E301" s="2" t="n">
+        <v>45920.29166666666</v>
+      </c>
+      <c r="F301" t="n">
+        <v>30</v>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>Kyoto Sanga</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>Shimizu S-Pulse</t>
+        </is>
+      </c>
+      <c r="I301" t="n">
+        <v>0</v>
+      </c>
+      <c r="J301" t="n">
+        <v>0</v>
+      </c>
+      <c r="K301" t="n">
+        <v>0</v>
+      </c>
+      <c r="L301" t="n">
+        <v>0</v>
+      </c>
+      <c r="M301" t="n">
+        <v>1</v>
+      </c>
+      <c r="N301" t="n">
+        <v>1</v>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P301" t="inlineStr">
+        <is>
+          <t>['75']</t>
+        </is>
+      </c>
+      <c r="Q301" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R301" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="S301" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="T301" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U301" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V301" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W301" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X301" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y301" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z301" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AA301" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB301" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="AC301" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD301" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE301" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AF301" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AG301" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AH301" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AI301" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AJ301" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AK301" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AL301" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM301" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AN301" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AO301" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AP301" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AQ301" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AR301" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS301" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT301" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AU301" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV301" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW301" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX301" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY301" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ301" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA301" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB301" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC301" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD301" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BE301" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF301" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BG301" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH301" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BI301" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ301" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK301" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BL301" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BM301" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BN301" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BO301" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BP301" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="n">
+        <v>301</v>
+      </c>
+      <c r="B302" t="n">
+        <v>7778377</v>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E302" s="2" t="n">
+        <v>45923.08333333334</v>
+      </c>
+      <c r="F302" t="n">
+        <v>31</v>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>Albirex Niigata</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>Nagoya Grampus</t>
+        </is>
+      </c>
+      <c r="I302" t="n">
+        <v>0</v>
+      </c>
+      <c r="J302" t="n">
+        <v>0</v>
+      </c>
+      <c r="K302" t="n">
+        <v>0</v>
+      </c>
+      <c r="L302" t="n">
+        <v>0</v>
+      </c>
+      <c r="M302" t="n">
+        <v>0</v>
+      </c>
+      <c r="N302" t="n">
+        <v>0</v>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q302" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="R302" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="S302" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T302" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U302" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="V302" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="W302" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X302" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="Y302" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z302" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AA302" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AB302" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AC302" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD302" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AE302" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF302" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AG302" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH302" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AI302" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ302" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AK302" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL302" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AM302" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN302" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AO302" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AP302" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AQ302" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AR302" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AS302" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AT302" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AU302" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV302" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW302" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX302" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY302" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ302" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA302" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB302" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC302" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD302" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE302" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF302" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG302" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH302" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI302" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ302" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK302" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL302" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM302" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN302" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO302" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP302" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="n">
+        <v>302</v>
+      </c>
+      <c r="B303" t="n">
+        <v>7778373</v>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E303" s="2" t="n">
+        <v>45923.25</v>
+      </c>
+      <c r="F303" t="n">
+        <v>31</v>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>Kashima Antlers</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>Cerezo Osaka</t>
+        </is>
+      </c>
+      <c r="I303" t="n">
+        <v>1</v>
+      </c>
+      <c r="J303" t="n">
+        <v>1</v>
+      </c>
+      <c r="K303" t="n">
+        <v>2</v>
+      </c>
+      <c r="L303" t="n">
+        <v>3</v>
+      </c>
+      <c r="M303" t="n">
+        <v>1</v>
+      </c>
+      <c r="N303" t="n">
+        <v>4</v>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>['31', '53', '68']</t>
+        </is>
+      </c>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>['28']</t>
+        </is>
+      </c>
+      <c r="Q303" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R303" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S303" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="T303" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="U303" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V303" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W303" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X303" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="Y303" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z303" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA303" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB303" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC303" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD303" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="AE303" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF303" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AG303" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH303" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI303" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AJ303" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK303" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AL303" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM303" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AN303" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AO303" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AP303" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AQ303" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AR303" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS303" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AT303" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AU303" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV303" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW303" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX303" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY303" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ303" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA303" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB303" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC303" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD303" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BE303" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF303" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BG303" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH303" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI303" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BJ303" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BK303" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BL303" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BM303" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BN303" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BO303" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP303" t="n">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="n">
+        <v>303</v>
+      </c>
+      <c r="B304" t="n">
+        <v>7778375</v>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E304" s="2" t="n">
+        <v>45923.25</v>
+      </c>
+      <c r="F304" t="n">
+        <v>31</v>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>Avispa Fukuoka</t>
+        </is>
+      </c>
+      <c r="I304" t="n">
+        <v>1</v>
+      </c>
+      <c r="J304" t="n">
+        <v>0</v>
+      </c>
+      <c r="K304" t="n">
+        <v>1</v>
+      </c>
+      <c r="L304" t="n">
+        <v>1</v>
+      </c>
+      <c r="M304" t="n">
+        <v>0</v>
+      </c>
+      <c r="N304" t="n">
+        <v>1</v>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>['41']</t>
+        </is>
+      </c>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q304" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="R304" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S304" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="T304" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U304" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="V304" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="W304" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X304" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Y304" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z304" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AA304" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AB304" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC304" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD304" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE304" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF304" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG304" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH304" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI304" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AJ304" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AK304" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL304" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM304" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AN304" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO304" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AP304" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ304" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AR304" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS304" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AT304" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AU304" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV304" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW304" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX304" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY304" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ304" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA304" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB304" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC304" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD304" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BE304" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF304" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BG304" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH304" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI304" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ304" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BK304" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BL304" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM304" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BN304" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO304" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BP304" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="n">
+        <v>304</v>
+      </c>
+      <c r="B305" t="n">
+        <v>7778380</v>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E305" s="2" t="n">
+        <v>45923.29166666666</v>
+      </c>
+      <c r="F305" t="n">
+        <v>31</v>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>Gamba Osaka</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>Yokohama F. Marinos</t>
+        </is>
+      </c>
+      <c r="I305" t="n">
+        <v>0</v>
+      </c>
+      <c r="J305" t="n">
+        <v>0</v>
+      </c>
+      <c r="K305" t="n">
+        <v>0</v>
+      </c>
+      <c r="L305" t="n">
+        <v>3</v>
+      </c>
+      <c r="M305" t="n">
+        <v>1</v>
+      </c>
+      <c r="N305" t="n">
+        <v>4</v>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>['65', '70', '79']</t>
+        </is>
+      </c>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>['59']</t>
+        </is>
+      </c>
+      <c r="Q305" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="R305" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="S305" t="n">
+        <v>4</v>
+      </c>
+      <c r="T305" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U305" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V305" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W305" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X305" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="Y305" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z305" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA305" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB305" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="AC305" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD305" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="AE305" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF305" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AG305" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH305" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI305" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AJ305" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AK305" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL305" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AM305" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AN305" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AO305" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AP305" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ305" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AR305" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AS305" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AT305" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU305" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV305" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW305" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX305" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY305" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ305" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA305" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB305" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC305" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD305" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BE305" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF305" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BG305" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH305" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI305" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ305" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BK305" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BL305" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BM305" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BN305" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BO305" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BP305" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="n">
+        <v>305</v>
+      </c>
+      <c r="B306" t="n">
+        <v>7778374</v>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E306" s="2" t="n">
+        <v>45923.29166666666</v>
+      </c>
+      <c r="F306" t="n">
+        <v>31</v>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>Kashiwa Reysol</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>Sanfrecce Hiroshima</t>
+        </is>
+      </c>
+      <c r="I306" t="n">
+        <v>0</v>
+      </c>
+      <c r="J306" t="n">
+        <v>0</v>
+      </c>
+      <c r="K306" t="n">
+        <v>0</v>
+      </c>
+      <c r="L306" t="n">
+        <v>0</v>
+      </c>
+      <c r="M306" t="n">
+        <v>0</v>
+      </c>
+      <c r="N306" t="n">
+        <v>0</v>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q306" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="R306" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="S306" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T306" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U306" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="V306" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W306" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X306" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="Y306" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z306" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AA306" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB306" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AC306" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD306" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE306" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF306" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AG306" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AH306" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AI306" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ306" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AK306" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL306" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM306" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN306" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO306" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP306" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AQ306" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AR306" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AS306" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AT306" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AU306" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV306" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW306" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX306" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY306" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ306" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA306" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB306" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC306" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD306" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BE306" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF306" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BG306" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH306" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI306" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BJ306" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BK306" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BL306" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BM306" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BN306" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BO306" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BP306" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="n">
+        <v>306</v>
+      </c>
+      <c r="B307" t="n">
+        <v>7778376</v>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E307" s="2" t="n">
+        <v>45923.29166666666</v>
+      </c>
+      <c r="F307" t="n">
+        <v>31</v>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>Shonan Bellmare</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>Kawasaki Frontale</t>
+        </is>
+      </c>
+      <c r="I307" t="n">
+        <v>0</v>
+      </c>
+      <c r="J307" t="n">
+        <v>1</v>
+      </c>
+      <c r="K307" t="n">
+        <v>1</v>
+      </c>
+      <c r="L307" t="n">
+        <v>1</v>
+      </c>
+      <c r="M307" t="n">
+        <v>2</v>
+      </c>
+      <c r="N307" t="n">
+        <v>3</v>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>['82']</t>
+        </is>
+      </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>['28', '80']</t>
+        </is>
+      </c>
+      <c r="Q307" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R307" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="S307" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T307" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U307" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="V307" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="W307" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X307" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="Y307" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z307" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="AA307" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AB307" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC307" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD307" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="AE307" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF307" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG307" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AH307" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI307" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AJ307" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AK307" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AL307" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AM307" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN307" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO307" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AP307" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AQ307" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AR307" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AS307" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AT307" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU307" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV307" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW307" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX307" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY307" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ307" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA307" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB307" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC307" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD307" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BE307" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF307" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BG307" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH307" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI307" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ307" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BK307" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BL307" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BM307" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BN307" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BO307" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BP307" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="n">
+        <v>307</v>
+      </c>
+      <c r="B308" t="n">
+        <v>7778379</v>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Japan J1 League</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E308" s="2" t="n">
+        <v>45923.29166666666</v>
+      </c>
+      <c r="F308" t="n">
+        <v>31</v>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>Kyoto Sanga</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>Machida Zelvia</t>
+        </is>
+      </c>
+      <c r="I308" t="n">
+        <v>0</v>
+      </c>
+      <c r="J308" t="n">
+        <v>1</v>
+      </c>
+      <c r="K308" t="n">
+        <v>1</v>
+      </c>
+      <c r="L308" t="n">
+        <v>1</v>
+      </c>
+      <c r="M308" t="n">
+        <v>1</v>
+      </c>
+      <c r="N308" t="n">
+        <v>2</v>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>['90+3']</t>
+        </is>
+      </c>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>['16']</t>
+        </is>
+      </c>
+      <c r="Q308" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R308" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="S308" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T308" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U308" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="V308" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="W308" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X308" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Y308" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z308" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AA308" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB308" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AC308" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD308" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AE308" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF308" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG308" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH308" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI308" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AJ308" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AK308" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL308" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AM308" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN308" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AO308" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AP308" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AQ308" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AR308" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS308" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AT308" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AU308" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV308" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW308" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX308" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY308" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ308" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA308" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB308" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC308" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD308" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BE308" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF308" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG308" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH308" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI308" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ308" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK308" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BL308" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BM308" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BN308" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO308" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BP308" t="n">
+        <v>1.43</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Japan J1 League_2025.xlsx
@@ -66983,13 +66983,13 @@
         <v>6</v>
       </c>
       <c r="AV305" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW305" t="n">
         <v>5</v>
       </c>
       <c r="AX305" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY305" t="n">
         <v>11</v>
@@ -67416,16 +67416,16 @@
         <v>2.8</v>
       </c>
       <c r="AU307" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV307" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW307" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX307" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY307" t="n">
         <v>9</v>
@@ -67634,13 +67634,13 @@
         <v>2.96</v>
       </c>
       <c r="AU308" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV308" t="n">
         <v>2</v>
       </c>
       <c r="AW308" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AX308" t="n">
         <v>7</v>
